--- a/Financial Analysis/AAPL.xlsx
+++ b/Financial Analysis/AAPL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2667ACAC-BC48-43A4-8B1D-6C6695039363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A1D402B-F206-4351-9656-9E8E5DBF48A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{9DABBB29-C94C-41BD-A4AD-A53C3313D92F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9DABBB29-C94C-41BD-A4AD-A53C3313D92F}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -911,14 +911,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="12">
-        <v>205.35</v>
+        <v>198.81</v>
       </c>
       <c r="E3" s="2">
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="F3" s="2">
         <f ca="1">TODAY()</f>
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="G3" s="2">
         <v>45861</v>
@@ -942,7 +942,7 @@
       </c>
       <c r="D5" s="3">
         <f>D3*D4</f>
-        <v>3067066.53</v>
+        <v>2969386.398</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -984,7 +984,7 @@
       </c>
       <c r="D9" s="3">
         <f>D5-D8</f>
-        <v>3032330.53</v>
+        <v>2934650.398</v>
       </c>
     </row>
   </sheetData>
@@ -8163,7 +8163,7 @@
       </c>
       <c r="BQ35" s="12">
         <f>Main!D3</f>
-        <v>205.35</v>
+        <v>198.81</v>
       </c>
     </row>
     <row r="36" spans="2:69" x14ac:dyDescent="0.3">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="BQ36" s="11">
         <f>BQ34/BQ35-1</f>
-        <v>-0.16472620891373135</v>
+        <v>-0.13724926814765226</v>
       </c>
     </row>
     <row r="37" spans="2:69" x14ac:dyDescent="0.3">
@@ -10715,13 +10715,13 @@
     <row r="79" spans="2:151" x14ac:dyDescent="0.3">
       <c r="BQ79" s="12">
         <f>Main!D3</f>
-        <v>205.35</v>
+        <v>198.81</v>
       </c>
     </row>
     <row r="80" spans="2:151" x14ac:dyDescent="0.3">
       <c r="BQ80" s="11">
         <f>BQ78/BQ79-1</f>
-        <v>-0.13436628886711866</v>
+        <v>-0.10589063638077978</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/AAPL.xlsx
+++ b/Financial Analysis/AAPL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A1D402B-F206-4351-9656-9E8E5DBF48A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3296D9E8-4915-4BC8-A8AC-940450D4BFB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9DABBB29-C94C-41BD-A4AD-A53C3313D92F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{9DABBB29-C94C-41BD-A4AD-A53C3313D92F}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -487,13 +487,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>32</xdr:col>
+      <xdr:col>33</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>32</xdr:col>
+      <xdr:col>33</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>36</xdr:row>
       <xdr:rowOff>129540</xdr:rowOff>
@@ -511,7 +511,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="23911560" y="0"/>
+          <a:off x="24635460" y="0"/>
           <a:ext cx="0" cy="6713220"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -911,17 +911,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="12">
-        <v>198.81</v>
+        <v>231.02</v>
       </c>
       <c r="E3" s="2">
-        <v>45804</v>
+        <v>45887</v>
       </c>
       <c r="F3" s="2">
         <f ca="1">TODAY()</f>
-        <v>45804</v>
+        <v>45887</v>
       </c>
       <c r="G3" s="2">
-        <v>45861</v>
+        <v>45961</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -929,8 +929,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="3">
-        <f>14935.8</f>
-        <v>14935.8</v>
+        <v>14902.9</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>90</v>
@@ -942,7 +941,7 @@
       </c>
       <c r="D5" s="3">
         <f>D3*D4</f>
-        <v>2969386.398</v>
+        <v>3442867.9580000001</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -950,11 +949,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="3">
-        <f>28162+20336+84424</f>
-        <v>132922</v>
+        <f>36269+19103+77614</f>
+        <v>132986</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -962,11 +961,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="3">
-        <f>5982+13638+78566</f>
-        <v>98186</v>
+        <f>9923+9345+82430</f>
+        <v>101698</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -975,7 +974,7 @@
       </c>
       <c r="D8" s="3">
         <f>D6-D7</f>
-        <v>34736</v>
+        <v>31288</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -984,7 +983,7 @@
       </c>
       <c r="D9" s="3">
         <f>D5-D8</f>
-        <v>2934650.398</v>
+        <v>3411579.9580000001</v>
       </c>
     </row>
   </sheetData>
@@ -1542,12 +1541,11 @@
         <v>68714</v>
       </c>
       <c r="AG3" s="3">
-        <f t="shared" ref="AG3:AH3" si="23">AC3*1.02</f>
-        <v>62795.28</v>
+        <v>66613</v>
       </c>
       <c r="AH3" s="3">
-        <f t="shared" si="23"/>
-        <v>71357.16</v>
+        <f>AD3*1.03</f>
+        <v>72056.740000000005</v>
       </c>
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
@@ -1593,47 +1591,47 @@
       </c>
       <c r="BD3" s="3">
         <f>SUM(AE3:AH3)</f>
-        <v>300826.44</v>
+        <v>305343.74</v>
       </c>
       <c r="BE3" s="3">
-        <f t="shared" ref="BE3:BI3" si="24">BD3*1.01</f>
-        <v>303834.70439999999</v>
+        <f>BD3*1.03</f>
+        <v>314504.05219999998</v>
       </c>
       <c r="BF3" s="3">
+        <f>BE3*1.02</f>
+        <v>320794.13324399997</v>
+      </c>
+      <c r="BG3" s="3">
+        <f t="shared" ref="BG3:BI3" si="23">BF3*1.01</f>
+        <v>324002.07457643998</v>
+      </c>
+      <c r="BH3" s="3">
+        <f t="shared" si="23"/>
+        <v>327242.0953222044</v>
+      </c>
+      <c r="BI3" s="3">
+        <f t="shared" si="23"/>
+        <v>330514.51627542643</v>
+      </c>
+      <c r="BJ3" s="3">
+        <f t="shared" ref="BJ3:BL3" si="24">BI3*1.01</f>
+        <v>333819.66143818072</v>
+      </c>
+      <c r="BK3" s="3">
         <f t="shared" si="24"/>
-        <v>306873.05144399998</v>
-      </c>
-      <c r="BG3" s="3">
+        <v>337157.85805256251</v>
+      </c>
+      <c r="BL3" s="3">
         <f t="shared" si="24"/>
-        <v>309941.78195843997</v>
-      </c>
-      <c r="BH3" s="3">
-        <f t="shared" si="24"/>
-        <v>313041.1997780244</v>
-      </c>
-      <c r="BI3" s="3">
-        <f t="shared" si="24"/>
-        <v>316171.61177580466</v>
-      </c>
-      <c r="BJ3" s="3">
-        <f t="shared" ref="BJ3:BL3" si="25">BI3*1.01</f>
-        <v>319333.32789356273</v>
-      </c>
-      <c r="BK3" s="3">
-        <f t="shared" si="25"/>
-        <v>322526.66117249837</v>
-      </c>
-      <c r="BL3" s="3">
-        <f t="shared" si="25"/>
-        <v>325751.92778422334</v>
+        <v>340529.43663308816</v>
       </c>
       <c r="BM3" s="3">
-        <f t="shared" ref="BM3" si="26">BL3*1.01</f>
-        <v>329009.44706206559</v>
+        <f t="shared" ref="BM3" si="25">BL3*1.01</f>
+        <v>343934.73099941906</v>
       </c>
       <c r="BN3" s="3">
-        <f t="shared" ref="BN3" si="27">BM3*1.01</f>
-        <v>332299.54153268627</v>
+        <f t="shared" ref="BN3" si="26">BM3*1.01</f>
+        <v>347374.07830941328</v>
       </c>
     </row>
     <row r="4" spans="2:66" x14ac:dyDescent="0.3">
@@ -1731,12 +1729,11 @@
         <v>26645</v>
       </c>
       <c r="AG4" s="3">
-        <f>AC4*1.12</f>
-        <v>27118.560000000001</v>
+        <v>27423</v>
       </c>
       <c r="AH4" s="3">
-        <f>AD4*1.1</f>
-        <v>27469.200000000001</v>
+        <f>AD4*1.11</f>
+        <v>27718.920000000002</v>
       </c>
       <c r="AI4" s="3"/>
       <c r="AJ4" s="3"/>
@@ -1782,47 +1779,47 @@
       </c>
       <c r="BD4" s="3">
         <f>SUM(AE4:AH4)</f>
-        <v>107572.76</v>
+        <v>108126.92</v>
       </c>
       <c r="BE4" s="3">
         <f>BD4*1.09</f>
-        <v>117254.30840000001</v>
+        <v>117858.34280000001</v>
       </c>
       <c r="BF4" s="3">
         <f>BE4*1.07</f>
-        <v>125462.10998800001</v>
+        <v>126108.42679600001</v>
       </c>
       <c r="BG4" s="3">
         <f>BF4*1.06</f>
-        <v>132989.83658728001</v>
+        <v>133674.93240376003</v>
       </c>
       <c r="BH4" s="3">
-        <f t="shared" ref="BH4" si="28">BG4*1.05</f>
-        <v>139639.32841664401</v>
+        <f t="shared" ref="BH4" si="27">BG4*1.05</f>
+        <v>140358.67902394803</v>
       </c>
       <c r="BI4" s="3">
         <f>BH4*1.04</f>
-        <v>145224.90155330978</v>
+        <v>145973.02618490596</v>
       </c>
       <c r="BJ4" s="3">
         <f>BI4*1.03</f>
-        <v>149581.64859990909</v>
+        <v>150352.21697045316</v>
       </c>
       <c r="BK4" s="3">
-        <f t="shared" ref="BK4" si="29">BJ4*1.03</f>
-        <v>154069.09805790638</v>
+        <f t="shared" ref="BK4:BN4" si="28">BJ4*1.03</f>
+        <v>154862.78347956674</v>
       </c>
       <c r="BL4" s="3">
-        <f>BK4*1.02</f>
-        <v>157150.4800190645</v>
+        <f t="shared" si="28"/>
+        <v>159508.66698395376</v>
       </c>
       <c r="BM4" s="3">
-        <f t="shared" ref="BM4:BN4" si="30">BL4*1.02</f>
-        <v>160293.48961944578</v>
+        <f t="shared" si="28"/>
+        <v>164293.92699347239</v>
       </c>
       <c r="BN4" s="3">
-        <f t="shared" si="30"/>
-        <v>163499.35941183471</v>
+        <f t="shared" si="28"/>
+        <v>169222.74480327655</v>
       </c>
     </row>
     <row r="5" spans="2:66" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1830,132 +1827,132 @@
         <v>31</v>
       </c>
       <c r="C5" s="9">
-        <f t="shared" ref="C5:N5" si="31">C3+C4</f>
+        <f t="shared" ref="C5:N5" si="29">C3+C4</f>
         <v>88293</v>
       </c>
       <c r="D5" s="9">
+        <f t="shared" si="29"/>
+        <v>61137</v>
+      </c>
+      <c r="E5" s="9">
+        <f t="shared" si="29"/>
+        <v>53265</v>
+      </c>
+      <c r="F5" s="9">
+        <f t="shared" si="29"/>
+        <v>62900</v>
+      </c>
+      <c r="G5" s="9">
+        <f t="shared" si="29"/>
+        <v>84310</v>
+      </c>
+      <c r="H5" s="9">
+        <f t="shared" si="29"/>
+        <v>58015</v>
+      </c>
+      <c r="I5" s="9">
+        <f t="shared" si="29"/>
+        <v>53809</v>
+      </c>
+      <c r="J5" s="9">
+        <f t="shared" si="29"/>
+        <v>64040</v>
+      </c>
+      <c r="K5" s="9">
+        <f t="shared" si="29"/>
+        <v>91819</v>
+      </c>
+      <c r="L5" s="9">
+        <f t="shared" si="29"/>
+        <v>58313</v>
+      </c>
+      <c r="M5" s="9">
+        <f t="shared" si="29"/>
+        <v>59685</v>
+      </c>
+      <c r="N5" s="9">
+        <f t="shared" si="29"/>
+        <v>64698</v>
+      </c>
+      <c r="O5" s="9">
+        <f t="shared" ref="O5:S5" si="30">O3+O4</f>
+        <v>111439</v>
+      </c>
+      <c r="P5" s="9">
+        <f t="shared" si="30"/>
+        <v>89584</v>
+      </c>
+      <c r="Q5" s="9">
+        <f t="shared" ref="Q5:R5" si="31">Q3+Q4</f>
+        <v>81434</v>
+      </c>
+      <c r="R5" s="9">
         <f t="shared" si="31"/>
-        <v>61137</v>
-      </c>
-      <c r="E5" s="9">
-        <f t="shared" si="31"/>
-        <v>53265</v>
-      </c>
-      <c r="F5" s="9">
-        <f t="shared" si="31"/>
-        <v>62900</v>
-      </c>
-      <c r="G5" s="9">
-        <f t="shared" si="31"/>
-        <v>84310</v>
-      </c>
-      <c r="H5" s="9">
-        <f t="shared" si="31"/>
-        <v>58015</v>
-      </c>
-      <c r="I5" s="9">
-        <f t="shared" si="31"/>
-        <v>53809</v>
-      </c>
-      <c r="J5" s="9">
-        <f t="shared" si="31"/>
-        <v>64040</v>
-      </c>
-      <c r="K5" s="9">
-        <f t="shared" si="31"/>
-        <v>91819</v>
-      </c>
-      <c r="L5" s="9">
-        <f t="shared" si="31"/>
-        <v>58313</v>
-      </c>
-      <c r="M5" s="9">
-        <f t="shared" si="31"/>
-        <v>59685</v>
-      </c>
-      <c r="N5" s="9">
-        <f t="shared" si="31"/>
-        <v>64698</v>
-      </c>
-      <c r="O5" s="9">
-        <f t="shared" ref="O5:S5" si="32">O3+O4</f>
-        <v>111439</v>
-      </c>
-      <c r="P5" s="9">
-        <f t="shared" si="32"/>
-        <v>89584</v>
-      </c>
-      <c r="Q5" s="9">
-        <f t="shared" ref="Q5:R5" si="33">Q3+Q4</f>
-        <v>81434</v>
-      </c>
-      <c r="R5" s="9">
-        <f t="shared" si="33"/>
         <v>83360</v>
       </c>
       <c r="S5" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>123945</v>
       </c>
       <c r="T5" s="9">
-        <f t="shared" ref="T5" si="34">T3+T4</f>
+        <f t="shared" ref="T5" si="32">T3+T4</f>
         <v>97278</v>
       </c>
       <c r="U5" s="9">
-        <f t="shared" ref="U5" si="35">U3+U4</f>
+        <f t="shared" ref="U5" si="33">U3+U4</f>
         <v>82959</v>
       </c>
       <c r="V5" s="9">
-        <f t="shared" ref="V5" si="36">V3+V4</f>
+        <f t="shared" ref="V5" si="34">V3+V4</f>
         <v>90146</v>
       </c>
       <c r="W5" s="9">
-        <f t="shared" ref="W5:X5" si="37">W3+W4</f>
+        <f t="shared" ref="W5:X5" si="35">W3+W4</f>
         <v>117154</v>
       </c>
       <c r="X5" s="9">
+        <f t="shared" si="35"/>
+        <v>94836</v>
+      </c>
+      <c r="Y5" s="9">
+        <f t="shared" ref="Y5:Z5" si="36">Y3+Y4</f>
+        <v>81797</v>
+      </c>
+      <c r="Z5" s="9">
+        <f t="shared" si="36"/>
+        <v>89498</v>
+      </c>
+      <c r="AA5" s="9">
+        <f t="shared" ref="AA5:AH5" si="37">AA3+AA4</f>
+        <v>119575</v>
+      </c>
+      <c r="AB5" s="9">
         <f t="shared" si="37"/>
-        <v>94836</v>
-      </c>
-      <c r="Y5" s="9">
-        <f t="shared" ref="Y5:Z5" si="38">Y3+Y4</f>
-        <v>81797</v>
-      </c>
-      <c r="Z5" s="9">
-        <f t="shared" si="38"/>
-        <v>89498</v>
-      </c>
-      <c r="AA5" s="9">
-        <f t="shared" ref="AA5:AH5" si="39">AA3+AA4</f>
-        <v>119575</v>
-      </c>
-      <c r="AB5" s="9">
-        <f t="shared" si="39"/>
         <v>90753</v>
       </c>
       <c r="AC5" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="37"/>
         <v>85777</v>
       </c>
       <c r="AD5" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="37"/>
         <v>94930</v>
       </c>
       <c r="AE5" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="37"/>
         <v>124300</v>
       </c>
       <c r="AF5" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="37"/>
         <v>95359</v>
       </c>
       <c r="AG5" s="9">
-        <f t="shared" si="39"/>
-        <v>89913.84</v>
+        <f t="shared" si="37"/>
+        <v>94036</v>
       </c>
       <c r="AH5" s="9">
-        <f t="shared" si="39"/>
-        <v>98826.36</v>
+        <f t="shared" si="37"/>
+        <v>99775.66</v>
       </c>
       <c r="AI5" s="9"/>
       <c r="AJ5" s="9">
@@ -2010,64 +2007,64 @@
         <v>274515</v>
       </c>
       <c r="AZ5" s="9">
-        <f t="shared" ref="AZ5:BI5" si="40">AZ3+AZ4</f>
+        <f t="shared" ref="AZ5:BI5" si="38">AZ3+AZ4</f>
         <v>365817</v>
       </c>
       <c r="BA5" s="9">
-        <f t="shared" ref="BA5:BB5" si="41">BA3+BA4</f>
+        <f t="shared" ref="BA5:BB5" si="39">BA3+BA4</f>
         <v>394328</v>
       </c>
       <c r="BB5" s="9">
+        <f t="shared" si="39"/>
+        <v>383285</v>
+      </c>
+      <c r="BC5" s="9">
+        <f t="shared" ref="BC5" si="40">BC3+BC4</f>
+        <v>391035</v>
+      </c>
+      <c r="BD5" s="9">
+        <f t="shared" si="38"/>
+        <v>413470.66</v>
+      </c>
+      <c r="BE5" s="9">
+        <f t="shared" si="38"/>
+        <v>432362.39500000002</v>
+      </c>
+      <c r="BF5" s="9">
+        <f t="shared" si="38"/>
+        <v>446902.56004000001</v>
+      </c>
+      <c r="BG5" s="9">
+        <f t="shared" si="38"/>
+        <v>457677.00698020001</v>
+      </c>
+      <c r="BH5" s="9">
+        <f t="shared" si="38"/>
+        <v>467600.77434615244</v>
+      </c>
+      <c r="BI5" s="9">
+        <f t="shared" si="38"/>
+        <v>476487.54246033239</v>
+      </c>
+      <c r="BJ5" s="9">
+        <f t="shared" ref="BJ5:BL5" si="41">BJ3+BJ4</f>
+        <v>484171.87840863387</v>
+      </c>
+      <c r="BK5" s="9">
         <f t="shared" si="41"/>
-        <v>383285</v>
-      </c>
-      <c r="BC5" s="9">
-        <f t="shared" ref="BC5" si="42">BC3+BC4</f>
-        <v>391035</v>
-      </c>
-      <c r="BD5" s="9">
-        <f t="shared" si="40"/>
-        <v>408399.2</v>
-      </c>
-      <c r="BE5" s="9">
-        <f t="shared" si="40"/>
-        <v>421089.01280000003</v>
-      </c>
-      <c r="BF5" s="9">
-        <f t="shared" si="40"/>
-        <v>432335.16143199999</v>
-      </c>
-      <c r="BG5" s="9">
-        <f t="shared" si="40"/>
-        <v>442931.61854572</v>
-      </c>
-      <c r="BH5" s="9">
-        <f t="shared" si="40"/>
-        <v>452680.52819466841</v>
-      </c>
-      <c r="BI5" s="9">
-        <f t="shared" si="40"/>
-        <v>461396.51332911442</v>
-      </c>
-      <c r="BJ5" s="9">
-        <f t="shared" ref="BJ5:BL5" si="43">BJ3+BJ4</f>
-        <v>468914.97649347183</v>
-      </c>
-      <c r="BK5" s="9">
-        <f t="shared" si="43"/>
-        <v>476595.75923040474</v>
+        <v>492020.64153212926</v>
       </c>
       <c r="BL5" s="9">
-        <f t="shared" si="43"/>
-        <v>482902.40780328785</v>
+        <f t="shared" si="41"/>
+        <v>500038.10361704195</v>
       </c>
       <c r="BM5" s="9">
-        <f t="shared" ref="BM5:BN5" si="44">BM3+BM4</f>
-        <v>489302.93668151135</v>
+        <f t="shared" ref="BM5:BN5" si="42">BM3+BM4</f>
+        <v>508228.65799289144</v>
       </c>
       <c r="BN5" s="9">
-        <f t="shared" si="44"/>
-        <v>495798.90094452095</v>
+        <f t="shared" si="42"/>
+        <v>516596.82311268983</v>
       </c>
     </row>
     <row r="6" spans="2:66" x14ac:dyDescent="0.3">
@@ -2165,12 +2162,11 @@
         <v>44030</v>
       </c>
       <c r="AG6" s="3">
-        <f>AG3*0.66</f>
-        <v>41444.8848</v>
+        <v>43620</v>
       </c>
       <c r="AH6" s="3">
         <f>AH3*0.66</f>
-        <v>47095.725600000005</v>
+        <v>47557.448400000008</v>
       </c>
       <c r="AI6" s="3"/>
       <c r="AJ6" s="3"/>
@@ -2216,47 +2212,47 @@
       </c>
       <c r="BD6" s="3">
         <f>SUM(AE6:AH6)</f>
-        <v>192017.61040000001</v>
+        <v>194654.44839999999</v>
       </c>
       <c r="BE6" s="3">
         <f>BE3*0.65</f>
-        <v>197492.55786</v>
+        <v>204427.63392999998</v>
       </c>
       <c r="BF6" s="3">
-        <f t="shared" ref="BF6:BN6" si="45">BF3*0.65</f>
-        <v>199467.4834386</v>
+        <f t="shared" ref="BF6:BN6" si="43">BF3*0.65</f>
+        <v>208516.18660859999</v>
       </c>
       <c r="BG6" s="3">
-        <f t="shared" si="45"/>
-        <v>201462.15827298598</v>
+        <f t="shared" si="43"/>
+        <v>210601.348474686</v>
       </c>
       <c r="BH6" s="3">
-        <f t="shared" si="45"/>
-        <v>203476.77985571587</v>
+        <f t="shared" si="43"/>
+        <v>212707.36195943286</v>
       </c>
       <c r="BI6" s="3">
-        <f t="shared" si="45"/>
-        <v>205511.54765427305</v>
+        <f t="shared" si="43"/>
+        <v>214834.43557902719</v>
       </c>
       <c r="BJ6" s="3">
-        <f t="shared" si="45"/>
-        <v>207566.66313081578</v>
+        <f t="shared" si="43"/>
+        <v>216982.77993481746</v>
       </c>
       <c r="BK6" s="3">
-        <f t="shared" si="45"/>
-        <v>209642.32976212393</v>
+        <f t="shared" si="43"/>
+        <v>219152.60773416565</v>
       </c>
       <c r="BL6" s="3">
-        <f t="shared" si="45"/>
-        <v>211738.75305974518</v>
+        <f t="shared" si="43"/>
+        <v>221344.13381150732</v>
       </c>
       <c r="BM6" s="3">
-        <f t="shared" si="45"/>
-        <v>213856.14059034263</v>
+        <f t="shared" si="43"/>
+        <v>223557.5751496224</v>
       </c>
       <c r="BN6" s="3">
-        <f t="shared" si="45"/>
-        <v>215994.70199624609</v>
+        <f t="shared" si="43"/>
+        <v>225793.15090111864</v>
       </c>
     </row>
     <row r="7" spans="2:66" x14ac:dyDescent="0.3">
@@ -2354,12 +2350,11 @@
         <v>6462</v>
       </c>
       <c r="AG7" s="3">
-        <f>AG4*0.25</f>
-        <v>6779.64</v>
+        <v>6698</v>
       </c>
       <c r="AH7" s="3">
-        <f t="shared" ref="AH7" si="46">AH4*0.25</f>
-        <v>6867.3</v>
+        <f t="shared" ref="AH7" si="44">AH4*0.25</f>
+        <v>6929.7300000000005</v>
       </c>
       <c r="AI7" s="3"/>
       <c r="AJ7" s="3"/>
@@ -2405,47 +2400,47 @@
       </c>
       <c r="BD7" s="3">
         <f>SUM(AE7:AH7)</f>
-        <v>26686.94</v>
+        <v>26667.73</v>
       </c>
       <c r="BE7" s="3">
         <f>BE4*0.24</f>
-        <v>28141.034016000001</v>
+        <v>28286.002272000002</v>
       </c>
       <c r="BF7" s="3">
-        <f t="shared" ref="BF7:BN7" si="47">BF4*0.24</f>
-        <v>30110.906397120001</v>
+        <f t="shared" ref="BF7:BN7" si="45">BF4*0.24</f>
+        <v>30266.022431040001</v>
       </c>
       <c r="BG7" s="3">
-        <f t="shared" si="47"/>
-        <v>31917.560780947199</v>
+        <f t="shared" si="45"/>
+        <v>32081.983776902405</v>
       </c>
       <c r="BH7" s="3">
-        <f t="shared" si="47"/>
-        <v>33513.438819994561</v>
+        <f t="shared" si="45"/>
+        <v>33686.082965747526</v>
       </c>
       <c r="BI7" s="3">
-        <f t="shared" si="47"/>
-        <v>34853.97637279435</v>
+        <f t="shared" si="45"/>
+        <v>35033.526284377433</v>
       </c>
       <c r="BJ7" s="3">
-        <f t="shared" si="47"/>
-        <v>35899.59566397818</v>
+        <f t="shared" si="45"/>
+        <v>36084.532072908754</v>
       </c>
       <c r="BK7" s="3">
-        <f t="shared" si="47"/>
-        <v>36976.58353389753</v>
+        <f t="shared" si="45"/>
+        <v>37167.068035096017</v>
       </c>
       <c r="BL7" s="3">
-        <f t="shared" si="47"/>
-        <v>37716.115204575479</v>
+        <f t="shared" si="45"/>
+        <v>38282.080076148901</v>
       </c>
       <c r="BM7" s="3">
-        <f t="shared" si="47"/>
-        <v>38470.43750866699</v>
+        <f t="shared" si="45"/>
+        <v>39430.542478433374</v>
       </c>
       <c r="BN7" s="3">
-        <f t="shared" si="47"/>
-        <v>39239.846258840327</v>
+        <f t="shared" si="45"/>
+        <v>40613.45875278637</v>
       </c>
     </row>
     <row r="8" spans="2:66" x14ac:dyDescent="0.3">
@@ -2453,132 +2448,132 @@
         <v>30</v>
       </c>
       <c r="C8" s="3">
-        <f t="shared" ref="C8:N8" si="48">C6+C7</f>
+        <f t="shared" ref="C8:N8" si="46">C6+C7</f>
         <v>54381</v>
       </c>
       <c r="D8" s="3">
+        <f t="shared" si="46"/>
+        <v>37715</v>
+      </c>
+      <c r="E8" s="3">
+        <f t="shared" si="46"/>
+        <v>32844</v>
+      </c>
+      <c r="F8" s="3">
+        <f t="shared" si="46"/>
+        <v>38816</v>
+      </c>
+      <c r="G8" s="3">
+        <f t="shared" si="46"/>
+        <v>52279</v>
+      </c>
+      <c r="H8" s="3">
+        <f t="shared" si="46"/>
+        <v>36194</v>
+      </c>
+      <c r="I8" s="3">
+        <f t="shared" si="46"/>
+        <v>33582</v>
+      </c>
+      <c r="J8" s="3">
+        <f t="shared" si="46"/>
+        <v>39727</v>
+      </c>
+      <c r="K8" s="3">
+        <f t="shared" si="46"/>
+        <v>56602</v>
+      </c>
+      <c r="L8" s="3">
+        <f t="shared" si="46"/>
+        <v>35943</v>
+      </c>
+      <c r="M8" s="3">
+        <f t="shared" si="46"/>
+        <v>37005</v>
+      </c>
+      <c r="N8" s="3">
+        <f t="shared" si="46"/>
+        <v>40009</v>
+      </c>
+      <c r="O8" s="3">
+        <f t="shared" ref="O8:S8" si="47">O6+O7</f>
+        <v>67111</v>
+      </c>
+      <c r="P8" s="3">
+        <f t="shared" si="47"/>
+        <v>51505</v>
+      </c>
+      <c r="Q8" s="3">
+        <f t="shared" ref="Q8:R8" si="48">Q6+Q7</f>
+        <v>46179</v>
+      </c>
+      <c r="R8" s="3">
         <f t="shared" si="48"/>
-        <v>37715</v>
-      </c>
-      <c r="E8" s="3">
-        <f t="shared" si="48"/>
-        <v>32844</v>
-      </c>
-      <c r="F8" s="3">
-        <f t="shared" si="48"/>
-        <v>38816</v>
-      </c>
-      <c r="G8" s="3">
-        <f t="shared" si="48"/>
-        <v>52279</v>
-      </c>
-      <c r="H8" s="3">
-        <f t="shared" si="48"/>
-        <v>36194</v>
-      </c>
-      <c r="I8" s="3">
-        <f t="shared" si="48"/>
-        <v>33582</v>
-      </c>
-      <c r="J8" s="3">
-        <f t="shared" si="48"/>
-        <v>39727</v>
-      </c>
-      <c r="K8" s="3">
-        <f t="shared" si="48"/>
-        <v>56602</v>
-      </c>
-      <c r="L8" s="3">
-        <f t="shared" si="48"/>
-        <v>35943</v>
-      </c>
-      <c r="M8" s="3">
-        <f t="shared" si="48"/>
-        <v>37005</v>
-      </c>
-      <c r="N8" s="3">
-        <f t="shared" si="48"/>
-        <v>40009</v>
-      </c>
-      <c r="O8" s="3">
-        <f t="shared" ref="O8:S8" si="49">O6+O7</f>
-        <v>67111</v>
-      </c>
-      <c r="P8" s="3">
-        <f t="shared" si="49"/>
-        <v>51505</v>
-      </c>
-      <c r="Q8" s="3">
-        <f t="shared" ref="Q8:R8" si="50">Q6+Q7</f>
-        <v>46179</v>
-      </c>
-      <c r="R8" s="3">
-        <f t="shared" si="50"/>
         <v>48186</v>
       </c>
       <c r="S8" s="3">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>69702</v>
       </c>
       <c r="T8" s="3">
-        <f t="shared" ref="T8" si="51">T6+T7</f>
+        <f t="shared" ref="T8" si="49">T6+T7</f>
         <v>54719</v>
       </c>
       <c r="U8" s="3">
-        <f t="shared" ref="U8" si="52">U6+U7</f>
+        <f t="shared" ref="U8" si="50">U6+U7</f>
         <v>47074</v>
       </c>
       <c r="V8" s="3">
-        <f t="shared" ref="V8" si="53">V6+V7</f>
+        <f t="shared" ref="V8" si="51">V6+V7</f>
         <v>52051</v>
       </c>
       <c r="W8" s="3">
-        <f t="shared" ref="W8:X8" si="54">W6+W7</f>
+        <f t="shared" ref="W8:X8" si="52">W6+W7</f>
         <v>66822</v>
       </c>
       <c r="X8" s="3">
+        <f t="shared" si="52"/>
+        <v>52860</v>
+      </c>
+      <c r="Y8" s="3">
+        <f t="shared" ref="Y8:Z8" si="53">Y6+Y7</f>
+        <v>45384</v>
+      </c>
+      <c r="Z8" s="3">
+        <f t="shared" si="53"/>
+        <v>49071</v>
+      </c>
+      <c r="AA8" s="3">
+        <f t="shared" ref="AA8:AH8" si="54">AA6+AA7</f>
+        <v>64720</v>
+      </c>
+      <c r="AB8" s="3">
         <f t="shared" si="54"/>
-        <v>52860</v>
-      </c>
-      <c r="Y8" s="3">
-        <f t="shared" ref="Y8:Z8" si="55">Y6+Y7</f>
-        <v>45384</v>
-      </c>
-      <c r="Z8" s="3">
-        <f t="shared" si="55"/>
-        <v>49071</v>
-      </c>
-      <c r="AA8" s="3">
-        <f t="shared" ref="AA8:AH8" si="56">AA6+AA7</f>
-        <v>64720</v>
-      </c>
-      <c r="AB8" s="3">
-        <f t="shared" si="56"/>
         <v>48482</v>
       </c>
       <c r="AC8" s="3">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>46099</v>
       </c>
       <c r="AD8" s="3">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>51051</v>
       </c>
       <c r="AE8" s="3">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>66025</v>
       </c>
       <c r="AF8" s="3">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>50492</v>
       </c>
       <c r="AG8" s="3">
-        <f t="shared" si="56"/>
-        <v>48224.524799999999</v>
+        <f t="shared" si="54"/>
+        <v>50318</v>
       </c>
       <c r="AH8" s="3">
-        <f t="shared" si="56"/>
-        <v>53963.025600000008</v>
+        <f t="shared" si="54"/>
+        <v>54487.178400000012</v>
       </c>
       <c r="AI8" s="3"/>
       <c r="AJ8" s="3">
@@ -2633,64 +2628,64 @@
         <v>169559</v>
       </c>
       <c r="AZ8" s="3">
-        <f t="shared" ref="AZ8:BN8" si="57">AZ6+AZ7</f>
+        <f t="shared" ref="AZ8:BN8" si="55">AZ6+AZ7</f>
         <v>212981</v>
       </c>
       <c r="BA8" s="3">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>223546</v>
       </c>
       <c r="BB8" s="3">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>214137</v>
       </c>
       <c r="BC8" s="3">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>210352</v>
       </c>
       <c r="BD8" s="3">
-        <f t="shared" si="57"/>
-        <v>218704.55040000001</v>
+        <f t="shared" si="55"/>
+        <v>221322.1784</v>
       </c>
       <c r="BE8" s="3">
-        <f t="shared" si="57"/>
-        <v>225633.59187599999</v>
+        <f t="shared" si="55"/>
+        <v>232713.63620199999</v>
       </c>
       <c r="BF8" s="3">
-        <f t="shared" si="57"/>
-        <v>229578.38983572001</v>
+        <f t="shared" si="55"/>
+        <v>238782.20903964</v>
       </c>
       <c r="BG8" s="3">
-        <f t="shared" si="57"/>
-        <v>233379.71905393316</v>
+        <f t="shared" si="55"/>
+        <v>242683.33225158841</v>
       </c>
       <c r="BH8" s="3">
-        <f t="shared" si="57"/>
-        <v>236990.21867571044</v>
+        <f t="shared" si="55"/>
+        <v>246393.4449251804</v>
       </c>
       <c r="BI8" s="3">
-        <f t="shared" si="57"/>
-        <v>240365.52402706741</v>
+        <f t="shared" si="55"/>
+        <v>249867.96186340463</v>
       </c>
       <c r="BJ8" s="3">
-        <f t="shared" si="57"/>
-        <v>243466.25879479398</v>
+        <f t="shared" si="55"/>
+        <v>253067.31200772623</v>
       </c>
       <c r="BK8" s="3">
-        <f t="shared" si="57"/>
-        <v>246618.91329602146</v>
+        <f t="shared" si="55"/>
+        <v>256319.67576926167</v>
       </c>
       <c r="BL8" s="3">
-        <f t="shared" si="57"/>
-        <v>249454.86826432066</v>
+        <f t="shared" si="55"/>
+        <v>259626.21388765622</v>
       </c>
       <c r="BM8" s="3">
-        <f t="shared" si="57"/>
-        <v>252326.57809900964</v>
+        <f t="shared" si="55"/>
+        <v>262988.11762805574</v>
       </c>
       <c r="BN8" s="3">
-        <f t="shared" si="57"/>
-        <v>255234.54825508641</v>
+        <f t="shared" si="55"/>
+        <v>266406.60965390503</v>
       </c>
     </row>
     <row r="9" spans="2:66" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2698,257 +2693,257 @@
         <v>26</v>
       </c>
       <c r="C9" s="9">
-        <f t="shared" ref="C9:N9" si="58">C5-C8</f>
+        <f t="shared" ref="C9:N9" si="56">C5-C8</f>
         <v>33912</v>
       </c>
       <c r="D9" s="9">
+        <f t="shared" si="56"/>
+        <v>23422</v>
+      </c>
+      <c r="E9" s="9">
+        <f t="shared" si="56"/>
+        <v>20421</v>
+      </c>
+      <c r="F9" s="9">
+        <f t="shared" si="56"/>
+        <v>24084</v>
+      </c>
+      <c r="G9" s="9">
+        <f t="shared" si="56"/>
+        <v>32031</v>
+      </c>
+      <c r="H9" s="9">
+        <f t="shared" si="56"/>
+        <v>21821</v>
+      </c>
+      <c r="I9" s="9">
+        <f t="shared" si="56"/>
+        <v>20227</v>
+      </c>
+      <c r="J9" s="9">
+        <f t="shared" si="56"/>
+        <v>24313</v>
+      </c>
+      <c r="K9" s="9">
+        <f t="shared" si="56"/>
+        <v>35217</v>
+      </c>
+      <c r="L9" s="9">
+        <f t="shared" si="56"/>
+        <v>22370</v>
+      </c>
+      <c r="M9" s="9">
+        <f t="shared" si="56"/>
+        <v>22680</v>
+      </c>
+      <c r="N9" s="9">
+        <f t="shared" si="56"/>
+        <v>24689</v>
+      </c>
+      <c r="O9" s="9">
+        <f t="shared" ref="O9:S9" si="57">O5-O8</f>
+        <v>44328</v>
+      </c>
+      <c r="P9" s="9">
+        <f t="shared" si="57"/>
+        <v>38079</v>
+      </c>
+      <c r="Q9" s="9">
+        <f t="shared" ref="Q9:R9" si="58">Q5-Q8</f>
+        <v>35255</v>
+      </c>
+      <c r="R9" s="9">
         <f t="shared" si="58"/>
-        <v>23422</v>
-      </c>
-      <c r="E9" s="9">
-        <f t="shared" si="58"/>
-        <v>20421</v>
-      </c>
-      <c r="F9" s="9">
-        <f t="shared" si="58"/>
-        <v>24084</v>
-      </c>
-      <c r="G9" s="9">
-        <f t="shared" si="58"/>
-        <v>32031</v>
-      </c>
-      <c r="H9" s="9">
-        <f t="shared" si="58"/>
-        <v>21821</v>
-      </c>
-      <c r="I9" s="9">
-        <f t="shared" si="58"/>
-        <v>20227</v>
-      </c>
-      <c r="J9" s="9">
-        <f t="shared" si="58"/>
-        <v>24313</v>
-      </c>
-      <c r="K9" s="9">
-        <f t="shared" si="58"/>
-        <v>35217</v>
-      </c>
-      <c r="L9" s="9">
-        <f t="shared" si="58"/>
-        <v>22370</v>
-      </c>
-      <c r="M9" s="9">
-        <f t="shared" si="58"/>
-        <v>22680</v>
-      </c>
-      <c r="N9" s="9">
-        <f t="shared" si="58"/>
-        <v>24689</v>
-      </c>
-      <c r="O9" s="9">
-        <f t="shared" ref="O9:S9" si="59">O5-O8</f>
-        <v>44328</v>
-      </c>
-      <c r="P9" s="9">
-        <f t="shared" si="59"/>
-        <v>38079</v>
-      </c>
-      <c r="Q9" s="9">
-        <f t="shared" ref="Q9:R9" si="60">Q5-Q8</f>
-        <v>35255</v>
-      </c>
-      <c r="R9" s="9">
-        <f t="shared" si="60"/>
         <v>35174</v>
       </c>
       <c r="S9" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="57"/>
         <v>54243</v>
       </c>
       <c r="T9" s="9">
-        <f t="shared" ref="T9" si="61">T5-T8</f>
+        <f t="shared" ref="T9" si="59">T5-T8</f>
         <v>42559</v>
       </c>
       <c r="U9" s="9">
-        <f t="shared" ref="U9" si="62">U5-U8</f>
+        <f t="shared" ref="U9" si="60">U5-U8</f>
         <v>35885</v>
       </c>
       <c r="V9" s="9">
-        <f t="shared" ref="V9" si="63">V5-V8</f>
+        <f t="shared" ref="V9" si="61">V5-V8</f>
         <v>38095</v>
       </c>
       <c r="W9" s="9">
-        <f t="shared" ref="W9:X9" si="64">W5-W8</f>
+        <f t="shared" ref="W9:X9" si="62">W5-W8</f>
         <v>50332</v>
       </c>
       <c r="X9" s="9">
+        <f t="shared" si="62"/>
+        <v>41976</v>
+      </c>
+      <c r="Y9" s="9">
+        <f t="shared" ref="Y9:Z9" si="63">Y5-Y8</f>
+        <v>36413</v>
+      </c>
+      <c r="Z9" s="9">
+        <f t="shared" si="63"/>
+        <v>40427</v>
+      </c>
+      <c r="AA9" s="9">
+        <f t="shared" ref="AA9:AH9" si="64">AA5-AA8</f>
+        <v>54855</v>
+      </c>
+      <c r="AB9" s="9">
         <f t="shared" si="64"/>
-        <v>41976</v>
-      </c>
-      <c r="Y9" s="9">
-        <f t="shared" ref="Y9:Z9" si="65">Y5-Y8</f>
-        <v>36413</v>
-      </c>
-      <c r="Z9" s="9">
-        <f t="shared" si="65"/>
-        <v>40427</v>
-      </c>
-      <c r="AA9" s="9">
-        <f t="shared" ref="AA9:AH9" si="66">AA5-AA8</f>
-        <v>54855</v>
-      </c>
-      <c r="AB9" s="9">
-        <f t="shared" si="66"/>
         <v>42271</v>
       </c>
       <c r="AC9" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>39678</v>
       </c>
       <c r="AD9" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>43879</v>
       </c>
       <c r="AE9" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>58275</v>
       </c>
       <c r="AF9" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>44867</v>
       </c>
       <c r="AG9" s="9">
-        <f t="shared" si="66"/>
-        <v>41689.315199999997</v>
+        <f t="shared" si="64"/>
+        <v>43718</v>
       </c>
       <c r="AH9" s="9">
-        <f t="shared" si="66"/>
-        <v>44863.334399999992</v>
+        <f t="shared" si="64"/>
+        <v>45288.481599999992</v>
       </c>
       <c r="AI9" s="9"/>
       <c r="AJ9" s="9">
-        <f t="shared" ref="AJ9" si="67">AJ5-AJ8</f>
+        <f t="shared" ref="AJ9" si="65">AJ5-AJ8</f>
         <v>4042</v>
       </c>
       <c r="AK9" s="9">
-        <f t="shared" ref="AK9:AL9" si="68">AK5-AK8</f>
+        <f t="shared" ref="AK9:AL9" si="66">AK5-AK8</f>
         <v>5598</v>
       </c>
       <c r="AL9" s="9">
+        <f t="shared" si="66"/>
+        <v>8154</v>
+      </c>
+      <c r="AM9" s="9">
+        <f t="shared" ref="AM9:AN9" si="67">AM5-AM8</f>
+        <v>13197</v>
+      </c>
+      <c r="AN9" s="9">
+        <f t="shared" si="67"/>
+        <v>17222</v>
+      </c>
+      <c r="AO9" s="9">
+        <f t="shared" ref="AO9:AP9" si="68">AO5-AO8</f>
+        <v>25684</v>
+      </c>
+      <c r="AP9" s="9">
         <f t="shared" si="68"/>
-        <v>8154</v>
-      </c>
-      <c r="AM9" s="9">
-        <f t="shared" ref="AM9:AN9" si="69">AM5-AM8</f>
-        <v>13197</v>
-      </c>
-      <c r="AN9" s="9">
+        <v>43818</v>
+      </c>
+      <c r="AQ9" s="9">
+        <f t="shared" ref="AQ9:AR9" si="69">AQ5-AQ8</f>
+        <v>68662</v>
+      </c>
+      <c r="AR9" s="9">
         <f t="shared" si="69"/>
-        <v>17222</v>
-      </c>
-      <c r="AO9" s="9">
-        <f t="shared" ref="AO9:AP9" si="70">AO5-AO8</f>
-        <v>25684</v>
-      </c>
-      <c r="AP9" s="9">
+        <v>64304</v>
+      </c>
+      <c r="AS9" s="9">
+        <f t="shared" ref="AS9:AT9" si="70">AS5-AS8</f>
+        <v>70537</v>
+      </c>
+      <c r="AT9" s="9">
         <f t="shared" si="70"/>
-        <v>43818</v>
-      </c>
-      <c r="AQ9" s="9">
-        <f t="shared" ref="AQ9:AR9" si="71">AQ5-AQ8</f>
-        <v>68662</v>
-      </c>
-      <c r="AR9" s="9">
+        <v>93626</v>
+      </c>
+      <c r="AU9" s="9">
+        <f t="shared" ref="AU9:AV9" si="71">AU5-AU8</f>
+        <v>84263</v>
+      </c>
+      <c r="AV9" s="9">
         <f t="shared" si="71"/>
-        <v>64304</v>
-      </c>
-      <c r="AS9" s="9">
-        <f t="shared" ref="AS9:AT9" si="72">AS5-AS8</f>
-        <v>70537</v>
-      </c>
-      <c r="AT9" s="9">
+        <v>88186</v>
+      </c>
+      <c r="AW9" s="9">
+        <f t="shared" ref="AW9:BN9" si="72">AW5-AW8</f>
+        <v>101839</v>
+      </c>
+      <c r="AX9" s="9">
         <f t="shared" si="72"/>
-        <v>93626</v>
-      </c>
-      <c r="AU9" s="9">
-        <f t="shared" ref="AU9:AV9" si="73">AU5-AU8</f>
-        <v>84263</v>
-      </c>
-      <c r="AV9" s="9">
-        <f t="shared" si="73"/>
-        <v>88186</v>
-      </c>
-      <c r="AW9" s="9">
-        <f t="shared" ref="AW9:BN9" si="74">AW5-AW8</f>
-        <v>101839</v>
-      </c>
-      <c r="AX9" s="9">
-        <f t="shared" si="74"/>
         <v>98392</v>
       </c>
       <c r="AY9" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="72"/>
         <v>104956</v>
       </c>
       <c r="AZ9" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="72"/>
         <v>152836</v>
       </c>
       <c r="BA9" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="72"/>
         <v>170782</v>
       </c>
       <c r="BB9" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="72"/>
         <v>169148</v>
       </c>
       <c r="BC9" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="72"/>
         <v>180683</v>
       </c>
       <c r="BD9" s="9">
-        <f t="shared" si="74"/>
-        <v>189694.6496</v>
+        <f t="shared" si="72"/>
+        <v>192148.48159999997</v>
       </c>
       <c r="BE9" s="9">
-        <f t="shared" si="74"/>
-        <v>195455.42092400003</v>
+        <f t="shared" si="72"/>
+        <v>199648.75879800002</v>
       </c>
       <c r="BF9" s="9">
-        <f t="shared" si="74"/>
-        <v>202756.77159627998</v>
+        <f t="shared" si="72"/>
+        <v>208120.35100036001</v>
       </c>
       <c r="BG9" s="9">
-        <f t="shared" si="74"/>
-        <v>209551.89949178684</v>
+        <f t="shared" si="72"/>
+        <v>214993.6747286116</v>
       </c>
       <c r="BH9" s="9">
-        <f t="shared" si="74"/>
-        <v>215690.30951895798</v>
+        <f t="shared" si="72"/>
+        <v>221207.32942097203</v>
       </c>
       <c r="BI9" s="9">
-        <f t="shared" si="74"/>
-        <v>221030.989302047</v>
+        <f t="shared" si="72"/>
+        <v>226619.58059692776</v>
       </c>
       <c r="BJ9" s="9">
-        <f t="shared" si="74"/>
-        <v>225448.71769867785</v>
+        <f t="shared" si="72"/>
+        <v>231104.56640090764</v>
       </c>
       <c r="BK9" s="9">
-        <f t="shared" si="74"/>
-        <v>229976.84593438328</v>
+        <f t="shared" si="72"/>
+        <v>235700.96576286759</v>
       </c>
       <c r="BL9" s="9">
-        <f t="shared" si="74"/>
-        <v>233447.53953896719</v>
+        <f t="shared" si="72"/>
+        <v>240411.88972938573</v>
       </c>
       <c r="BM9" s="9">
-        <f t="shared" si="74"/>
-        <v>236976.35858250171</v>
+        <f t="shared" si="72"/>
+        <v>245240.5403648357</v>
       </c>
       <c r="BN9" s="9">
-        <f t="shared" si="74"/>
-        <v>240564.35268943454</v>
+        <f t="shared" si="72"/>
+        <v>250190.2134587848</v>
       </c>
     </row>
     <row r="10" spans="2:66" x14ac:dyDescent="0.3">
@@ -3046,12 +3041,11 @@
         <v>8550</v>
       </c>
       <c r="AG10" s="3">
-        <f t="shared" ref="AG10:AH10" si="75">AC10*1.03</f>
-        <v>8246.18</v>
+        <v>8866</v>
       </c>
       <c r="AH10" s="3">
-        <f t="shared" si="75"/>
-        <v>7997.95</v>
+        <f>AD10*1.11</f>
+        <v>8619.1500000000015</v>
       </c>
       <c r="AI10" s="3"/>
       <c r="AJ10" s="3">
@@ -3123,47 +3117,47 @@
       </c>
       <c r="BD10" s="3">
         <f>SUM(AE10:AH10)</f>
-        <v>33062.129999999997</v>
+        <v>34303.15</v>
       </c>
       <c r="BE10" s="3">
-        <f>BD10*1.04</f>
-        <v>34384.6152</v>
+        <f>BD10*1.05</f>
+        <v>36018.307500000003</v>
       </c>
       <c r="BF10" s="3">
         <f>BE10*1.04</f>
-        <v>35759.999808</v>
+        <v>37459.039800000006</v>
       </c>
       <c r="BG10" s="3">
         <f>BF10*1.03</f>
-        <v>36832.799802239999</v>
+        <v>38582.810994000007</v>
       </c>
       <c r="BH10" s="3">
         <f>BG10*1.03</f>
-        <v>37937.783796307202</v>
+        <v>39740.295323820006</v>
       </c>
       <c r="BI10" s="3">
         <f>BH10*1.03</f>
-        <v>39075.917310196419</v>
+        <v>40932.504183534606</v>
       </c>
       <c r="BJ10" s="3">
         <f>BI10*1.02</f>
-        <v>39857.435656400346</v>
+        <v>41751.154267205296</v>
       </c>
       <c r="BK10" s="3">
         <f>BJ10*1.02</f>
-        <v>40654.584369528355</v>
+        <v>42586.177352549406</v>
       </c>
       <c r="BL10" s="3">
         <f>BK10*1.02</f>
-        <v>41467.676056918921</v>
+        <v>43437.900899600398</v>
       </c>
       <c r="BM10" s="3">
-        <f t="shared" ref="BM10:BN10" si="76">BL10*1.02</f>
-        <v>42297.0295780573</v>
+        <f t="shared" ref="BM10:BN10" si="73">BL10*1.02</f>
+        <v>44306.658917592409</v>
       </c>
       <c r="BN10" s="3">
-        <f t="shared" si="76"/>
-        <v>43142.970169618449</v>
+        <f t="shared" si="73"/>
+        <v>45192.792095944256</v>
       </c>
     </row>
     <row r="11" spans="2:66" x14ac:dyDescent="0.3">
@@ -3261,12 +3255,11 @@
         <v>6728</v>
       </c>
       <c r="AG11" s="3">
-        <f t="shared" ref="AG11:AH11" si="77">AG5*0.07</f>
-        <v>6293.9688000000006</v>
+        <v>6650</v>
       </c>
       <c r="AH11" s="3">
-        <f t="shared" si="77"/>
-        <v>6917.8452000000007</v>
+        <f t="shared" ref="AH11" si="74">AH5*0.07</f>
+        <v>6984.2962000000007</v>
       </c>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3">
@@ -3338,47 +3331,47 @@
       </c>
       <c r="BD11" s="3">
         <f>SUM(AE11:AH11)</f>
-        <v>27114.814000000002</v>
+        <v>27537.296200000001</v>
       </c>
       <c r="BE11" s="3">
         <f>BD11*1.02</f>
-        <v>27657.110280000004</v>
+        <v>28088.042124</v>
       </c>
       <c r="BF11" s="3">
-        <f t="shared" ref="BF11:BJ11" si="78">BE11*1.02</f>
-        <v>28210.252485600005</v>
+        <f t="shared" ref="BF11:BJ11" si="75">BE11*1.02</f>
+        <v>28649.802966480001</v>
       </c>
       <c r="BG11" s="3">
-        <f t="shared" si="78"/>
-        <v>28774.457535312005</v>
+        <f t="shared" si="75"/>
+        <v>29222.799025809603</v>
       </c>
       <c r="BH11" s="3">
-        <f t="shared" si="78"/>
-        <v>29349.946686018247</v>
+        <f t="shared" si="75"/>
+        <v>29807.255006325795</v>
       </c>
       <c r="BI11" s="3">
-        <f t="shared" si="78"/>
-        <v>29936.945619738613</v>
+        <f t="shared" si="75"/>
+        <v>30403.400106452311</v>
       </c>
       <c r="BJ11" s="3">
-        <f t="shared" si="78"/>
-        <v>30535.684532133386</v>
+        <f t="shared" si="75"/>
+        <v>31011.468108581357</v>
       </c>
       <c r="BK11" s="3">
         <f>BJ11*1.01</f>
-        <v>30841.04137745472</v>
+        <v>31321.582789667173</v>
       </c>
       <c r="BL11" s="3">
-        <f t="shared" ref="BL11:BN11" si="79">BK11*1.01</f>
-        <v>31149.451791229269</v>
+        <f t="shared" ref="BL11:BN11" si="76">BK11*1.01</f>
+        <v>31634.798617563843</v>
       </c>
       <c r="BM11" s="3">
-        <f t="shared" si="79"/>
-        <v>31460.94630914156</v>
+        <f t="shared" si="76"/>
+        <v>31951.146603739482</v>
       </c>
       <c r="BN11" s="3">
-        <f t="shared" si="79"/>
-        <v>31775.555772232976</v>
+        <f t="shared" si="76"/>
+        <v>32270.658069776877</v>
       </c>
     </row>
     <row r="12" spans="2:66" x14ac:dyDescent="0.3">
@@ -3386,257 +3379,257 @@
         <v>29</v>
       </c>
       <c r="C12" s="3">
-        <f t="shared" ref="C12:S12" si="80">C10+C11</f>
+        <f t="shared" ref="C12:S12" si="77">C10+C11</f>
         <v>7638</v>
       </c>
       <c r="D12" s="3">
-        <f t="shared" si="80"/>
+        <f t="shared" si="77"/>
         <v>7528</v>
       </c>
       <c r="E12" s="3">
-        <f t="shared" si="80"/>
+        <f t="shared" si="77"/>
         <v>7809</v>
       </c>
       <c r="F12" s="3">
-        <f t="shared" si="80"/>
+        <f t="shared" si="77"/>
         <v>7966</v>
       </c>
       <c r="G12" s="3">
-        <f t="shared" si="80"/>
+        <f t="shared" si="77"/>
         <v>8685</v>
       </c>
       <c r="H12" s="3">
-        <f t="shared" si="80"/>
+        <f t="shared" si="77"/>
         <v>8406</v>
       </c>
       <c r="I12" s="3">
-        <f t="shared" si="80"/>
+        <f t="shared" si="77"/>
         <v>8683</v>
       </c>
       <c r="J12" s="3">
-        <f t="shared" si="80"/>
+        <f t="shared" si="77"/>
         <v>8688</v>
       </c>
       <c r="K12" s="3">
-        <f t="shared" si="80"/>
+        <f t="shared" si="77"/>
         <v>9648</v>
       </c>
       <c r="L12" s="3">
-        <f t="shared" si="80"/>
+        <f t="shared" si="77"/>
         <v>9517</v>
       </c>
       <c r="M12" s="3">
-        <f t="shared" si="80"/>
+        <f t="shared" si="77"/>
         <v>9589</v>
       </c>
       <c r="N12" s="3">
-        <f t="shared" si="80"/>
+        <f t="shared" si="77"/>
         <v>9914</v>
       </c>
       <c r="O12" s="3">
-        <f t="shared" si="80"/>
+        <f t="shared" si="77"/>
         <v>10794</v>
       </c>
       <c r="P12" s="3">
-        <f t="shared" si="80"/>
+        <f t="shared" si="77"/>
         <v>10576</v>
       </c>
       <c r="Q12" s="3">
-        <f t="shared" ref="Q12:R12" si="81">Q10+Q11</f>
+        <f t="shared" ref="Q12:R12" si="78">Q10+Q11</f>
         <v>11129</v>
       </c>
       <c r="R12" s="3">
-        <f t="shared" si="81"/>
+        <f t="shared" si="78"/>
         <v>11388</v>
       </c>
       <c r="S12" s="3">
-        <f t="shared" si="80"/>
+        <f t="shared" si="77"/>
         <v>12755</v>
       </c>
       <c r="T12" s="3">
-        <f t="shared" ref="T12" si="82">T10+T11</f>
+        <f t="shared" ref="T12" si="79">T10+T11</f>
         <v>12580</v>
       </c>
       <c r="U12" s="3">
-        <f t="shared" ref="U12" si="83">U10+U11</f>
+        <f t="shared" ref="U12" si="80">U10+U11</f>
         <v>12809</v>
       </c>
       <c r="V12" s="3">
-        <f t="shared" ref="V12" si="84">V10+V11</f>
+        <f t="shared" ref="V12" si="81">V10+V11</f>
         <v>13201</v>
       </c>
       <c r="W12" s="3">
-        <f t="shared" ref="W12:X12" si="85">W10+W11</f>
+        <f t="shared" ref="W12:X12" si="82">W10+W11</f>
         <v>14316</v>
       </c>
       <c r="X12" s="3">
+        <f t="shared" si="82"/>
+        <v>13658</v>
+      </c>
+      <c r="Y12" s="3">
+        <f t="shared" ref="Y12:Z12" si="83">Y10+Y11</f>
+        <v>13415</v>
+      </c>
+      <c r="Z12" s="3">
+        <f t="shared" si="83"/>
+        <v>13458</v>
+      </c>
+      <c r="AA12" s="3">
+        <f t="shared" ref="AA12:AD12" si="84">AA10+AA11</f>
+        <v>14482</v>
+      </c>
+      <c r="AB12" s="3">
+        <f t="shared" si="84"/>
+        <v>14371</v>
+      </c>
+      <c r="AC12" s="3">
+        <f t="shared" si="84"/>
+        <v>14326</v>
+      </c>
+      <c r="AD12" s="3">
+        <f t="shared" si="84"/>
+        <v>14288</v>
+      </c>
+      <c r="AE12" s="3">
+        <f t="shared" ref="AE12:AH12" si="85">AE10+AE11</f>
+        <v>15443</v>
+      </c>
+      <c r="AF12" s="3">
         <f t="shared" si="85"/>
-        <v>13658</v>
-      </c>
-      <c r="Y12" s="3">
-        <f t="shared" ref="Y12:Z12" si="86">Y10+Y11</f>
-        <v>13415</v>
-      </c>
-      <c r="Z12" s="3">
-        <f t="shared" si="86"/>
-        <v>13458</v>
-      </c>
-      <c r="AA12" s="3">
-        <f t="shared" ref="AA12:AD12" si="87">AA10+AA11</f>
-        <v>14482</v>
-      </c>
-      <c r="AB12" s="3">
-        <f t="shared" si="87"/>
-        <v>14371</v>
-      </c>
-      <c r="AC12" s="3">
-        <f t="shared" si="87"/>
-        <v>14326</v>
-      </c>
-      <c r="AD12" s="3">
-        <f t="shared" si="87"/>
-        <v>14288</v>
-      </c>
-      <c r="AE12" s="3">
-        <f t="shared" ref="AE12:AH12" si="88">AE10+AE11</f>
-        <v>15443</v>
-      </c>
-      <c r="AF12" s="3">
-        <f t="shared" si="88"/>
         <v>15278</v>
       </c>
       <c r="AG12" s="3">
-        <f t="shared" si="88"/>
-        <v>14540.148800000001</v>
+        <f t="shared" si="85"/>
+        <v>15516</v>
       </c>
       <c r="AH12" s="3">
-        <f t="shared" si="88"/>
-        <v>14915.7952</v>
+        <f t="shared" si="85"/>
+        <v>15603.446200000002</v>
       </c>
       <c r="AI12" s="3"/>
       <c r="AJ12" s="3">
-        <f t="shared" ref="AJ12" si="89">AJ10+AJ11</f>
+        <f t="shared" ref="AJ12" si="86">AJ10+AJ11</f>
         <v>2399</v>
       </c>
       <c r="AK12" s="3">
-        <f t="shared" ref="AK12:AL12" si="90">AK10+AK11</f>
+        <f t="shared" ref="AK12:AL12" si="87">AK10+AK11</f>
         <v>3145</v>
       </c>
       <c r="AL12" s="3">
+        <f t="shared" si="87"/>
+        <v>3745</v>
+      </c>
+      <c r="AM12" s="3">
+        <f t="shared" ref="AM12:AN12" si="88">AM10+AM11</f>
+        <v>4870</v>
+      </c>
+      <c r="AN12" s="3">
+        <f t="shared" si="88"/>
+        <v>5482</v>
+      </c>
+      <c r="AO12" s="3">
+        <f t="shared" ref="AO12:AP12" si="89">AO10+AO11</f>
+        <v>7299</v>
+      </c>
+      <c r="AP12" s="3">
+        <f t="shared" si="89"/>
+        <v>10028</v>
+      </c>
+      <c r="AQ12" s="3">
+        <f t="shared" ref="AQ12:AR12" si="90">AQ10+AQ11</f>
+        <v>13421</v>
+      </c>
+      <c r="AR12" s="3">
         <f t="shared" si="90"/>
-        <v>3745</v>
-      </c>
-      <c r="AM12" s="3">
-        <f t="shared" ref="AM12:AN12" si="91">AM10+AM11</f>
-        <v>4870</v>
-      </c>
-      <c r="AN12" s="3">
+        <v>15305</v>
+      </c>
+      <c r="AS12" s="3">
+        <f t="shared" ref="AS12:AT12" si="91">AS10+AS11</f>
+        <v>18034</v>
+      </c>
+      <c r="AT12" s="3">
         <f t="shared" si="91"/>
-        <v>5482</v>
-      </c>
-      <c r="AO12" s="3">
-        <f t="shared" ref="AO12:AP12" si="92">AO10+AO11</f>
-        <v>7299</v>
-      </c>
-      <c r="AP12" s="3">
+        <v>22396</v>
+      </c>
+      <c r="AU12" s="3">
+        <f t="shared" ref="AU12:AV12" si="92">AU10+AU11</f>
+        <v>24239</v>
+      </c>
+      <c r="AV12" s="3">
         <f t="shared" si="92"/>
-        <v>10028</v>
-      </c>
-      <c r="AQ12" s="3">
-        <f t="shared" ref="AQ12:AR12" si="93">AQ10+AQ11</f>
-        <v>13421</v>
-      </c>
-      <c r="AR12" s="3">
+        <v>26842</v>
+      </c>
+      <c r="AW12" s="3">
+        <f t="shared" ref="AW12:BC12" si="93">AW10+AW11</f>
+        <v>30941</v>
+      </c>
+      <c r="AX12" s="3">
         <f t="shared" si="93"/>
-        <v>15305</v>
-      </c>
-      <c r="AS12" s="3">
-        <f t="shared" ref="AS12:AT12" si="94">AS10+AS11</f>
-        <v>18034</v>
-      </c>
-      <c r="AT12" s="3">
+        <v>34462</v>
+      </c>
+      <c r="AY12" s="3">
+        <f t="shared" si="93"/>
+        <v>38668</v>
+      </c>
+      <c r="AZ12" s="3">
+        <f t="shared" si="93"/>
+        <v>43887</v>
+      </c>
+      <c r="BA12" s="3">
+        <f t="shared" si="93"/>
+        <v>51345</v>
+      </c>
+      <c r="BB12" s="3">
+        <f t="shared" si="93"/>
+        <v>54847</v>
+      </c>
+      <c r="BC12" s="3">
+        <f t="shared" si="93"/>
+        <v>57467</v>
+      </c>
+      <c r="BD12" s="3">
+        <f t="shared" ref="BD12:BI12" si="94">BD10+BD11</f>
+        <v>61840.446200000006</v>
+      </c>
+      <c r="BE12" s="3">
         <f t="shared" si="94"/>
-        <v>22396</v>
-      </c>
-      <c r="AU12" s="3">
-        <f t="shared" ref="AU12:AV12" si="95">AU10+AU11</f>
-        <v>24239</v>
-      </c>
-      <c r="AV12" s="3">
+        <v>64106.349624000002</v>
+      </c>
+      <c r="BF12" s="3">
+        <f t="shared" si="94"/>
+        <v>66108.842766480011</v>
+      </c>
+      <c r="BG12" s="3">
+        <f t="shared" si="94"/>
+        <v>67805.61001980961</v>
+      </c>
+      <c r="BH12" s="3">
+        <f t="shared" si="94"/>
+        <v>69547.550330145808</v>
+      </c>
+      <c r="BI12" s="3">
+        <f t="shared" si="94"/>
+        <v>71335.904289986909</v>
+      </c>
+      <c r="BJ12" s="3">
+        <f t="shared" ref="BJ12:BL12" si="95">BJ10+BJ11</f>
+        <v>72762.622375786654</v>
+      </c>
+      <c r="BK12" s="3">
         <f t="shared" si="95"/>
-        <v>26842</v>
-      </c>
-      <c r="AW12" s="3">
-        <f t="shared" ref="AW12:BC12" si="96">AW10+AW11</f>
-        <v>30941</v>
-      </c>
-      <c r="AX12" s="3">
+        <v>73907.760142216575</v>
+      </c>
+      <c r="BL12" s="3">
+        <f t="shared" si="95"/>
+        <v>75072.699517164234</v>
+      </c>
+      <c r="BM12" s="3">
+        <f t="shared" ref="BM12:BN12" si="96">BM10+BM11</f>
+        <v>76257.805521331888</v>
+      </c>
+      <c r="BN12" s="3">
         <f t="shared" si="96"/>
-        <v>34462</v>
-      </c>
-      <c r="AY12" s="3">
-        <f t="shared" si="96"/>
-        <v>38668</v>
-      </c>
-      <c r="AZ12" s="3">
-        <f t="shared" si="96"/>
-        <v>43887</v>
-      </c>
-      <c r="BA12" s="3">
-        <f t="shared" si="96"/>
-        <v>51345</v>
-      </c>
-      <c r="BB12" s="3">
-        <f t="shared" si="96"/>
-        <v>54847</v>
-      </c>
-      <c r="BC12" s="3">
-        <f t="shared" si="96"/>
-        <v>57467</v>
-      </c>
-      <c r="BD12" s="3">
-        <f t="shared" ref="BD12:BI12" si="97">BD10+BD11</f>
-        <v>60176.944000000003</v>
-      </c>
-      <c r="BE12" s="3">
-        <f t="shared" si="97"/>
-        <v>62041.725480000008</v>
-      </c>
-      <c r="BF12" s="3">
-        <f t="shared" si="97"/>
-        <v>63970.252293600002</v>
-      </c>
-      <c r="BG12" s="3">
-        <f t="shared" si="97"/>
-        <v>65607.257337552001</v>
-      </c>
-      <c r="BH12" s="3">
-        <f t="shared" si="97"/>
-        <v>67287.730482325453</v>
-      </c>
-      <c r="BI12" s="3">
-        <f t="shared" si="97"/>
-        <v>69012.862929935029</v>
-      </c>
-      <c r="BJ12" s="3">
-        <f t="shared" ref="BJ12:BL12" si="98">BJ10+BJ11</f>
-        <v>70393.120188533736</v>
-      </c>
-      <c r="BK12" s="3">
-        <f t="shared" si="98"/>
-        <v>71495.625746983074</v>
-      </c>
-      <c r="BL12" s="3">
-        <f t="shared" si="98"/>
-        <v>72617.127848148186</v>
-      </c>
-      <c r="BM12" s="3">
-        <f t="shared" ref="BM12:BN12" si="99">BM10+BM11</f>
-        <v>73757.97588719886</v>
-      </c>
-      <c r="BN12" s="3">
-        <f t="shared" si="99"/>
-        <v>74918.525941851432</v>
+        <v>77463.450165721137</v>
       </c>
     </row>
     <row r="13" spans="2:66" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -3644,257 +3637,257 @@
         <v>32</v>
       </c>
       <c r="C13" s="9">
-        <f t="shared" ref="C13:N13" si="100">C9-C12</f>
+        <f t="shared" ref="C13:N13" si="97">C9-C12</f>
         <v>26274</v>
       </c>
       <c r="D13" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="97"/>
         <v>15894</v>
       </c>
       <c r="E13" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="97"/>
         <v>12612</v>
       </c>
       <c r="F13" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="97"/>
         <v>16118</v>
       </c>
       <c r="G13" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="97"/>
         <v>23346</v>
       </c>
       <c r="H13" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="97"/>
         <v>13415</v>
       </c>
       <c r="I13" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="97"/>
         <v>11544</v>
       </c>
       <c r="J13" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="97"/>
         <v>15625</v>
       </c>
       <c r="K13" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="97"/>
         <v>25569</v>
       </c>
       <c r="L13" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="97"/>
         <v>12853</v>
       </c>
       <c r="M13" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="97"/>
         <v>13091</v>
       </c>
       <c r="N13" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="97"/>
         <v>14775</v>
       </c>
       <c r="O13" s="9">
-        <f t="shared" ref="O13:S13" si="101">O9-O12</f>
+        <f t="shared" ref="O13:S13" si="98">O9-O12</f>
         <v>33534</v>
       </c>
       <c r="P13" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="98"/>
         <v>27503</v>
       </c>
       <c r="Q13" s="9">
-        <f t="shared" ref="Q13:R13" si="102">Q9-Q12</f>
+        <f t="shared" ref="Q13:R13" si="99">Q9-Q12</f>
         <v>24126</v>
       </c>
       <c r="R13" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="99"/>
         <v>23786</v>
       </c>
       <c r="S13" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="98"/>
         <v>41488</v>
       </c>
       <c r="T13" s="9">
-        <f t="shared" ref="T13" si="103">T9-T12</f>
+        <f t="shared" ref="T13" si="100">T9-T12</f>
         <v>29979</v>
       </c>
       <c r="U13" s="9">
-        <f t="shared" ref="U13" si="104">U9-U12</f>
+        <f t="shared" ref="U13" si="101">U9-U12</f>
         <v>23076</v>
       </c>
       <c r="V13" s="9">
-        <f t="shared" ref="V13" si="105">V9-V12</f>
+        <f t="shared" ref="V13" si="102">V9-V12</f>
         <v>24894</v>
       </c>
       <c r="W13" s="9">
-        <f t="shared" ref="W13:X13" si="106">W9-W12</f>
+        <f t="shared" ref="W13:X13" si="103">W9-W12</f>
         <v>36016</v>
       </c>
       <c r="X13" s="9">
+        <f t="shared" si="103"/>
+        <v>28318</v>
+      </c>
+      <c r="Y13" s="9">
+        <f t="shared" ref="Y13:Z13" si="104">Y9-Y12</f>
+        <v>22998</v>
+      </c>
+      <c r="Z13" s="9">
+        <f t="shared" si="104"/>
+        <v>26969</v>
+      </c>
+      <c r="AA13" s="9">
+        <f t="shared" ref="AA13:AD13" si="105">AA9-AA12</f>
+        <v>40373</v>
+      </c>
+      <c r="AB13" s="9">
+        <f t="shared" si="105"/>
+        <v>27900</v>
+      </c>
+      <c r="AC13" s="9">
+        <f t="shared" si="105"/>
+        <v>25352</v>
+      </c>
+      <c r="AD13" s="9">
+        <f t="shared" si="105"/>
+        <v>29591</v>
+      </c>
+      <c r="AE13" s="9">
+        <f t="shared" ref="AE13:AH13" si="106">AE9-AE12</f>
+        <v>42832</v>
+      </c>
+      <c r="AF13" s="9">
         <f t="shared" si="106"/>
-        <v>28318</v>
-      </c>
-      <c r="Y13" s="9">
-        <f t="shared" ref="Y13:Z13" si="107">Y9-Y12</f>
-        <v>22998</v>
-      </c>
-      <c r="Z13" s="9">
-        <f t="shared" si="107"/>
-        <v>26969</v>
-      </c>
-      <c r="AA13" s="9">
-        <f t="shared" ref="AA13:AD13" si="108">AA9-AA12</f>
-        <v>40373</v>
-      </c>
-      <c r="AB13" s="9">
-        <f t="shared" si="108"/>
-        <v>27900</v>
-      </c>
-      <c r="AC13" s="9">
-        <f t="shared" si="108"/>
-        <v>25352</v>
-      </c>
-      <c r="AD13" s="9">
-        <f t="shared" si="108"/>
-        <v>29591</v>
-      </c>
-      <c r="AE13" s="9">
-        <f t="shared" ref="AE13:AH13" si="109">AE9-AE12</f>
-        <v>42832</v>
-      </c>
-      <c r="AF13" s="9">
-        <f t="shared" si="109"/>
         <v>29589</v>
       </c>
       <c r="AG13" s="9">
-        <f t="shared" si="109"/>
-        <v>27149.166399999995</v>
+        <f t="shared" si="106"/>
+        <v>28202</v>
       </c>
       <c r="AH13" s="9">
-        <f t="shared" si="109"/>
-        <v>29947.539199999992</v>
+        <f t="shared" si="106"/>
+        <v>29685.03539999999</v>
       </c>
       <c r="AI13" s="9"/>
       <c r="AJ13" s="9">
-        <f t="shared" ref="AJ13" si="110">AJ9-AJ12</f>
+        <f t="shared" ref="AJ13" si="107">AJ9-AJ12</f>
         <v>1643</v>
       </c>
       <c r="AK13" s="9">
-        <f t="shared" ref="AK13:AL13" si="111">AK9-AK12</f>
+        <f t="shared" ref="AK13:AL13" si="108">AK9-AK12</f>
         <v>2453</v>
       </c>
       <c r="AL13" s="9">
+        <f t="shared" si="108"/>
+        <v>4409</v>
+      </c>
+      <c r="AM13" s="9">
+        <f t="shared" ref="AM13:AN13" si="109">AM9-AM12</f>
+        <v>8327</v>
+      </c>
+      <c r="AN13" s="9">
+        <f t="shared" si="109"/>
+        <v>11740</v>
+      </c>
+      <c r="AO13" s="9">
+        <f t="shared" ref="AO13:AP13" si="110">AO9-AO12</f>
+        <v>18385</v>
+      </c>
+      <c r="AP13" s="9">
+        <f t="shared" si="110"/>
+        <v>33790</v>
+      </c>
+      <c r="AQ13" s="9">
+        <f t="shared" ref="AQ13:AR13" si="111">AQ9-AQ12</f>
+        <v>55241</v>
+      </c>
+      <c r="AR13" s="9">
         <f t="shared" si="111"/>
-        <v>4409</v>
-      </c>
-      <c r="AM13" s="9">
-        <f t="shared" ref="AM13:AN13" si="112">AM9-AM12</f>
-        <v>8327</v>
-      </c>
-      <c r="AN13" s="9">
+        <v>48999</v>
+      </c>
+      <c r="AS13" s="9">
+        <f t="shared" ref="AS13:AT13" si="112">AS9-AS12</f>
+        <v>52503</v>
+      </c>
+      <c r="AT13" s="9">
         <f t="shared" si="112"/>
-        <v>11740</v>
-      </c>
-      <c r="AO13" s="9">
-        <f t="shared" ref="AO13:AP13" si="113">AO9-AO12</f>
-        <v>18385</v>
-      </c>
-      <c r="AP13" s="9">
+        <v>71230</v>
+      </c>
+      <c r="AU13" s="9">
+        <f t="shared" ref="AU13:AV13" si="113">AU9-AU12</f>
+        <v>60024</v>
+      </c>
+      <c r="AV13" s="9">
         <f t="shared" si="113"/>
-        <v>33790</v>
-      </c>
-      <c r="AQ13" s="9">
-        <f t="shared" ref="AQ13:AR13" si="114">AQ9-AQ12</f>
-        <v>55241</v>
-      </c>
-      <c r="AR13" s="9">
+        <v>61344</v>
+      </c>
+      <c r="AW13" s="9">
+        <f t="shared" ref="AW13:BC13" si="114">AW9-AW12</f>
+        <v>70898</v>
+      </c>
+      <c r="AX13" s="9">
         <f t="shared" si="114"/>
-        <v>48999</v>
-      </c>
-      <c r="AS13" s="9">
-        <f t="shared" ref="AS13:AT13" si="115">AS9-AS12</f>
-        <v>52503</v>
-      </c>
-      <c r="AT13" s="9">
+        <v>63930</v>
+      </c>
+      <c r="AY13" s="9">
+        <f t="shared" si="114"/>
+        <v>66288</v>
+      </c>
+      <c r="AZ13" s="9">
+        <f t="shared" si="114"/>
+        <v>108949</v>
+      </c>
+      <c r="BA13" s="9">
+        <f t="shared" si="114"/>
+        <v>119437</v>
+      </c>
+      <c r="BB13" s="9">
+        <f t="shared" si="114"/>
+        <v>114301</v>
+      </c>
+      <c r="BC13" s="9">
+        <f t="shared" si="114"/>
+        <v>123216</v>
+      </c>
+      <c r="BD13" s="9">
+        <f t="shared" ref="BD13:BI13" si="115">BD9-BD12</f>
+        <v>130308.03539999996</v>
+      </c>
+      <c r="BE13" s="9">
         <f t="shared" si="115"/>
-        <v>71230</v>
-      </c>
-      <c r="AU13" s="9">
-        <f t="shared" ref="AU13:AV13" si="116">AU9-AU12</f>
-        <v>60024</v>
-      </c>
-      <c r="AV13" s="9">
+        <v>135542.40917400003</v>
+      </c>
+      <c r="BF13" s="9">
+        <f t="shared" si="115"/>
+        <v>142011.50823387998</v>
+      </c>
+      <c r="BG13" s="9">
+        <f t="shared" si="115"/>
+        <v>147188.06470880198</v>
+      </c>
+      <c r="BH13" s="9">
+        <f t="shared" si="115"/>
+        <v>151659.77909082623</v>
+      </c>
+      <c r="BI13" s="9">
+        <f t="shared" si="115"/>
+        <v>155283.67630694085</v>
+      </c>
+      <c r="BJ13" s="9">
+        <f t="shared" ref="BJ13:BL13" si="116">BJ9-BJ12</f>
+        <v>158341.94402512099</v>
+      </c>
+      <c r="BK13" s="9">
         <f t="shared" si="116"/>
-        <v>61344</v>
-      </c>
-      <c r="AW13" s="9">
-        <f t="shared" ref="AW13:BC13" si="117">AW9-AW12</f>
-        <v>70898</v>
-      </c>
-      <c r="AX13" s="9">
+        <v>161793.20562065102</v>
+      </c>
+      <c r="BL13" s="9">
+        <f t="shared" si="116"/>
+        <v>165339.1902122215</v>
+      </c>
+      <c r="BM13" s="9">
+        <f t="shared" ref="BM13:BN13" si="117">BM9-BM12</f>
+        <v>168982.7348435038</v>
+      </c>
+      <c r="BN13" s="9">
         <f t="shared" si="117"/>
-        <v>63930</v>
-      </c>
-      <c r="AY13" s="9">
-        <f t="shared" si="117"/>
-        <v>66288</v>
-      </c>
-      <c r="AZ13" s="9">
-        <f t="shared" si="117"/>
-        <v>108949</v>
-      </c>
-      <c r="BA13" s="9">
-        <f t="shared" si="117"/>
-        <v>119437</v>
-      </c>
-      <c r="BB13" s="9">
-        <f t="shared" si="117"/>
-        <v>114301</v>
-      </c>
-      <c r="BC13" s="9">
-        <f t="shared" si="117"/>
-        <v>123216</v>
-      </c>
-      <c r="BD13" s="9">
-        <f t="shared" ref="BD13:BI13" si="118">BD9-BD12</f>
-        <v>129517.7056</v>
-      </c>
-      <c r="BE13" s="9">
-        <f t="shared" si="118"/>
-        <v>133413.69544400001</v>
-      </c>
-      <c r="BF13" s="9">
-        <f t="shared" si="118"/>
-        <v>138786.51930267998</v>
-      </c>
-      <c r="BG13" s="9">
-        <f t="shared" si="118"/>
-        <v>143944.64215423484</v>
-      </c>
-      <c r="BH13" s="9">
-        <f t="shared" si="118"/>
-        <v>148402.57903663252</v>
-      </c>
-      <c r="BI13" s="9">
-        <f t="shared" si="118"/>
-        <v>152018.12637211196</v>
-      </c>
-      <c r="BJ13" s="9">
-        <f t="shared" ref="BJ13:BL13" si="119">BJ9-BJ12</f>
-        <v>155055.59751014411</v>
-      </c>
-      <c r="BK13" s="9">
-        <f t="shared" si="119"/>
-        <v>158481.22018740021</v>
-      </c>
-      <c r="BL13" s="9">
-        <f t="shared" si="119"/>
-        <v>160830.41169081902</v>
-      </c>
-      <c r="BM13" s="9">
-        <f t="shared" ref="BM13:BN13" si="120">BM9-BM12</f>
-        <v>163218.38269530283</v>
-      </c>
-      <c r="BN13" s="9">
-        <f t="shared" si="120"/>
-        <v>165645.82674758311</v>
+        <v>172726.76329306368</v>
       </c>
     </row>
     <row r="14" spans="2:66" x14ac:dyDescent="0.3">
@@ -3992,7 +3985,7 @@
         <v>279</v>
       </c>
       <c r="AG14" s="3">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
@@ -4067,47 +4060,47 @@
       </c>
       <c r="BD14" s="3">
         <f>SUM(AE14:AH14)</f>
-        <v>527</v>
+        <v>698</v>
       </c>
       <c r="BE14" s="3">
         <f>BD17*0.005</f>
-        <v>545.35616352</v>
+        <v>547.39714867999987</v>
       </c>
       <c r="BF14" s="3">
-        <f t="shared" ref="BF14:BN14" si="121">BE17*0.005</f>
-        <v>558.04702497801611</v>
+        <f t="shared" ref="BF14:BN14" si="118">BE17*0.005</f>
+        <v>566.97905050634415</v>
       </c>
       <c r="BG14" s="3">
-        <f t="shared" si="121"/>
-        <v>580.55958356634835</v>
+        <f t="shared" si="118"/>
+        <v>594.06702257016934</v>
       </c>
       <c r="BH14" s="3">
-        <f t="shared" si="121"/>
-        <v>602.12914679680762</v>
+        <f t="shared" si="118"/>
+        <v>615.69479028217359</v>
       </c>
       <c r="BI14" s="3">
-        <f t="shared" si="121"/>
-        <v>620.76188953731003</v>
+        <f t="shared" si="118"/>
+        <v>634.38515406228498</v>
       </c>
       <c r="BJ14" s="3">
-        <f t="shared" si="121"/>
-        <v>635.86893082681365</v>
+        <f t="shared" si="118"/>
+        <v>649.52702284208999</v>
       </c>
       <c r="BK14" s="3">
-        <f t="shared" si="121"/>
-        <v>648.56286003313267</v>
+        <f t="shared" si="118"/>
+        <v>662.30815140957145</v>
       </c>
       <c r="BL14" s="3">
-        <f t="shared" si="121"/>
-        <v>662.89716077494177</v>
+        <f t="shared" si="118"/>
+        <v>676.74976937081408</v>
       </c>
       <c r="BM14" s="3">
-        <f t="shared" si="121"/>
-        <v>672.70356102618507</v>
+        <f t="shared" si="118"/>
+        <v>691.58224985997276</v>
       </c>
       <c r="BN14" s="3">
-        <f t="shared" si="121"/>
-        <v>682.69185236396186</v>
+        <f t="shared" si="118"/>
+        <v>706.82284089330415</v>
       </c>
     </row>
     <row r="15" spans="2:66" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -4115,257 +4108,257 @@
         <v>34</v>
       </c>
       <c r="C15" s="9">
-        <f t="shared" ref="C15:N15" si="122">C13-C14</f>
+        <f t="shared" ref="C15:N15" si="119">C13-C14</f>
         <v>27030</v>
       </c>
       <c r="D15" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="119"/>
         <v>16168</v>
       </c>
       <c r="E15" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="119"/>
         <v>13284</v>
       </c>
       <c r="F15" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="119"/>
         <v>16421</v>
       </c>
       <c r="G15" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="119"/>
         <v>23906</v>
       </c>
       <c r="H15" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="119"/>
         <v>13793</v>
       </c>
       <c r="I15" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="119"/>
         <v>11911</v>
       </c>
       <c r="J15" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="119"/>
         <v>16127</v>
       </c>
       <c r="K15" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="119"/>
         <v>25918</v>
       </c>
       <c r="L15" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="119"/>
         <v>13135</v>
       </c>
       <c r="M15" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="119"/>
         <v>13137</v>
       </c>
       <c r="N15" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="119"/>
         <v>14901</v>
       </c>
       <c r="O15" s="9">
-        <f t="shared" ref="O15:S15" si="123">O13-O14</f>
+        <f t="shared" ref="O15:S15" si="120">O13-O14</f>
         <v>33579</v>
       </c>
       <c r="P15" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="120"/>
         <v>28011</v>
       </c>
       <c r="Q15" s="9">
-        <f t="shared" ref="Q15:R15" si="124">Q13-Q14</f>
+        <f t="shared" ref="Q15:R15" si="121">Q13-Q14</f>
         <v>24369</v>
       </c>
       <c r="R15" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="121"/>
         <v>23248</v>
       </c>
       <c r="S15" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="120"/>
         <v>41241</v>
       </c>
       <c r="T15" s="9">
-        <f t="shared" ref="T15" si="125">T13-T14</f>
+        <f t="shared" ref="T15" si="122">T13-T14</f>
         <v>30139</v>
       </c>
       <c r="U15" s="9">
-        <f t="shared" ref="U15" si="126">U13-U14</f>
+        <f t="shared" ref="U15" si="123">U13-U14</f>
         <v>23066</v>
       </c>
       <c r="V15" s="9">
-        <f t="shared" ref="V15" si="127">V13-V14</f>
+        <f t="shared" ref="V15" si="124">V13-V14</f>
         <v>24657</v>
       </c>
       <c r="W15" s="9">
-        <f t="shared" ref="W15:X15" si="128">W13-W14</f>
+        <f t="shared" ref="W15:X15" si="125">W13-W14</f>
         <v>35623</v>
       </c>
       <c r="X15" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="125"/>
         <v>28382</v>
       </c>
       <c r="Y15" s="9">
-        <f t="shared" ref="Y15:Z15" si="129">Y13-Y14</f>
+        <f t="shared" ref="Y15:Z15" si="126">Y13-Y14</f>
         <v>22733</v>
       </c>
       <c r="Z15" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="126"/>
         <v>26998</v>
       </c>
       <c r="AA15" s="9">
-        <f t="shared" ref="AA15:AH15" si="130">AA13-AA14</f>
+        <f t="shared" ref="AA15:AH15" si="127">AA13-AA14</f>
         <v>40323</v>
       </c>
       <c r="AB15" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="127"/>
         <v>28058</v>
       </c>
       <c r="AC15" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="127"/>
         <v>25494</v>
       </c>
       <c r="AD15" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="127"/>
         <v>29610</v>
       </c>
       <c r="AE15" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="127"/>
         <v>42584</v>
       </c>
       <c r="AF15" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="127"/>
         <v>29310</v>
       </c>
       <c r="AG15" s="9">
-        <f t="shared" si="130"/>
-        <v>27149.166399999995</v>
+        <f t="shared" si="127"/>
+        <v>28031</v>
       </c>
       <c r="AH15" s="9">
-        <f t="shared" si="130"/>
-        <v>29947.539199999992</v>
+        <f t="shared" si="127"/>
+        <v>29685.03539999999</v>
       </c>
       <c r="AI15" s="9"/>
       <c r="AJ15" s="9">
-        <f t="shared" ref="AJ15" si="131">AJ13-AJ14</f>
+        <f t="shared" ref="AJ15" si="128">AJ13-AJ14</f>
         <v>1808</v>
       </c>
       <c r="AK15" s="9">
-        <f t="shared" ref="AK15:AL15" si="132">AK13-AK14</f>
+        <f t="shared" ref="AK15:AL15" si="129">AK13-AK14</f>
         <v>2818</v>
       </c>
       <c r="AL15" s="9">
+        <f t="shared" si="129"/>
+        <v>5008</v>
+      </c>
+      <c r="AM15" s="9">
+        <f t="shared" ref="AM15:AN15" si="130">AM13-AM14</f>
+        <v>8947</v>
+      </c>
+      <c r="AN15" s="9">
+        <f t="shared" si="130"/>
+        <v>12066</v>
+      </c>
+      <c r="AO15" s="9">
+        <f t="shared" ref="AO15:AP15" si="131">AO13-AO14</f>
+        <v>18540</v>
+      </c>
+      <c r="AP15" s="9">
+        <f t="shared" si="131"/>
+        <v>34205</v>
+      </c>
+      <c r="AQ15" s="9">
+        <f t="shared" ref="AQ15:AR15" si="132">AQ13-AQ14</f>
+        <v>55763</v>
+      </c>
+      <c r="AR15" s="9">
         <f t="shared" si="132"/>
-        <v>5008</v>
-      </c>
-      <c r="AM15" s="9">
-        <f t="shared" ref="AM15:AN15" si="133">AM13-AM14</f>
-        <v>8947</v>
-      </c>
-      <c r="AN15" s="9">
+        <v>50155</v>
+      </c>
+      <c r="AS15" s="9">
+        <f t="shared" ref="AS15:AT15" si="133">AS13-AS14</f>
+        <v>53483</v>
+      </c>
+      <c r="AT15" s="9">
         <f t="shared" si="133"/>
-        <v>12066</v>
-      </c>
-      <c r="AO15" s="9">
-        <f t="shared" ref="AO15:AP15" si="134">AO13-AO14</f>
-        <v>18540</v>
-      </c>
-      <c r="AP15" s="9">
+        <v>72515</v>
+      </c>
+      <c r="AU15" s="9">
+        <f t="shared" ref="AU15:AV15" si="134">AU13-AU14</f>
+        <v>61372</v>
+      </c>
+      <c r="AV15" s="9">
         <f t="shared" si="134"/>
-        <v>34205</v>
-      </c>
-      <c r="AQ15" s="9">
-        <f t="shared" ref="AQ15:AR15" si="135">AQ13-AQ14</f>
-        <v>55763</v>
-      </c>
-      <c r="AR15" s="9">
+        <v>64089</v>
+      </c>
+      <c r="AW15" s="9">
+        <f t="shared" ref="AW15:BC15" si="135">AW13-AW14</f>
+        <v>72903</v>
+      </c>
+      <c r="AX15" s="9">
         <f t="shared" si="135"/>
-        <v>50155</v>
-      </c>
-      <c r="AS15" s="9">
-        <f t="shared" ref="AS15:AT15" si="136">AS13-AS14</f>
-        <v>53483</v>
-      </c>
-      <c r="AT15" s="9">
+        <v>65737</v>
+      </c>
+      <c r="AY15" s="9">
+        <f t="shared" si="135"/>
+        <v>67091</v>
+      </c>
+      <c r="AZ15" s="9">
+        <f t="shared" si="135"/>
+        <v>109207</v>
+      </c>
+      <c r="BA15" s="9">
+        <f t="shared" si="135"/>
+        <v>119103</v>
+      </c>
+      <c r="BB15" s="9">
+        <f t="shared" si="135"/>
+        <v>113736</v>
+      </c>
+      <c r="BC15" s="9">
+        <f t="shared" si="135"/>
+        <v>123485</v>
+      </c>
+      <c r="BD15" s="9">
+        <f t="shared" ref="BD15:BI15" si="136">BD13-BD14</f>
+        <v>129610.03539999996</v>
+      </c>
+      <c r="BE15" s="9">
         <f t="shared" si="136"/>
-        <v>72515</v>
-      </c>
-      <c r="AU15" s="9">
-        <f t="shared" ref="AU15:AV15" si="137">AU13-AU14</f>
-        <v>61372</v>
-      </c>
-      <c r="AV15" s="9">
+        <v>134995.01202532003</v>
+      </c>
+      <c r="BF15" s="9">
+        <f t="shared" si="136"/>
+        <v>141444.52918337364</v>
+      </c>
+      <c r="BG15" s="9">
+        <f t="shared" si="136"/>
+        <v>146593.9976862318</v>
+      </c>
+      <c r="BH15" s="9">
+        <f t="shared" si="136"/>
+        <v>151044.08430054405</v>
+      </c>
+      <c r="BI15" s="9">
+        <f t="shared" si="136"/>
+        <v>154649.29115287858</v>
+      </c>
+      <c r="BJ15" s="9">
+        <f t="shared" ref="BJ15:BL15" si="137">BJ13-BJ14</f>
+        <v>157692.4170022789</v>
+      </c>
+      <c r="BK15" s="9">
         <f t="shared" si="137"/>
-        <v>64089</v>
-      </c>
-      <c r="AW15" s="9">
-        <f t="shared" ref="AW15:BC15" si="138">AW13-AW14</f>
-        <v>72903</v>
-      </c>
-      <c r="AX15" s="9">
+        <v>161130.89746924143</v>
+      </c>
+      <c r="BL15" s="9">
+        <f t="shared" si="137"/>
+        <v>164662.44044285067</v>
+      </c>
+      <c r="BM15" s="9">
+        <f t="shared" ref="BM15:BN15" si="138">BM13-BM14</f>
+        <v>168291.15259364384</v>
+      </c>
+      <c r="BN15" s="9">
         <f t="shared" si="138"/>
-        <v>65737</v>
-      </c>
-      <c r="AY15" s="9">
-        <f t="shared" si="138"/>
-        <v>67091</v>
-      </c>
-      <c r="AZ15" s="9">
-        <f t="shared" si="138"/>
-        <v>109207</v>
-      </c>
-      <c r="BA15" s="9">
-        <f t="shared" si="138"/>
-        <v>119103</v>
-      </c>
-      <c r="BB15" s="9">
-        <f t="shared" si="138"/>
-        <v>113736</v>
-      </c>
-      <c r="BC15" s="9">
-        <f t="shared" si="138"/>
-        <v>123485</v>
-      </c>
-      <c r="BD15" s="9">
-        <f t="shared" ref="BD15:BI15" si="139">BD13-BD14</f>
-        <v>128990.7056</v>
-      </c>
-      <c r="BE15" s="9">
-        <f t="shared" si="139"/>
-        <v>132868.33928048002</v>
-      </c>
-      <c r="BF15" s="9">
-        <f t="shared" si="139"/>
-        <v>138228.47227770198</v>
-      </c>
-      <c r="BG15" s="9">
-        <f t="shared" si="139"/>
-        <v>143364.08257066848</v>
-      </c>
-      <c r="BH15" s="9">
-        <f t="shared" si="139"/>
-        <v>147800.44988983573</v>
-      </c>
-      <c r="BI15" s="9">
-        <f t="shared" si="139"/>
-        <v>151397.36448257466</v>
-      </c>
-      <c r="BJ15" s="9">
-        <f t="shared" ref="BJ15:BL15" si="140">BJ13-BJ14</f>
-        <v>154419.72857931731</v>
-      </c>
-      <c r="BK15" s="9">
-        <f t="shared" si="140"/>
-        <v>157832.65732736708</v>
-      </c>
-      <c r="BL15" s="9">
-        <f t="shared" si="140"/>
-        <v>160167.51453004408</v>
-      </c>
-      <c r="BM15" s="9">
-        <f t="shared" ref="BM15:BN15" si="141">BM13-BM14</f>
-        <v>162545.67913427664</v>
-      </c>
-      <c r="BN15" s="9">
-        <f t="shared" si="141"/>
-        <v>164963.13489521915</v>
+        <v>172019.94045217038</v>
       </c>
     </row>
     <row r="16" spans="2:66" x14ac:dyDescent="0.3">
@@ -4463,12 +4456,11 @@
         <v>4530</v>
       </c>
       <c r="AG16" s="3">
-        <f t="shared" ref="AG16:AH16" si="142">AG15*0.16</f>
-        <v>4343.8666239999993</v>
+        <v>4597</v>
       </c>
       <c r="AH16" s="3">
-        <f t="shared" si="142"/>
-        <v>4791.6062719999991</v>
+        <f t="shared" ref="AH16" si="139">AH15*0.16</f>
+        <v>4749.6056639999988</v>
       </c>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3">
@@ -4540,47 +4532,47 @@
       </c>
       <c r="BD16" s="3">
         <f>SUM(AE16:AH16)</f>
-        <v>19919.472895999999</v>
+        <v>20130.605663999999</v>
       </c>
       <c r="BE16" s="3">
-        <f t="shared" ref="BE16:BL16" si="143">BE15*0.16</f>
-        <v>21258.934284876803</v>
+        <f t="shared" ref="BE16:BL16" si="140">BE15*0.16</f>
+        <v>21599.201924051205</v>
       </c>
       <c r="BF16" s="3">
-        <f t="shared" si="143"/>
-        <v>22116.555564432318</v>
+        <f t="shared" si="140"/>
+        <v>22631.124669339784</v>
       </c>
       <c r="BG16" s="3">
-        <f t="shared" si="143"/>
-        <v>22938.253211306957</v>
+        <f t="shared" si="140"/>
+        <v>23455.039629797087</v>
       </c>
       <c r="BH16" s="3">
-        <f t="shared" si="143"/>
-        <v>23648.071982373716</v>
+        <f t="shared" si="140"/>
+        <v>24167.053488087051</v>
       </c>
       <c r="BI16" s="3">
-        <f t="shared" si="143"/>
-        <v>24223.578317211945</v>
+        <f t="shared" si="140"/>
+        <v>24743.886584460572</v>
       </c>
       <c r="BJ16" s="3">
-        <f t="shared" si="143"/>
-        <v>24707.156572690768</v>
+        <f t="shared" si="140"/>
+        <v>25230.786720364624</v>
       </c>
       <c r="BK16" s="3">
-        <f t="shared" si="143"/>
-        <v>25253.225172378734</v>
+        <f t="shared" si="140"/>
+        <v>25780.943595078628</v>
       </c>
       <c r="BL16" s="3">
-        <f t="shared" si="143"/>
-        <v>25626.802324807053</v>
+        <f t="shared" si="140"/>
+        <v>26345.990470856108</v>
       </c>
       <c r="BM16" s="3">
-        <f t="shared" ref="BM16:BN16" si="144">BM15*0.16</f>
-        <v>26007.308661484261</v>
+        <f t="shared" ref="BM16:BN16" si="141">BM15*0.16</f>
+        <v>26926.584414983015</v>
       </c>
       <c r="BN16" s="3">
-        <f t="shared" si="144"/>
-        <v>26394.101583235064</v>
+        <f t="shared" si="141"/>
+        <v>27523.190472347262</v>
       </c>
     </row>
     <row r="17" spans="2:179" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -4588,709 +4580,709 @@
         <v>36</v>
       </c>
       <c r="C17" s="9">
-        <f t="shared" ref="C17:N17" si="145">C15-C16</f>
+        <f t="shared" ref="C17:N17" si="142">C15-C16</f>
         <v>20065</v>
       </c>
       <c r="D17" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="142"/>
         <v>13822</v>
       </c>
       <c r="E17" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="142"/>
         <v>11519</v>
       </c>
       <c r="F17" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="142"/>
         <v>14125</v>
       </c>
       <c r="G17" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="142"/>
         <v>19965</v>
       </c>
       <c r="H17" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="142"/>
         <v>11561</v>
       </c>
       <c r="I17" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="142"/>
         <v>10044</v>
       </c>
       <c r="J17" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="142"/>
         <v>13686</v>
       </c>
       <c r="K17" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="142"/>
         <v>22236</v>
       </c>
       <c r="L17" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="142"/>
         <v>11249</v>
       </c>
       <c r="M17" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="142"/>
         <v>11253</v>
       </c>
       <c r="N17" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="142"/>
         <v>12673</v>
       </c>
       <c r="O17" s="9">
-        <f t="shared" ref="O17:S17" si="146">O15-O16</f>
+        <f t="shared" ref="O17:S17" si="143">O15-O16</f>
         <v>28755</v>
       </c>
       <c r="P17" s="9">
-        <f t="shared" si="146"/>
+        <f t="shared" si="143"/>
         <v>23630</v>
       </c>
       <c r="Q17" s="9">
-        <f t="shared" ref="Q17:R17" si="147">Q15-Q16</f>
+        <f t="shared" ref="Q17:R17" si="144">Q15-Q16</f>
         <v>21744</v>
       </c>
       <c r="R17" s="9">
-        <f t="shared" si="147"/>
+        <f t="shared" si="144"/>
         <v>20551</v>
       </c>
       <c r="S17" s="9">
-        <f t="shared" si="146"/>
+        <f t="shared" si="143"/>
         <v>34630</v>
       </c>
       <c r="T17" s="9">
-        <f t="shared" ref="T17" si="148">T15-T16</f>
+        <f t="shared" ref="T17" si="145">T15-T16</f>
         <v>25010</v>
       </c>
       <c r="U17" s="9">
-        <f t="shared" ref="U17" si="149">U15-U16</f>
+        <f t="shared" ref="U17" si="146">U15-U16</f>
         <v>19442</v>
       </c>
       <c r="V17" s="9">
-        <f t="shared" ref="V17" si="150">V15-V16</f>
+        <f t="shared" ref="V17" si="147">V15-V16</f>
         <v>20721</v>
       </c>
       <c r="W17" s="9">
-        <f t="shared" ref="W17:X17" si="151">W15-W16</f>
+        <f t="shared" ref="W17:X17" si="148">W15-W16</f>
         <v>29998</v>
       </c>
       <c r="X17" s="9">
+        <f t="shared" si="148"/>
+        <v>24160</v>
+      </c>
+      <c r="Y17" s="9">
+        <f t="shared" ref="Y17:Z17" si="149">Y15-Y16</f>
+        <v>19881</v>
+      </c>
+      <c r="Z17" s="9">
+        <f t="shared" si="149"/>
+        <v>22956</v>
+      </c>
+      <c r="AA17" s="9">
+        <f t="shared" ref="AA17:AD17" si="150">AA15-AA16</f>
+        <v>33916</v>
+      </c>
+      <c r="AB17" s="9">
+        <f t="shared" si="150"/>
+        <v>23636</v>
+      </c>
+      <c r="AC17" s="9">
+        <f t="shared" si="150"/>
+        <v>21448</v>
+      </c>
+      <c r="AD17" s="9">
+        <f t="shared" si="150"/>
+        <v>14736</v>
+      </c>
+      <c r="AE17" s="9">
+        <f t="shared" ref="AE17:AH17" si="151">AE15-AE16</f>
+        <v>36330</v>
+      </c>
+      <c r="AF17" s="9">
         <f t="shared" si="151"/>
-        <v>24160</v>
-      </c>
-      <c r="Y17" s="9">
-        <f t="shared" ref="Y17:Z17" si="152">Y15-Y16</f>
-        <v>19881</v>
-      </c>
-      <c r="Z17" s="9">
-        <f t="shared" si="152"/>
-        <v>22956</v>
-      </c>
-      <c r="AA17" s="9">
-        <f t="shared" ref="AA17:AD17" si="153">AA15-AA16</f>
-        <v>33916</v>
-      </c>
-      <c r="AB17" s="9">
-        <f t="shared" si="153"/>
-        <v>23636</v>
-      </c>
-      <c r="AC17" s="9">
-        <f t="shared" si="153"/>
-        <v>21448</v>
-      </c>
-      <c r="AD17" s="9">
-        <f t="shared" si="153"/>
-        <v>14736</v>
-      </c>
-      <c r="AE17" s="9">
-        <f t="shared" ref="AE17:AH17" si="154">AE15-AE16</f>
-        <v>36330</v>
-      </c>
-      <c r="AF17" s="9">
-        <f t="shared" si="154"/>
         <v>24780</v>
       </c>
       <c r="AG17" s="9">
-        <f t="shared" si="154"/>
-        <v>22805.299775999996</v>
+        <f t="shared" si="151"/>
+        <v>23434</v>
       </c>
       <c r="AH17" s="9">
-        <f t="shared" si="154"/>
-        <v>25155.932927999995</v>
+        <f t="shared" si="151"/>
+        <v>24935.429735999991</v>
       </c>
       <c r="AI17" s="9"/>
       <c r="AJ17" s="9">
-        <f t="shared" ref="AJ17:AY17" si="155">AJ15-AJ16</f>
+        <f t="shared" ref="AJ17:AY17" si="152">AJ15-AJ16</f>
         <v>1328</v>
       </c>
       <c r="AK17" s="9">
-        <f t="shared" si="155"/>
+        <f t="shared" si="152"/>
         <v>1989</v>
       </c>
       <c r="AL17" s="9">
-        <f t="shared" si="155"/>
+        <f t="shared" si="152"/>
         <v>3496</v>
       </c>
       <c r="AM17" s="9">
-        <f t="shared" si="155"/>
+        <f t="shared" si="152"/>
         <v>6119</v>
       </c>
       <c r="AN17" s="9">
-        <f t="shared" si="155"/>
+        <f t="shared" si="152"/>
         <v>8235</v>
       </c>
       <c r="AO17" s="9">
-        <f t="shared" si="155"/>
+        <f t="shared" si="152"/>
         <v>14013</v>
       </c>
       <c r="AP17" s="9">
-        <f t="shared" si="155"/>
+        <f t="shared" si="152"/>
         <v>25922</v>
       </c>
       <c r="AQ17" s="9">
-        <f t="shared" si="155"/>
+        <f t="shared" si="152"/>
         <v>41733</v>
       </c>
       <c r="AR17" s="9">
-        <f t="shared" si="155"/>
+        <f t="shared" si="152"/>
         <v>37037</v>
       </c>
       <c r="AS17" s="9">
-        <f t="shared" si="155"/>
+        <f t="shared" si="152"/>
         <v>39510</v>
       </c>
       <c r="AT17" s="9">
-        <f t="shared" si="155"/>
+        <f t="shared" si="152"/>
         <v>53394</v>
       </c>
       <c r="AU17" s="9">
-        <f t="shared" si="155"/>
+        <f t="shared" si="152"/>
         <v>45687</v>
       </c>
       <c r="AV17" s="9">
-        <f t="shared" si="155"/>
+        <f t="shared" si="152"/>
         <v>48351</v>
       </c>
       <c r="AW17" s="9">
-        <f t="shared" si="155"/>
+        <f t="shared" si="152"/>
         <v>59531</v>
       </c>
       <c r="AX17" s="9">
-        <f t="shared" si="155"/>
+        <f t="shared" si="152"/>
         <v>55256</v>
       </c>
       <c r="AY17" s="9">
-        <f t="shared" si="155"/>
+        <f t="shared" si="152"/>
         <v>57411</v>
       </c>
       <c r="AZ17" s="9">
-        <f t="shared" ref="AZ17:BI17" si="156">AZ15-AZ16</f>
+        <f t="shared" ref="AZ17:BI17" si="153">AZ15-AZ16</f>
         <v>94680</v>
       </c>
       <c r="BA17" s="9">
-        <f t="shared" ref="BA17:BB17" si="157">BA15-BA16</f>
+        <f t="shared" ref="BA17:BB17" si="154">BA15-BA16</f>
         <v>99803</v>
       </c>
       <c r="BB17" s="9">
+        <f t="shared" si="154"/>
+        <v>96995</v>
+      </c>
+      <c r="BC17" s="9">
+        <f t="shared" ref="BC17" si="155">BC15-BC16</f>
+        <v>93736</v>
+      </c>
+      <c r="BD17" s="9">
+        <f t="shared" si="153"/>
+        <v>109479.42973599996</v>
+      </c>
+      <c r="BE17" s="9">
+        <f t="shared" si="153"/>
+        <v>113395.81010126883</v>
+      </c>
+      <c r="BF17" s="9">
+        <f t="shared" si="153"/>
+        <v>118813.40451403386</v>
+      </c>
+      <c r="BG17" s="9">
+        <f t="shared" si="153"/>
+        <v>123138.95805643471</v>
+      </c>
+      <c r="BH17" s="9">
+        <f t="shared" si="153"/>
+        <v>126877.030812457</v>
+      </c>
+      <c r="BI17" s="9">
+        <f t="shared" si="153"/>
+        <v>129905.404568418</v>
+      </c>
+      <c r="BJ17" s="9">
+        <f t="shared" ref="BJ17:BL17" si="156">BJ15-BJ16</f>
+        <v>132461.63028191429</v>
+      </c>
+      <c r="BK17" s="9">
+        <f t="shared" si="156"/>
+        <v>135349.95387416281</v>
+      </c>
+      <c r="BL17" s="9">
+        <f t="shared" si="156"/>
+        <v>138316.44997199456</v>
+      </c>
+      <c r="BM17" s="9">
+        <f t="shared" ref="BM17:BN17" si="157">BM15-BM16</f>
+        <v>141364.56817866082</v>
+      </c>
+      <c r="BN17" s="9">
         <f t="shared" si="157"/>
-        <v>96995</v>
-      </c>
-      <c r="BC17" s="9">
-        <f t="shared" ref="BC17" si="158">BC15-BC16</f>
-        <v>93736</v>
-      </c>
-      <c r="BD17" s="9">
-        <f t="shared" si="156"/>
-        <v>109071.23270399999</v>
-      </c>
-      <c r="BE17" s="9">
-        <f t="shared" si="156"/>
-        <v>111609.40499560322</v>
-      </c>
-      <c r="BF17" s="9">
-        <f t="shared" si="156"/>
-        <v>116111.91671326966</v>
-      </c>
-      <c r="BG17" s="9">
-        <f t="shared" si="156"/>
-        <v>120425.82935936152</v>
-      </c>
-      <c r="BH17" s="9">
-        <f t="shared" si="156"/>
-        <v>124152.37790746201</v>
-      </c>
-      <c r="BI17" s="9">
-        <f t="shared" si="156"/>
-        <v>127173.78616536272</v>
-      </c>
-      <c r="BJ17" s="9">
-        <f t="shared" ref="BJ17:BL17" si="159">BJ15-BJ16</f>
-        <v>129712.57200662653</v>
-      </c>
-      <c r="BK17" s="9">
-        <f t="shared" si="159"/>
-        <v>132579.43215498835</v>
-      </c>
-      <c r="BL17" s="9">
-        <f t="shared" si="159"/>
-        <v>134540.71220523701</v>
-      </c>
-      <c r="BM17" s="9">
-        <f t="shared" ref="BM17:BN17" si="160">BM15-BM16</f>
-        <v>136538.37047279236</v>
-      </c>
-      <c r="BN17" s="9">
-        <f t="shared" si="160"/>
-        <v>138569.03331198409</v>
+        <v>144496.74997982313</v>
       </c>
       <c r="BO17" s="6">
         <f>BN17*(1+$BQ$29)</f>
-        <v>137183.34297886424</v>
+        <v>143051.78248002491</v>
       </c>
       <c r="BP17" s="6">
-        <f t="shared" ref="BP17:CT17" si="161">BM17*(1+$BQ$29)</f>
-        <v>135172.98676806444</v>
+        <f t="shared" ref="BP17:CT17" si="158">BM17*(1+$BQ$29)</f>
+        <v>139950.92249687421</v>
       </c>
       <c r="BQ17" s="6">
+        <f t="shared" si="158"/>
+        <v>143051.78248002491</v>
+      </c>
+      <c r="BR17" s="6">
+        <f t="shared" si="158"/>
+        <v>141621.26465522466</v>
+      </c>
+      <c r="BS17" s="6">
+        <f t="shared" si="158"/>
+        <v>138551.41327190548</v>
+      </c>
+      <c r="BT17" s="6">
+        <f t="shared" si="158"/>
+        <v>141621.26465522466</v>
+      </c>
+      <c r="BU17" s="6">
+        <f t="shared" si="158"/>
+        <v>140205.05200867241</v>
+      </c>
+      <c r="BV17" s="6">
+        <f t="shared" si="158"/>
+        <v>137165.89913918643</v>
+      </c>
+      <c r="BW17" s="6">
+        <f t="shared" si="158"/>
+        <v>140205.05200867241</v>
+      </c>
+      <c r="BX17" s="6">
+        <f t="shared" si="158"/>
+        <v>138803.00148858569</v>
+      </c>
+      <c r="BY17" s="6">
+        <f t="shared" si="158"/>
+        <v>135794.24014779457</v>
+      </c>
+      <c r="BZ17" s="6">
+        <f t="shared" si="158"/>
+        <v>138803.00148858569</v>
+      </c>
+      <c r="CA17" s="6">
+        <f t="shared" si="158"/>
+        <v>137414.97147369984</v>
+      </c>
+      <c r="CB17" s="6">
+        <f t="shared" si="158"/>
+        <v>134436.29774631662</v>
+      </c>
+      <c r="CC17" s="6">
+        <f t="shared" si="158"/>
+        <v>137414.97147369984</v>
+      </c>
+      <c r="CD17" s="6">
+        <f t="shared" si="158"/>
+        <v>136040.82175896285</v>
+      </c>
+      <c r="CE17" s="6">
+        <f t="shared" si="158"/>
+        <v>133091.93476885345</v>
+      </c>
+      <c r="CF17" s="6">
+        <f t="shared" si="158"/>
+        <v>136040.82175896285</v>
+      </c>
+      <c r="CG17" s="6">
+        <f t="shared" si="158"/>
+        <v>134680.41354137321</v>
+      </c>
+      <c r="CH17" s="6">
+        <f t="shared" si="158"/>
+        <v>131761.01542116492</v>
+      </c>
+      <c r="CI17" s="6">
+        <f t="shared" si="158"/>
+        <v>134680.41354137321</v>
+      </c>
+      <c r="CJ17" s="6">
+        <f t="shared" si="158"/>
+        <v>133333.60940595949</v>
+      </c>
+      <c r="CK17" s="6">
+        <f t="shared" si="158"/>
+        <v>130443.40526695327</v>
+      </c>
+      <c r="CL17" s="6">
+        <f t="shared" si="158"/>
+        <v>133333.60940595949</v>
+      </c>
+      <c r="CM17" s="6">
+        <f t="shared" si="158"/>
+        <v>132000.27331189989</v>
+      </c>
+      <c r="CN17" s="6">
+        <f t="shared" si="158"/>
+        <v>129138.97121428374</v>
+      </c>
+      <c r="CO17" s="6">
+        <f t="shared" si="158"/>
+        <v>132000.27331189989</v>
+      </c>
+      <c r="CP17" s="6">
+        <f t="shared" si="158"/>
+        <v>130680.27057878088</v>
+      </c>
+      <c r="CQ17" s="6">
+        <f t="shared" si="158"/>
+        <v>127847.58150214089</v>
+      </c>
+      <c r="CR17" s="6">
+        <f t="shared" si="158"/>
+        <v>130680.27057878088</v>
+      </c>
+      <c r="CS17" s="6">
+        <f t="shared" si="158"/>
+        <v>129373.46787299307</v>
+      </c>
+      <c r="CT17" s="6">
+        <f t="shared" si="158"/>
+        <v>126569.10568711949</v>
+      </c>
+      <c r="CU17" s="6">
+        <f t="shared" ref="CU17:DZ17" si="159">CR17*(1+$BQ$29)</f>
+        <v>129373.46787299307</v>
+      </c>
+      <c r="CV17" s="6">
+        <f t="shared" si="159"/>
+        <v>128079.73319426314</v>
+      </c>
+      <c r="CW17" s="6">
+        <f t="shared" si="159"/>
+        <v>125303.4146302483</v>
+      </c>
+      <c r="CX17" s="6">
+        <f t="shared" si="159"/>
+        <v>128079.73319426314</v>
+      </c>
+      <c r="CY17" s="6">
+        <f t="shared" si="159"/>
+        <v>126798.9358623205</v>
+      </c>
+      <c r="CZ17" s="6">
+        <f t="shared" si="159"/>
+        <v>124050.38048394582</v>
+      </c>
+      <c r="DA17" s="6">
+        <f t="shared" si="159"/>
+        <v>126798.9358623205</v>
+      </c>
+      <c r="DB17" s="6">
+        <f t="shared" si="159"/>
+        <v>125530.9465036973</v>
+      </c>
+      <c r="DC17" s="6">
+        <f t="shared" si="159"/>
+        <v>122809.87667910635</v>
+      </c>
+      <c r="DD17" s="6">
+        <f t="shared" si="159"/>
+        <v>125530.9465036973</v>
+      </c>
+      <c r="DE17" s="6">
+        <f t="shared" si="159"/>
+        <v>124275.63703866032</v>
+      </c>
+      <c r="DF17" s="6">
+        <f t="shared" si="159"/>
+        <v>121581.77791231529</v>
+      </c>
+      <c r="DG17" s="6">
+        <f t="shared" si="159"/>
+        <v>124275.63703866032</v>
+      </c>
+      <c r="DH17" s="6">
+        <f t="shared" si="159"/>
+        <v>123032.88066827372</v>
+      </c>
+      <c r="DI17" s="6">
+        <f t="shared" si="159"/>
+        <v>120365.96013319213</v>
+      </c>
+      <c r="DJ17" s="6">
+        <f t="shared" si="159"/>
+        <v>123032.88066827372</v>
+      </c>
+      <c r="DK17" s="6">
+        <f t="shared" si="159"/>
+        <v>121802.55186159098</v>
+      </c>
+      <c r="DL17" s="6">
+        <f t="shared" si="159"/>
+        <v>119162.30053186021</v>
+      </c>
+      <c r="DM17" s="6">
+        <f t="shared" si="159"/>
+        <v>121802.55186159098</v>
+      </c>
+      <c r="DN17" s="6">
+        <f t="shared" si="159"/>
+        <v>120584.52634297508</v>
+      </c>
+      <c r="DO17" s="6">
+        <f t="shared" si="159"/>
+        <v>117970.67752654161</v>
+      </c>
+      <c r="DP17" s="6">
+        <f t="shared" si="159"/>
+        <v>120584.52634297508</v>
+      </c>
+      <c r="DQ17" s="6">
+        <f t="shared" si="159"/>
+        <v>119378.68107954532</v>
+      </c>
+      <c r="DR17" s="6">
+        <f t="shared" si="159"/>
+        <v>116790.9707512762</v>
+      </c>
+      <c r="DS17" s="6">
+        <f t="shared" si="159"/>
+        <v>119378.68107954532</v>
+      </c>
+      <c r="DT17" s="6">
+        <f t="shared" si="159"/>
+        <v>118184.89426874986</v>
+      </c>
+      <c r="DU17" s="6">
+        <f t="shared" si="159"/>
+        <v>115623.06104376343</v>
+      </c>
+      <c r="DV17" s="6">
+        <f t="shared" si="159"/>
+        <v>118184.89426874986</v>
+      </c>
+      <c r="DW17" s="6">
+        <f t="shared" si="159"/>
+        <v>117003.04532606236</v>
+      </c>
+      <c r="DX17" s="6">
+        <f t="shared" si="159"/>
+        <v>114466.8304333258</v>
+      </c>
+      <c r="DY17" s="6">
+        <f t="shared" si="159"/>
+        <v>117003.04532606236</v>
+      </c>
+      <c r="DZ17" s="6">
+        <f t="shared" si="159"/>
+        <v>115833.01487280174</v>
+      </c>
+      <c r="EA17" s="6">
+        <f t="shared" ref="EA17:FF17" si="160">DX17*(1+$BQ$29)</f>
+        <v>113322.16212899254</v>
+      </c>
+      <c r="EB17" s="6">
+        <f t="shared" si="160"/>
+        <v>115833.01487280174</v>
+      </c>
+      <c r="EC17" s="6">
+        <f t="shared" si="160"/>
+        <v>114674.68472407373</v>
+      </c>
+      <c r="ED17" s="6">
+        <f t="shared" si="160"/>
+        <v>112188.94050770262</v>
+      </c>
+      <c r="EE17" s="6">
+        <f t="shared" si="160"/>
+        <v>114674.68472407373</v>
+      </c>
+      <c r="EF17" s="6">
+        <f t="shared" si="160"/>
+        <v>113527.93787683299</v>
+      </c>
+      <c r="EG17" s="6">
+        <f t="shared" si="160"/>
+        <v>111067.05110262558</v>
+      </c>
+      <c r="EH17" s="6">
+        <f t="shared" si="160"/>
+        <v>113527.93787683299</v>
+      </c>
+      <c r="EI17" s="6">
+        <f t="shared" si="160"/>
+        <v>112392.65849806466</v>
+      </c>
+      <c r="EJ17" s="6">
+        <f t="shared" si="160"/>
+        <v>109956.38059159933</v>
+      </c>
+      <c r="EK17" s="6">
+        <f t="shared" si="160"/>
+        <v>112392.65849806466</v>
+      </c>
+      <c r="EL17" s="6">
+        <f t="shared" si="160"/>
+        <v>111268.731913084</v>
+      </c>
+      <c r="EM17" s="6">
+        <f t="shared" si="160"/>
+        <v>108856.81678568333</v>
+      </c>
+      <c r="EN17" s="6">
+        <f t="shared" si="160"/>
+        <v>111268.731913084</v>
+      </c>
+      <c r="EO17" s="6">
+        <f t="shared" si="160"/>
+        <v>110156.04459395316</v>
+      </c>
+      <c r="EP17" s="6">
+        <f t="shared" si="160"/>
+        <v>107768.2486178265</v>
+      </c>
+      <c r="EQ17" s="6">
+        <f t="shared" si="160"/>
+        <v>110156.04459395316</v>
+      </c>
+      <c r="ER17" s="6">
+        <f t="shared" si="160"/>
+        <v>109054.48414801364</v>
+      </c>
+      <c r="ES17" s="6">
+        <f t="shared" si="160"/>
+        <v>106690.56613164823</v>
+      </c>
+      <c r="ET17" s="6">
+        <f t="shared" si="160"/>
+        <v>109054.48414801364</v>
+      </c>
+      <c r="EU17" s="6">
+        <f t="shared" si="160"/>
+        <v>107963.9393065335</v>
+      </c>
+      <c r="EV17" s="6">
+        <f t="shared" si="160"/>
+        <v>105623.66047033174</v>
+      </c>
+      <c r="EW17" s="6">
+        <f t="shared" si="160"/>
+        <v>107963.9393065335</v>
+      </c>
+      <c r="EX17" s="6">
+        <f t="shared" si="160"/>
+        <v>106884.29991346816</v>
+      </c>
+      <c r="EY17" s="6">
+        <f t="shared" si="160"/>
+        <v>104567.42386562843</v>
+      </c>
+      <c r="EZ17" s="6">
+        <f t="shared" si="160"/>
+        <v>106884.29991346816</v>
+      </c>
+      <c r="FA17" s="6">
+        <f t="shared" si="160"/>
+        <v>105815.45691433348</v>
+      </c>
+      <c r="FB17" s="6">
+        <f t="shared" si="160"/>
+        <v>103521.74962697215</v>
+      </c>
+      <c r="FC17" s="6">
+        <f t="shared" si="160"/>
+        <v>105815.45691433348</v>
+      </c>
+      <c r="FD17" s="6">
+        <f t="shared" si="160"/>
+        <v>104757.30234519014</v>
+      </c>
+      <c r="FE17" s="6">
+        <f t="shared" si="160"/>
+        <v>102486.53213070243</v>
+      </c>
+      <c r="FF17" s="6">
+        <f t="shared" si="160"/>
+        <v>104757.30234519014</v>
+      </c>
+      <c r="FG17" s="6">
+        <f t="shared" ref="FG17:FW17" si="161">FD17*(1+$BQ$29)</f>
+        <v>103709.72932173824</v>
+      </c>
+      <c r="FH17" s="6">
         <f t="shared" si="161"/>
-        <v>137183.34297886424</v>
-      </c>
-      <c r="BR17" s="6">
+        <v>101461.66680939541</v>
+      </c>
+      <c r="FI17" s="6">
         <f t="shared" si="161"/>
-        <v>135811.50954907559</v>
-      </c>
-      <c r="BS17" s="6">
+        <v>103709.72932173824</v>
+      </c>
+      <c r="FJ17" s="6">
         <f t="shared" si="161"/>
-        <v>133821.2569003838</v>
-      </c>
-      <c r="BT17" s="6">
+        <v>102672.63202852085</v>
+      </c>
+      <c r="FK17" s="6">
         <f t="shared" si="161"/>
-        <v>135811.50954907559</v>
-      </c>
-      <c r="BU17" s="6">
+        <v>100447.05014130146</v>
+      </c>
+      <c r="FL17" s="6">
         <f t="shared" si="161"/>
-        <v>134453.39445358483</v>
-      </c>
-      <c r="BV17" s="6">
+        <v>102672.63202852085</v>
+      </c>
+      <c r="FM17" s="6">
         <f t="shared" si="161"/>
-        <v>132483.04433137996</v>
-      </c>
-      <c r="BW17" s="6">
+        <v>101645.90570823564</v>
+      </c>
+      <c r="FN17" s="6">
         <f t="shared" si="161"/>
-        <v>134453.39445358483</v>
-      </c>
-      <c r="BX17" s="6">
+        <v>99442.579639888441</v>
+      </c>
+      <c r="FO17" s="6">
         <f t="shared" si="161"/>
-        <v>133108.86050904897</v>
-      </c>
-      <c r="BY17" s="6">
+        <v>101645.90570823564</v>
+      </c>
+      <c r="FP17" s="6">
         <f t="shared" si="161"/>
-        <v>131158.21388806615</v>
-      </c>
-      <c r="BZ17" s="6">
+        <v>100629.44665115328</v>
+      </c>
+      <c r="FQ17" s="6">
         <f t="shared" si="161"/>
-        <v>133108.86050904897</v>
-      </c>
-      <c r="CA17" s="6">
+        <v>98448.153843489563</v>
+      </c>
+      <c r="FR17" s="6">
         <f t="shared" si="161"/>
-        <v>131777.77190395849</v>
-      </c>
-      <c r="CB17" s="6">
+        <v>100629.44665115328</v>
+      </c>
+      <c r="FS17" s="6">
         <f t="shared" si="161"/>
-        <v>129846.63174918549</v>
-      </c>
-      <c r="CC17" s="6">
+        <v>99623.152184641745</v>
+      </c>
+      <c r="FT17" s="6">
         <f t="shared" si="161"/>
-        <v>131777.77190395849</v>
-      </c>
-      <c r="CD17" s="6">
+        <v>97463.672305054672</v>
+      </c>
+      <c r="FU17" s="6">
         <f t="shared" si="161"/>
-        <v>130459.99418491891</v>
-      </c>
-      <c r="CE17" s="6">
+        <v>99623.152184641745</v>
+      </c>
+      <c r="FV17" s="6">
         <f t="shared" si="161"/>
-        <v>128548.16543169363</v>
-      </c>
-      <c r="CF17" s="6">
+        <v>98626.920662795324</v>
+      </c>
+      <c r="FW17" s="6">
         <f t="shared" si="161"/>
-        <v>130459.99418491891</v>
-      </c>
-      <c r="CG17" s="6">
-        <f t="shared" si="161"/>
-        <v>129155.39424306972</v>
-      </c>
-      <c r="CH17" s="6">
-        <f t="shared" si="161"/>
-        <v>127262.68377737669</v>
-      </c>
-      <c r="CI17" s="6">
-        <f t="shared" si="161"/>
-        <v>129155.39424306972</v>
-      </c>
-      <c r="CJ17" s="6">
-        <f t="shared" si="161"/>
-        <v>127863.84030063903</v>
-      </c>
-      <c r="CK17" s="6">
-        <f t="shared" si="161"/>
-        <v>125990.05693960292</v>
-      </c>
-      <c r="CL17" s="6">
-        <f t="shared" si="161"/>
-        <v>127863.84030063903</v>
-      </c>
-      <c r="CM17" s="6">
-        <f t="shared" si="161"/>
-        <v>126585.20189763264</v>
-      </c>
-      <c r="CN17" s="6">
-        <f t="shared" si="161"/>
-        <v>124730.15637020688</v>
-      </c>
-      <c r="CO17" s="6">
-        <f t="shared" si="161"/>
-        <v>126585.20189763264</v>
-      </c>
-      <c r="CP17" s="6">
-        <f t="shared" si="161"/>
-        <v>125319.34987865631</v>
-      </c>
-      <c r="CQ17" s="6">
-        <f t="shared" si="161"/>
-        <v>123482.85480650481</v>
-      </c>
-      <c r="CR17" s="6">
-        <f t="shared" si="161"/>
-        <v>125319.34987865631</v>
-      </c>
-      <c r="CS17" s="6">
-        <f t="shared" si="161"/>
-        <v>124066.15637986975</v>
-      </c>
-      <c r="CT17" s="6">
-        <f t="shared" si="161"/>
-        <v>122248.02625843976</v>
-      </c>
-      <c r="CU17" s="6">
-        <f t="shared" ref="CU17:DZ17" si="162">CR17*(1+$BQ$29)</f>
-        <v>124066.15637986975</v>
-      </c>
-      <c r="CV17" s="6">
-        <f t="shared" si="162"/>
-        <v>122825.49481607105</v>
-      </c>
-      <c r="CW17" s="6">
-        <f t="shared" si="162"/>
-        <v>121025.54599585535</v>
-      </c>
-      <c r="CX17" s="6">
-        <f t="shared" si="162"/>
-        <v>122825.49481607105</v>
-      </c>
-      <c r="CY17" s="6">
-        <f t="shared" si="162"/>
-        <v>121597.23986791034</v>
-      </c>
-      <c r="CZ17" s="6">
-        <f t="shared" si="162"/>
-        <v>119815.2905358968</v>
-      </c>
-      <c r="DA17" s="6">
-        <f t="shared" si="162"/>
-        <v>121597.23986791034</v>
-      </c>
-      <c r="DB17" s="6">
-        <f t="shared" si="162"/>
-        <v>120381.26746923123</v>
-      </c>
-      <c r="DC17" s="6">
-        <f t="shared" si="162"/>
-        <v>118617.13763053784</v>
-      </c>
-      <c r="DD17" s="6">
-        <f t="shared" si="162"/>
-        <v>120381.26746923123</v>
-      </c>
-      <c r="DE17" s="6">
-        <f t="shared" si="162"/>
-        <v>119177.45479453892</v>
-      </c>
-      <c r="DF17" s="6">
-        <f t="shared" si="162"/>
-        <v>117430.96625423245</v>
-      </c>
-      <c r="DG17" s="6">
-        <f t="shared" si="162"/>
-        <v>119177.45479453892</v>
-      </c>
-      <c r="DH17" s="6">
-        <f t="shared" si="162"/>
-        <v>117985.68024659353</v>
-      </c>
-      <c r="DI17" s="6">
-        <f t="shared" si="162"/>
-        <v>116256.65659169013</v>
-      </c>
-      <c r="DJ17" s="6">
-        <f t="shared" si="162"/>
-        <v>117985.68024659353</v>
-      </c>
-      <c r="DK17" s="6">
-        <f t="shared" si="162"/>
-        <v>116805.8234441276</v>
-      </c>
-      <c r="DL17" s="6">
-        <f t="shared" si="162"/>
-        <v>115094.09002577323</v>
-      </c>
-      <c r="DM17" s="6">
-        <f t="shared" si="162"/>
-        <v>116805.8234441276</v>
-      </c>
-      <c r="DN17" s="6">
-        <f t="shared" si="162"/>
-        <v>115637.76520968632</v>
-      </c>
-      <c r="DO17" s="6">
-        <f t="shared" si="162"/>
-        <v>113943.1491255155</v>
-      </c>
-      <c r="DP17" s="6">
-        <f t="shared" si="162"/>
-        <v>115637.76520968632</v>
-      </c>
-      <c r="DQ17" s="6">
-        <f t="shared" si="162"/>
-        <v>114481.38755758945</v>
-      </c>
-      <c r="DR17" s="6">
-        <f t="shared" si="162"/>
-        <v>112803.71763426035</v>
-      </c>
-      <c r="DS17" s="6">
-        <f t="shared" si="162"/>
-        <v>114481.38755758945</v>
-      </c>
-      <c r="DT17" s="6">
-        <f t="shared" si="162"/>
-        <v>113336.57368201355</v>
-      </c>
-      <c r="DU17" s="6">
-        <f t="shared" si="162"/>
-        <v>111675.68045791774</v>
-      </c>
-      <c r="DV17" s="6">
-        <f t="shared" si="162"/>
-        <v>113336.57368201355</v>
-      </c>
-      <c r="DW17" s="6">
-        <f t="shared" si="162"/>
-        <v>112203.20794519341</v>
-      </c>
-      <c r="DX17" s="6">
-        <f t="shared" si="162"/>
-        <v>110558.92365333856</v>
-      </c>
-      <c r="DY17" s="6">
-        <f t="shared" si="162"/>
-        <v>112203.20794519341</v>
-      </c>
-      <c r="DZ17" s="6">
-        <f t="shared" si="162"/>
-        <v>111081.17586574148</v>
-      </c>
-      <c r="EA17" s="6">
-        <f t="shared" ref="EA17:FF17" si="163">DX17*(1+$BQ$29)</f>
-        <v>109453.33441680517</v>
-      </c>
-      <c r="EB17" s="6">
-        <f t="shared" si="163"/>
-        <v>111081.17586574148</v>
-      </c>
-      <c r="EC17" s="6">
-        <f t="shared" si="163"/>
-        <v>109970.36410708405</v>
-      </c>
-      <c r="ED17" s="6">
-        <f t="shared" si="163"/>
-        <v>108358.80107263711</v>
-      </c>
-      <c r="EE17" s="6">
-        <f t="shared" si="163"/>
-        <v>109970.36410708405</v>
-      </c>
-      <c r="EF17" s="6">
-        <f t="shared" si="163"/>
-        <v>108870.66046601321</v>
-      </c>
-      <c r="EG17" s="6">
-        <f t="shared" si="163"/>
-        <v>107275.21306191075</v>
-      </c>
-      <c r="EH17" s="6">
-        <f t="shared" si="163"/>
-        <v>108870.66046601321</v>
-      </c>
-      <c r="EI17" s="6">
-        <f t="shared" si="163"/>
-        <v>107781.95386135307</v>
-      </c>
-      <c r="EJ17" s="6">
-        <f t="shared" si="163"/>
-        <v>106202.46093129164</v>
-      </c>
-      <c r="EK17" s="6">
-        <f t="shared" si="163"/>
-        <v>107781.95386135307</v>
-      </c>
-      <c r="EL17" s="6">
-        <f t="shared" si="163"/>
-        <v>106704.13432273954</v>
-      </c>
-      <c r="EM17" s="6">
-        <f t="shared" si="163"/>
-        <v>105140.43632197872</v>
-      </c>
-      <c r="EN17" s="6">
-        <f t="shared" si="163"/>
-        <v>106704.13432273954</v>
-      </c>
-      <c r="EO17" s="6">
-        <f t="shared" si="163"/>
-        <v>105637.09297951215</v>
-      </c>
-      <c r="EP17" s="6">
-        <f t="shared" si="163"/>
-        <v>104089.03195875893</v>
-      </c>
-      <c r="EQ17" s="6">
-        <f t="shared" si="163"/>
-        <v>105637.09297951215</v>
-      </c>
-      <c r="ER17" s="6">
-        <f t="shared" si="163"/>
-        <v>104580.72204971702</v>
-      </c>
-      <c r="ES17" s="6">
-        <f t="shared" si="163"/>
-        <v>103048.14163917134</v>
-      </c>
-      <c r="ET17" s="6">
-        <f t="shared" si="163"/>
-        <v>104580.72204971702</v>
-      </c>
-      <c r="EU17" s="6">
-        <f t="shared" si="163"/>
-        <v>103534.91482921985</v>
-      </c>
-      <c r="EV17" s="6">
-        <f t="shared" si="163"/>
-        <v>102017.66022277962</v>
-      </c>
-      <c r="EW17" s="6">
-        <f t="shared" si="163"/>
-        <v>103534.91482921985</v>
-      </c>
-      <c r="EX17" s="6">
-        <f t="shared" si="163"/>
-        <v>102499.56568092766</v>
-      </c>
-      <c r="EY17" s="6">
-        <f t="shared" si="163"/>
-        <v>100997.48362055182</v>
-      </c>
-      <c r="EZ17" s="6">
-        <f t="shared" si="163"/>
-        <v>102499.56568092766</v>
-      </c>
-      <c r="FA17" s="6">
-        <f t="shared" si="163"/>
-        <v>101474.57002411838</v>
-      </c>
-      <c r="FB17" s="6">
-        <f t="shared" si="163"/>
-        <v>99987.508784346297</v>
-      </c>
-      <c r="FC17" s="6">
-        <f t="shared" si="163"/>
-        <v>101474.57002411838</v>
-      </c>
-      <c r="FD17" s="6">
-        <f t="shared" si="163"/>
-        <v>100459.8243238772</v>
-      </c>
-      <c r="FE17" s="6">
-        <f t="shared" si="163"/>
-        <v>98987.633696502831</v>
-      </c>
-      <c r="FF17" s="6">
-        <f t="shared" si="163"/>
-        <v>100459.8243238772</v>
-      </c>
-      <c r="FG17" s="6">
-        <f t="shared" ref="FG17:FW17" si="164">FD17*(1+$BQ$29)</f>
-        <v>99455.226080638429</v>
-      </c>
-      <c r="FH17" s="6">
-        <f t="shared" si="164"/>
-        <v>97997.757359537805</v>
-      </c>
-      <c r="FI17" s="6">
-        <f t="shared" si="164"/>
-        <v>99455.226080638429</v>
-      </c>
-      <c r="FJ17" s="6">
-        <f t="shared" si="164"/>
-        <v>98460.673819832038</v>
-      </c>
-      <c r="FK17" s="6">
-        <f t="shared" si="164"/>
-        <v>97017.779785942432</v>
-      </c>
-      <c r="FL17" s="6">
-        <f t="shared" si="164"/>
-        <v>98460.673819832038</v>
-      </c>
-      <c r="FM17" s="6">
-        <f t="shared" si="164"/>
-        <v>97476.067081633722</v>
-      </c>
-      <c r="FN17" s="6">
-        <f t="shared" si="164"/>
-        <v>96047.601988083014</v>
-      </c>
-      <c r="FO17" s="6">
-        <f t="shared" si="164"/>
-        <v>97476.067081633722</v>
-      </c>
-      <c r="FP17" s="6">
-        <f t="shared" si="164"/>
-        <v>96501.306410817386</v>
-      </c>
-      <c r="FQ17" s="6">
-        <f t="shared" si="164"/>
-        <v>95087.125968202177</v>
-      </c>
-      <c r="FR17" s="6">
-        <f t="shared" si="164"/>
-        <v>96501.306410817386</v>
-      </c>
-      <c r="FS17" s="6">
-        <f t="shared" si="164"/>
-        <v>95536.293346709208</v>
-      </c>
-      <c r="FT17" s="6">
-        <f t="shared" si="164"/>
-        <v>94136.254708520151</v>
-      </c>
-      <c r="FU17" s="6">
-        <f t="shared" si="164"/>
-        <v>95536.293346709208</v>
-      </c>
-      <c r="FV17" s="6">
-        <f t="shared" si="164"/>
-        <v>94580.930413242109</v>
-      </c>
-      <c r="FW17" s="6">
-        <f t="shared" si="164"/>
-        <v>93194.892161434953</v>
+        <v>96489.03558200413</v>
       </c>
     </row>
     <row r="18" spans="2:179" x14ac:dyDescent="0.3">
@@ -5389,12 +5381,10 @@
         <v>14935.8</v>
       </c>
       <c r="AG18" s="3">
-        <f>14935.8</f>
-        <v>14935.8</v>
+        <v>14902.9</v>
       </c>
       <c r="AH18" s="3">
-        <f>14935.8</f>
-        <v>14935.8</v>
+        <v>14902.9</v>
       </c>
       <c r="AI18" s="3"/>
       <c r="AJ18" s="3">
@@ -5460,48 +5450,37 @@
         <v>15172</v>
       </c>
       <c r="BD18" s="3">
-        <f t="shared" ref="BD18:BN18" si="165">14935.8</f>
-        <v>14935.8</v>
+        <v>14902.9</v>
       </c>
       <c r="BE18" s="3">
-        <f t="shared" si="165"/>
-        <v>14935.8</v>
+        <v>14902.9</v>
       </c>
       <c r="BF18" s="3">
-        <f t="shared" si="165"/>
-        <v>14935.8</v>
+        <v>14902.9</v>
       </c>
       <c r="BG18" s="3">
-        <f t="shared" si="165"/>
-        <v>14935.8</v>
+        <v>14902.9</v>
       </c>
       <c r="BH18" s="3">
-        <f t="shared" si="165"/>
-        <v>14935.8</v>
+        <v>14902.9</v>
       </c>
       <c r="BI18" s="3">
-        <f t="shared" si="165"/>
-        <v>14935.8</v>
+        <v>14902.9</v>
       </c>
       <c r="BJ18" s="3">
-        <f t="shared" si="165"/>
-        <v>14935.8</v>
+        <v>14902.9</v>
       </c>
       <c r="BK18" s="3">
-        <f t="shared" si="165"/>
-        <v>14935.8</v>
+        <v>14902.9</v>
       </c>
       <c r="BL18" s="3">
-        <f t="shared" si="165"/>
-        <v>14935.8</v>
+        <v>14902.9</v>
       </c>
       <c r="BM18" s="3">
-        <f t="shared" si="165"/>
-        <v>14935.8</v>
+        <v>14902.9</v>
       </c>
       <c r="BN18" s="3">
-        <f t="shared" si="165"/>
-        <v>14935.8</v>
+        <v>14902.9</v>
       </c>
     </row>
     <row r="19" spans="2:179" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -5509,257 +5488,257 @@
         <v>37</v>
       </c>
       <c r="C19" s="7">
-        <f t="shared" ref="C19:N19" si="166">C17/C18</f>
+        <f t="shared" ref="C19:N19" si="162">C17/C18</f>
         <v>1.1732178198601657</v>
       </c>
       <c r="D19" s="7">
-        <f t="shared" si="166"/>
+        <f t="shared" si="162"/>
         <v>0.80818423653661653</v>
       </c>
       <c r="E19" s="7">
-        <f t="shared" si="166"/>
+        <f t="shared" si="162"/>
         <v>0.67352584435431095</v>
       </c>
       <c r="F19" s="7">
-        <f t="shared" si="166"/>
+        <f t="shared" si="162"/>
         <v>0.82590090732742794</v>
       </c>
       <c r="G19" s="7">
-        <f t="shared" si="166"/>
+        <f t="shared" si="162"/>
         <v>1.167370733790591</v>
       </c>
       <c r="H19" s="7">
-        <f t="shared" si="166"/>
+        <f t="shared" si="162"/>
         <v>0.67598162050353239</v>
       </c>
       <c r="I19" s="7">
-        <f t="shared" si="166"/>
+        <f t="shared" si="162"/>
         <v>0.58728132482808393</v>
       </c>
       <c r="J19" s="7">
-        <f t="shared" si="166"/>
+        <f t="shared" si="162"/>
         <v>0.80023219948199498</v>
       </c>
       <c r="K19" s="7">
-        <f t="shared" si="166"/>
+        <f t="shared" si="162"/>
         <v>1.3001580584306327</v>
       </c>
       <c r="L19" s="7">
-        <f t="shared" si="166"/>
+        <f t="shared" si="162"/>
         <v>0.65773871196645928</v>
       </c>
       <c r="M19" s="7">
-        <f t="shared" si="166"/>
+        <f t="shared" si="162"/>
         <v>0.65797259540924224</v>
       </c>
       <c r="N19" s="7">
-        <f t="shared" si="166"/>
+        <f t="shared" si="162"/>
         <v>0.74100121759720317</v>
       </c>
       <c r="O19" s="7">
-        <f t="shared" ref="O19:S19" si="167">O17/O18</f>
+        <f t="shared" ref="O19:S19" si="163">O17/O18</f>
         <v>1.6813295993062081</v>
       </c>
       <c r="P19" s="7">
-        <f t="shared" si="167"/>
+        <f t="shared" si="163"/>
         <v>1.4160214770248569</v>
       </c>
       <c r="Q19" s="7">
-        <f t="shared" ref="Q19:R19" si="168">Q17/Q18</f>
+        <f t="shared" ref="Q19:R19" si="164">Q17/Q18</f>
         <v>1.3980582524271845</v>
       </c>
       <c r="R19" s="7">
+        <f t="shared" si="164"/>
+        <v>1.3213527936732463</v>
+      </c>
+      <c r="S19" s="7">
+        <f t="shared" si="163"/>
+        <v>2.2265800810133092</v>
+      </c>
+      <c r="T19" s="7">
+        <f t="shared" ref="T19" si="165">T17/T18</f>
+        <v>1.6080498939111425</v>
+      </c>
+      <c r="U19" s="7">
+        <f t="shared" ref="U19" si="166">U17/U18</f>
+        <v>1.2500482222079341</v>
+      </c>
+      <c r="V19" s="7">
+        <f t="shared" ref="V19" si="167">V17/V18</f>
+        <v>1.3322831608049894</v>
+      </c>
+      <c r="W19" s="7">
+        <f t="shared" ref="W19:X19" si="168">W17/W18</f>
+        <v>1.9287597248119335</v>
+      </c>
+      <c r="X19" s="7">
         <f t="shared" si="168"/>
-        <v>1.3213527936732463</v>
-      </c>
-      <c r="S19" s="7">
-        <f t="shared" si="167"/>
-        <v>2.2265800810133092</v>
-      </c>
-      <c r="T19" s="7">
-        <f t="shared" ref="T19" si="169">T17/T18</f>
-        <v>1.6080498939111425</v>
-      </c>
-      <c r="U19" s="7">
-        <f t="shared" ref="U19" si="170">U17/U18</f>
-        <v>1.2500482222079341</v>
-      </c>
-      <c r="V19" s="7">
-        <f t="shared" ref="V19" si="171">V17/V18</f>
-        <v>1.3322831608049894</v>
-      </c>
-      <c r="W19" s="7">
-        <f t="shared" ref="W19:X19" si="172">W17/W18</f>
-        <v>1.9287597248119335</v>
-      </c>
-      <c r="X19" s="7">
-        <f t="shared" si="172"/>
         <v>1.5533980582524272</v>
       </c>
       <c r="Y19" s="7">
-        <f t="shared" ref="Y19:Z19" si="173">Y17/Y18</f>
+        <f t="shared" ref="Y19:Z19" si="169">Y17/Y18</f>
         <v>1.2782742879187294</v>
       </c>
       <c r="Z19" s="7">
-        <f t="shared" si="173"/>
+        <f t="shared" si="169"/>
         <v>1.4759853404487879</v>
       </c>
       <c r="AA19" s="7">
-        <f t="shared" ref="AA19:AD19" si="174">AA17/AA18</f>
+        <f t="shared" ref="AA19:AD19" si="170">AA17/AA18</f>
         <v>2.1806725390599886</v>
       </c>
       <c r="AB19" s="7">
-        <f t="shared" si="174"/>
+        <f t="shared" si="170"/>
         <v>1.5197068089757604</v>
       </c>
       <c r="AC19" s="7">
-        <f t="shared" si="174"/>
+        <f t="shared" si="170"/>
         <v>1.3790265543625024</v>
       </c>
       <c r="AD19" s="7">
-        <f t="shared" si="174"/>
+        <f t="shared" si="170"/>
         <v>0.9712628526232534</v>
       </c>
       <c r="AE19" s="7">
-        <f t="shared" ref="AE19:AH19" si="175">AE17/AE18</f>
+        <f t="shared" ref="AE19:AH19" si="171">AE17/AE18</f>
         <v>2.4184368363943789</v>
       </c>
       <c r="AF19" s="7">
-        <f t="shared" si="175"/>
+        <f t="shared" si="171"/>
         <v>1.6591009520748805</v>
       </c>
       <c r="AG19" s="7">
-        <f t="shared" si="175"/>
-        <v>1.5268884007552321</v>
+        <f t="shared" si="171"/>
+        <v>1.5724456313871797</v>
       </c>
       <c r="AH19" s="7">
-        <f t="shared" si="175"/>
-        <v>1.6842708745430439</v>
+        <f t="shared" si="171"/>
+        <v>1.6731931191915661</v>
       </c>
       <c r="AI19" s="7"/>
       <c r="AJ19" s="7">
-        <f t="shared" ref="AJ19:AY19" si="176">AJ17/AJ18</f>
+        <f t="shared" ref="AJ19:AY19" si="172">AJ17/AJ18</f>
         <v>1.6427511133102426</v>
       </c>
       <c r="AK19" s="7">
+        <f t="shared" si="172"/>
+        <v>2.3563558820045016</v>
+      </c>
+      <c r="AL19" s="7">
+        <f t="shared" si="172"/>
+        <v>4.0434883182974781</v>
+      </c>
+      <c r="AM19" s="7">
+        <f t="shared" si="172"/>
+        <v>6.9407894736842106</v>
+      </c>
+      <c r="AN19" s="7">
+        <f t="shared" si="172"/>
+        <v>9.2217245240761478</v>
+      </c>
+      <c r="AO19" s="7">
+        <f t="shared" si="172"/>
+        <v>15.407366684991754</v>
+      </c>
+      <c r="AP19" s="7">
+        <f t="shared" si="172"/>
+        <v>28.045007032348806</v>
+      </c>
+      <c r="AQ19" s="7">
+        <f t="shared" si="172"/>
+        <v>6.3775845469688406</v>
+      </c>
+      <c r="AR19" s="7">
+        <f t="shared" si="172"/>
+        <v>5.7179689067975854</v>
+      </c>
+      <c r="AS19" s="7">
+        <f t="shared" si="172"/>
+        <v>6.4923754436703032</v>
+      </c>
+      <c r="AT19" s="7">
+        <f t="shared" si="172"/>
+        <v>3.1219931359887214</v>
+      </c>
+      <c r="AU19" s="7">
+        <f t="shared" si="172"/>
+        <v>2.6713582126065982</v>
+      </c>
+      <c r="AV19" s="7">
+        <f t="shared" si="172"/>
+        <v>2.8271245855000684</v>
+      </c>
+      <c r="AW19" s="7">
+        <f t="shared" si="172"/>
+        <v>3.4808288080785212</v>
+      </c>
+      <c r="AX19" s="7">
+        <f t="shared" si="172"/>
+        <v>3.2308658786042024</v>
+      </c>
+      <c r="AY19" s="7">
+        <f t="shared" si="172"/>
+        <v>3.3568705834035373</v>
+      </c>
+      <c r="AZ19" s="7">
+        <f t="shared" ref="AZ19:BI19" si="173">AZ17/AZ18</f>
+        <v>5.6736738656247754</v>
+      </c>
+      <c r="BA19" s="7">
+        <f t="shared" ref="BA19:BB19" si="174">BA17/BA18</f>
+        <v>6.4169613579373754</v>
+      </c>
+      <c r="BB19" s="7">
+        <f t="shared" si="174"/>
+        <v>6.2364174114318782</v>
+      </c>
+      <c r="BC19" s="7">
+        <f t="shared" ref="BC19" si="175">BC17/BC18</f>
+        <v>6.1782230424466125</v>
+      </c>
+      <c r="BD19" s="7">
+        <f t="shared" si="173"/>
+        <v>7.3461829399647023</v>
+      </c>
+      <c r="BE19" s="7">
+        <f t="shared" si="173"/>
+        <v>7.6089761121170261</v>
+      </c>
+      <c r="BF19" s="7">
+        <f t="shared" si="173"/>
+        <v>7.9725022991521017</v>
+      </c>
+      <c r="BG19" s="7">
+        <f t="shared" si="173"/>
+        <v>8.2627514145860683</v>
+      </c>
+      <c r="BH19" s="7">
+        <f t="shared" si="173"/>
+        <v>8.5135799617830763</v>
+      </c>
+      <c r="BI19" s="7">
+        <f t="shared" si="173"/>
+        <v>8.7167869722280908</v>
+      </c>
+      <c r="BJ19" s="7">
+        <f t="shared" ref="BJ19:BL19" si="176">BJ17/BJ18</f>
+        <v>8.8883123608099286</v>
+      </c>
+      <c r="BK19" s="7">
         <f t="shared" si="176"/>
-        <v>2.3563558820045016</v>
-      </c>
-      <c r="AL19" s="7">
+        <v>9.082121860454194</v>
+      </c>
+      <c r="BL19" s="7">
         <f t="shared" si="176"/>
-        <v>4.0434883182974781</v>
-      </c>
-      <c r="AM19" s="7">
-        <f t="shared" si="176"/>
-        <v>6.9407894736842106</v>
-      </c>
-      <c r="AN19" s="7">
-        <f t="shared" si="176"/>
-        <v>9.2217245240761478</v>
-      </c>
-      <c r="AO19" s="7">
-        <f t="shared" si="176"/>
-        <v>15.407366684991754</v>
-      </c>
-      <c r="AP19" s="7">
-        <f t="shared" si="176"/>
-        <v>28.045007032348806</v>
-      </c>
-      <c r="AQ19" s="7">
-        <f t="shared" si="176"/>
-        <v>6.3775845469688406</v>
-      </c>
-      <c r="AR19" s="7">
-        <f t="shared" si="176"/>
-        <v>5.7179689067975854</v>
-      </c>
-      <c r="AS19" s="7">
-        <f t="shared" si="176"/>
-        <v>6.4923754436703032</v>
-      </c>
-      <c r="AT19" s="7">
-        <f t="shared" si="176"/>
-        <v>3.1219931359887214</v>
-      </c>
-      <c r="AU19" s="7">
-        <f t="shared" si="176"/>
-        <v>2.6713582126065982</v>
-      </c>
-      <c r="AV19" s="7">
-        <f t="shared" si="176"/>
-        <v>2.8271245855000684</v>
-      </c>
-      <c r="AW19" s="7">
-        <f t="shared" si="176"/>
-        <v>3.4808288080785212</v>
-      </c>
-      <c r="AX19" s="7">
-        <f t="shared" si="176"/>
-        <v>3.2308658786042024</v>
-      </c>
-      <c r="AY19" s="7">
-        <f t="shared" si="176"/>
-        <v>3.3568705834035373</v>
-      </c>
-      <c r="AZ19" s="7">
-        <f t="shared" ref="AZ19:BI19" si="177">AZ17/AZ18</f>
-        <v>5.6736738656247754</v>
-      </c>
-      <c r="BA19" s="7">
-        <f t="shared" ref="BA19:BB19" si="178">BA17/BA18</f>
-        <v>6.4169613579373754</v>
-      </c>
-      <c r="BB19" s="7">
-        <f t="shared" si="178"/>
-        <v>6.2364174114318782</v>
-      </c>
-      <c r="BC19" s="7">
-        <f t="shared" ref="BC19" si="179">BC17/BC18</f>
-        <v>6.1782230424466125</v>
-      </c>
-      <c r="BD19" s="7">
+        <v>9.2811768160555701</v>
+      </c>
+      <c r="BM19" s="7">
+        <f t="shared" ref="BM19:BN19" si="177">BM17/BM18</f>
+        <v>9.4857086995592006</v>
+      </c>
+      <c r="BN19" s="7">
         <f t="shared" si="177"/>
-        <v>7.3026709452456515</v>
-      </c>
-      <c r="BE19" s="7">
-        <f t="shared" si="177"/>
-        <v>7.4726097695204299</v>
-      </c>
-      <c r="BF19" s="7">
-        <f t="shared" si="177"/>
-        <v>7.7740674562641212</v>
-      </c>
-      <c r="BG19" s="7">
-        <f t="shared" si="177"/>
-        <v>8.0628978266555205</v>
-      </c>
-      <c r="BH19" s="7">
-        <f t="shared" si="177"/>
-        <v>8.3124022755702409</v>
-      </c>
-      <c r="BI19" s="7">
-        <f t="shared" si="177"/>
-        <v>8.5146953069378757</v>
-      </c>
-      <c r="BJ19" s="7">
-        <f t="shared" ref="BJ19:BL19" si="180">BJ17/BJ18</f>
-        <v>8.6846752103420339</v>
-      </c>
-      <c r="BK19" s="7">
-        <f t="shared" si="180"/>
-        <v>8.8766207471302749</v>
-      </c>
-      <c r="BL19" s="7">
-        <f t="shared" si="180"/>
-        <v>9.0079347745174019</v>
-      </c>
-      <c r="BM19" s="7">
-        <f t="shared" ref="BM19:BN19" si="181">BM17/BM18</f>
-        <v>9.1416844409266567</v>
-      </c>
-      <c r="BN19" s="7">
-        <f t="shared" si="181"/>
-        <v>9.2776438698954262</v>
+        <v>9.6958813371775374</v>
       </c>
     </row>
     <row r="21" spans="2:179" x14ac:dyDescent="0.3">
@@ -5771,128 +5750,128 @@
         <v>0.36113637512000402</v>
       </c>
       <c r="D21" s="10">
-        <f t="shared" ref="D21:M21" si="182">(D3-D6)/D3</f>
+        <f t="shared" ref="D21:M21" si="178">(D3-D6)/D3</f>
         <v>0.33831185290619453</v>
       </c>
       <c r="E21" s="10">
+        <f t="shared" si="178"/>
+        <v>0.32808910546467107</v>
+      </c>
+      <c r="F21" s="10">
+        <f t="shared" si="178"/>
+        <v>0.33659012255979809</v>
+      </c>
+      <c r="G21" s="10">
+        <f t="shared" si="178"/>
+        <v>0.34311976577926057</v>
+      </c>
+      <c r="H21" s="10">
+        <f t="shared" si="178"/>
+        <v>0.3117792333297541</v>
+      </c>
+      <c r="I21" s="10">
+        <f t="shared" si="178"/>
+        <v>0.30412711904424611</v>
+      </c>
+      <c r="J21" s="10">
+        <f t="shared" si="178"/>
+        <v>0.31615206970831961</v>
+      </c>
+      <c r="K21" s="10">
+        <f t="shared" si="178"/>
+        <v>0.3416894215210356</v>
+      </c>
+      <c r="L21" s="10">
+        <f t="shared" si="178"/>
+        <v>0.30343600578227509</v>
+      </c>
+      <c r="M21" s="10">
+        <f t="shared" si="178"/>
+        <v>0.29736293494379851</v>
+      </c>
+      <c r="N21" s="10">
+        <f t="shared" ref="N21:AY21" si="179">(N3-N6)/N3</f>
+        <v>0.2981515085046561</v>
+      </c>
+      <c r="O21" s="10">
+        <f t="shared" ref="O21:S21" si="180">(O3-O6)/O3</f>
+        <v>0.35063441961579467</v>
+      </c>
+      <c r="P21" s="10">
+        <f t="shared" si="180"/>
+        <v>0.3609647372838215</v>
+      </c>
+      <c r="Q21" s="10">
+        <f t="shared" ref="Q21:R21" si="181">(Q3-Q6)/Q3</f>
+        <v>0.36043347720022517</v>
+      </c>
+      <c r="R21" s="10">
+        <f t="shared" si="181"/>
+        <v>0.34253184395310604</v>
+      </c>
+      <c r="S21" s="10">
+        <f t="shared" si="180"/>
+        <v>0.38418446983117716</v>
+      </c>
+      <c r="T21" s="10">
+        <f t="shared" ref="T21:U21" si="182">(T3-T6)/T3</f>
+        <v>0.36364692668190091</v>
+      </c>
+      <c r="U21" s="10">
         <f t="shared" si="182"/>
-        <v>0.32808910546467107</v>
-      </c>
-      <c r="F21" s="10">
-        <f t="shared" si="182"/>
-        <v>0.33659012255979809</v>
-      </c>
-      <c r="G21" s="10">
-        <f t="shared" si="182"/>
-        <v>0.34311976577926057</v>
-      </c>
-      <c r="H21" s="10">
-        <f t="shared" si="182"/>
-        <v>0.3117792333297541</v>
-      </c>
-      <c r="I21" s="10">
-        <f t="shared" si="182"/>
-        <v>0.30412711904424611</v>
-      </c>
-      <c r="J21" s="10">
-        <f t="shared" si="182"/>
-        <v>0.31615206970831961</v>
-      </c>
-      <c r="K21" s="10">
-        <f t="shared" si="182"/>
-        <v>0.3416894215210356</v>
-      </c>
-      <c r="L21" s="10">
-        <f t="shared" si="182"/>
-        <v>0.30343600578227509</v>
-      </c>
-      <c r="M21" s="10">
-        <f t="shared" si="182"/>
-        <v>0.29736293494379851</v>
-      </c>
-      <c r="N21" s="10">
-        <f t="shared" ref="N21:AY21" si="183">(N3-N6)/N3</f>
-        <v>0.2981515085046561</v>
-      </c>
-      <c r="O21" s="10">
-        <f t="shared" ref="O21:S21" si="184">(O3-O6)/O3</f>
-        <v>0.35063441961579467</v>
-      </c>
-      <c r="P21" s="10">
+        <v>0.34519769552521506</v>
+      </c>
+      <c r="V21" s="10">
+        <f t="shared" ref="V21:V22" si="183">(V3-V6)/V3</f>
+        <v>0.34627526142224979</v>
+      </c>
+      <c r="W21" s="10">
+        <f t="shared" ref="W21:X21" si="184">(W3-W6)/W3</f>
+        <v>0.36957920073038136</v>
+      </c>
+      <c r="X21" s="10">
         <f t="shared" si="184"/>
-        <v>0.3609647372838215</v>
-      </c>
-      <c r="Q21" s="10">
-        <f t="shared" ref="Q21:R21" si="185">(Q3-Q6)/Q3</f>
-        <v>0.36043347720022517</v>
-      </c>
-      <c r="R21" s="10">
+        <v>0.36702782399329087</v>
+      </c>
+      <c r="Y21" s="10">
+        <f t="shared" ref="Y21:Z21" si="185">(Y3-Y6)/Y3</f>
+        <v>0.35402086359434837</v>
+      </c>
+      <c r="Z21" s="10">
         <f t="shared" si="185"/>
-        <v>0.34253184395310604</v>
-      </c>
-      <c r="S21" s="10">
-        <f t="shared" si="184"/>
-        <v>0.38418446983117716</v>
-      </c>
-      <c r="T21" s="10">
-        <f t="shared" ref="T21:U21" si="186">(T3-T6)/T3</f>
-        <v>0.36364692668190091</v>
-      </c>
-      <c r="U21" s="10">
+        <v>0.36612884020004766</v>
+      </c>
+      <c r="AA21" s="10">
+        <f t="shared" ref="AA21:AD21" si="186">(AA3-AA6)/AA3</f>
+        <v>0.39414045491301913</v>
+      </c>
+      <c r="AB21" s="10">
         <f t="shared" si="186"/>
-        <v>0.34519769552521506</v>
-      </c>
-      <c r="V21" s="10">
-        <f t="shared" ref="V21:V22" si="187">(V3-V6)/V3</f>
-        <v>0.34627526142224979</v>
-      </c>
-      <c r="W21" s="10">
-        <f t="shared" ref="W21:X21" si="188">(W3-W6)/W3</f>
-        <v>0.36957920073038136</v>
-      </c>
-      <c r="X21" s="10">
-        <f t="shared" si="188"/>
-        <v>0.36702782399329087</v>
-      </c>
-      <c r="Y21" s="10">
-        <f t="shared" ref="Y21:Z21" si="189">(Y3-Y6)/Y3</f>
-        <v>0.35402086359434837</v>
-      </c>
-      <c r="Z21" s="10">
-        <f t="shared" si="189"/>
-        <v>0.36612884020004766</v>
-      </c>
-      <c r="AA21" s="10">
-        <f t="shared" ref="AA21:AD21" si="190">(AA3-AA6)/AA3</f>
-        <v>0.39414045491301913</v>
-      </c>
-      <c r="AB21" s="10">
-        <f t="shared" si="190"/>
         <v>0.36572675896301171</v>
       </c>
       <c r="AC21" s="10">
-        <f t="shared" si="190"/>
+        <f t="shared" si="186"/>
         <v>0.35346956013254499</v>
       </c>
       <c r="AD21" s="10">
-        <f t="shared" si="190"/>
+        <f t="shared" si="186"/>
         <v>0.36296063352297092</v>
       </c>
       <c r="AE21" s="10">
-        <f t="shared" ref="AE21:AH21" si="191">(AE3-AE6)/AE3</f>
+        <f t="shared" ref="AE21:AH21" si="187">(AE3-AE6)/AE3</f>
         <v>0.39315026541445486</v>
       </c>
       <c r="AF21" s="10">
-        <f t="shared" si="191"/>
+        <f t="shared" si="187"/>
         <v>0.35922810489856505</v>
       </c>
       <c r="AG21" s="10">
-        <f t="shared" si="191"/>
-        <v>0.33999999999999997</v>
+        <f t="shared" si="187"/>
+        <v>0.3451728641556453</v>
       </c>
       <c r="AH21" s="10">
-        <f t="shared" si="191"/>
-        <v>0.33999999999999997</v>
+        <f t="shared" si="187"/>
+        <v>0.33999999999999991</v>
       </c>
       <c r="AI21" s="10"/>
       <c r="AJ21" s="10"/>
@@ -5908,75 +5887,75 @@
       <c r="AT21" s="10"/>
       <c r="AU21" s="10"/>
       <c r="AW21" s="10">
-        <f t="shared" si="183"/>
+        <f t="shared" si="179"/>
         <v>0.34396294836770025</v>
       </c>
       <c r="AX21" s="10">
-        <f t="shared" si="183"/>
+        <f t="shared" si="179"/>
         <v>0.32207795851002652</v>
       </c>
       <c r="AY21" s="10">
-        <f t="shared" si="183"/>
+        <f t="shared" si="179"/>
         <v>0.31466339293399231</v>
       </c>
       <c r="AZ21" s="10">
-        <f t="shared" ref="AZ21:BA21" si="192">(AZ3-AZ6)/AZ3</f>
+        <f t="shared" ref="AZ21:BA21" si="188">(AZ3-AZ6)/AZ3</f>
         <v>0.35349303276483562</v>
       </c>
       <c r="BA21" s="10">
-        <f t="shared" si="192"/>
+        <f t="shared" si="188"/>
         <v>0.36283479707399452</v>
       </c>
       <c r="BB21" s="10">
-        <f t="shared" ref="BB21:BC21" si="193">(BB3-BB6)/BB3</f>
+        <f t="shared" ref="BB21:BC21" si="189">(BB3-BB6)/BB3</f>
         <v>0.36500662562691849</v>
       </c>
       <c r="BC21" s="10">
-        <f t="shared" si="193"/>
+        <f t="shared" si="189"/>
         <v>0.37180617636485724</v>
       </c>
       <c r="BD21" s="10">
-        <f t="shared" ref="BD21:BN21" si="194">(BD3-BD6)/BD3</f>
-        <v>0.36169968836515831</v>
+        <f t="shared" ref="BD21:BN21" si="190">(BD3-BD6)/BD3</f>
+        <v>0.36250715865339173</v>
       </c>
       <c r="BE21" s="10">
-        <f t="shared" si="194"/>
+        <f t="shared" si="190"/>
+        <v>0.35000000000000003</v>
+      </c>
+      <c r="BF21" s="10">
+        <f t="shared" si="190"/>
         <v>0.35</v>
       </c>
-      <c r="BF21" s="10">
-        <f t="shared" si="194"/>
+      <c r="BG21" s="10">
+        <f t="shared" si="190"/>
+        <v>0.34999999999999992</v>
+      </c>
+      <c r="BH21" s="10">
+        <f t="shared" si="190"/>
         <v>0.35</v>
       </c>
-      <c r="BG21" s="10">
-        <f t="shared" si="194"/>
+      <c r="BI21" s="10">
+        <f t="shared" si="190"/>
         <v>0.35</v>
       </c>
-      <c r="BH21" s="10">
-        <f t="shared" si="194"/>
+      <c r="BJ21" s="10">
+        <f t="shared" si="190"/>
+        <v>0.35000000000000003</v>
+      </c>
+      <c r="BK21" s="10">
+        <f t="shared" si="190"/>
         <v>0.35</v>
       </c>
-      <c r="BI21" s="10">
-        <f t="shared" si="194"/>
-        <v>0.34999999999999992</v>
-      </c>
-      <c r="BJ21" s="10">
-        <f t="shared" si="194"/>
+      <c r="BL21" s="10">
+        <f t="shared" si="190"/>
         <v>0.35</v>
       </c>
-      <c r="BK21" s="10">
-        <f t="shared" si="194"/>
-        <v>0.35000000000000003</v>
-      </c>
-      <c r="BL21" s="10">
-        <f t="shared" si="194"/>
+      <c r="BM21" s="10">
+        <f t="shared" si="190"/>
         <v>0.35</v>
       </c>
-      <c r="BM21" s="10">
-        <f t="shared" si="194"/>
-        <v>0.35</v>
-      </c>
       <c r="BN21" s="10">
-        <f t="shared" si="194"/>
+        <f t="shared" si="190"/>
         <v>0.35</v>
       </c>
     </row>
@@ -5989,127 +5968,127 @@
         <v>0.58308686603132875</v>
       </c>
       <c r="D22" s="10">
-        <f t="shared" ref="D22:M22" si="195">(D4-D7)/D4</f>
+        <f t="shared" ref="D22:M22" si="191">(D4-D7)/D4</f>
         <v>0.61634517766497465</v>
       </c>
       <c r="E22" s="10">
+        <f t="shared" si="191"/>
+        <v>0.61769911504424779</v>
+      </c>
+      <c r="F22" s="10">
+        <f t="shared" si="191"/>
+        <v>0.61137843192754038</v>
+      </c>
+      <c r="G22" s="10">
+        <f t="shared" si="191"/>
+        <v>0.62841379310344825</v>
+      </c>
+      <c r="H22" s="10">
+        <f t="shared" si="191"/>
+        <v>0.63781659388646283</v>
+      </c>
+      <c r="I22" s="10">
+        <f t="shared" si="191"/>
+        <v>0.64129201222173726</v>
+      </c>
+      <c r="J22" s="10">
+        <f t="shared" si="191"/>
+        <v>0.64119574774198707</v>
+      </c>
+      <c r="K22" s="10">
+        <f t="shared" si="191"/>
+        <v>0.64396382225717652</v>
+      </c>
+      <c r="L22" s="10">
+        <f t="shared" si="191"/>
+        <v>0.65373089601438417</v>
+      </c>
+      <c r="M22" s="10">
+        <f t="shared" si="191"/>
+        <v>0.67224080267558528</v>
+      </c>
+      <c r="N22" s="10">
+        <f t="shared" ref="N22:AY22" si="192">(N4-N7)/N4</f>
+        <v>0.66925561894288266</v>
+      </c>
+      <c r="O22" s="10">
+        <f t="shared" ref="O22:S22" si="193">(O4-O7)/O4</f>
+        <v>0.6839667533785927</v>
+      </c>
+      <c r="P22" s="10">
+        <f t="shared" si="193"/>
+        <v>0.70072776758771671</v>
+      </c>
+      <c r="Q22" s="10">
+        <f t="shared" ref="Q22:R22" si="194">(Q4-Q7)/Q4</f>
+        <v>0.69804414960539862</v>
+      </c>
+      <c r="R22" s="10">
+        <f t="shared" si="194"/>
+        <v>0.704765552333534</v>
+      </c>
+      <c r="S22" s="10">
+        <f t="shared" si="193"/>
+        <v>0.72366263578602175</v>
+      </c>
+      <c r="T22" s="10">
+        <f t="shared" ref="T22:U22" si="195">(T4-T7)/T4</f>
+        <v>0.72609858231168967</v>
+      </c>
+      <c r="U22" s="10">
         <f t="shared" si="195"/>
-        <v>0.61769911504424779</v>
-      </c>
-      <c r="F22" s="10">
-        <f t="shared" si="195"/>
-        <v>0.61137843192754038</v>
-      </c>
-      <c r="G22" s="10">
-        <f t="shared" si="195"/>
-        <v>0.62841379310344825</v>
-      </c>
-      <c r="H22" s="10">
-        <f t="shared" si="195"/>
-        <v>0.63781659388646283</v>
-      </c>
-      <c r="I22" s="10">
-        <f t="shared" si="195"/>
-        <v>0.64129201222173726</v>
-      </c>
-      <c r="J22" s="10">
-        <f t="shared" si="195"/>
-        <v>0.64119574774198707</v>
-      </c>
-      <c r="K22" s="10">
-        <f t="shared" si="195"/>
-        <v>0.64396382225717652</v>
-      </c>
-      <c r="L22" s="10">
-        <f t="shared" si="195"/>
-        <v>0.65373089601438417</v>
-      </c>
-      <c r="M22" s="10">
-        <f t="shared" si="195"/>
-        <v>0.67224080267558528</v>
-      </c>
-      <c r="N22" s="10">
-        <f t="shared" ref="N22:AY22" si="196">(N4-N7)/N4</f>
-        <v>0.66925561894288266</v>
-      </c>
-      <c r="O22" s="10">
-        <f t="shared" ref="O22:S22" si="197">(O4-O7)/O4</f>
-        <v>0.6839667533785927</v>
-      </c>
-      <c r="P22" s="10">
+        <v>0.71490512140379514</v>
+      </c>
+      <c r="V22" s="10">
+        <f t="shared" si="183"/>
+        <v>0.70481550969355844</v>
+      </c>
+      <c r="W22" s="10">
+        <f t="shared" ref="W22:X22" si="196">(W4-W7)/W4</f>
+        <v>0.70832129442357705</v>
+      </c>
+      <c r="X22" s="10">
+        <f t="shared" si="196"/>
+        <v>0.70990577318601422</v>
+      </c>
+      <c r="Y22" s="10">
+        <f t="shared" ref="Y22:Z22" si="197">(Y4-Y7)/Y4</f>
+        <v>0.70546363079243857</v>
+      </c>
+      <c r="Z22" s="10">
         <f t="shared" si="197"/>
-        <v>0.70072776758771671</v>
-      </c>
-      <c r="Q22" s="10">
-        <f t="shared" ref="Q22:R22" si="198">(Q4-Q7)/Q4</f>
-        <v>0.69804414960539862</v>
-      </c>
-      <c r="R22" s="10">
+        <v>0.70937528009321504</v>
+      </c>
+      <c r="AA22" s="10">
+        <f t="shared" ref="AA22:AD22" si="198">(AA4-AA7)/AA4</f>
+        <v>0.728338452221309</v>
+      </c>
+      <c r="AB22" s="10">
         <f t="shared" si="198"/>
-        <v>0.704765552333534</v>
-      </c>
-      <c r="S22" s="10">
-        <f t="shared" si="197"/>
-        <v>0.72366263578602175</v>
-      </c>
-      <c r="T22" s="10">
-        <f t="shared" ref="T22:U22" si="199">(T4-T7)/T4</f>
-        <v>0.72609858231168967</v>
-      </c>
-      <c r="U22" s="10">
+        <v>0.74617672937528801</v>
+      </c>
+      <c r="AC22" s="10">
+        <f t="shared" si="198"/>
+        <v>0.73997439392062114</v>
+      </c>
+      <c r="AD22" s="10">
+        <f t="shared" si="198"/>
+        <v>0.74030914624379307</v>
+      </c>
+      <c r="AE22" s="10">
+        <f t="shared" ref="AE22:AH22" si="199">(AE4-AE7)/AE4</f>
+        <v>0.75026575550493546</v>
+      </c>
+      <c r="AF22" s="10">
         <f t="shared" si="199"/>
-        <v>0.71490512140379514</v>
-      </c>
-      <c r="V22" s="10">
-        <f t="shared" si="187"/>
-        <v>0.70481550969355844</v>
-      </c>
-      <c r="W22" s="10">
-        <f t="shared" ref="W22:X22" si="200">(W4-W7)/W4</f>
-        <v>0.70832129442357705</v>
-      </c>
-      <c r="X22" s="10">
-        <f t="shared" si="200"/>
-        <v>0.70990577318601422</v>
-      </c>
-      <c r="Y22" s="10">
-        <f t="shared" ref="Y22:Z22" si="201">(Y4-Y7)/Y4</f>
-        <v>0.70546363079243857</v>
-      </c>
-      <c r="Z22" s="10">
-        <f t="shared" si="201"/>
-        <v>0.70937528009321504</v>
-      </c>
-      <c r="AA22" s="10">
-        <f t="shared" ref="AA22:AD22" si="202">(AA4-AA7)/AA4</f>
-        <v>0.728338452221309</v>
-      </c>
-      <c r="AB22" s="10">
-        <f t="shared" si="202"/>
-        <v>0.74617672937528801</v>
-      </c>
-      <c r="AC22" s="10">
-        <f t="shared" si="202"/>
-        <v>0.73997439392062114</v>
-      </c>
-      <c r="AD22" s="10">
-        <f t="shared" si="202"/>
-        <v>0.74030914624379307</v>
-      </c>
-      <c r="AE22" s="10">
-        <f t="shared" ref="AE22:AH22" si="203">(AE4-AE7)/AE4</f>
-        <v>0.75026575550493546</v>
-      </c>
-      <c r="AF22" s="10">
-        <f t="shared" si="203"/>
         <v>0.75747795083505343</v>
       </c>
       <c r="AG22" s="10">
-        <f t="shared" si="203"/>
-        <v>0.75</v>
+        <f t="shared" si="199"/>
+        <v>0.75575247055391459</v>
       </c>
       <c r="AH22" s="10">
-        <f t="shared" si="203"/>
+        <f t="shared" si="199"/>
         <v>0.75</v>
       </c>
       <c r="AI22" s="10"/>
@@ -6126,75 +6105,75 @@
       <c r="AT22" s="10"/>
       <c r="AU22" s="10"/>
       <c r="AW22" s="10">
-        <f t="shared" si="196"/>
+        <f t="shared" si="192"/>
         <v>0.60772869075173597</v>
       </c>
       <c r="AX22" s="10">
-        <f t="shared" si="196"/>
+        <f t="shared" si="192"/>
         <v>0.63738091637683347</v>
       </c>
       <c r="AY22" s="10">
-        <f t="shared" si="196"/>
+        <f t="shared" si="192"/>
         <v>0.66015101919357233</v>
       </c>
       <c r="AZ22" s="10">
-        <f t="shared" ref="AZ22:BA22" si="204">(AZ4-AZ7)/AZ4</f>
+        <f t="shared" ref="AZ22:BA22" si="200">(AZ4-AZ7)/AZ4</f>
         <v>0.69725977347460721</v>
       </c>
       <c r="BA22" s="10">
-        <f t="shared" si="204"/>
+        <f t="shared" si="200"/>
         <v>0.71745446633132381</v>
       </c>
       <c r="BB22" s="10">
-        <f t="shared" ref="BB22:BC22" si="205">(BB4-BB7)/BB4</f>
+        <f t="shared" ref="BB22:BC22" si="201">(BB4-BB7)/BB4</f>
         <v>0.70827464788732397</v>
       </c>
       <c r="BC22" s="10">
-        <f t="shared" si="205"/>
+        <f t="shared" si="201"/>
         <v>0.7388035645582256</v>
       </c>
       <c r="BD22" s="10">
-        <f t="shared" ref="BD22:BN22" si="206">(BD4-BD7)/BD4</f>
-        <v>0.75191730694647974</v>
+        <f t="shared" ref="BD22:BN22" si="202">(BD4-BD7)/BD4</f>
+        <v>0.75336641421026329</v>
       </c>
       <c r="BE22" s="10">
-        <f t="shared" si="206"/>
+        <f t="shared" si="202"/>
         <v>0.76</v>
       </c>
       <c r="BF22" s="10">
-        <f t="shared" si="206"/>
+        <f t="shared" si="202"/>
         <v>0.76</v>
       </c>
       <c r="BG22" s="10">
-        <f t="shared" si="206"/>
+        <f t="shared" si="202"/>
         <v>0.76</v>
       </c>
       <c r="BH22" s="10">
-        <f t="shared" si="206"/>
+        <f t="shared" si="202"/>
         <v>0.76</v>
       </c>
       <c r="BI22" s="10">
-        <f t="shared" si="206"/>
+        <f t="shared" si="202"/>
+        <v>0.7599999999999999</v>
+      </c>
+      <c r="BJ22" s="10">
+        <f t="shared" si="202"/>
         <v>0.76</v>
       </c>
-      <c r="BJ22" s="10">
-        <f t="shared" si="206"/>
+      <c r="BK22" s="10">
+        <f t="shared" si="202"/>
         <v>0.76</v>
       </c>
-      <c r="BK22" s="10">
-        <f t="shared" si="206"/>
+      <c r="BL22" s="10">
+        <f t="shared" si="202"/>
         <v>0.76</v>
       </c>
-      <c r="BL22" s="10">
-        <f t="shared" si="206"/>
+      <c r="BM22" s="10">
+        <f t="shared" si="202"/>
         <v>0.76</v>
       </c>
-      <c r="BM22" s="10">
-        <f t="shared" si="206"/>
-        <v>0.76</v>
-      </c>
       <c r="BN22" s="10">
-        <f t="shared" si="206"/>
+        <f t="shared" si="202"/>
         <v>0.76</v>
       </c>
     </row>
@@ -6207,253 +6186,253 @@
         <v>0.38408480853521798</v>
       </c>
       <c r="D23" s="11">
-        <f t="shared" ref="D23:M23" si="207">D9/D5</f>
+        <f t="shared" ref="D23:M23" si="203">D9/D5</f>
         <v>0.38310679294044525</v>
       </c>
       <c r="E23" s="11">
+        <f t="shared" si="203"/>
+        <v>0.38338496198254013</v>
+      </c>
+      <c r="F23" s="11">
+        <f t="shared" si="203"/>
+        <v>0.38289348171701115</v>
+      </c>
+      <c r="G23" s="11">
+        <f t="shared" si="203"/>
+        <v>0.37991934527339583</v>
+      </c>
+      <c r="H23" s="11">
+        <f t="shared" si="203"/>
+        <v>0.37612686374213566</v>
+      </c>
+      <c r="I23" s="11">
+        <f t="shared" si="203"/>
+        <v>0.37590365923916075</v>
+      </c>
+      <c r="J23" s="11">
+        <f t="shared" si="203"/>
+        <v>0.37965334166146159</v>
+      </c>
+      <c r="K23" s="11">
+        <f t="shared" si="203"/>
+        <v>0.38354806739345887</v>
+      </c>
+      <c r="L23" s="11">
+        <f t="shared" si="203"/>
+        <v>0.38361943305952362</v>
+      </c>
+      <c r="M23" s="11">
+        <f t="shared" si="203"/>
+        <v>0.37999497361146017</v>
+      </c>
+      <c r="N23" s="11">
+        <f t="shared" ref="N23:BI23" si="204">N9/N5</f>
+        <v>0.38160375900336951</v>
+      </c>
+      <c r="O23" s="11">
+        <f t="shared" ref="O23:S23" si="205">O9/O5</f>
+        <v>0.39777815665969724</v>
+      </c>
+      <c r="P23" s="11">
+        <f t="shared" si="205"/>
+        <v>0.42506474370423292</v>
+      </c>
+      <c r="Q23" s="11">
+        <f t="shared" ref="Q23:R23" si="206">Q9/Q5</f>
+        <v>0.43292727853230839</v>
+      </c>
+      <c r="R23" s="11">
+        <f t="shared" si="206"/>
+        <v>0.42195297504798462</v>
+      </c>
+      <c r="S23" s="11">
+        <f t="shared" si="205"/>
+        <v>0.43763766186615033</v>
+      </c>
+      <c r="T23" s="11">
+        <f t="shared" ref="T23:U23" si="207">T9/T5</f>
+        <v>0.43749871502292398</v>
+      </c>
+      <c r="U23" s="11">
         <f t="shared" si="207"/>
-        <v>0.38338496198254013</v>
-      </c>
-      <c r="F23" s="11">
-        <f t="shared" si="207"/>
-        <v>0.38289348171701115</v>
-      </c>
-      <c r="G23" s="11">
-        <f t="shared" si="207"/>
-        <v>0.37991934527339583</v>
-      </c>
-      <c r="H23" s="11">
-        <f t="shared" si="207"/>
-        <v>0.37612686374213566</v>
-      </c>
-      <c r="I23" s="11">
-        <f t="shared" si="207"/>
-        <v>0.37590365923916075</v>
-      </c>
-      <c r="J23" s="11">
-        <f t="shared" si="207"/>
-        <v>0.37965334166146159</v>
-      </c>
-      <c r="K23" s="11">
-        <f t="shared" si="207"/>
-        <v>0.38354806739345887</v>
-      </c>
-      <c r="L23" s="11">
-        <f t="shared" si="207"/>
-        <v>0.38361943305952362</v>
-      </c>
-      <c r="M23" s="11">
-        <f t="shared" si="207"/>
-        <v>0.37999497361146017</v>
-      </c>
-      <c r="N23" s="11">
-        <f t="shared" ref="N23:BI23" si="208">N9/N5</f>
-        <v>0.38160375900336951</v>
-      </c>
-      <c r="O23" s="11">
-        <f t="shared" ref="O23:S23" si="209">O9/O5</f>
-        <v>0.39777815665969724</v>
-      </c>
-      <c r="P23" s="11">
+        <v>0.43256307332537758</v>
+      </c>
+      <c r="V23" s="11">
+        <f t="shared" ref="V23" si="208">V9/V5</f>
+        <v>0.4225922392563175</v>
+      </c>
+      <c r="W23" s="11">
+        <f t="shared" ref="W23:X23" si="209">W9/W5</f>
+        <v>0.42962254809908323</v>
+      </c>
+      <c r="X23" s="11">
         <f t="shared" si="209"/>
-        <v>0.42506474370423292</v>
-      </c>
-      <c r="Q23" s="11">
-        <f t="shared" ref="Q23:R23" si="210">Q9/Q5</f>
-        <v>0.43292727853230839</v>
-      </c>
-      <c r="R23" s="11">
+        <v>0.44261672782487665</v>
+      </c>
+      <c r="Y23" s="11">
+        <f t="shared" ref="Y23:Z23" si="210">Y9/Y5</f>
+        <v>0.44516302553883397</v>
+      </c>
+      <c r="Z23" s="11">
         <f t="shared" si="210"/>
-        <v>0.42195297504798462</v>
-      </c>
-      <c r="S23" s="11">
-        <f t="shared" si="209"/>
-        <v>0.43763766186615033</v>
-      </c>
-      <c r="T23" s="11">
-        <f t="shared" ref="T23:U23" si="211">T9/T5</f>
-        <v>0.43749871502292398</v>
-      </c>
-      <c r="U23" s="11">
+        <v>0.45170841806520817</v>
+      </c>
+      <c r="AA23" s="11">
+        <f t="shared" ref="AA23:AD23" si="211">AA9/AA5</f>
+        <v>0.45874973865774621</v>
+      </c>
+      <c r="AB23" s="11">
         <f t="shared" si="211"/>
-        <v>0.43256307332537758</v>
-      </c>
-      <c r="V23" s="11">
-        <f t="shared" ref="V23" si="212">V9/V5</f>
-        <v>0.4225922392563175</v>
-      </c>
-      <c r="W23" s="11">
-        <f t="shared" ref="W23:X23" si="213">W9/W5</f>
-        <v>0.42962254809908323</v>
-      </c>
-      <c r="X23" s="11">
-        <f t="shared" si="213"/>
-        <v>0.44261672782487665</v>
-      </c>
-      <c r="Y23" s="11">
-        <f t="shared" ref="Y23:Z23" si="214">Y9/Y5</f>
-        <v>0.44516302553883397</v>
-      </c>
-      <c r="Z23" s="11">
-        <f t="shared" si="214"/>
-        <v>0.45170841806520817</v>
-      </c>
-      <c r="AA23" s="11">
-        <f t="shared" ref="AA23:AD23" si="215">AA9/AA5</f>
-        <v>0.45874973865774621</v>
-      </c>
-      <c r="AB23" s="11">
-        <f t="shared" si="215"/>
         <v>0.46578074554009236</v>
       </c>
       <c r="AC23" s="11">
-        <f t="shared" si="215"/>
+        <f t="shared" si="211"/>
         <v>0.46257155181458898</v>
       </c>
       <c r="AD23" s="11">
-        <f t="shared" si="215"/>
+        <f t="shared" si="211"/>
         <v>0.4622247972190035</v>
       </c>
       <c r="AE23" s="11">
-        <f t="shared" ref="AE23:AH23" si="216">AE9/AE5</f>
+        <f t="shared" ref="AE23:AH23" si="212">AE9/AE5</f>
         <v>0.46882542236524538</v>
       </c>
       <c r="AF23" s="11">
-        <f t="shared" si="216"/>
+        <f t="shared" si="212"/>
         <v>0.47050619238876246</v>
       </c>
       <c r="AG23" s="11">
-        <f t="shared" si="216"/>
-        <v>0.46365848906019363</v>
+        <f t="shared" si="212"/>
+        <v>0.46490705687183631</v>
       </c>
       <c r="AH23" s="11">
-        <f t="shared" si="216"/>
-        <v>0.45396121439664472</v>
+        <f t="shared" si="212"/>
+        <v>0.45390310221951918</v>
       </c>
       <c r="AI23" s="11"/>
       <c r="AJ23" s="11">
-        <f t="shared" ref="AJ23:AP23" si="217">AJ9/AJ5</f>
+        <f t="shared" ref="AJ23:AP23" si="213">AJ9/AJ5</f>
         <v>0.29014428253535279</v>
       </c>
       <c r="AK23" s="11">
+        <f t="shared" si="213"/>
+        <v>0.28982655966865128</v>
+      </c>
+      <c r="AL23" s="11">
+        <f t="shared" si="213"/>
+        <v>0.33966508372906773</v>
+      </c>
+      <c r="AM23" s="11">
+        <f t="shared" si="213"/>
+        <v>0.35200448107545812</v>
+      </c>
+      <c r="AN23" s="11">
+        <f t="shared" si="213"/>
+        <v>0.40139843841044165</v>
+      </c>
+      <c r="AO23" s="11">
+        <f t="shared" si="213"/>
+        <v>0.39377539287083174</v>
+      </c>
+      <c r="AP23" s="11">
+        <f t="shared" si="213"/>
+        <v>0.40478895878945764</v>
+      </c>
+      <c r="AQ23" s="11">
+        <f t="shared" si="204"/>
+        <v>0.43871239808827661</v>
+      </c>
+      <c r="AR23" s="11">
+        <f t="shared" si="204"/>
+        <v>0.37624480720847231</v>
+      </c>
+      <c r="AS23" s="11">
+        <f t="shared" si="204"/>
+        <v>0.38588035777783858</v>
+      </c>
+      <c r="AT23" s="11">
+        <f t="shared" si="204"/>
+        <v>0.40059902017414373</v>
+      </c>
+      <c r="AU23" s="11">
+        <f t="shared" si="204"/>
+        <v>0.39075955648097049</v>
+      </c>
+      <c r="AV23" s="11">
+        <f t="shared" si="204"/>
+        <v>0.38469860491899105</v>
+      </c>
+      <c r="AW23" s="11">
+        <f t="shared" si="204"/>
+        <v>0.38343718820007905</v>
+      </c>
+      <c r="AX23" s="11">
+        <f t="shared" si="204"/>
+        <v>0.37817768109034722</v>
+      </c>
+      <c r="AY23" s="11">
+        <f t="shared" si="204"/>
+        <v>0.38233247727810865</v>
+      </c>
+      <c r="AZ23" s="11">
+        <f t="shared" si="204"/>
+        <v>0.41779359625167778</v>
+      </c>
+      <c r="BA23" s="11">
+        <f t="shared" ref="BA23:BB23" si="214">BA9/BA5</f>
+        <v>0.43309630561360085</v>
+      </c>
+      <c r="BB23" s="11">
+        <f t="shared" si="214"/>
+        <v>0.44131129577207562</v>
+      </c>
+      <c r="BC23" s="11">
+        <f t="shared" ref="BC23" si="215">BC9/BC5</f>
+        <v>0.46206349815233932</v>
+      </c>
+      <c r="BD23" s="11">
+        <f t="shared" si="204"/>
+        <v>0.46472095891882625</v>
+      </c>
+      <c r="BE23" s="11">
+        <f t="shared" si="204"/>
+        <v>0.46176254250326282</v>
+      </c>
+      <c r="BF23" s="11">
+        <f t="shared" si="204"/>
+        <v>0.46569514164728032</v>
+      </c>
+      <c r="BG23" s="11">
+        <f t="shared" si="204"/>
+        <v>0.46974978303402654</v>
+      </c>
+      <c r="BH23" s="11">
+        <f t="shared" si="204"/>
+        <v>0.47306878336608166</v>
+      </c>
+      <c r="BI23" s="11">
+        <f t="shared" si="204"/>
+        <v>0.47560441858937758</v>
+      </c>
+      <c r="BJ23" s="11">
+        <f t="shared" ref="BJ23:BL23" si="216">BJ9/BJ5</f>
+        <v>0.47731926761318183</v>
+      </c>
+      <c r="BK23" s="11">
+        <f t="shared" si="216"/>
+        <v>0.47904690548938317</v>
+      </c>
+      <c r="BL23" s="11">
+        <f t="shared" si="216"/>
+        <v>0.48078714000064887</v>
+      </c>
+      <c r="BM23" s="11">
+        <f t="shared" ref="BM23:BN23" si="217">BM9/BM5</f>
+        <v>0.48253977123868891</v>
+      </c>
+      <c r="BN23" s="11">
         <f t="shared" si="217"/>
-        <v>0.28982655966865128</v>
-      </c>
-      <c r="AL23" s="11">
-        <f t="shared" si="217"/>
-        <v>0.33966508372906773</v>
-      </c>
-      <c r="AM23" s="11">
-        <f t="shared" si="217"/>
-        <v>0.35200448107545812</v>
-      </c>
-      <c r="AN23" s="11">
-        <f t="shared" si="217"/>
-        <v>0.40139843841044165</v>
-      </c>
-      <c r="AO23" s="11">
-        <f t="shared" si="217"/>
-        <v>0.39377539287083174</v>
-      </c>
-      <c r="AP23" s="11">
-        <f t="shared" si="217"/>
-        <v>0.40478895878945764</v>
-      </c>
-      <c r="AQ23" s="11">
-        <f t="shared" si="208"/>
-        <v>0.43871239808827661</v>
-      </c>
-      <c r="AR23" s="11">
-        <f t="shared" si="208"/>
-        <v>0.37624480720847231</v>
-      </c>
-      <c r="AS23" s="11">
-        <f t="shared" si="208"/>
-        <v>0.38588035777783858</v>
-      </c>
-      <c r="AT23" s="11">
-        <f t="shared" si="208"/>
-        <v>0.40059902017414373</v>
-      </c>
-      <c r="AU23" s="11">
-        <f t="shared" si="208"/>
-        <v>0.39075955648097049</v>
-      </c>
-      <c r="AV23" s="11">
-        <f t="shared" si="208"/>
-        <v>0.38469860491899105</v>
-      </c>
-      <c r="AW23" s="11">
-        <f t="shared" si="208"/>
-        <v>0.38343718820007905</v>
-      </c>
-      <c r="AX23" s="11">
-        <f t="shared" si="208"/>
-        <v>0.37817768109034722</v>
-      </c>
-      <c r="AY23" s="11">
-        <f t="shared" si="208"/>
-        <v>0.38233247727810865</v>
-      </c>
-      <c r="AZ23" s="11">
-        <f t="shared" si="208"/>
-        <v>0.41779359625167778</v>
-      </c>
-      <c r="BA23" s="11">
-        <f t="shared" ref="BA23:BB23" si="218">BA9/BA5</f>
-        <v>0.43309630561360085</v>
-      </c>
-      <c r="BB23" s="11">
-        <f t="shared" si="218"/>
-        <v>0.44131129577207562</v>
-      </c>
-      <c r="BC23" s="11">
-        <f t="shared" ref="BC23" si="219">BC9/BC5</f>
-        <v>0.46206349815233932</v>
-      </c>
-      <c r="BD23" s="11">
-        <f t="shared" si="208"/>
-        <v>0.46448340153457696</v>
-      </c>
-      <c r="BE23" s="11">
-        <f t="shared" si="208"/>
-        <v>0.46416651820082833</v>
-      </c>
-      <c r="BF23" s="11">
-        <f t="shared" si="208"/>
-        <v>0.46898052641543164</v>
-      </c>
-      <c r="BG23" s="11">
-        <f t="shared" si="208"/>
-        <v>0.47310214651148597</v>
-      </c>
-      <c r="BH23" s="11">
-        <f t="shared" si="208"/>
-        <v>0.47647357481699237</v>
-      </c>
-      <c r="BI23" s="11">
-        <f t="shared" si="208"/>
-        <v>0.47904781010858111</v>
-      </c>
-      <c r="BJ23" s="11">
-        <f t="shared" ref="BJ23:BL23" si="220">BJ9/BJ5</f>
-        <v>0.48078805114004824</v>
-      </c>
-      <c r="BK23" s="11">
-        <f t="shared" si="220"/>
-        <v>0.48254068879199491</v>
-      </c>
-      <c r="BL23" s="11">
-        <f t="shared" si="220"/>
-        <v>0.48342591746625324</v>
-      </c>
-      <c r="BM23" s="11">
-        <f t="shared" ref="BM23:BN23" si="221">BM9/BM5</f>
-        <v>0.48431419641519602</v>
-      </c>
-      <c r="BN23" s="11">
-        <f t="shared" si="221"/>
-        <v>0.48520549809841812</v>
+        <v>0.48430459163742978</v>
       </c>
     </row>
     <row r="24" spans="2:179" x14ac:dyDescent="0.3">
@@ -6469,165 +6448,165 @@
         <v>0.14528911065453487</v>
       </c>
       <c r="H24" s="10">
-        <f t="shared" ref="H24:N24" si="222">H10/D10-1</f>
+        <f t="shared" ref="H24:N24" si="218">H10/D10-1</f>
         <v>0.1687388987566607</v>
       </c>
       <c r="I24" s="10">
+        <f t="shared" si="218"/>
+        <v>0.15022966765738999</v>
+      </c>
+      <c r="J24" s="10">
+        <f t="shared" si="218"/>
+        <v>9.6000000000000085E-2</v>
+      </c>
+      <c r="K24" s="10">
+        <f t="shared" si="218"/>
+        <v>0.1406970784213224</v>
+      </c>
+      <c r="L24" s="10">
+        <f t="shared" si="218"/>
+        <v>0.15628166160081047</v>
+      </c>
+      <c r="M24" s="10">
+        <f t="shared" si="218"/>
+        <v>0.11768851303735017</v>
+      </c>
+      <c r="N24" s="10">
+        <f t="shared" si="218"/>
+        <v>0.21119221411192224</v>
+      </c>
+      <c r="O24" s="10">
+        <f t="shared" ref="O24" si="219">O10/K10-1</f>
+        <v>0.15996405302179295</v>
+      </c>
+      <c r="P24" s="10">
+        <f t="shared" ref="P24" si="220">P10/L10-1</f>
+        <v>0.15268346111719611</v>
+      </c>
+      <c r="Q24" s="10">
+        <f t="shared" ref="Q24:S24" si="221">Q10/M10-1</f>
+        <v>0.20155527532576722</v>
+      </c>
+      <c r="R24" s="10">
+        <f t="shared" si="221"/>
+        <v>0.15950180795500191</v>
+      </c>
+      <c r="S24" s="10">
+        <f t="shared" si="221"/>
+        <v>0.22138291690877399</v>
+      </c>
+      <c r="T24" s="10">
+        <f t="shared" ref="T24:U24" si="222">T10/P10-1</f>
+        <v>0.2137970353477765</v>
+      </c>
+      <c r="U24" s="10">
         <f t="shared" si="222"/>
-        <v>0.15022966765738999</v>
-      </c>
-      <c r="J24" s="10">
-        <f t="shared" si="222"/>
-        <v>9.6000000000000085E-2</v>
-      </c>
-      <c r="K24" s="10">
-        <f t="shared" si="222"/>
-        <v>0.1406970784213224</v>
-      </c>
-      <c r="L24" s="10">
-        <f t="shared" si="222"/>
-        <v>0.15628166160081047</v>
-      </c>
-      <c r="M24" s="10">
-        <f t="shared" si="222"/>
-        <v>0.11768851303735017</v>
-      </c>
-      <c r="N24" s="10">
-        <f t="shared" si="222"/>
-        <v>0.21119221411192224</v>
-      </c>
-      <c r="O24" s="10">
-        <f t="shared" ref="O24" si="223">O10/K10-1</f>
-        <v>0.15996405302179295</v>
-      </c>
-      <c r="P24" s="10">
-        <f t="shared" ref="P24" si="224">P10/L10-1</f>
-        <v>0.15268346111719611</v>
-      </c>
-      <c r="Q24" s="10">
-        <f t="shared" ref="Q24:S24" si="225">Q10/M10-1</f>
-        <v>0.20155527532576722</v>
-      </c>
-      <c r="R24" s="10">
+        <v>0.1889102676228791</v>
+      </c>
+      <c r="V24" s="10">
+        <f t="shared" ref="V24" si="223">V10/R10-1</f>
+        <v>0.17134442134442129</v>
+      </c>
+      <c r="W24" s="10">
+        <f t="shared" ref="W24:X24" si="224">W10/S10-1</f>
+        <v>0.22248652077386621</v>
+      </c>
+      <c r="X24" s="10">
+        <f t="shared" si="224"/>
+        <v>0.1675277908251136</v>
+      </c>
+      <c r="Y24" s="10">
+        <f t="shared" ref="Y24:AA24" si="225">Y10/U10-1</f>
+        <v>9.4894806532293652E-2</v>
+      </c>
+      <c r="Z24" s="10">
         <f t="shared" si="225"/>
-        <v>0.15950180795500191</v>
-      </c>
-      <c r="S24" s="10">
+        <v>8.0757284425380771E-2</v>
+      </c>
+      <c r="AA24" s="10">
         <f t="shared" si="225"/>
-        <v>0.22138291690877399</v>
-      </c>
-      <c r="T24" s="10">
-        <f t="shared" ref="T24:U24" si="226">T10/P10-1</f>
-        <v>0.2137970353477765</v>
-      </c>
-      <c r="U24" s="10">
-        <f t="shared" si="226"/>
-        <v>0.1889102676228791</v>
-      </c>
-      <c r="V24" s="10">
-        <f t="shared" ref="V24" si="227">V10/R10-1</f>
-        <v>0.17134442134442129</v>
-      </c>
-      <c r="W24" s="10">
-        <f t="shared" ref="W24:X24" si="228">W10/S10-1</f>
-        <v>0.22248652077386621</v>
-      </c>
-      <c r="X24" s="10">
-        <f t="shared" si="228"/>
-        <v>0.1675277908251136</v>
-      </c>
-      <c r="Y24" s="10">
-        <f t="shared" ref="Y24:AA24" si="229">Y10/U10-1</f>
-        <v>9.4894806532293652E-2</v>
-      </c>
-      <c r="Z24" s="10">
-        <f t="shared" si="229"/>
-        <v>8.0757284425380771E-2</v>
-      </c>
-      <c r="AA24" s="10">
-        <f t="shared" si="229"/>
         <v>-1.6863406408094139E-3</v>
       </c>
       <c r="AB24" s="10">
-        <f t="shared" ref="AB24" si="230">AB10/X10-1</f>
+        <f t="shared" ref="AB24" si="226">AB10/X10-1</f>
         <v>5.980957489607075E-2</v>
       </c>
       <c r="AC24" s="10">
-        <f t="shared" ref="AC24" si="231">AC10/Y10-1</f>
+        <f t="shared" ref="AC24" si="227">AC10/Y10-1</f>
         <v>7.5786079011018526E-2</v>
       </c>
       <c r="AD24" s="10">
-        <f t="shared" ref="AD24" si="232">AD10/Z10-1</f>
+        <f t="shared" ref="AD24" si="228">AD10/Z10-1</f>
         <v>6.2679622280005454E-2</v>
       </c>
       <c r="AE24" s="10">
-        <f t="shared" ref="AE24" si="233">AE10/AA10-1</f>
+        <f t="shared" ref="AE24" si="229">AE10/AA10-1</f>
         <v>7.4324324324324342E-2</v>
       </c>
       <c r="AF24" s="10">
-        <f t="shared" ref="AF24" si="234">AF10/AB10-1</f>
+        <f t="shared" ref="AF24" si="230">AF10/AB10-1</f>
         <v>8.1867645198026029E-2</v>
       </c>
       <c r="AG24" s="10">
-        <f t="shared" ref="AG24" si="235">AG10/AC10-1</f>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" ref="AG24" si="231">AG10/AC10-1</f>
+        <v>0.10741943542343235</v>
       </c>
       <c r="AH24" s="10">
-        <f t="shared" ref="AH24" si="236">AH10/AD10-1</f>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" ref="AH24" si="232">AH10/AD10-1</f>
+        <v>0.1100000000000001</v>
       </c>
       <c r="AI24" s="10"/>
       <c r="AJ24" s="10"/>
       <c r="AK24" s="10">
-        <f t="shared" ref="AK24:AP24" si="237">AK10/AJ10-1</f>
+        <f t="shared" ref="AK24:AP24" si="233">AK10/AJ10-1</f>
         <v>0.33084112149532707</v>
       </c>
       <c r="AL24" s="10">
-        <f t="shared" si="237"/>
+        <f t="shared" si="233"/>
         <v>9.8314606741572996E-2</v>
       </c>
       <c r="AM24" s="10">
-        <f t="shared" si="237"/>
+        <f t="shared" si="233"/>
         <v>0.41815856777493599</v>
       </c>
       <c r="AN24" s="10">
-        <f t="shared" si="237"/>
+        <f t="shared" si="233"/>
         <v>0.20198376916140659</v>
       </c>
       <c r="AO24" s="10">
-        <f t="shared" si="237"/>
+        <f t="shared" si="233"/>
         <v>0.33683420855213808</v>
       </c>
       <c r="AP24" s="10">
-        <f t="shared" si="237"/>
+        <f t="shared" si="233"/>
         <v>0.3630751964085297</v>
       </c>
       <c r="AQ24" s="10">
-        <f t="shared" ref="AQ24:AW24" si="238">AQ10/AP10-1</f>
+        <f t="shared" ref="AQ24:AW24" si="234">AQ10/AP10-1</f>
         <v>0.39193083573487031</v>
       </c>
       <c r="AR24" s="10">
-        <f t="shared" si="238"/>
+        <f t="shared" si="234"/>
         <v>0.32357290742383915</v>
       </c>
       <c r="AS24" s="10">
-        <f t="shared" si="238"/>
+        <f t="shared" si="234"/>
         <v>0.34994413407821234</v>
       </c>
       <c r="AT24" s="10">
-        <f t="shared" si="238"/>
+        <f t="shared" si="234"/>
         <v>0.33537493792418482</v>
       </c>
       <c r="AU24" s="10">
-        <f t="shared" si="238"/>
+        <f t="shared" si="234"/>
         <v>0.24519647948431889</v>
       </c>
       <c r="AV24" s="10">
-        <f t="shared" si="238"/>
+        <f t="shared" si="234"/>
         <v>0.15291189646590353</v>
       </c>
       <c r="AW24" s="10">
-        <f t="shared" si="238"/>
+        <f t="shared" si="234"/>
         <v>0.22925481391935065</v>
       </c>
       <c r="AX24" s="10">
@@ -6635,67 +6614,67 @@
         <v>0.13915425681371163</v>
       </c>
       <c r="AY24" s="10">
-        <f t="shared" ref="AY24:BL24" si="239">AY10/AX10-1</f>
+        <f t="shared" ref="AY24:BL24" si="235">AY10/AX10-1</f>
         <v>0.15631744465684161</v>
       </c>
       <c r="AZ24" s="10">
-        <f t="shared" si="239"/>
+        <f t="shared" si="235"/>
         <v>0.16862201365187723</v>
       </c>
       <c r="BA24" s="10">
-        <f t="shared" si="239"/>
+        <f t="shared" si="235"/>
         <v>0.19791001186456136</v>
       </c>
       <c r="BB24" s="10">
-        <f t="shared" si="239"/>
+        <f t="shared" si="235"/>
         <v>0.1395756352138966</v>
       </c>
       <c r="BC24" s="10">
-        <f t="shared" si="239"/>
+        <f t="shared" si="235"/>
         <v>4.8637807120173848E-2</v>
       </c>
       <c r="BD24" s="10">
-        <f t="shared" si="239"/>
-        <v>5.394102645839971E-2</v>
+        <f t="shared" si="235"/>
+        <v>9.3501753267453136E-2</v>
       </c>
       <c r="BE24" s="10">
-        <f t="shared" si="239"/>
+        <f t="shared" si="235"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="BF24" s="10">
+        <f t="shared" si="235"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="BF24" s="10">
-        <f t="shared" si="239"/>
-        <v>4.0000000000000036E-2</v>
-      </c>
       <c r="BG24" s="10">
-        <f t="shared" si="239"/>
+        <f t="shared" si="235"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BH24" s="10">
-        <f t="shared" si="239"/>
+        <f t="shared" si="235"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BI24" s="10">
-        <f t="shared" si="239"/>
+        <f t="shared" si="235"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BJ24" s="10">
-        <f t="shared" si="239"/>
+        <f t="shared" si="235"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BK24" s="10">
-        <f t="shared" si="239"/>
+        <f t="shared" si="235"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BL24" s="10">
-        <f t="shared" si="239"/>
+        <f t="shared" si="235"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BM24" s="10">
-        <f t="shared" ref="BM24" si="240">BM10/BL10-1</f>
+        <f t="shared" ref="BM24" si="236">BM10/BL10-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BN24" s="10">
-        <f t="shared" ref="BN24" si="241">BN10/BM10-1</f>
+        <f t="shared" ref="BN24" si="237">BN10/BM10-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -6708,253 +6687,253 @@
         <v>4.7919993657481341E-2</v>
       </c>
       <c r="D25" s="10">
-        <f t="shared" ref="D25:N25" si="242">D11/D5</f>
+        <f t="shared" ref="D25:N25" si="238">D11/D5</f>
         <v>6.788033433109246E-2</v>
       </c>
       <c r="E25" s="10">
-        <f t="shared" si="242"/>
+        <f t="shared" si="238"/>
         <v>7.7123814887825021E-2</v>
       </c>
       <c r="F25" s="10">
-        <f t="shared" si="242"/>
+        <f t="shared" si="238"/>
         <v>6.7027027027027022E-2</v>
       </c>
       <c r="G25" s="10">
-        <f t="shared" si="242"/>
+        <f t="shared" si="238"/>
         <v>5.6731111374688649E-2</v>
       </c>
       <c r="H25" s="10">
-        <f t="shared" si="242"/>
+        <f t="shared" si="238"/>
         <v>7.6842195983797296E-2</v>
       </c>
       <c r="I25" s="10">
-        <f t="shared" si="242"/>
+        <f t="shared" si="238"/>
         <v>8.2253898046795143E-2</v>
       </c>
       <c r="J25" s="10">
-        <f t="shared" si="242"/>
+        <f t="shared" si="238"/>
         <v>7.1486570893191756E-2</v>
       </c>
       <c r="K25" s="10">
-        <f t="shared" si="242"/>
+        <f t="shared" si="238"/>
         <v>5.6600485738245894E-2</v>
       </c>
       <c r="L25" s="10">
-        <f t="shared" si="242"/>
+        <f t="shared" si="238"/>
         <v>8.4921029616037591E-2</v>
       </c>
       <c r="M25" s="10">
-        <f t="shared" si="242"/>
+        <f t="shared" si="238"/>
         <v>8.0941610119795587E-2</v>
       </c>
       <c r="N25" s="10">
-        <f t="shared" si="242"/>
+        <f t="shared" si="238"/>
         <v>7.6292930229682532E-2</v>
       </c>
       <c r="O25" s="10">
-        <f t="shared" ref="O25:S25" si="243">O11/O5</f>
+        <f t="shared" ref="O25:S25" si="239">O11/O5</f>
         <v>5.0529886305512431E-2</v>
       </c>
       <c r="P25" s="10">
+        <f t="shared" si="239"/>
+        <v>5.9318628326486871E-2</v>
+      </c>
+      <c r="Q25" s="10">
+        <f t="shared" ref="Q25:R25" si="240">Q11/Q5</f>
+        <v>6.645872731291598E-2</v>
+      </c>
+      <c r="R25" s="10">
+        <f t="shared" si="240"/>
+        <v>6.7370441458733207E-2</v>
+      </c>
+      <c r="S25" s="10">
+        <f t="shared" si="239"/>
+        <v>5.2031142845617009E-2</v>
+      </c>
+      <c r="T25" s="10">
+        <f t="shared" ref="T25:U25" si="241">T11/T5</f>
+        <v>6.3662904253788108E-2</v>
+      </c>
+      <c r="U25" s="10">
+        <f t="shared" si="241"/>
+        <v>7.2469533142877809E-2</v>
+      </c>
+      <c r="V25" s="10">
+        <f t="shared" ref="V25" si="242">V11/V5</f>
+        <v>7.1439664544183878E-2</v>
+      </c>
+      <c r="W25" s="10">
+        <f t="shared" ref="W25:X25" si="243">W11/W5</f>
+        <v>5.6395855028424126E-2</v>
+      </c>
+      <c r="X25" s="10">
         <f t="shared" si="243"/>
-        <v>5.9318628326486871E-2</v>
-      </c>
-      <c r="Q25" s="10">
-        <f t="shared" ref="Q25:R25" si="244">Q11/Q5</f>
-        <v>6.645872731291598E-2</v>
-      </c>
-      <c r="R25" s="10">
+        <v>6.5386562065038595E-2</v>
+      </c>
+      <c r="Y25" s="10">
+        <f t="shared" ref="Y25:Z25" si="244">Y11/Y5</f>
+        <v>7.3022237979387991E-2</v>
+      </c>
+      <c r="Z25" s="10">
         <f t="shared" si="244"/>
-        <v>6.7370441458733207E-2</v>
-      </c>
-      <c r="S25" s="10">
-        <f t="shared" si="243"/>
-        <v>5.2031142845617009E-2</v>
-      </c>
-      <c r="T25" s="10">
-        <f t="shared" ref="T25:U25" si="245">T11/T5</f>
-        <v>6.3662904253788108E-2</v>
-      </c>
-      <c r="U25" s="10">
+        <v>6.8727792799839107E-2</v>
+      </c>
+      <c r="AA25" s="10">
+        <f t="shared" ref="AA25:AD25" si="245">AA11/AA5</f>
+        <v>5.6750993100564501E-2</v>
+      </c>
+      <c r="AB25" s="10">
         <f t="shared" si="245"/>
-        <v>7.2469533142877809E-2</v>
-      </c>
-      <c r="V25" s="10">
-        <f t="shared" ref="V25" si="246">V11/V5</f>
-        <v>7.1439664544183878E-2</v>
-      </c>
-      <c r="W25" s="10">
-        <f t="shared" ref="W25:X25" si="247">W11/W5</f>
-        <v>5.6395855028424126E-2</v>
-      </c>
-      <c r="X25" s="10">
-        <f t="shared" si="247"/>
-        <v>6.5386562065038595E-2</v>
-      </c>
-      <c r="Y25" s="10">
-        <f t="shared" ref="Y25:Z25" si="248">Y11/Y5</f>
-        <v>7.3022237979387991E-2</v>
-      </c>
-      <c r="Z25" s="10">
-        <f t="shared" si="248"/>
-        <v>6.8727792799839107E-2</v>
-      </c>
-      <c r="AA25" s="10">
-        <f t="shared" ref="AA25:AD25" si="249">AA11/AA5</f>
-        <v>5.6750993100564501E-2</v>
-      </c>
-      <c r="AB25" s="10">
-        <f t="shared" si="249"/>
         <v>7.1270371227397447E-2</v>
       </c>
       <c r="AC25" s="10">
-        <f t="shared" si="249"/>
+        <f t="shared" si="245"/>
         <v>7.3679424554367726E-2</v>
       </c>
       <c r="AD25" s="10">
-        <f t="shared" si="249"/>
+        <f t="shared" si="245"/>
         <v>6.8713789107763615E-2</v>
       </c>
       <c r="AE25" s="10">
-        <f t="shared" ref="AE25:AH25" si="250">AE11/AE5</f>
+        <f t="shared" ref="AE25:AH25" si="246">AE11/AE5</f>
         <v>5.7723250201126307E-2</v>
       </c>
       <c r="AF25" s="10">
-        <f t="shared" si="250"/>
+        <f t="shared" si="246"/>
         <v>7.0554431149655511E-2</v>
       </c>
       <c r="AG25" s="10">
-        <f t="shared" si="250"/>
-        <v>7.0000000000000007E-2</v>
+        <f t="shared" si="246"/>
+        <v>7.0717597515844999E-2</v>
       </c>
       <c r="AH25" s="10">
-        <f t="shared" si="250"/>
+        <f t="shared" si="246"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AI25" s="10"/>
       <c r="AJ25" s="10">
-        <f t="shared" ref="AJ25:AP25" si="251">AJ11/AJ5</f>
+        <f t="shared" ref="AJ25:AP25" si="247">AJ11/AJ5</f>
         <v>0.13380231139185988</v>
       </c>
       <c r="AK25" s="10">
-        <f t="shared" si="251"/>
+        <f t="shared" si="247"/>
         <v>0.12596427646906549</v>
       </c>
       <c r="AL25" s="10">
-        <f t="shared" si="251"/>
+        <f t="shared" si="247"/>
         <v>0.12342747646421728</v>
       </c>
       <c r="AM25" s="10">
-        <f t="shared" si="251"/>
+        <f t="shared" si="247"/>
         <v>0.10031740951161612</v>
       </c>
       <c r="AN25" s="10">
-        <f t="shared" si="251"/>
+        <f t="shared" si="247"/>
         <v>9.6702016082041722E-2</v>
       </c>
       <c r="AO25" s="10">
-        <f t="shared" si="251"/>
+        <f t="shared" si="247"/>
         <v>8.4584131851284022E-2</v>
       </c>
       <c r="AP25" s="10">
-        <f t="shared" si="251"/>
+        <f t="shared" si="247"/>
         <v>7.0199262810741903E-2</v>
       </c>
       <c r="AQ25" s="10">
-        <f t="shared" ref="AQ25:AW25" si="252">AQ11/AQ5</f>
+        <f t="shared" ref="AQ25:AW25" si="248">AQ11/AQ5</f>
         <v>6.4150075395506934E-2</v>
       </c>
       <c r="AR25" s="10">
+        <f t="shared" si="248"/>
+        <v>6.3366684219764782E-2</v>
+      </c>
+      <c r="AS25" s="10">
+        <f t="shared" si="248"/>
+        <v>6.5609015563883044E-2</v>
+      </c>
+      <c r="AT25" s="10">
+        <f t="shared" si="248"/>
+        <v>6.1309714823609952E-2</v>
+      </c>
+      <c r="AU25" s="10">
+        <f t="shared" si="248"/>
+        <v>6.5822972653369755E-2</v>
+      </c>
+      <c r="AV25" s="10">
+        <f t="shared" si="248"/>
+        <v>6.6573893924984945E-2</v>
+      </c>
+      <c r="AW25" s="10">
+        <f t="shared" si="248"/>
+        <v>6.2896515371147807E-2</v>
+      </c>
+      <c r="AX25" s="10">
+        <f t="shared" ref="AX25:BI25" si="249">AX11/AX5</f>
+        <v>7.0126146348213125E-2</v>
+      </c>
+      <c r="AY25" s="10">
+        <f t="shared" si="249"/>
+        <v>7.2549769593646979E-2</v>
+      </c>
+      <c r="AZ25" s="10">
+        <f t="shared" si="249"/>
+        <v>6.006555190163388E-2</v>
+      </c>
+      <c r="BA25" s="10">
+        <f t="shared" ref="BA25:BB25" si="250">BA11/BA5</f>
+        <v>6.3637378020328261E-2</v>
+      </c>
+      <c r="BB25" s="10">
+        <f t="shared" si="250"/>
+        <v>6.5048201729783317E-2</v>
+      </c>
+      <c r="BC25" s="10">
+        <f t="shared" ref="BC25" si="251">BC11/BC5</f>
+        <v>6.6738271510222866E-2</v>
+      </c>
+      <c r="BD25" s="10">
+        <f t="shared" si="249"/>
+        <v>6.6600363372820701E-2</v>
+      </c>
+      <c r="BE25" s="10">
+        <f t="shared" si="249"/>
+        <v>6.4964119101986184E-2</v>
+      </c>
+      <c r="BF25" s="10">
+        <f t="shared" si="249"/>
+        <v>6.4107493508015936E-2</v>
+      </c>
+      <c r="BG25" s="10">
+        <f t="shared" si="249"/>
+        <v>6.3850266847846782E-2</v>
+      </c>
+      <c r="BH25" s="10">
+        <f t="shared" si="249"/>
+        <v>6.3745093339516751E-2</v>
+      </c>
+      <c r="BI25" s="10">
+        <f t="shared" si="249"/>
+        <v>6.380733470903574E-2</v>
+      </c>
+      <c r="BJ25" s="10">
+        <f t="shared" ref="BJ25:BL25" si="252">BJ11/BJ5</f>
+        <v>6.4050535546403914E-2</v>
+      </c>
+      <c r="BK25" s="10">
         <f t="shared" si="252"/>
-        <v>6.3366684219764782E-2</v>
-      </c>
-      <c r="AS25" s="10">
+        <v>6.3659082863136041E-2</v>
+      </c>
+      <c r="BL25" s="10">
         <f t="shared" si="252"/>
-        <v>6.5609015563883044E-2</v>
-      </c>
-      <c r="AT25" s="10">
-        <f t="shared" si="252"/>
-        <v>6.1309714823609952E-2</v>
-      </c>
-      <c r="AU25" s="10">
-        <f t="shared" si="252"/>
-        <v>6.5822972653369755E-2</v>
-      </c>
-      <c r="AV25" s="10">
-        <f t="shared" si="252"/>
-        <v>6.6573893924984945E-2</v>
-      </c>
-      <c r="AW25" s="10">
-        <f t="shared" si="252"/>
-        <v>6.2896515371147807E-2</v>
-      </c>
-      <c r="AX25" s="10">
-        <f t="shared" ref="AX25:BI25" si="253">AX11/AX5</f>
-        <v>7.0126146348213125E-2</v>
-      </c>
-      <c r="AY25" s="10">
+        <v>6.3264776001533671E-2</v>
+      </c>
+      <c r="BM25" s="10">
+        <f t="shared" ref="BM25:BN25" si="253">BM11/BM5</f>
+        <v>6.2867660257337116E-2</v>
+      </c>
+      <c r="BN25" s="10">
         <f t="shared" si="253"/>
-        <v>7.2549769593646979E-2</v>
-      </c>
-      <c r="AZ25" s="10">
-        <f t="shared" si="253"/>
-        <v>6.006555190163388E-2</v>
-      </c>
-      <c r="BA25" s="10">
-        <f t="shared" ref="BA25:BB25" si="254">BA11/BA5</f>
-        <v>6.3637378020328261E-2</v>
-      </c>
-      <c r="BB25" s="10">
-        <f t="shared" si="254"/>
-        <v>6.5048201729783317E-2</v>
-      </c>
-      <c r="BC25" s="10">
-        <f t="shared" ref="BC25" si="255">BC11/BC5</f>
-        <v>6.6738271510222866E-2</v>
-      </c>
-      <c r="BD25" s="10">
-        <f t="shared" si="253"/>
-        <v>6.6392916538524069E-2</v>
-      </c>
-      <c r="BE25" s="10">
-        <f t="shared" si="253"/>
-        <v>6.5679961811627691E-2</v>
-      </c>
-      <c r="BF25" s="10">
-        <f t="shared" si="253"/>
-        <v>6.5250886354375467E-2</v>
-      </c>
-      <c r="BG25" s="10">
-        <f t="shared" si="253"/>
-        <v>6.4963656534133538E-2</v>
-      </c>
-      <c r="BH25" s="10">
-        <f t="shared" si="253"/>
-        <v>6.4835893876567949E-2</v>
-      </c>
-      <c r="BI25" s="10">
-        <f t="shared" si="253"/>
-        <v>6.4883337335461339E-2</v>
-      </c>
-      <c r="BJ25" s="10">
-        <f t="shared" ref="BJ25:BL25" si="256">BJ11/BJ5</f>
-        <v>6.5119874738226668E-2</v>
-      </c>
-      <c r="BK25" s="10">
-        <f t="shared" si="256"/>
-        <v>6.4711111628974805E-2</v>
-      </c>
-      <c r="BL25" s="10">
-        <f t="shared" si="256"/>
-        <v>6.4504652053667372E-2</v>
-      </c>
-      <c r="BM25" s="10">
-        <f t="shared" ref="BM25:BN25" si="257">BM11/BM5</f>
-        <v>6.4297481070749382E-2</v>
-      </c>
-      <c r="BN25" s="10">
-        <f t="shared" si="257"/>
-        <v>6.408960510339777E-2</v>
+        <v>6.2467782661407102E-2</v>
       </c>
     </row>
     <row r="26" spans="2:179" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -6966,253 +6945,253 @@
         <v>0.29757738439060855</v>
       </c>
       <c r="D26" s="11">
-        <f t="shared" ref="D26:BI26" si="258">D13/D5</f>
+        <f t="shared" ref="D26:BI26" si="254">D13/D5</f>
         <v>0.25997350213455028</v>
       </c>
       <c r="E26" s="11">
-        <f t="shared" si="258"/>
+        <f t="shared" si="254"/>
         <v>0.23677837228949591</v>
       </c>
       <c r="F26" s="11">
-        <f t="shared" si="258"/>
+        <f t="shared" si="254"/>
         <v>0.25624801271860098</v>
       </c>
       <c r="G26" s="11">
-        <f t="shared" si="258"/>
+        <f t="shared" si="254"/>
         <v>0.27690665401494485</v>
       </c>
       <c r="H26" s="11">
-        <f t="shared" si="258"/>
+        <f t="shared" si="254"/>
         <v>0.2312333017323106</v>
       </c>
       <c r="I26" s="11">
-        <f t="shared" si="258"/>
+        <f t="shared" si="254"/>
         <v>0.2145366016837332</v>
       </c>
       <c r="J26" s="11">
-        <f t="shared" si="258"/>
+        <f t="shared" si="254"/>
         <v>0.24398813241723921</v>
       </c>
       <c r="K26" s="11">
-        <f t="shared" si="258"/>
+        <f t="shared" si="254"/>
         <v>0.2784717759940753</v>
       </c>
       <c r="L26" s="11">
-        <f t="shared" si="258"/>
+        <f t="shared" si="254"/>
         <v>0.22041397287054346</v>
       </c>
       <c r="M26" s="11">
-        <f t="shared" si="258"/>
+        <f t="shared" si="254"/>
         <v>0.21933484124989527</v>
       </c>
       <c r="N26" s="11">
-        <f t="shared" si="258"/>
+        <f t="shared" si="254"/>
         <v>0.2283687285542057</v>
       </c>
       <c r="O26" s="11">
-        <f t="shared" ref="O26:S26" si="259">O13/O5</f>
+        <f t="shared" ref="O26:S26" si="255">O13/O5</f>
         <v>0.30091799100853384</v>
       </c>
       <c r="P26" s="11">
+        <f t="shared" si="255"/>
+        <v>0.30700794784782998</v>
+      </c>
+      <c r="Q26" s="11">
+        <f t="shared" ref="Q26:R26" si="256">Q13/Q5</f>
+        <v>0.29626445956234498</v>
+      </c>
+      <c r="R26" s="11">
+        <f t="shared" si="256"/>
+        <v>0.28534069097888676</v>
+      </c>
+      <c r="S26" s="11">
+        <f t="shared" si="255"/>
+        <v>0.33472911371979508</v>
+      </c>
+      <c r="T26" s="11">
+        <f t="shared" ref="T26:U26" si="257">T13/T5</f>
+        <v>0.30817862209338187</v>
+      </c>
+      <c r="U26" s="11">
+        <f t="shared" si="257"/>
+        <v>0.27816150146457891</v>
+      </c>
+      <c r="V26" s="11">
+        <f t="shared" ref="V26" si="258">V13/V5</f>
+        <v>0.27615202005635303</v>
+      </c>
+      <c r="W26" s="11">
+        <f t="shared" ref="W26:X26" si="259">W13/W5</f>
+        <v>0.30742441572630896</v>
+      </c>
+      <c r="X26" s="11">
         <f t="shared" si="259"/>
-        <v>0.30700794784782998</v>
-      </c>
-      <c r="Q26" s="11">
-        <f t="shared" ref="Q26:R26" si="260">Q13/Q5</f>
-        <v>0.29626445956234498</v>
-      </c>
-      <c r="R26" s="11">
+        <v>0.29859968788223878</v>
+      </c>
+      <c r="Y26" s="11">
+        <f t="shared" ref="Y26:Z26" si="260">Y13/Y5</f>
+        <v>0.28115945572576012</v>
+      </c>
+      <c r="Z26" s="11">
         <f t="shared" si="260"/>
-        <v>0.28534069097888676</v>
-      </c>
-      <c r="S26" s="11">
-        <f t="shared" si="259"/>
-        <v>0.33472911371979508</v>
-      </c>
-      <c r="T26" s="11">
-        <f t="shared" ref="T26:U26" si="261">T13/T5</f>
-        <v>0.30817862209338187</v>
-      </c>
-      <c r="U26" s="11">
+        <v>0.30133634271156895</v>
+      </c>
+      <c r="AA26" s="11">
+        <f t="shared" ref="AA26:AD26" si="261">AA13/AA5</f>
+        <v>0.33763746602550698</v>
+      </c>
+      <c r="AB26" s="11">
         <f t="shared" si="261"/>
-        <v>0.27816150146457891</v>
-      </c>
-      <c r="V26" s="11">
-        <f t="shared" ref="V26" si="262">V13/V5</f>
-        <v>0.27615202005635303</v>
-      </c>
-      <c r="W26" s="11">
-        <f t="shared" ref="W26:X26" si="263">W13/W5</f>
-        <v>0.30742441572630896</v>
-      </c>
-      <c r="X26" s="11">
-        <f t="shared" si="263"/>
-        <v>0.29859968788223878</v>
-      </c>
-      <c r="Y26" s="11">
-        <f t="shared" ref="Y26:Z26" si="264">Y13/Y5</f>
-        <v>0.28115945572576012</v>
-      </c>
-      <c r="Z26" s="11">
-        <f t="shared" si="264"/>
-        <v>0.30133634271156895</v>
-      </c>
-      <c r="AA26" s="11">
-        <f t="shared" ref="AA26:AD26" si="265">AA13/AA5</f>
-        <v>0.33763746602550698</v>
-      </c>
-      <c r="AB26" s="11">
-        <f t="shared" si="265"/>
         <v>0.30742785362467356</v>
       </c>
       <c r="AC26" s="11">
-        <f t="shared" si="265"/>
+        <f t="shared" si="261"/>
         <v>0.29555708406682446</v>
       </c>
       <c r="AD26" s="11">
-        <f t="shared" si="265"/>
+        <f t="shared" si="261"/>
         <v>0.31171389444854103</v>
       </c>
       <c r="AE26" s="11">
-        <f t="shared" ref="AE26:AH26" si="266">AE13/AE5</f>
+        <f t="shared" ref="AE26:AH26" si="262">AE13/AE5</f>
         <v>0.34458567980691873</v>
       </c>
       <c r="AF26" s="11">
-        <f t="shared" si="266"/>
+        <f t="shared" si="262"/>
         <v>0.31029058610094484</v>
       </c>
       <c r="AG26" s="11">
-        <f t="shared" si="266"/>
-        <v>0.30194646786301194</v>
+        <f t="shared" si="262"/>
+        <v>0.29990641881832492</v>
       </c>
       <c r="AH26" s="11">
-        <f t="shared" si="266"/>
-        <v>0.3030318955388015</v>
+        <f t="shared" si="262"/>
+        <v>0.29751780544473461</v>
       </c>
       <c r="AI26" s="11"/>
       <c r="AJ26" s="11">
-        <f t="shared" ref="AJ26:AP26" si="267">AJ13/AJ5</f>
+        <f t="shared" ref="AJ26:AP26" si="263">AJ13/AJ5</f>
         <v>0.11793841073864045</v>
       </c>
       <c r="AK26" s="11">
+        <f t="shared" si="263"/>
+        <v>0.1269997411338338</v>
+      </c>
+      <c r="AL26" s="11">
+        <f t="shared" si="263"/>
+        <v>0.1836624177289011</v>
+      </c>
+      <c r="AM26" s="11">
+        <f t="shared" si="263"/>
+        <v>0.22210663892667573</v>
+      </c>
+      <c r="AN26" s="11">
+        <f t="shared" si="263"/>
+        <v>0.2736277823097541</v>
+      </c>
+      <c r="AO26" s="11">
+        <f t="shared" si="263"/>
+        <v>0.28187044844768111</v>
+      </c>
+      <c r="AP26" s="11">
+        <f t="shared" si="263"/>
+        <v>0.31215068961376086</v>
+      </c>
+      <c r="AQ26" s="11">
+        <f t="shared" ref="AQ26:AW26" si="264">AQ13/AQ5</f>
+        <v>0.35295959311984054</v>
+      </c>
+      <c r="AR26" s="11">
+        <f t="shared" si="264"/>
+        <v>0.28669475162366159</v>
+      </c>
+      <c r="AS26" s="11">
+        <f t="shared" si="264"/>
+        <v>0.28722339232473537</v>
+      </c>
+      <c r="AT26" s="11">
+        <f t="shared" si="264"/>
+        <v>0.30477290717326661</v>
+      </c>
+      <c r="AU26" s="11">
+        <f t="shared" si="264"/>
+        <v>0.27835410106706115</v>
+      </c>
+      <c r="AV26" s="11">
+        <f t="shared" si="264"/>
+        <v>0.26760428208729942</v>
+      </c>
+      <c r="AW26" s="11">
+        <f t="shared" si="264"/>
+        <v>0.26694026619477024</v>
+      </c>
+      <c r="AX26" s="11">
+        <f t="shared" si="254"/>
+        <v>0.24572017188496928</v>
+      </c>
+      <c r="AY26" s="11">
+        <f t="shared" si="254"/>
+        <v>0.24147314354406862</v>
+      </c>
+      <c r="AZ26" s="11">
+        <f t="shared" si="254"/>
+        <v>0.29782377527561593</v>
+      </c>
+      <c r="BA26" s="11">
+        <f t="shared" ref="BA26:BB26" si="265">BA13/BA5</f>
+        <v>0.30288744395528594</v>
+      </c>
+      <c r="BB26" s="11">
+        <f t="shared" si="265"/>
+        <v>0.29821412265024722</v>
+      </c>
+      <c r="BC26" s="11">
+        <f t="shared" ref="BC26" si="266">BC13/BC5</f>
+        <v>0.31510222870075566</v>
+      </c>
+      <c r="BD26" s="11">
+        <f t="shared" si="254"/>
+        <v>0.31515666770648243</v>
+      </c>
+      <c r="BE26" s="11">
+        <f t="shared" si="254"/>
+        <v>0.31349259496538784</v>
+      </c>
+      <c r="BF26" s="11">
+        <f t="shared" si="254"/>
+        <v>0.31776839278157021</v>
+      </c>
+      <c r="BG26" s="11">
+        <f t="shared" si="254"/>
+        <v>0.32159811933739907</v>
+      </c>
+      <c r="BH26" s="11">
+        <f t="shared" si="254"/>
+        <v>0.32433603067251665</v>
+      </c>
+      <c r="BI26" s="11">
+        <f t="shared" si="254"/>
+        <v>0.32589241579147521</v>
+      </c>
+      <c r="BJ26" s="11">
+        <f t="shared" ref="BJ26:BL26" si="267">BJ13/BJ5</f>
+        <v>0.32703663943795336</v>
+      </c>
+      <c r="BK26" s="11">
         <f t="shared" si="267"/>
-        <v>0.1269997411338338</v>
-      </c>
-      <c r="AL26" s="11">
+        <v>0.32883418288475569</v>
+      </c>
+      <c r="BL26" s="11">
         <f t="shared" si="267"/>
-        <v>0.1836624177289011</v>
-      </c>
-      <c r="AM26" s="11">
-        <f t="shared" si="267"/>
-        <v>0.22210663892667573</v>
-      </c>
-      <c r="AN26" s="11">
-        <f t="shared" si="267"/>
-        <v>0.2736277823097541</v>
-      </c>
-      <c r="AO26" s="11">
-        <f t="shared" si="267"/>
-        <v>0.28187044844768111</v>
-      </c>
-      <c r="AP26" s="11">
-        <f t="shared" si="267"/>
-        <v>0.31215068961376086</v>
-      </c>
-      <c r="AQ26" s="11">
-        <f t="shared" ref="AQ26:AW26" si="268">AQ13/AQ5</f>
-        <v>0.35295959311984054</v>
-      </c>
-      <c r="AR26" s="11">
+        <v>0.33065318225998191</v>
+      </c>
+      <c r="BM26" s="11">
+        <f t="shared" ref="BM26:BN26" si="268">BM13/BM5</f>
+        <v>0.33249351878513578</v>
+      </c>
+      <c r="BN26" s="11">
         <f t="shared" si="268"/>
-        <v>0.28669475162366159</v>
-      </c>
-      <c r="AS26" s="11">
-        <f t="shared" si="268"/>
-        <v>0.28722339232473537</v>
-      </c>
-      <c r="AT26" s="11">
-        <f t="shared" si="268"/>
-        <v>0.30477290717326661</v>
-      </c>
-      <c r="AU26" s="11">
-        <f t="shared" si="268"/>
-        <v>0.27835410106706115</v>
-      </c>
-      <c r="AV26" s="11">
-        <f t="shared" si="268"/>
-        <v>0.26760428208729942</v>
-      </c>
-      <c r="AW26" s="11">
-        <f t="shared" si="268"/>
-        <v>0.26694026619477024</v>
-      </c>
-      <c r="AX26" s="11">
-        <f t="shared" si="258"/>
-        <v>0.24572017188496928</v>
-      </c>
-      <c r="AY26" s="11">
-        <f t="shared" si="258"/>
-        <v>0.24147314354406862</v>
-      </c>
-      <c r="AZ26" s="11">
-        <f t="shared" si="258"/>
-        <v>0.29782377527561593</v>
-      </c>
-      <c r="BA26" s="11">
-        <f t="shared" ref="BA26:BB26" si="269">BA13/BA5</f>
-        <v>0.30288744395528594</v>
-      </c>
-      <c r="BB26" s="11">
-        <f t="shared" si="269"/>
-        <v>0.29821412265024722</v>
-      </c>
-      <c r="BC26" s="11">
-        <f t="shared" ref="BC26" si="270">BC13/BC5</f>
-        <v>0.31510222870075566</v>
-      </c>
-      <c r="BD26" s="11">
-        <f t="shared" si="258"/>
-        <v>0.31713506196877955</v>
-      </c>
-      <c r="BE26" s="11">
-        <f t="shared" si="258"/>
-        <v>0.31683015084358429</v>
-      </c>
-      <c r="BF26" s="11">
-        <f t="shared" si="258"/>
-        <v>0.32101603497384995</v>
-      </c>
-      <c r="BG26" s="11">
-        <f t="shared" si="258"/>
-        <v>0.32498163627796345</v>
-      </c>
-      <c r="BH26" s="11">
-        <f t="shared" si="258"/>
-        <v>0.32783071016656196</v>
-      </c>
-      <c r="BI26" s="11">
-        <f t="shared" si="258"/>
-        <v>0.32947393831664551</v>
-      </c>
-      <c r="BJ26" s="11">
-        <f t="shared" ref="BJ26:BL26" si="271">BJ13/BJ5</f>
-        <v>0.33066889581911824</v>
-      </c>
-      <c r="BK26" s="11">
-        <f t="shared" si="271"/>
-        <v>0.33252755006320622</v>
-      </c>
-      <c r="BL26" s="11">
-        <f t="shared" si="271"/>
-        <v>0.33304951288694734</v>
-      </c>
-      <c r="BM26" s="11">
-        <f t="shared" ref="BM26:BN26" si="272">BM13/BM5</f>
-        <v>0.33357327426289723</v>
-      </c>
-      <c r="BN26" s="11">
-        <f t="shared" si="272"/>
-        <v>0.33409881795223784</v>
+        <v>0.33435506291409239</v>
       </c>
     </row>
     <row r="28" spans="2:179" x14ac:dyDescent="0.3">
@@ -7220,116 +7199,116 @@
         <v>52</v>
       </c>
       <c r="G28" s="11">
-        <f t="shared" ref="G28:N28" si="273">G3/C3-1</f>
+        <f t="shared" ref="G28:N28" si="269">G3/C3-1</f>
         <v>-7.2368753473801228E-2</v>
       </c>
       <c r="H28" s="11">
+        <f t="shared" si="269"/>
+        <v>-9.2070115233879979E-2</v>
+      </c>
+      <c r="I28" s="11">
+        <f t="shared" si="269"/>
+        <v>-1.7194570135746656E-2</v>
+      </c>
+      <c r="J28" s="11">
+        <f t="shared" si="269"/>
+        <v>-1.4760712032274692E-2</v>
+      </c>
+      <c r="K28" s="11">
+        <f t="shared" si="269"/>
+        <v>7.719752161775717E-2</v>
+      </c>
+      <c r="L28" s="11">
+        <f t="shared" si="269"/>
+        <v>-3.4360571244496985E-2</v>
+      </c>
+      <c r="M28" s="11">
+        <f t="shared" si="269"/>
+        <v>9.8573924540775293E-2</v>
+      </c>
+      <c r="N28" s="11">
+        <f t="shared" si="269"/>
+        <v>-2.6781035921519925E-2</v>
+      </c>
+      <c r="O28" s="11">
+        <f t="shared" ref="O28:O30" si="270">O3/K3-1</f>
+        <v>0.20952164239482207</v>
+      </c>
+      <c r="P28" s="11">
+        <f t="shared" ref="P28:P30" si="271">P3/L3-1</f>
+        <v>0.61643500500389181</v>
+      </c>
+      <c r="Q28" s="11">
+        <f t="shared" ref="Q28:S30" si="272">Q3/M3-1</f>
+        <v>0.37436867330052226</v>
+      </c>
+      <c r="R28" s="11">
+        <f t="shared" si="272"/>
+        <v>0.2977925781172106</v>
+      </c>
+      <c r="S28" s="11">
+        <f t="shared" si="272"/>
+        <v>9.1463032254018639E-2</v>
+      </c>
+      <c r="T28" s="11">
+        <f t="shared" ref="T28:U30" si="273">T3/P3-1</f>
+        <v>6.5682484212264303E-2</v>
+      </c>
+      <c r="U28" s="11">
         <f t="shared" si="273"/>
-        <v>-9.2070115233879979E-2</v>
-      </c>
-      <c r="I28" s="11">
-        <f t="shared" si="273"/>
-        <v>-1.7194570135746656E-2</v>
-      </c>
-      <c r="J28" s="11">
-        <f t="shared" si="273"/>
-        <v>-1.4760712032274692E-2</v>
-      </c>
-      <c r="K28" s="11">
-        <f t="shared" si="273"/>
-        <v>7.719752161775717E-2</v>
-      </c>
-      <c r="L28" s="11">
-        <f t="shared" si="273"/>
-        <v>-3.4360571244496985E-2</v>
-      </c>
-      <c r="M28" s="11">
-        <f t="shared" si="273"/>
-        <v>9.8573924540775293E-2</v>
-      </c>
-      <c r="N28" s="11">
-        <f t="shared" si="273"/>
-        <v>-2.6781035921519925E-2</v>
-      </c>
-      <c r="O28" s="11">
-        <f t="shared" ref="O28:O30" si="274">O3/K3-1</f>
-        <v>0.20952164239482207</v>
-      </c>
-      <c r="P28" s="11">
-        <f t="shared" ref="P28:P30" si="275">P3/L3-1</f>
-        <v>0.61643500500389181</v>
-      </c>
-      <c r="Q28" s="11">
-        <f t="shared" ref="Q28:S30" si="276">Q3/M3-1</f>
-        <v>0.37436867330052226</v>
-      </c>
-      <c r="R28" s="11">
+        <v>-9.2731594420466523E-3</v>
+      </c>
+      <c r="V28" s="11">
+        <f t="shared" ref="V28:V30" si="274">V3/R3-1</f>
+        <v>9.0269348370542124E-2</v>
+      </c>
+      <c r="W28" s="11">
+        <f t="shared" ref="W28:X30" si="275">W3/S3-1</f>
+        <v>-7.6999683995824908E-2</v>
+      </c>
+      <c r="X28" s="11">
+        <f t="shared" si="275"/>
+        <v>-4.5547852356791485E-2</v>
+      </c>
+      <c r="Y28" s="11">
+        <f t="shared" ref="Y28:AA30" si="276">Y3/U3-1</f>
+        <v>-4.3737668692289455E-2</v>
+      </c>
+      <c r="Z28" s="11">
         <f t="shared" si="276"/>
-        <v>0.2977925781172106</v>
-      </c>
-      <c r="S28" s="11">
+        <v>-5.3186391950167722E-2</v>
+      </c>
+      <c r="AA28" s="11">
         <f t="shared" si="276"/>
-        <v>9.1463032254018639E-2</v>
-      </c>
-      <c r="T28" s="11">
-        <f t="shared" ref="T28:U30" si="277">T3/P3-1</f>
-        <v>6.5682484212264303E-2</v>
-      </c>
-      <c r="U28" s="11">
-        <f t="shared" si="277"/>
-        <v>-9.2731594420466523E-3</v>
-      </c>
-      <c r="V28" s="11">
-        <f t="shared" ref="V28:V30" si="278">V3/R3-1</f>
-        <v>9.0269348370542124E-2</v>
-      </c>
-      <c r="W28" s="11">
-        <f t="shared" ref="W28:X30" si="279">W3/S3-1</f>
-        <v>-7.6999683995824908E-2</v>
-      </c>
-      <c r="X28" s="11">
-        <f t="shared" si="279"/>
-        <v>-4.5547852356791485E-2</v>
-      </c>
-      <c r="Y28" s="11">
-        <f t="shared" ref="Y28:AA30" si="280">Y3/U3-1</f>
-        <v>-4.3737668692289455E-2</v>
-      </c>
-      <c r="Z28" s="11">
-        <f t="shared" si="280"/>
-        <v>-5.3186391950167722E-2</v>
-      </c>
-      <c r="AA28" s="11">
-        <f t="shared" si="280"/>
         <v>7.2623148109718372E-4</v>
       </c>
       <c r="AB28" s="14">
-        <f t="shared" ref="AB28:AB30" si="281">AB3/X3-1</f>
+        <f t="shared" ref="AB28:AB30" si="277">AB3/X3-1</f>
         <v>-9.5267080577310703E-2</v>
       </c>
       <c r="AC28" s="11">
-        <f t="shared" ref="AC28:AC30" si="282">AC3/Y3-1</f>
+        <f t="shared" ref="AC28:AC30" si="278">AC3/Y3-1</f>
         <v>1.6175888023240548E-2</v>
       </c>
       <c r="AD28" s="11">
-        <f t="shared" ref="AD28:AD30" si="283">AD3/Z3-1</f>
+        <f t="shared" ref="AD28:AD30" si="279">AD3/Z3-1</f>
         <v>4.1289592760181071E-2</v>
       </c>
       <c r="AE28" s="11">
-        <f t="shared" ref="AE28:AE30" si="284">AE3/AA3-1</f>
+        <f t="shared" ref="AE28:AE30" si="280">AE3/AA3-1</f>
         <v>1.5571544091729006E-2</v>
       </c>
       <c r="AF28" s="11">
-        <f t="shared" ref="AF28:AF30" si="285">AF3/AB3-1</f>
+        <f t="shared" ref="AF28:AF30" si="281">AF3/AB3-1</f>
         <v>2.7330084023562407E-2</v>
       </c>
       <c r="AG28" s="11">
-        <f t="shared" ref="AG28:AG30" si="286">AG3/AC3-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="AG28:AG30" si="282">AG3/AC3-1</f>
+        <v>8.2012214930803795E-2</v>
       </c>
       <c r="AH28" s="11">
-        <f t="shared" ref="AH28:AH30" si="287">AH3/AD3-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="AH28:AH30" si="283">AH3/AD3-1</f>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AI28" s="11"/>
       <c r="AJ28" s="11"/>
@@ -7345,71 +7324,71 @@
       <c r="AT28" s="11"/>
       <c r="AU28" s="11"/>
       <c r="AX28" s="11">
-        <f t="shared" ref="AX28:AY28" si="288">AX3/AW3-1</f>
+        <f t="shared" ref="AX28:AY28" si="284">AX3/AW3-1</f>
         <v>-5.2973915969660834E-2</v>
       </c>
       <c r="AY28" s="11">
-        <f t="shared" si="288"/>
+        <f t="shared" si="284"/>
         <v>3.2092312151970948E-2</v>
       </c>
       <c r="AZ28" s="11">
-        <f t="shared" ref="AZ28:BL28" si="289">AZ3/AY3-1</f>
+        <f t="shared" ref="AZ28:BL28" si="285">AZ3/AY3-1</f>
         <v>0.34720743656765429</v>
       </c>
       <c r="BA28" s="11">
-        <f t="shared" si="289"/>
+        <f t="shared" si="285"/>
         <v>6.3239764351428418E-2</v>
       </c>
       <c r="BB28" s="11">
-        <f t="shared" si="289"/>
+        <f t="shared" si="285"/>
         <v>-5.7286708686618226E-2</v>
       </c>
       <c r="BC28" s="11">
-        <f t="shared" si="289"/>
+        <f t="shared" si="285"/>
         <v>-1.0798933190197424E-2</v>
       </c>
       <c r="BD28" s="11">
-        <f t="shared" si="289"/>
-        <v>2.0214063337244736E-2</v>
+        <f t="shared" si="285"/>
+        <v>3.5533903535843292E-2</v>
       </c>
       <c r="BE28" s="11">
-        <f t="shared" si="289"/>
+        <f t="shared" si="285"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="BF28" s="11">
+        <f t="shared" si="285"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="BG28" s="11">
+        <f t="shared" si="285"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BF28" s="11">
-        <f t="shared" si="289"/>
+      <c r="BH28" s="11">
+        <f t="shared" si="285"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BG28" s="11">
-        <f t="shared" si="289"/>
+      <c r="BI28" s="11">
+        <f t="shared" si="285"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BH28" s="11">
-        <f t="shared" si="289"/>
+      <c r="BJ28" s="11">
+        <f t="shared" si="285"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BI28" s="11">
-        <f t="shared" si="289"/>
+      <c r="BK28" s="11">
+        <f t="shared" si="285"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BJ28" s="11">
-        <f t="shared" si="289"/>
+      <c r="BL28" s="11">
+        <f t="shared" si="285"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BK28" s="11">
-        <f t="shared" si="289"/>
+      <c r="BM28" s="11">
+        <f t="shared" ref="BM28:BM30" si="286">BM3/BL3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BL28" s="11">
-        <f t="shared" si="289"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="BM28" s="11">
-        <f t="shared" ref="BM28:BM30" si="290">BM3/BL3-1</f>
-        <v>1.0000000000000009E-2</v>
-      </c>
       <c r="BN28" s="11">
-        <f t="shared" ref="BN28:BN30" si="291">BN3/BM3-1</f>
+        <f t="shared" ref="BN28:BN30" si="287">BN3/BM3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -7418,116 +7397,116 @@
         <v>53</v>
       </c>
       <c r="G29" s="11">
-        <f t="shared" ref="G29:N29" si="292">G4/C4-1</f>
+        <f t="shared" ref="G29:N29" si="288">G4/C4-1</f>
         <v>0.19125862635557023</v>
       </c>
       <c r="H29" s="11">
-        <f t="shared" si="292"/>
+        <f t="shared" si="288"/>
         <v>0.1624365482233503</v>
       </c>
       <c r="I29" s="11">
-        <f t="shared" si="292"/>
+        <f t="shared" si="288"/>
         <v>0.12635201573254662</v>
       </c>
       <c r="J29" s="11">
-        <f t="shared" si="292"/>
+        <f t="shared" si="288"/>
         <v>0.18039437682800274</v>
       </c>
       <c r="K29" s="11">
-        <f t="shared" si="292"/>
+        <f t="shared" si="288"/>
         <v>0.16919540229885066</v>
       </c>
       <c r="L29" s="11">
-        <f t="shared" si="292"/>
+        <f t="shared" si="288"/>
         <v>0.16576419213973792</v>
       </c>
       <c r="M29" s="11">
-        <f t="shared" si="292"/>
+        <f t="shared" si="288"/>
         <v>0.14849410737669144</v>
       </c>
       <c r="N29" s="11">
-        <f t="shared" si="292"/>
+        <f t="shared" si="288"/>
         <v>0.16289665094716654</v>
       </c>
       <c r="O29" s="11">
+        <f t="shared" si="270"/>
+        <v>0.23955957530475813</v>
+      </c>
+      <c r="P29" s="11">
+        <f t="shared" si="271"/>
+        <v>0.26618219958046141</v>
+      </c>
+      <c r="Q29" s="11">
+        <f t="shared" si="272"/>
+        <v>0.32912739434478566</v>
+      </c>
+      <c r="R29" s="11">
+        <f t="shared" si="272"/>
+        <v>0.25623754209911342</v>
+      </c>
+      <c r="S29" s="11">
+        <f t="shared" si="272"/>
+        <v>0.23824630416851722</v>
+      </c>
+      <c r="T29" s="11">
+        <f t="shared" si="273"/>
+        <v>0.17277084196201398</v>
+      </c>
+      <c r="U29" s="11">
+        <f t="shared" si="273"/>
+        <v>0.12112547180601618</v>
+      </c>
+      <c r="V29" s="11">
         <f t="shared" si="274"/>
-        <v>0.23955957530475813</v>
-      </c>
-      <c r="P29" s="11">
+        <v>4.984406631285232E-2</v>
+      </c>
+      <c r="W29" s="11">
         <f t="shared" si="275"/>
-        <v>0.26618219958046141</v>
-      </c>
-      <c r="Q29" s="11">
+        <v>6.4050010248001721E-2</v>
+      </c>
+      <c r="X29" s="11">
+        <f t="shared" si="275"/>
+        <v>5.4790373845921003E-2</v>
+      </c>
+      <c r="Y29" s="11">
         <f t="shared" si="276"/>
-        <v>0.32912739434478566</v>
-      </c>
-      <c r="R29" s="11">
+        <v>8.2075086716996593E-2</v>
+      </c>
+      <c r="Z29" s="11">
         <f t="shared" si="276"/>
-        <v>0.25623754209911342</v>
-      </c>
-      <c r="S29" s="11">
+        <v>0.16291432145090678</v>
+      </c>
+      <c r="AA29" s="11">
         <f t="shared" si="276"/>
-        <v>0.23824630416851722</v>
-      </c>
-      <c r="T29" s="11">
+        <v>0.11321390734855052</v>
+      </c>
+      <c r="AB29" s="11">
         <f t="shared" si="277"/>
-        <v>0.17277084196201398</v>
-      </c>
-      <c r="U29" s="11">
-        <f t="shared" si="277"/>
-        <v>0.12112547180601618</v>
-      </c>
-      <c r="V29" s="11">
+        <v>0.14157937532883724</v>
+      </c>
+      <c r="AC29" s="11">
         <f t="shared" si="278"/>
-        <v>4.984406631285232E-2</v>
-      </c>
-      <c r="W29" s="11">
+        <v>0.1414227124876255</v>
+      </c>
+      <c r="AD29" s="11">
         <f t="shared" si="279"/>
-        <v>6.4050010248001721E-2</v>
-      </c>
-      <c r="X29" s="11">
-        <f t="shared" si="279"/>
-        <v>5.4790373845921003E-2</v>
-      </c>
-      <c r="Y29" s="11">
+        <v>0.11911804248453883</v>
+      </c>
+      <c r="AE29" s="11">
         <f t="shared" si="280"/>
-        <v>8.2075086716996593E-2</v>
-      </c>
-      <c r="Z29" s="11">
-        <f t="shared" si="280"/>
-        <v>0.16291432145090678</v>
-      </c>
-      <c r="AA29" s="11">
-        <f t="shared" si="280"/>
-        <v>0.11321390734855052</v>
-      </c>
-      <c r="AB29" s="11">
+        <v>0.13942120517368162</v>
+      </c>
+      <c r="AF29" s="11">
         <f t="shared" si="281"/>
-        <v>0.14157937532883724</v>
-      </c>
-      <c r="AC29" s="11">
+        <v>0.11639502241588806</v>
+      </c>
+      <c r="AG29" s="11">
         <f t="shared" si="282"/>
-        <v>0.1414227124876255</v>
-      </c>
-      <c r="AD29" s="11">
+        <v>0.13257341097757402</v>
+      </c>
+      <c r="AH29" s="11">
         <f t="shared" si="283"/>
-        <v>0.11911804248453883</v>
-      </c>
-      <c r="AE29" s="11">
-        <f t="shared" si="284"/>
-        <v>0.13942120517368162</v>
-      </c>
-      <c r="AF29" s="11">
-        <f t="shared" si="285"/>
-        <v>0.11639502241588806</v>
-      </c>
-      <c r="AG29" s="11">
-        <f t="shared" si="286"/>
-        <v>0.12000000000000011</v>
-      </c>
-      <c r="AH29" s="11">
-        <f t="shared" si="287"/>
-        <v>0.10000000000000009</v>
+        <v>0.1100000000000001</v>
       </c>
       <c r="AI29" s="11"/>
       <c r="AJ29" s="11"/>
@@ -7543,72 +7522,72 @@
       <c r="AT29" s="11"/>
       <c r="AU29" s="11"/>
       <c r="AX29" s="11">
-        <f t="shared" ref="AX29:AY29" si="293">AX4/AW4-1</f>
+        <f t="shared" ref="AX29:AY29" si="289">AX4/AW4-1</f>
         <v>0.16461205595250084</v>
       </c>
       <c r="AY29" s="11">
-        <f t="shared" si="293"/>
+        <f t="shared" si="289"/>
         <v>0.16152167807997242</v>
       </c>
       <c r="AZ29" s="11">
-        <f t="shared" ref="AZ29:BL29" si="294">AZ4/AY4-1</f>
+        <f t="shared" ref="AZ29:BL29" si="290">AZ4/AY4-1</f>
         <v>0.27259708376729663</v>
       </c>
       <c r="BA29" s="11">
-        <f t="shared" si="294"/>
+        <f t="shared" si="290"/>
         <v>0.14181951041286078</v>
       </c>
       <c r="BB29" s="11">
-        <f t="shared" si="294"/>
+        <f t="shared" si="290"/>
         <v>9.0504166186691215E-2</v>
       </c>
       <c r="BC29" s="11">
-        <f t="shared" si="294"/>
+        <f t="shared" si="290"/>
         <v>0.12874413145539898</v>
       </c>
       <c r="BD29" s="11">
-        <f t="shared" si="294"/>
-        <v>0.11858041572648137</v>
+        <f t="shared" si="290"/>
+        <v>0.12434277157919915</v>
       </c>
       <c r="BE29" s="11">
-        <f t="shared" si="294"/>
+        <f t="shared" si="290"/>
         <v>9.000000000000008E-2</v>
       </c>
       <c r="BF29" s="11">
-        <f t="shared" si="294"/>
+        <f t="shared" si="290"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="BG29" s="11">
-        <f t="shared" si="294"/>
+        <f t="shared" si="290"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="BH29" s="11">
-        <f t="shared" si="294"/>
+        <f t="shared" si="290"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BI29" s="11">
-        <f t="shared" si="294"/>
+        <f t="shared" si="290"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="BJ29" s="11">
-        <f t="shared" si="294"/>
+        <f t="shared" si="290"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BK29" s="11">
-        <f t="shared" si="294"/>
+        <f t="shared" si="290"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BL29" s="11">
-        <f t="shared" si="294"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="290"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="BM29" s="11">
-        <f t="shared" si="290"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="286"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="BN29" s="11">
-        <f t="shared" si="291"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="287"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="BP29" t="s">
         <v>43</v>
@@ -7626,165 +7605,165 @@
         <v>-4.5111163965433243E-2</v>
       </c>
       <c r="H30" s="11">
-        <f t="shared" ref="H30:N30" si="295">H5/D5-1</f>
+        <f t="shared" ref="H30:N30" si="291">H5/D5-1</f>
         <v>-5.1065639465462831E-2</v>
       </c>
       <c r="I30" s="11">
-        <f t="shared" si="295"/>
+        <f t="shared" si="291"/>
         <v>1.0213085515817122E-2</v>
       </c>
       <c r="J30" s="11">
-        <f t="shared" si="295"/>
+        <f t="shared" si="291"/>
         <v>1.8124006359300449E-2</v>
       </c>
       <c r="K30" s="11">
-        <f t="shared" si="295"/>
+        <f t="shared" si="291"/>
         <v>8.9064167951607098E-2</v>
       </c>
       <c r="L30" s="11">
-        <f t="shared" si="295"/>
+        <f t="shared" si="291"/>
         <v>5.1366026027750422E-3</v>
       </c>
       <c r="M30" s="11">
-        <f t="shared" si="295"/>
+        <f t="shared" si="291"/>
         <v>0.10920106301919752</v>
       </c>
       <c r="N30" s="11">
-        <f t="shared" si="295"/>
+        <f t="shared" si="291"/>
         <v>1.0274828232354816E-2</v>
       </c>
       <c r="O30" s="11">
+        <f t="shared" si="270"/>
+        <v>0.21368126422635836</v>
+      </c>
+      <c r="P30" s="11">
+        <f t="shared" si="271"/>
+        <v>0.53626121105070901</v>
+      </c>
+      <c r="Q30" s="11">
+        <f t="shared" si="272"/>
+        <v>0.36439641450950822</v>
+      </c>
+      <c r="R30" s="11">
+        <f t="shared" si="272"/>
+        <v>0.28844786546724777</v>
+      </c>
+      <c r="S30" s="11">
+        <f t="shared" si="272"/>
+        <v>0.11222283042740866</v>
+      </c>
+      <c r="T30" s="11">
+        <f t="shared" si="273"/>
+        <v>8.5885872477228009E-2</v>
+      </c>
+      <c r="U30" s="11">
+        <f t="shared" si="273"/>
+        <v>1.8726821720657316E-2</v>
+      </c>
+      <c r="V30" s="11">
         <f t="shared" si="274"/>
-        <v>0.21368126422635836</v>
-      </c>
-      <c r="P30" s="11">
+        <v>8.1405950095969182E-2</v>
+      </c>
+      <c r="W30" s="11">
         <f t="shared" si="275"/>
-        <v>0.53626121105070901</v>
-      </c>
-      <c r="Q30" s="11">
+        <v>-5.4790431239662762E-2</v>
+      </c>
+      <c r="X30" s="11">
+        <f t="shared" si="275"/>
+        <v>-2.5103312156911084E-2</v>
+      </c>
+      <c r="Y30" s="11">
         <f t="shared" si="276"/>
-        <v>0.36439641450950822</v>
-      </c>
-      <c r="R30" s="11">
+        <v>-1.4006919080509661E-2</v>
+      </c>
+      <c r="Z30" s="11">
         <f t="shared" si="276"/>
-        <v>0.28844786546724777</v>
-      </c>
-      <c r="S30" s="11">
+        <v>-7.1883389168682088E-3</v>
+      </c>
+      <c r="AA30" s="11">
         <f t="shared" si="276"/>
-        <v>0.11222283042740866</v>
-      </c>
-      <c r="T30" s="11">
+        <v>2.0665107465387411E-2</v>
+      </c>
+      <c r="AB30" s="11">
         <f t="shared" si="277"/>
-        <v>8.5885872477228009E-2</v>
-      </c>
-      <c r="U30" s="11">
-        <f t="shared" si="277"/>
-        <v>1.8726821720657316E-2</v>
-      </c>
-      <c r="V30" s="11">
+        <v>-4.3053270909781061E-2</v>
+      </c>
+      <c r="AC30" s="11">
         <f t="shared" si="278"/>
-        <v>8.1405950095969182E-2</v>
-      </c>
-      <c r="W30" s="11">
+        <v>4.8657041211780383E-2</v>
+      </c>
+      <c r="AD30" s="11">
         <f t="shared" si="279"/>
-        <v>-5.4790431239662762E-2</v>
-      </c>
-      <c r="X30" s="11">
-        <f t="shared" si="279"/>
-        <v>-2.5103312156911084E-2</v>
-      </c>
-      <c r="Y30" s="11">
+        <v>6.0694093722764686E-2</v>
+      </c>
+      <c r="AE30" s="11">
         <f t="shared" si="280"/>
-        <v>-1.4006919080509661E-2</v>
-      </c>
-      <c r="Z30" s="11">
-        <f t="shared" si="280"/>
-        <v>-7.1883389168682088E-3</v>
-      </c>
-      <c r="AA30" s="11">
-        <f t="shared" si="280"/>
-        <v>2.0665107465387411E-2</v>
-      </c>
-      <c r="AB30" s="11">
+        <v>3.9514948776918191E-2</v>
+      </c>
+      <c r="AF30" s="11">
         <f t="shared" si="281"/>
-        <v>-4.3053270909781061E-2</v>
-      </c>
-      <c r="AC30" s="11">
+        <v>5.075314314678292E-2</v>
+      </c>
+      <c r="AG30" s="11">
         <f t="shared" si="282"/>
-        <v>4.8657041211780383E-2</v>
-      </c>
-      <c r="AD30" s="11">
+        <v>9.628455180293094E-2</v>
+      </c>
+      <c r="AH30" s="11">
         <f t="shared" si="283"/>
-        <v>6.0694093722764686E-2</v>
-      </c>
-      <c r="AE30" s="11">
-        <f t="shared" si="284"/>
-        <v>3.9514948776918191E-2</v>
-      </c>
-      <c r="AF30" s="11">
-        <f t="shared" si="285"/>
-        <v>5.075314314678292E-2</v>
-      </c>
-      <c r="AG30" s="11">
-        <f t="shared" si="286"/>
-        <v>4.8227846625552351E-2</v>
-      </c>
-      <c r="AH30" s="11">
-        <f t="shared" si="287"/>
-        <v>4.1044559148846416E-2</v>
+        <v>5.1044559148846647E-2</v>
       </c>
       <c r="AI30" s="11"/>
       <c r="AJ30" s="11"/>
       <c r="AK30" s="11">
-        <f t="shared" ref="AK30:AP30" si="296">AK5/AJ5-1</f>
+        <f t="shared" ref="AK30:AP30" si="292">AK5/AJ5-1</f>
         <v>0.38647620414902017</v>
       </c>
       <c r="AL30" s="11">
-        <f t="shared" si="296"/>
+        <f t="shared" si="292"/>
         <v>0.24286823712140815</v>
       </c>
       <c r="AM30" s="11">
-        <f t="shared" si="296"/>
+        <f t="shared" si="292"/>
         <v>0.56173456635841035</v>
       </c>
       <c r="AN30" s="11">
-        <f t="shared" si="296"/>
+        <f t="shared" si="292"/>
         <v>0.14440799125123371</v>
       </c>
       <c r="AO30" s="11">
-        <f t="shared" si="296"/>
+        <f t="shared" si="292"/>
         <v>0.52021908868430256</v>
       </c>
       <c r="AP30" s="11">
-        <f t="shared" si="296"/>
+        <f t="shared" si="292"/>
         <v>0.65962437715599842</v>
       </c>
       <c r="AQ30" s="11">
-        <f t="shared" ref="AQ30:AW30" si="297">AQ5/AP5-1</f>
+        <f t="shared" ref="AQ30:AW30" si="293">AQ5/AP5-1</f>
         <v>0.44581474193756976</v>
       </c>
       <c r="AR30" s="11">
-        <f t="shared" si="297"/>
+        <f t="shared" si="293"/>
         <v>9.2020855163953197E-2</v>
       </c>
       <c r="AS30" s="11">
-        <f t="shared" si="297"/>
+        <f t="shared" si="293"/>
         <v>6.9539523725937524E-2</v>
       </c>
       <c r="AT30" s="11">
-        <f t="shared" si="297"/>
+        <f t="shared" si="293"/>
         <v>0.27856341803659834</v>
       </c>
       <c r="AU30" s="11">
-        <f t="shared" si="297"/>
+        <f t="shared" si="293"/>
         <v>-7.7342061913013738E-2</v>
       </c>
       <c r="AV30" s="11">
-        <f t="shared" si="297"/>
+        <f t="shared" si="293"/>
         <v>6.304518199398057E-2</v>
       </c>
       <c r="AW30" s="11">
-        <f t="shared" si="297"/>
+        <f t="shared" si="293"/>
         <v>0.15861957650261305</v>
       </c>
       <c r="AX30" s="11">
@@ -7792,68 +7771,68 @@
         <v>-2.04107758052674E-2</v>
       </c>
       <c r="AY30" s="11">
-        <f t="shared" ref="AY30:BL30" si="298">AY5/AX5-1</f>
+        <f t="shared" ref="AY30:BL30" si="294">AY5/AX5-1</f>
         <v>5.5120803769784787E-2</v>
       </c>
       <c r="AZ30" s="11">
-        <f t="shared" si="298"/>
+        <f t="shared" si="294"/>
         <v>0.33259384733074704</v>
       </c>
       <c r="BA30" s="11">
-        <f t="shared" si="298"/>
+        <f t="shared" si="294"/>
         <v>7.7937876041846099E-2</v>
       </c>
       <c r="BB30" s="11">
-        <f t="shared" si="298"/>
+        <f t="shared" si="294"/>
         <v>-2.800460530319937E-2</v>
       </c>
       <c r="BC30" s="11">
-        <f t="shared" si="298"/>
+        <f t="shared" si="294"/>
         <v>2.021994077514111E-2</v>
       </c>
       <c r="BD30" s="11">
-        <f t="shared" si="298"/>
-        <v>4.4405743731379621E-2</v>
+        <f t="shared" si="294"/>
+        <v>5.7375068727863132E-2</v>
       </c>
       <c r="BE30" s="11">
-        <f t="shared" si="298"/>
-        <v>3.1072080454614071E-2</v>
+        <f t="shared" si="294"/>
+        <v>4.5690630140479804E-2</v>
       </c>
       <c r="BF30" s="11">
-        <f t="shared" si="298"/>
-        <v>2.6707295346462656E-2</v>
+        <f t="shared" si="294"/>
+        <v>3.3629578354056333E-2</v>
       </c>
       <c r="BG30" s="11">
-        <f t="shared" si="298"/>
-        <v>2.4509820294564832E-2</v>
+        <f t="shared" si="294"/>
+        <v>2.4109163615521956E-2</v>
       </c>
       <c r="BH30" s="11">
-        <f t="shared" si="298"/>
-        <v>2.2009965513315688E-2</v>
+        <f t="shared" si="294"/>
+        <v>2.1682905661856378E-2</v>
       </c>
       <c r="BI30" s="11">
-        <f t="shared" si="298"/>
-        <v>1.9254164010999553E-2</v>
+        <f t="shared" si="294"/>
+        <v>1.9005032929225507E-2</v>
       </c>
       <c r="BJ30" s="11">
-        <f t="shared" si="298"/>
-        <v>1.6295015127248069E-2</v>
+        <f t="shared" si="294"/>
+        <v>1.61270448092381E-2</v>
       </c>
       <c r="BK30" s="11">
-        <f t="shared" si="298"/>
-        <v>1.6379904933661038E-2</v>
+        <f t="shared" si="294"/>
+        <v>1.6210695981130785E-2</v>
       </c>
       <c r="BL30" s="11">
-        <f t="shared" si="298"/>
-        <v>1.3232699726634101E-2</v>
+        <f t="shared" si="294"/>
+        <v>1.6294970999482183E-2</v>
       </c>
       <c r="BM30" s="11">
-        <f t="shared" si="290"/>
-        <v>1.3254290669908464E-2</v>
+        <f t="shared" si="286"/>
+        <v>1.6379860487836462E-2</v>
       </c>
       <c r="BN30" s="11">
-        <f t="shared" si="291"/>
-        <v>1.3275956010126766E-2</v>
+        <f t="shared" si="287"/>
+        <v>1.6465354694570333E-2</v>
       </c>
       <c r="BP30" t="s">
         <v>44</v>
@@ -7868,7 +7847,7 @@
       </c>
       <c r="BQ31" s="3">
         <f>NPV(BQ30,BD17:FW17)</f>
-        <v>2527104.2880269065</v>
+        <v>2610911.3716823566</v>
       </c>
     </row>
     <row r="32" spans="2:179" x14ac:dyDescent="0.3">
@@ -7880,252 +7859,252 @@
         <v>0.25767665556788755</v>
       </c>
       <c r="D32" s="10">
-        <f t="shared" ref="D32:M32" si="299">D16/D15</f>
+        <f t="shared" ref="D32:M32" si="295">D16/D15</f>
         <v>0.14510143493320138</v>
       </c>
       <c r="E32" s="10">
+        <f t="shared" si="295"/>
+        <v>0.13286660644384221</v>
+      </c>
+      <c r="F32" s="10">
+        <f t="shared" si="295"/>
+        <v>0.13982096096461846</v>
+      </c>
+      <c r="G32" s="10">
+        <f t="shared" si="295"/>
+        <v>0.16485401154521878</v>
+      </c>
+      <c r="H32" s="10">
+        <f t="shared" si="295"/>
+        <v>0.16182121365910243</v>
+      </c>
+      <c r="I32" s="10">
+        <f t="shared" si="295"/>
+        <v>0.15674586516665268</v>
+      </c>
+      <c r="J32" s="10">
+        <f t="shared" si="295"/>
+        <v>0.15136107149500838</v>
+      </c>
+      <c r="K32" s="10">
+        <f t="shared" si="295"/>
+        <v>0.14206343082027933</v>
+      </c>
+      <c r="L32" s="10">
+        <f t="shared" si="295"/>
+        <v>0.14358583936048724</v>
+      </c>
+      <c r="M32" s="10">
+        <f t="shared" si="295"/>
+        <v>0.14341173783968944</v>
+      </c>
+      <c r="N32" s="10">
+        <f t="shared" ref="N32:BI32" si="296">N16/N15</f>
+        <v>0.14952016643178309</v>
+      </c>
+      <c r="O32" s="10">
+        <f t="shared" ref="O32:S32" si="297">O16/O15</f>
+        <v>0.14366121683194855</v>
+      </c>
+      <c r="P32" s="10">
+        <f t="shared" si="297"/>
+        <v>0.1564028417407447</v>
+      </c>
+      <c r="Q32" s="10">
+        <f t="shared" ref="Q32:R32" si="298">Q16/Q15</f>
+        <v>0.10771882309491568</v>
+      </c>
+      <c r="R32" s="10">
+        <f t="shared" si="298"/>
+        <v>0.11600997935306263</v>
+      </c>
+      <c r="S32" s="10">
+        <f t="shared" si="297"/>
+        <v>0.16030164157028201</v>
+      </c>
+      <c r="T32" s="10">
+        <f t="shared" ref="T32:U32" si="299">T16/T15</f>
+        <v>0.17017817445834302</v>
+      </c>
+      <c r="U32" s="10">
         <f t="shared" si="299"/>
-        <v>0.13286660644384221</v>
-      </c>
-      <c r="F32" s="10">
-        <f t="shared" si="299"/>
-        <v>0.13982096096461846</v>
-      </c>
-      <c r="G32" s="10">
-        <f t="shared" si="299"/>
-        <v>0.16485401154521878</v>
-      </c>
-      <c r="H32" s="10">
-        <f t="shared" si="299"/>
-        <v>0.16182121365910243</v>
-      </c>
-      <c r="I32" s="10">
-        <f t="shared" si="299"/>
-        <v>0.15674586516665268</v>
-      </c>
-      <c r="J32" s="10">
-        <f t="shared" si="299"/>
-        <v>0.15136107149500838</v>
-      </c>
-      <c r="K32" s="10">
-        <f t="shared" si="299"/>
-        <v>0.14206343082027933</v>
-      </c>
-      <c r="L32" s="10">
-        <f t="shared" si="299"/>
-        <v>0.14358583936048724</v>
-      </c>
-      <c r="M32" s="10">
-        <f t="shared" si="299"/>
-        <v>0.14341173783968944</v>
-      </c>
-      <c r="N32" s="10">
-        <f t="shared" ref="N32:BI32" si="300">N16/N15</f>
-        <v>0.14952016643178309</v>
-      </c>
-      <c r="O32" s="10">
-        <f t="shared" ref="O32:S32" si="301">O16/O15</f>
-        <v>0.14366121683194855</v>
-      </c>
-      <c r="P32" s="10">
+        <v>0.15711436746726784</v>
+      </c>
+      <c r="V32" s="10">
+        <f t="shared" ref="V32" si="300">V16/V15</f>
+        <v>0.15963012531938192</v>
+      </c>
+      <c r="W32" s="10">
+        <f t="shared" ref="W32:X32" si="301">W16/W15</f>
+        <v>0.15790360160570419</v>
+      </c>
+      <c r="X32" s="10">
         <f t="shared" si="301"/>
-        <v>0.1564028417407447</v>
-      </c>
-      <c r="Q32" s="10">
-        <f t="shared" ref="Q32:R32" si="302">Q16/Q15</f>
-        <v>0.10771882309491568</v>
-      </c>
-      <c r="R32" s="10">
+        <v>0.14875625396377987</v>
+      </c>
+      <c r="Y32" s="10">
+        <f t="shared" ref="Y32:Z32" si="302">Y16/Y15</f>
+        <v>0.12545638499098227</v>
+      </c>
+      <c r="Z32" s="10">
         <f t="shared" si="302"/>
-        <v>0.11600997935306263</v>
-      </c>
-      <c r="S32" s="10">
-        <f t="shared" si="301"/>
-        <v>0.16030164157028201</v>
-      </c>
-      <c r="T32" s="10">
-        <f t="shared" ref="T32:U32" si="303">T16/T15</f>
-        <v>0.17017817445834302</v>
-      </c>
-      <c r="U32" s="10">
+        <v>0.14971479368842136</v>
+      </c>
+      <c r="AA32" s="10">
+        <f t="shared" ref="AA32:AD32" si="303">AA16/AA15</f>
+        <v>0.15889194752374575</v>
+      </c>
+      <c r="AB32" s="10">
         <f t="shared" si="303"/>
-        <v>0.15711436746726784</v>
-      </c>
-      <c r="V32" s="10">
-        <f t="shared" ref="V32" si="304">V16/V15</f>
-        <v>0.15963012531938192</v>
-      </c>
-      <c r="W32" s="10">
-        <f t="shared" ref="W32:X32" si="305">W16/W15</f>
-        <v>0.15790360160570419</v>
-      </c>
-      <c r="X32" s="10">
+        <v>0.1576021099151757</v>
+      </c>
+      <c r="AC32" s="10">
+        <f t="shared" si="303"/>
+        <v>0.15870400878638111</v>
+      </c>
+      <c r="AD32" s="10">
+        <f t="shared" si="303"/>
+        <v>0.50233029381965555</v>
+      </c>
+      <c r="AE32" s="10">
+        <f t="shared" ref="AE32:AH32" si="304">AE16/AE15</f>
+        <v>0.14686267142588766</v>
+      </c>
+      <c r="AF32" s="10">
+        <f t="shared" si="304"/>
+        <v>0.15455475946775846</v>
+      </c>
+      <c r="AG32" s="10">
+        <f t="shared" si="304"/>
+        <v>0.16399700331775535</v>
+      </c>
+      <c r="AH32" s="10">
+        <f t="shared" si="304"/>
+        <v>0.16</v>
+      </c>
+      <c r="AI32" s="10"/>
+      <c r="AJ32" s="10">
+        <f t="shared" ref="AJ32:AP32" si="305">AJ16/AJ15</f>
+        <v>0.26548672566371684</v>
+      </c>
+      <c r="AK32" s="10">
         <f t="shared" si="305"/>
-        <v>0.14875625396377987</v>
-      </c>
-      <c r="Y32" s="10">
-        <f t="shared" ref="Y32:Z32" si="306">Y16/Y15</f>
-        <v>0.12545638499098227</v>
-      </c>
-      <c r="Z32" s="10">
+        <v>0.29418026969481903</v>
+      </c>
+      <c r="AL32" s="10">
+        <f t="shared" si="305"/>
+        <v>0.30191693290734822</v>
+      </c>
+      <c r="AM32" s="10">
+        <f t="shared" si="305"/>
+        <v>0.3160836034424947</v>
+      </c>
+      <c r="AN32" s="10">
+        <f t="shared" si="305"/>
+        <v>0.31750372948781702</v>
+      </c>
+      <c r="AO32" s="10">
+        <f t="shared" si="305"/>
+        <v>0.24417475728155341</v>
+      </c>
+      <c r="AP32" s="10">
+        <f t="shared" si="305"/>
+        <v>0.24215757930127174</v>
+      </c>
+      <c r="AQ32" s="10">
+        <f t="shared" si="296"/>
+        <v>0.25160052364471064</v>
+      </c>
+      <c r="AR32" s="10">
+        <f t="shared" si="296"/>
+        <v>0.26154919748778788</v>
+      </c>
+      <c r="AS32" s="10">
+        <f t="shared" si="296"/>
+        <v>0.26126058747639436</v>
+      </c>
+      <c r="AT32" s="10">
+        <f t="shared" si="296"/>
+        <v>0.26368337585327173</v>
+      </c>
+      <c r="AU32" s="10">
+        <f t="shared" si="296"/>
+        <v>0.25557257381216192</v>
+      </c>
+      <c r="AV32" s="10">
+        <f t="shared" si="296"/>
+        <v>0.24556476150353415</v>
+      </c>
+      <c r="AW32" s="10">
+        <f t="shared" si="296"/>
+        <v>0.18342180705869443</v>
+      </c>
+      <c r="AX32" s="10">
+        <f t="shared" si="296"/>
+        <v>0.15943836804235059</v>
+      </c>
+      <c r="AY32" s="10">
+        <f t="shared" si="296"/>
+        <v>0.14428164731484103</v>
+      </c>
+      <c r="AZ32" s="10">
+        <f t="shared" si="296"/>
+        <v>0.13302260844085087</v>
+      </c>
+      <c r="BA32" s="10">
+        <f t="shared" ref="BA32:BB32" si="306">BA16/BA15</f>
+        <v>0.16204461684424407</v>
+      </c>
+      <c r="BB32" s="10">
         <f t="shared" si="306"/>
-        <v>0.14971479368842136</v>
-      </c>
-      <c r="AA32" s="10">
-        <f t="shared" ref="AA32:AD32" si="307">AA16/AA15</f>
-        <v>0.15889194752374575</v>
-      </c>
-      <c r="AB32" s="10">
-        <f t="shared" si="307"/>
-        <v>0.1576021099151757</v>
-      </c>
-      <c r="AC32" s="10">
-        <f t="shared" si="307"/>
-        <v>0.15870400878638111</v>
-      </c>
-      <c r="AD32" s="10">
-        <f t="shared" si="307"/>
-        <v>0.50233029381965555</v>
-      </c>
-      <c r="AE32" s="10">
-        <f t="shared" ref="AE32:AH32" si="308">AE16/AE15</f>
-        <v>0.14686267142588766</v>
-      </c>
-      <c r="AF32" s="10">
-        <f t="shared" si="308"/>
-        <v>0.15455475946775846</v>
-      </c>
-      <c r="AG32" s="10">
+        <v>0.14719174228036858</v>
+      </c>
+      <c r="BC32" s="10">
+        <f t="shared" ref="BC32" si="307">BC16/BC15</f>
+        <v>0.24091185164189982</v>
+      </c>
+      <c r="BD32" s="10">
+        <f t="shared" si="296"/>
+        <v>0.15531672066806645</v>
+      </c>
+      <c r="BE32" s="10">
+        <f t="shared" si="296"/>
+        <v>0.16</v>
+      </c>
+      <c r="BF32" s="10">
+        <f t="shared" si="296"/>
+        <v>0.16</v>
+      </c>
+      <c r="BG32" s="10">
+        <f t="shared" si="296"/>
+        <v>0.16</v>
+      </c>
+      <c r="BH32" s="10">
+        <f t="shared" si="296"/>
+        <v>0.16</v>
+      </c>
+      <c r="BI32" s="10">
+        <f t="shared" si="296"/>
+        <v>0.16</v>
+      </c>
+      <c r="BJ32" s="10">
+        <f t="shared" ref="BJ32:BL32" si="308">BJ16/BJ15</f>
+        <v>0.16</v>
+      </c>
+      <c r="BK32" s="10">
         <f t="shared" si="308"/>
         <v>0.16</v>
       </c>
-      <c r="AH32" s="10">
+      <c r="BL32" s="10">
         <f t="shared" si="308"/>
         <v>0.16</v>
       </c>
-      <c r="AI32" s="10"/>
-      <c r="AJ32" s="10">
-        <f t="shared" ref="AJ32:AP32" si="309">AJ16/AJ15</f>
-        <v>0.26548672566371684</v>
-      </c>
-      <c r="AK32" s="10">
+      <c r="BM32" s="10">
+        <f t="shared" ref="BM32:BN32" si="309">BM16/BM15</f>
+        <v>0.16</v>
+      </c>
+      <c r="BN32" s="10">
         <f t="shared" si="309"/>
-        <v>0.29418026969481903</v>
-      </c>
-      <c r="AL32" s="10">
-        <f t="shared" si="309"/>
-        <v>0.30191693290734822</v>
-      </c>
-      <c r="AM32" s="10">
-        <f t="shared" si="309"/>
-        <v>0.3160836034424947</v>
-      </c>
-      <c r="AN32" s="10">
-        <f t="shared" si="309"/>
-        <v>0.31750372948781702</v>
-      </c>
-      <c r="AO32" s="10">
-        <f t="shared" si="309"/>
-        <v>0.24417475728155341</v>
-      </c>
-      <c r="AP32" s="10">
-        <f t="shared" si="309"/>
-        <v>0.24215757930127174</v>
-      </c>
-      <c r="AQ32" s="10">
-        <f t="shared" si="300"/>
-        <v>0.25160052364471064</v>
-      </c>
-      <c r="AR32" s="10">
-        <f t="shared" si="300"/>
-        <v>0.26154919748778788</v>
-      </c>
-      <c r="AS32" s="10">
-        <f t="shared" si="300"/>
-        <v>0.26126058747639436</v>
-      </c>
-      <c r="AT32" s="10">
-        <f t="shared" si="300"/>
-        <v>0.26368337585327173</v>
-      </c>
-      <c r="AU32" s="10">
-        <f t="shared" si="300"/>
-        <v>0.25557257381216192</v>
-      </c>
-      <c r="AV32" s="10">
-        <f t="shared" si="300"/>
-        <v>0.24556476150353415</v>
-      </c>
-      <c r="AW32" s="10">
-        <f t="shared" si="300"/>
-        <v>0.18342180705869443</v>
-      </c>
-      <c r="AX32" s="10">
-        <f t="shared" si="300"/>
-        <v>0.15943836804235059</v>
-      </c>
-      <c r="AY32" s="10">
-        <f t="shared" si="300"/>
-        <v>0.14428164731484103</v>
-      </c>
-      <c r="AZ32" s="10">
-        <f t="shared" si="300"/>
-        <v>0.13302260844085087</v>
-      </c>
-      <c r="BA32" s="10">
-        <f t="shared" ref="BA32:BB32" si="310">BA16/BA15</f>
-        <v>0.16204461684424407</v>
-      </c>
-      <c r="BB32" s="10">
-        <f t="shared" si="310"/>
-        <v>0.14719174228036858</v>
-      </c>
-      <c r="BC32" s="10">
-        <f t="shared" ref="BC32" si="311">BC16/BC15</f>
-        <v>0.24091185164189982</v>
-      </c>
-      <c r="BD32" s="10">
-        <f t="shared" si="300"/>
-        <v>0.15442564488150221</v>
-      </c>
-      <c r="BE32" s="10">
-        <f t="shared" si="300"/>
-        <v>0.16</v>
-      </c>
-      <c r="BF32" s="10">
-        <f t="shared" si="300"/>
-        <v>0.16</v>
-      </c>
-      <c r="BG32" s="10">
-        <f t="shared" si="300"/>
-        <v>0.16</v>
-      </c>
-      <c r="BH32" s="10">
-        <f t="shared" si="300"/>
-        <v>0.16</v>
-      </c>
-      <c r="BI32" s="10">
-        <f t="shared" si="300"/>
-        <v>0.16</v>
-      </c>
-      <c r="BJ32" s="10">
-        <f t="shared" ref="BJ32:BL32" si="312">BJ16/BJ15</f>
-        <v>0.16</v>
-      </c>
-      <c r="BK32" s="10">
-        <f t="shared" si="312"/>
-        <v>0.16</v>
-      </c>
-      <c r="BL32" s="10">
-        <f t="shared" si="312"/>
-        <v>0.16</v>
-      </c>
-      <c r="BM32" s="10">
-        <f t="shared" ref="BM32:BN32" si="313">BM16/BM15</f>
-        <v>0.16</v>
-      </c>
-      <c r="BN32" s="10">
-        <f t="shared" si="313"/>
         <v>0.16</v>
       </c>
       <c r="BP32" t="s">
@@ -8133,7 +8112,7 @@
       </c>
       <c r="BQ32" s="3">
         <f>Main!D8</f>
-        <v>34736</v>
+        <v>31288</v>
       </c>
     </row>
     <row r="33" spans="2:69" x14ac:dyDescent="0.3">
@@ -8142,7 +8121,7 @@
       </c>
       <c r="BQ33" s="3">
         <f>BQ31+BQ32</f>
-        <v>2561840.2880269065</v>
+        <v>2642199.3716823566</v>
       </c>
     </row>
     <row r="34" spans="2:69" x14ac:dyDescent="0.3">
@@ -8151,7 +8130,7 @@
       </c>
       <c r="BQ34" s="12">
         <f>BQ33/BI18</f>
-        <v>171.52347299956526</v>
+        <v>177.2943099452024</v>
       </c>
     </row>
     <row r="35" spans="2:69" x14ac:dyDescent="0.3">
@@ -8163,7 +8142,7 @@
       </c>
       <c r="BQ35" s="12">
         <f>Main!D3</f>
-        <v>198.81</v>
+        <v>231.02</v>
       </c>
     </row>
     <row r="36" spans="2:69" x14ac:dyDescent="0.3">
@@ -8173,7 +8152,7 @@
       </c>
       <c r="BQ36" s="11">
         <f>BQ34/BQ35-1</f>
-        <v>-0.13724926814765226</v>
+        <v>-0.23255860988138521</v>
       </c>
     </row>
     <row r="37" spans="2:69" x14ac:dyDescent="0.3">
@@ -8868,71 +8847,71 @@
         <v>94</v>
       </c>
       <c r="AJ60" s="9">
-        <f t="shared" ref="AJ60" si="314">AJ17</f>
+        <f t="shared" ref="AJ60" si="310">AJ17</f>
         <v>1328</v>
       </c>
       <c r="AK60" s="9">
-        <f t="shared" ref="AK60:AL60" si="315">AK17</f>
+        <f t="shared" ref="AK60:AL60" si="311">AK17</f>
         <v>1989</v>
       </c>
       <c r="AL60" s="9">
+        <f t="shared" si="311"/>
+        <v>3496</v>
+      </c>
+      <c r="AM60" s="9">
+        <f t="shared" ref="AM60:AN60" si="312">AM17</f>
+        <v>6119</v>
+      </c>
+      <c r="AN60" s="9">
+        <f t="shared" si="312"/>
+        <v>8235</v>
+      </c>
+      <c r="AO60" s="9">
+        <f t="shared" ref="AO60:AP60" si="313">AO17</f>
+        <v>14013</v>
+      </c>
+      <c r="AP60" s="9">
+        <f t="shared" si="313"/>
+        <v>25922</v>
+      </c>
+      <c r="AQ60" s="9">
+        <f t="shared" ref="AQ60:AW60" si="314">AQ17</f>
+        <v>41733</v>
+      </c>
+      <c r="AR60" s="9">
+        <f t="shared" si="314"/>
+        <v>37037</v>
+      </c>
+      <c r="AS60" s="9">
+        <f t="shared" si="314"/>
+        <v>39510</v>
+      </c>
+      <c r="AT60" s="9">
+        <f t="shared" si="314"/>
+        <v>53394</v>
+      </c>
+      <c r="AU60" s="9">
+        <f t="shared" si="314"/>
+        <v>45687</v>
+      </c>
+      <c r="AV60" s="9">
+        <f t="shared" si="314"/>
+        <v>48351</v>
+      </c>
+      <c r="AW60" s="9">
+        <f t="shared" si="314"/>
+        <v>59531</v>
+      </c>
+      <c r="AX60" s="9">
+        <f t="shared" ref="AX60:AZ60" si="315">AX17</f>
+        <v>55256</v>
+      </c>
+      <c r="AY60" s="9">
         <f t="shared" si="315"/>
-        <v>3496</v>
-      </c>
-      <c r="AM60" s="9">
-        <f t="shared" ref="AM60:AN60" si="316">AM17</f>
-        <v>6119</v>
-      </c>
-      <c r="AN60" s="9">
-        <f t="shared" si="316"/>
-        <v>8235</v>
-      </c>
-      <c r="AO60" s="9">
-        <f t="shared" ref="AO60:AP60" si="317">AO17</f>
-        <v>14013</v>
-      </c>
-      <c r="AP60" s="9">
-        <f t="shared" si="317"/>
-        <v>25922</v>
-      </c>
-      <c r="AQ60" s="9">
-        <f t="shared" ref="AQ60:AW60" si="318">AQ17</f>
-        <v>41733</v>
-      </c>
-      <c r="AR60" s="9">
-        <f t="shared" si="318"/>
-        <v>37037</v>
-      </c>
-      <c r="AS60" s="9">
-        <f t="shared" si="318"/>
-        <v>39510</v>
-      </c>
-      <c r="AT60" s="9">
-        <f t="shared" si="318"/>
-        <v>53394</v>
-      </c>
-      <c r="AU60" s="9">
-        <f t="shared" si="318"/>
-        <v>45687</v>
-      </c>
-      <c r="AV60" s="9">
-        <f t="shared" si="318"/>
-        <v>48351</v>
-      </c>
-      <c r="AW60" s="9">
-        <f t="shared" si="318"/>
-        <v>59531</v>
-      </c>
-      <c r="AX60" s="9">
-        <f t="shared" ref="AX60:AZ60" si="319">AX17</f>
-        <v>55256</v>
-      </c>
-      <c r="AY60" s="9">
-        <f t="shared" si="319"/>
         <v>57411</v>
       </c>
       <c r="AZ60" s="9">
-        <f t="shared" si="319"/>
+        <f t="shared" si="315"/>
         <v>94680</v>
       </c>
       <c r="BA60" s="9">
@@ -8948,48 +8927,48 @@
         <v>93736</v>
       </c>
       <c r="BD60" s="9">
-        <f t="shared" ref="BD60:BN60" si="320">BD17</f>
-        <v>109071.23270399999</v>
+        <f t="shared" ref="BD60:BN60" si="316">BD17</f>
+        <v>109479.42973599996</v>
       </c>
       <c r="BE60" s="9">
-        <f t="shared" si="320"/>
-        <v>111609.40499560322</v>
+        <f t="shared" si="316"/>
+        <v>113395.81010126883</v>
       </c>
       <c r="BF60" s="9">
-        <f t="shared" si="320"/>
-        <v>116111.91671326966</v>
+        <f t="shared" si="316"/>
+        <v>118813.40451403386</v>
       </c>
       <c r="BG60" s="9">
-        <f t="shared" si="320"/>
-        <v>120425.82935936152</v>
+        <f t="shared" si="316"/>
+        <v>123138.95805643471</v>
       </c>
       <c r="BH60" s="9">
-        <f t="shared" si="320"/>
-        <v>124152.37790746201</v>
+        <f t="shared" si="316"/>
+        <v>126877.030812457</v>
       </c>
       <c r="BI60" s="9">
-        <f t="shared" si="320"/>
-        <v>127173.78616536272</v>
+        <f t="shared" si="316"/>
+        <v>129905.404568418</v>
       </c>
       <c r="BJ60" s="9">
-        <f t="shared" si="320"/>
-        <v>129712.57200662653</v>
+        <f t="shared" si="316"/>
+        <v>132461.63028191429</v>
       </c>
       <c r="BK60" s="9">
-        <f t="shared" si="320"/>
-        <v>132579.43215498835</v>
+        <f t="shared" si="316"/>
+        <v>135349.95387416281</v>
       </c>
       <c r="BL60" s="9">
-        <f t="shared" si="320"/>
-        <v>134540.71220523701</v>
+        <f t="shared" si="316"/>
+        <v>138316.44997199456</v>
       </c>
       <c r="BM60" s="9">
-        <f t="shared" si="320"/>
-        <v>136538.37047279236</v>
+        <f t="shared" si="316"/>
+        <v>141364.56817866082</v>
       </c>
       <c r="BN60" s="9">
-        <f t="shared" si="320"/>
-        <v>138569.03331198409</v>
+        <f t="shared" si="316"/>
+        <v>144496.74997982313</v>
       </c>
     </row>
     <row r="61" spans="2:66" x14ac:dyDescent="0.3">
@@ -9061,43 +9040,43 @@
         <v>11502.224999999999</v>
       </c>
       <c r="BE61" s="3">
-        <f t="shared" ref="BE61:BN61" si="321">BD61*1.005</f>
+        <f t="shared" ref="BE61:BN61" si="317">BD61*1.005</f>
         <v>11559.736124999998</v>
       </c>
       <c r="BF61" s="3">
-        <f t="shared" si="321"/>
+        <f t="shared" si="317"/>
         <v>11617.534805624997</v>
       </c>
       <c r="BG61" s="3">
-        <f t="shared" si="321"/>
+        <f t="shared" si="317"/>
         <v>11675.622479653121</v>
       </c>
       <c r="BH61" s="3">
-        <f t="shared" si="321"/>
+        <f t="shared" si="317"/>
         <v>11734.000592051385</v>
       </c>
       <c r="BI61" s="3">
-        <f t="shared" si="321"/>
+        <f t="shared" si="317"/>
         <v>11792.670595011641</v>
       </c>
       <c r="BJ61" s="3">
-        <f t="shared" si="321"/>
+        <f t="shared" si="317"/>
         <v>11851.633947986698</v>
       </c>
       <c r="BK61" s="3">
-        <f t="shared" si="321"/>
+        <f t="shared" si="317"/>
         <v>11910.892117726631</v>
       </c>
       <c r="BL61" s="3">
-        <f t="shared" si="321"/>
+        <f t="shared" si="317"/>
         <v>11970.446578315263</v>
       </c>
       <c r="BM61" s="3">
-        <f t="shared" si="321"/>
+        <f t="shared" si="317"/>
         <v>12030.298811206838</v>
       </c>
       <c r="BN61" s="3">
-        <f t="shared" si="321"/>
+        <f t="shared" si="317"/>
         <v>12090.450305262872</v>
       </c>
     </row>
@@ -9170,43 +9149,43 @@
         <v>11804.88</v>
       </c>
       <c r="BE62" s="3">
-        <f t="shared" ref="BE62:BN62" si="322">BD62*1.01</f>
+        <f t="shared" ref="BE62:BN62" si="318">BD62*1.01</f>
         <v>11922.9288</v>
       </c>
       <c r="BF62" s="3">
-        <f t="shared" si="322"/>
+        <f t="shared" si="318"/>
         <v>12042.158088</v>
       </c>
       <c r="BG62" s="3">
-        <f t="shared" si="322"/>
+        <f t="shared" si="318"/>
         <v>12162.57966888</v>
       </c>
       <c r="BH62" s="3">
-        <f t="shared" si="322"/>
+        <f t="shared" si="318"/>
         <v>12284.205465568801</v>
       </c>
       <c r="BI62" s="3">
-        <f t="shared" si="322"/>
+        <f t="shared" si="318"/>
         <v>12407.047520224489</v>
       </c>
       <c r="BJ62" s="3">
-        <f t="shared" si="322"/>
+        <f t="shared" si="318"/>
         <v>12531.117995426734</v>
       </c>
       <c r="BK62" s="3">
-        <f t="shared" si="322"/>
+        <f t="shared" si="318"/>
         <v>12656.429175381001</v>
       </c>
       <c r="BL62" s="3">
-        <f t="shared" si="322"/>
+        <f t="shared" si="318"/>
         <v>12782.993467134811</v>
       </c>
       <c r="BM62" s="3">
-        <f t="shared" si="322"/>
+        <f t="shared" si="318"/>
         <v>12910.823401806159</v>
       </c>
       <c r="BN62" s="3">
-        <f t="shared" si="322"/>
+        <f t="shared" si="318"/>
         <v>13039.931635824221</v>
       </c>
     </row>
@@ -9997,128 +9976,128 @@
         <v>101</v>
       </c>
       <c r="AJ71" s="9">
-        <f t="shared" ref="AJ71:AQ71" si="323">AJ60+SUM(AJ61:AJ70)</f>
+        <f t="shared" ref="AJ71:AQ71" si="319">AJ60+SUM(AJ61:AJ70)</f>
         <v>2535</v>
       </c>
       <c r="AK71" s="9">
-        <f t="shared" si="323"/>
+        <f t="shared" si="319"/>
         <v>2220</v>
       </c>
       <c r="AL71" s="9">
-        <f t="shared" si="323"/>
+        <f t="shared" si="319"/>
         <v>5470</v>
       </c>
       <c r="AM71" s="9">
-        <f t="shared" si="323"/>
+        <f t="shared" si="319"/>
         <v>9596</v>
       </c>
       <c r="AN71" s="9">
-        <f t="shared" si="323"/>
+        <f t="shared" si="319"/>
         <v>10159</v>
       </c>
       <c r="AO71" s="9">
-        <f t="shared" si="323"/>
+        <f t="shared" si="319"/>
         <v>18595</v>
       </c>
       <c r="AP71" s="9">
-        <f t="shared" si="323"/>
+        <f t="shared" si="319"/>
         <v>37529</v>
       </c>
       <c r="AQ71" s="9">
-        <f t="shared" si="323"/>
+        <f t="shared" si="319"/>
         <v>50856</v>
       </c>
       <c r="AR71" s="9">
-        <f t="shared" ref="AR71:AW71" si="324">AR60+SUM(AR61:AR70)</f>
+        <f t="shared" ref="AR71:AW71" si="320">AR60+SUM(AR61:AR70)</f>
         <v>53666</v>
       </c>
       <c r="AS71" s="9">
-        <f t="shared" si="324"/>
+        <f t="shared" si="320"/>
         <v>59713</v>
       </c>
       <c r="AT71" s="9">
-        <f t="shared" si="324"/>
+        <f t="shared" si="320"/>
         <v>81266</v>
       </c>
       <c r="AU71" s="9">
-        <f t="shared" si="324"/>
+        <f t="shared" si="320"/>
         <v>65824</v>
       </c>
       <c r="AV71" s="9">
-        <f t="shared" si="324"/>
+        <f t="shared" si="320"/>
         <v>64225</v>
       </c>
       <c r="AW71" s="9">
-        <f t="shared" si="324"/>
+        <f t="shared" si="320"/>
         <v>77434</v>
       </c>
       <c r="AX71" s="9">
-        <f t="shared" ref="AX71:BD71" si="325">AX60+SUM(AX61:AX70)</f>
+        <f t="shared" ref="AX71:BD71" si="321">AX60+SUM(AX61:AX70)</f>
         <v>69391</v>
       </c>
       <c r="AY71" s="9">
-        <f t="shared" si="325"/>
+        <f t="shared" si="321"/>
         <v>80674</v>
       </c>
       <c r="AZ71" s="9">
-        <f t="shared" si="325"/>
+        <f t="shared" si="321"/>
         <v>104038</v>
       </c>
       <c r="BA71" s="9">
-        <f t="shared" si="325"/>
+        <f t="shared" si="321"/>
         <v>122151</v>
       </c>
       <c r="BB71" s="9">
-        <f t="shared" si="325"/>
+        <f t="shared" si="321"/>
         <v>110543</v>
       </c>
       <c r="BC71" s="9">
-        <f t="shared" si="325"/>
+        <f t="shared" si="321"/>
         <v>118254</v>
       </c>
       <c r="BD71" s="9">
-        <f t="shared" si="325"/>
-        <v>132378.33770400001</v>
+        <f t="shared" si="321"/>
+        <v>132786.53473599994</v>
       </c>
       <c r="BE71" s="9">
-        <f t="shared" ref="BE71:BN71" si="326">BE60+SUM(BE61:BE70)</f>
-        <v>135092.06992060321</v>
+        <f t="shared" ref="BE71:BN71" si="322">BE60+SUM(BE61:BE70)</f>
+        <v>136878.47502626883</v>
       </c>
       <c r="BF71" s="9">
-        <f t="shared" si="326"/>
-        <v>139771.60960689466</v>
+        <f t="shared" si="322"/>
+        <v>142473.09740765885</v>
       </c>
       <c r="BG71" s="9">
-        <f t="shared" si="326"/>
-        <v>144264.03150789463</v>
+        <f t="shared" si="322"/>
+        <v>146977.16020496783</v>
       </c>
       <c r="BH71" s="9">
-        <f t="shared" si="326"/>
-        <v>148170.58396508219</v>
+        <f t="shared" si="322"/>
+        <v>150895.23687007718</v>
       </c>
       <c r="BI71" s="9">
-        <f t="shared" si="326"/>
-        <v>151373.50428059883</v>
+        <f t="shared" si="322"/>
+        <v>154105.12268365413</v>
       </c>
       <c r="BJ71" s="9">
-        <f t="shared" si="326"/>
-        <v>154095.32395003998</v>
+        <f t="shared" si="322"/>
+        <v>156844.38222532772</v>
       </c>
       <c r="BK71" s="9">
-        <f t="shared" si="326"/>
-        <v>157146.75344809599</v>
+        <f t="shared" si="322"/>
+        <v>159917.27516727045</v>
       </c>
       <c r="BL71" s="9">
-        <f t="shared" si="326"/>
-        <v>159294.15225068707</v>
+        <f t="shared" si="322"/>
+        <v>163069.89001744462</v>
       </c>
       <c r="BM71" s="9">
-        <f t="shared" si="326"/>
-        <v>161479.49268580537</v>
+        <f t="shared" si="322"/>
+        <v>166305.69039167382</v>
       </c>
       <c r="BN71" s="9">
-        <f t="shared" si="326"/>
-        <v>163699.41525307117</v>
+        <f t="shared" si="322"/>
+        <v>169627.13192091021</v>
       </c>
     </row>
     <row r="72" spans="2:151" x14ac:dyDescent="0.3">
@@ -10224,504 +10203,504 @@
         <v>103</v>
       </c>
       <c r="AJ73" s="9">
-        <f t="shared" ref="AJ73:AW73" si="327">AJ71-AJ72</f>
+        <f t="shared" ref="AJ73:AW73" si="323">AJ71-AJ72</f>
         <v>2275</v>
       </c>
       <c r="AK73" s="9">
-        <f t="shared" si="327"/>
+        <f t="shared" si="323"/>
         <v>1563</v>
       </c>
       <c r="AL73" s="9">
-        <f t="shared" si="327"/>
+        <f t="shared" si="323"/>
         <v>4735</v>
       </c>
       <c r="AM73" s="9">
-        <f t="shared" si="327"/>
+        <f t="shared" si="323"/>
         <v>8505</v>
       </c>
       <c r="AN73" s="9">
-        <f t="shared" si="327"/>
+        <f t="shared" si="323"/>
         <v>9015</v>
       </c>
       <c r="AO73" s="9">
-        <f t="shared" si="327"/>
+        <f t="shared" si="323"/>
         <v>16590</v>
       </c>
       <c r="AP73" s="9">
-        <f t="shared" si="327"/>
+        <f t="shared" si="323"/>
         <v>33269</v>
       </c>
       <c r="AQ73" s="9">
-        <f t="shared" si="327"/>
+        <f t="shared" si="323"/>
         <v>42561</v>
       </c>
       <c r="AR73" s="9">
-        <f t="shared" si="327"/>
+        <f t="shared" si="323"/>
         <v>45501</v>
       </c>
       <c r="AS73" s="9">
-        <f t="shared" si="327"/>
+        <f t="shared" si="323"/>
         <v>50142</v>
       </c>
       <c r="AT73" s="9">
-        <f t="shared" si="327"/>
+        <f t="shared" si="323"/>
         <v>70019</v>
       </c>
       <c r="AU73" s="9">
-        <f t="shared" si="327"/>
+        <f t="shared" si="323"/>
         <v>53090</v>
       </c>
       <c r="AV73" s="9">
-        <f t="shared" si="327"/>
+        <f t="shared" si="323"/>
         <v>51774</v>
       </c>
       <c r="AW73" s="9">
-        <f t="shared" si="327"/>
+        <f t="shared" si="323"/>
         <v>64121</v>
       </c>
       <c r="AX73" s="9">
-        <f t="shared" ref="AX73:BD73" si="328">AX71-AX72</f>
+        <f t="shared" ref="AX73:BD73" si="324">AX71-AX72</f>
         <v>58896</v>
       </c>
       <c r="AY73" s="9">
-        <f t="shared" si="328"/>
+        <f t="shared" si="324"/>
         <v>73365</v>
       </c>
       <c r="AZ73" s="9">
-        <f t="shared" si="328"/>
+        <f t="shared" si="324"/>
         <v>92953</v>
       </c>
       <c r="BA73" s="9">
-        <f t="shared" si="328"/>
+        <f t="shared" si="324"/>
         <v>111443</v>
       </c>
       <c r="BB73" s="9">
-        <f t="shared" si="328"/>
+        <f t="shared" si="324"/>
         <v>99584</v>
       </c>
       <c r="BC73" s="9">
-        <f t="shared" si="328"/>
+        <f t="shared" si="324"/>
         <v>108807</v>
       </c>
       <c r="BD73" s="9">
-        <f t="shared" si="328"/>
-        <v>122378.33770400001</v>
+        <f t="shared" si="324"/>
+        <v>122786.53473599994</v>
       </c>
       <c r="BE73" s="9">
-        <f t="shared" ref="BE73:BN73" si="329">BE71-BE72</f>
-        <v>125092.06992060321</v>
+        <f t="shared" ref="BE73:BN73" si="325">BE71-BE72</f>
+        <v>126878.47502626883</v>
       </c>
       <c r="BF73" s="9">
-        <f t="shared" si="329"/>
-        <v>129771.60960689466</v>
+        <f t="shared" si="325"/>
+        <v>132473.09740765885</v>
       </c>
       <c r="BG73" s="9">
-        <f t="shared" si="329"/>
-        <v>134264.03150789463</v>
+        <f t="shared" si="325"/>
+        <v>136977.16020496783</v>
       </c>
       <c r="BH73" s="9">
-        <f t="shared" si="329"/>
-        <v>138170.58396508219</v>
+        <f t="shared" si="325"/>
+        <v>140895.23687007718</v>
       </c>
       <c r="BI73" s="9">
-        <f t="shared" si="329"/>
-        <v>141373.50428059883</v>
+        <f t="shared" si="325"/>
+        <v>144105.12268365413</v>
       </c>
       <c r="BJ73" s="9">
-        <f t="shared" si="329"/>
-        <v>144095.32395003998</v>
+        <f t="shared" si="325"/>
+        <v>146844.38222532772</v>
       </c>
       <c r="BK73" s="9">
-        <f t="shared" si="329"/>
-        <v>147146.75344809599</v>
+        <f t="shared" si="325"/>
+        <v>149917.27516727045</v>
       </c>
       <c r="BL73" s="9">
-        <f t="shared" si="329"/>
-        <v>149294.15225068707</v>
+        <f t="shared" si="325"/>
+        <v>153069.89001744462</v>
       </c>
       <c r="BM73" s="9">
-        <f t="shared" si="329"/>
-        <v>151479.49268580537</v>
+        <f t="shared" si="325"/>
+        <v>156305.69039167382</v>
       </c>
       <c r="BN73" s="9">
-        <f t="shared" si="329"/>
-        <v>153699.41525307117</v>
+        <f t="shared" si="325"/>
+        <v>159627.13192091021</v>
       </c>
       <c r="BO73" s="6">
         <f>BN73*(1+$BQ$29)</f>
-        <v>152162.42110054046</v>
+        <v>158030.8606017011</v>
       </c>
       <c r="BP73" s="6">
-        <f t="shared" ref="BP73:EA73" si="330">BO73*(1+$BQ$29)</f>
-        <v>150640.79688953506</v>
+        <f t="shared" ref="BP73:EA73" si="326">BO73*(1+$BQ$29)</f>
+        <v>156450.5519956841</v>
       </c>
       <c r="BQ73" s="6">
-        <f t="shared" si="330"/>
-        <v>149134.3889206397</v>
+        <f t="shared" si="326"/>
+        <v>154886.04647572726</v>
       </c>
       <c r="BR73" s="6">
-        <f t="shared" si="330"/>
-        <v>147643.04503143331</v>
+        <f t="shared" si="326"/>
+        <v>153337.18601096998</v>
       </c>
       <c r="BS73" s="6">
-        <f t="shared" si="330"/>
-        <v>146166.61458111898</v>
+        <f t="shared" si="326"/>
+        <v>151803.81415086027</v>
       </c>
       <c r="BT73" s="6">
-        <f t="shared" si="330"/>
-        <v>144704.9484353078</v>
+        <f t="shared" si="326"/>
+        <v>150285.77600935166</v>
       </c>
       <c r="BU73" s="6">
-        <f t="shared" si="330"/>
-        <v>143257.89895095472</v>
+        <f t="shared" si="326"/>
+        <v>148782.91824925813</v>
       </c>
       <c r="BV73" s="6">
-        <f t="shared" si="330"/>
-        <v>141825.31996144517</v>
+        <f t="shared" si="326"/>
+        <v>147295.08906676556</v>
       </c>
       <c r="BW73" s="6">
-        <f t="shared" si="330"/>
-        <v>140407.06676183073</v>
+        <f t="shared" si="326"/>
+        <v>145822.13817609791</v>
       </c>
       <c r="BX73" s="6">
-        <f t="shared" si="330"/>
-        <v>139002.99609421243</v>
+        <f t="shared" si="326"/>
+        <v>144363.91679433692</v>
       </c>
       <c r="BY73" s="6">
-        <f t="shared" si="330"/>
-        <v>137612.9661332703</v>
+        <f t="shared" si="326"/>
+        <v>142920.27762639357</v>
       </c>
       <c r="BZ73" s="6">
-        <f t="shared" si="330"/>
-        <v>136236.8364719376</v>
+        <f t="shared" si="326"/>
+        <v>141491.07485012963</v>
       </c>
       <c r="CA73" s="6">
-        <f t="shared" si="330"/>
-        <v>134874.46810721821</v>
+        <f t="shared" si="326"/>
+        <v>140076.16410162832</v>
       </c>
       <c r="CB73" s="6">
-        <f t="shared" si="330"/>
-        <v>133525.72342614603</v>
+        <f t="shared" si="326"/>
+        <v>138675.40246061204</v>
       </c>
       <c r="CC73" s="6">
-        <f t="shared" si="330"/>
-        <v>132190.46619188457</v>
+        <f t="shared" si="326"/>
+        <v>137288.64843600593</v>
       </c>
       <c r="CD73" s="6">
-        <f t="shared" si="330"/>
-        <v>130868.56152996572</v>
+        <f t="shared" si="326"/>
+        <v>135915.76195164587</v>
       </c>
       <c r="CE73" s="6">
-        <f t="shared" si="330"/>
-        <v>129559.87591466606</v>
+        <f t="shared" si="326"/>
+        <v>134556.60433212941</v>
       </c>
       <c r="CF73" s="6">
-        <f t="shared" si="330"/>
-        <v>128264.2771555194</v>
+        <f t="shared" si="326"/>
+        <v>133211.03828880811</v>
       </c>
       <c r="CG73" s="6">
-        <f t="shared" si="330"/>
-        <v>126981.63438396421</v>
+        <f t="shared" si="326"/>
+        <v>131878.92790592002</v>
       </c>
       <c r="CH73" s="6">
-        <f t="shared" si="330"/>
-        <v>125711.81804012456</v>
+        <f t="shared" si="326"/>
+        <v>130560.13862686082</v>
       </c>
       <c r="CI73" s="6">
-        <f t="shared" si="330"/>
-        <v>124454.69985972332</v>
+        <f t="shared" si="326"/>
+        <v>129254.53724059221</v>
       </c>
       <c r="CJ73" s="6">
-        <f t="shared" si="330"/>
-        <v>123210.15286112609</v>
+        <f t="shared" si="326"/>
+        <v>127961.99186818629</v>
       </c>
       <c r="CK73" s="6">
-        <f t="shared" si="330"/>
-        <v>121978.05133251482</v>
+        <f t="shared" si="326"/>
+        <v>126682.37194950442</v>
       </c>
       <c r="CL73" s="6">
-        <f t="shared" si="330"/>
-        <v>120758.27081918967</v>
+        <f t="shared" si="326"/>
+        <v>125415.54823000937</v>
       </c>
       <c r="CM73" s="6">
-        <f t="shared" si="330"/>
-        <v>119550.68811099777</v>
+        <f t="shared" si="326"/>
+        <v>124161.39274770928</v>
       </c>
       <c r="CN73" s="6">
-        <f t="shared" si="330"/>
-        <v>118355.18122988779</v>
+        <f t="shared" si="326"/>
+        <v>122919.77882023218</v>
       </c>
       <c r="CO73" s="6">
-        <f t="shared" si="330"/>
-        <v>117171.62941758892</v>
+        <f t="shared" si="326"/>
+        <v>121690.58103202986</v>
       </c>
       <c r="CP73" s="6">
-        <f t="shared" si="330"/>
-        <v>115999.91312341303</v>
+        <f t="shared" si="326"/>
+        <v>120473.67522170956</v>
       </c>
       <c r="CQ73" s="6">
-        <f t="shared" si="330"/>
-        <v>114839.9139921789</v>
+        <f t="shared" si="326"/>
+        <v>119268.93846949247</v>
       </c>
       <c r="CR73" s="6">
-        <f t="shared" si="330"/>
-        <v>113691.51485225711</v>
+        <f t="shared" si="326"/>
+        <v>118076.24908479754</v>
       </c>
       <c r="CS73" s="6">
-        <f t="shared" si="330"/>
-        <v>112554.59970373454</v>
+        <f t="shared" si="326"/>
+        <v>116895.48659394956</v>
       </c>
       <c r="CT73" s="6">
-        <f t="shared" si="330"/>
-        <v>111429.05370669719</v>
+        <f t="shared" si="326"/>
+        <v>115726.53172801007</v>
       </c>
       <c r="CU73" s="6">
-        <f t="shared" si="330"/>
-        <v>110314.76316963021</v>
+        <f t="shared" si="326"/>
+        <v>114569.26641072996</v>
       </c>
       <c r="CV73" s="6">
-        <f t="shared" si="330"/>
-        <v>109211.6155379339</v>
+        <f t="shared" si="326"/>
+        <v>113423.57374662266</v>
       </c>
       <c r="CW73" s="6">
-        <f t="shared" si="330"/>
-        <v>108119.49938255457</v>
+        <f t="shared" si="326"/>
+        <v>112289.33800915643</v>
       </c>
       <c r="CX73" s="6">
-        <f t="shared" si="330"/>
-        <v>107038.30438872903</v>
+        <f t="shared" si="326"/>
+        <v>111166.44462906486</v>
       </c>
       <c r="CY73" s="6">
-        <f t="shared" si="330"/>
-        <v>105967.92134484173</v>
+        <f t="shared" si="326"/>
+        <v>110054.78018277421</v>
       </c>
       <c r="CZ73" s="6">
-        <f t="shared" si="330"/>
-        <v>104908.24213139332</v>
+        <f t="shared" si="326"/>
+        <v>108954.23238094646</v>
       </c>
       <c r="DA73" s="6">
-        <f t="shared" si="330"/>
-        <v>103859.15971007939</v>
+        <f t="shared" si="326"/>
+        <v>107864.69005713699</v>
       </c>
       <c r="DB73" s="6">
-        <f t="shared" si="330"/>
-        <v>102820.5681129786</v>
+        <f t="shared" si="326"/>
+        <v>106786.04315656562</v>
       </c>
       <c r="DC73" s="6">
-        <f t="shared" si="330"/>
-        <v>101792.36243184881</v>
+        <f t="shared" si="326"/>
+        <v>105718.18272499996</v>
       </c>
       <c r="DD73" s="6">
-        <f t="shared" si="330"/>
-        <v>100774.43880753033</v>
+        <f t="shared" si="326"/>
+        <v>104661.00089774997</v>
       </c>
       <c r="DE73" s="6">
-        <f t="shared" si="330"/>
-        <v>99766.694419455031</v>
+        <f t="shared" si="326"/>
+        <v>103614.39088877247</v>
       </c>
       <c r="DF73" s="6">
-        <f t="shared" si="330"/>
-        <v>98769.027475260475</v>
+        <f t="shared" si="326"/>
+        <v>102578.24697988475</v>
       </c>
       <c r="DG73" s="6">
-        <f t="shared" si="330"/>
-        <v>97781.337200507871</v>
+        <f t="shared" si="326"/>
+        <v>101552.46451008589</v>
       </c>
       <c r="DH73" s="6">
-        <f t="shared" si="330"/>
-        <v>96803.523828502788</v>
+        <f t="shared" si="326"/>
+        <v>100536.93986498503</v>
       </c>
       <c r="DI73" s="6">
-        <f t="shared" si="330"/>
-        <v>95835.488590217763</v>
+        <f t="shared" si="326"/>
+        <v>99531.570466335179</v>
       </c>
       <c r="DJ73" s="6">
-        <f t="shared" si="330"/>
-        <v>94877.13370431558</v>
+        <f t="shared" si="326"/>
+        <v>98536.254761671822</v>
       </c>
       <c r="DK73" s="6">
-        <f t="shared" si="330"/>
-        <v>93928.362367272421</v>
+        <f t="shared" si="326"/>
+        <v>97550.8922140551</v>
       </c>
       <c r="DL73" s="6">
-        <f t="shared" si="330"/>
-        <v>92989.07874359969</v>
+        <f t="shared" si="326"/>
+        <v>96575.38329191455</v>
       </c>
       <c r="DM73" s="6">
-        <f t="shared" si="330"/>
-        <v>92059.187956163689</v>
+        <f t="shared" si="326"/>
+        <v>95609.629458995405</v>
       </c>
       <c r="DN73" s="6">
-        <f t="shared" si="330"/>
-        <v>91138.596076602058</v>
+        <f t="shared" si="326"/>
+        <v>94653.533164405453</v>
       </c>
       <c r="DO73" s="6">
-        <f t="shared" si="330"/>
-        <v>90227.210115836031</v>
+        <f t="shared" si="326"/>
+        <v>93706.997832761394</v>
       </c>
       <c r="DP73" s="6">
-        <f t="shared" si="330"/>
-        <v>89324.938014677668</v>
+        <f t="shared" si="326"/>
+        <v>92769.927854433772</v>
       </c>
       <c r="DQ73" s="6">
-        <f t="shared" si="330"/>
-        <v>88431.688634530889</v>
+        <f t="shared" si="326"/>
+        <v>91842.228575889429</v>
       </c>
       <c r="DR73" s="6">
-        <f t="shared" si="330"/>
-        <v>87547.371748185586</v>
+        <f t="shared" si="326"/>
+        <v>90923.806290130538</v>
       </c>
       <c r="DS73" s="6">
-        <f t="shared" si="330"/>
-        <v>86671.898030703727</v>
+        <f t="shared" si="326"/>
+        <v>90014.568227229232</v>
       </c>
       <c r="DT73" s="6">
-        <f t="shared" si="330"/>
-        <v>85805.179050396691</v>
+        <f t="shared" si="326"/>
+        <v>89114.422544956935</v>
       </c>
       <c r="DU73" s="6">
-        <f t="shared" si="330"/>
-        <v>84947.127259892717</v>
+        <f t="shared" si="326"/>
+        <v>88223.278319507372</v>
       </c>
       <c r="DV73" s="6">
-        <f t="shared" si="330"/>
-        <v>84097.655987293794</v>
+        <f t="shared" si="326"/>
+        <v>87341.045536312304</v>
       </c>
       <c r="DW73" s="6">
-        <f t="shared" si="330"/>
-        <v>83256.679427420851</v>
+        <f t="shared" si="326"/>
+        <v>86467.635080949185</v>
       </c>
       <c r="DX73" s="6">
-        <f t="shared" si="330"/>
-        <v>82424.112633146637</v>
+        <f t="shared" si="326"/>
+        <v>85602.958730139697</v>
       </c>
       <c r="DY73" s="6">
-        <f t="shared" si="330"/>
-        <v>81599.871506815165</v>
+        <f t="shared" si="326"/>
+        <v>84746.9291428383</v>
       </c>
       <c r="DZ73" s="6">
-        <f t="shared" si="330"/>
-        <v>80783.87279174701</v>
+        <f t="shared" si="326"/>
+        <v>83899.45985140992</v>
       </c>
       <c r="EA73" s="6">
-        <f t="shared" si="330"/>
-        <v>79976.034063829546</v>
+        <f t="shared" si="326"/>
+        <v>83060.465252895825</v>
       </c>
       <c r="EB73" s="6">
-        <f t="shared" ref="EB73:EU73" si="331">EA73*(1+$BQ$29)</f>
-        <v>79176.273723191247</v>
+        <f t="shared" ref="EB73:EU73" si="327">EA73*(1+$BQ$29)</f>
+        <v>82229.860600366868</v>
       </c>
       <c r="EC73" s="6">
-        <f t="shared" si="331"/>
-        <v>78384.510985959336</v>
+        <f t="shared" si="327"/>
+        <v>81407.561994363205</v>
       </c>
       <c r="ED73" s="6">
-        <f t="shared" si="331"/>
-        <v>77600.665876099738</v>
+        <f t="shared" si="327"/>
+        <v>80593.486374419575</v>
       </c>
       <c r="EE73" s="6">
-        <f t="shared" si="331"/>
-        <v>76824.659217338747</v>
+        <f t="shared" si="327"/>
+        <v>79787.551510675374</v>
       </c>
       <c r="EF73" s="6">
-        <f t="shared" si="331"/>
-        <v>76056.412625165365</v>
+        <f t="shared" si="327"/>
+        <v>78989.675995568614</v>
       </c>
       <c r="EG73" s="6">
-        <f t="shared" si="331"/>
-        <v>75295.848498913707</v>
+        <f t="shared" si="327"/>
+        <v>78199.779235612921</v>
       </c>
       <c r="EH73" s="6">
-        <f t="shared" si="331"/>
-        <v>74542.890013924567</v>
+        <f t="shared" si="327"/>
+        <v>77417.781443256798</v>
       </c>
       <c r="EI73" s="6">
-        <f t="shared" si="331"/>
-        <v>73797.461113785321</v>
+        <f t="shared" si="327"/>
+        <v>76643.603628824232</v>
       </c>
       <c r="EJ73" s="6">
-        <f t="shared" si="331"/>
-        <v>73059.486502647473</v>
+        <f t="shared" si="327"/>
+        <v>75877.167592535989</v>
       </c>
       <c r="EK73" s="6">
-        <f t="shared" si="331"/>
-        <v>72328.891637620996</v>
+        <f t="shared" si="327"/>
+        <v>75118.395916610621</v>
       </c>
       <c r="EL73" s="6">
-        <f t="shared" si="331"/>
-        <v>71605.602721244781</v>
+        <f t="shared" si="327"/>
+        <v>74367.21195744451</v>
       </c>
       <c r="EM73" s="6">
-        <f t="shared" si="331"/>
-        <v>70889.546694032339</v>
+        <f t="shared" si="327"/>
+        <v>73623.539837870063</v>
       </c>
       <c r="EN73" s="6">
-        <f t="shared" si="331"/>
-        <v>70180.651227092021</v>
+        <f t="shared" si="327"/>
+        <v>72887.30443949136</v>
       </c>
       <c r="EO73" s="6">
-        <f t="shared" si="331"/>
-        <v>69478.844714821098</v>
+        <f t="shared" si="327"/>
+        <v>72158.431395096442</v>
       </c>
       <c r="EP73" s="6">
-        <f t="shared" si="331"/>
-        <v>68784.056267672888</v>
+        <f t="shared" si="327"/>
+        <v>71436.847081145475</v>
       </c>
       <c r="EQ73" s="6">
-        <f t="shared" si="331"/>
-        <v>68096.215704996153</v>
+        <f t="shared" si="327"/>
+        <v>70722.478610334016</v>
       </c>
       <c r="ER73" s="6">
-        <f t="shared" si="331"/>
-        <v>67415.253547946195</v>
+        <f t="shared" si="327"/>
+        <v>70015.253824230676</v>
       </c>
       <c r="ES73" s="6">
-        <f t="shared" si="331"/>
-        <v>66741.101012466737</v>
+        <f t="shared" si="327"/>
+        <v>69315.101285988363</v>
       </c>
       <c r="ET73" s="6">
-        <f t="shared" si="331"/>
-        <v>66073.690002342075</v>
+        <f t="shared" si="327"/>
+        <v>68621.950273128474</v>
       </c>
       <c r="EU73" s="6">
-        <f t="shared" si="331"/>
-        <v>65412.95310231865</v>
+        <f t="shared" si="327"/>
+        <v>67935.730770397189</v>
       </c>
     </row>
     <row r="75" spans="2:151" x14ac:dyDescent="0.3">
       <c r="BQ75" s="3">
         <f>NPV(BQ30,BD73:EU73)</f>
-        <v>2620220.1826553484</v>
+        <v>2700460.8344837613</v>
       </c>
     </row>
     <row r="76" spans="2:151" x14ac:dyDescent="0.3">
       <c r="BQ76" s="3">
         <f>Main!D8</f>
-        <v>34736</v>
+        <v>31288</v>
       </c>
     </row>
     <row r="77" spans="2:151" x14ac:dyDescent="0.3">
       <c r="BQ77" s="3">
         <f>BQ75+BQ76</f>
-        <v>2654956.1826553484</v>
+        <v>2731748.8344837613</v>
       </c>
     </row>
     <row r="78" spans="2:151" x14ac:dyDescent="0.3">
       <c r="BQ78" s="12">
         <f>BQ77/BN18</f>
-        <v>177.75788258113718</v>
+        <v>183.30317149573315</v>
       </c>
     </row>
     <row r="79" spans="2:151" x14ac:dyDescent="0.3">
       <c r="BQ79" s="12">
         <f>Main!D3</f>
-        <v>198.81</v>
+        <v>231.02</v>
       </c>
     </row>
     <row r="80" spans="2:151" x14ac:dyDescent="0.3">
       <c r="BQ80" s="11">
         <f>BQ78/BQ79-1</f>
-        <v>-0.10589063638077978</v>
+        <v>-0.2065484741765512</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/AAPL.xlsx
+++ b/Financial Analysis/AAPL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3296D9E8-4915-4BC8-A8AC-940450D4BFB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2714F36-CB7D-4339-9EC2-24F42B1A1969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{9DABBB29-C94C-41BD-A4AD-A53C3313D92F}"/>
   </bookViews>
@@ -343,7 +343,7 @@
     <t>D/T</t>
   </si>
   <si>
-    <t>Slightly overvalued</t>
+    <t>Overvalued</t>
   </si>
 </sst>
 </file>
@@ -911,14 +911,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="12">
-        <v>231.02</v>
+        <v>256.69</v>
       </c>
       <c r="E3" s="2">
-        <v>45887</v>
+        <v>45937</v>
       </c>
       <c r="F3" s="2">
         <f ca="1">TODAY()</f>
-        <v>45887</v>
+        <v>45937</v>
       </c>
       <c r="G3" s="2">
         <v>45961</v>
@@ -941,7 +941,7 @@
       </c>
       <c r="D5" s="3">
         <f>D3*D4</f>
-        <v>3442867.9580000001</v>
+        <v>3825425.4010000001</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -983,7 +983,7 @@
       </c>
       <c r="D9" s="3">
         <f>D5-D8</f>
-        <v>3411579.9580000001</v>
+        <v>3794137.4010000001</v>
       </c>
     </row>
   </sheetData>
@@ -1544,8 +1544,8 @@
         <v>66613</v>
       </c>
       <c r="AH3" s="3">
-        <f>AD3*1.03</f>
-        <v>72056.740000000005</v>
+        <f>AD3*1.06</f>
+        <v>74155.48000000001</v>
       </c>
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
@@ -1591,47 +1591,47 @@
       </c>
       <c r="BD3" s="3">
         <f>SUM(AE3:AH3)</f>
-        <v>305343.74</v>
+        <v>307442.48</v>
       </c>
       <c r="BE3" s="3">
         <f>BD3*1.03</f>
-        <v>314504.05219999998</v>
+        <v>316665.75439999998</v>
       </c>
       <c r="BF3" s="3">
         <f>BE3*1.02</f>
-        <v>320794.13324399997</v>
+        <v>322999.06948800001</v>
       </c>
       <c r="BG3" s="3">
         <f t="shared" ref="BG3:BI3" si="23">BF3*1.01</f>
-        <v>324002.07457643998</v>
+        <v>326229.06018288003</v>
       </c>
       <c r="BH3" s="3">
         <f t="shared" si="23"/>
-        <v>327242.0953222044</v>
+        <v>329491.3507847088</v>
       </c>
       <c r="BI3" s="3">
         <f t="shared" si="23"/>
-        <v>330514.51627542643</v>
+        <v>332786.26429255592</v>
       </c>
       <c r="BJ3" s="3">
         <f t="shared" ref="BJ3:BL3" si="24">BI3*1.01</f>
-        <v>333819.66143818072</v>
+        <v>336114.1269354815</v>
       </c>
       <c r="BK3" s="3">
         <f t="shared" si="24"/>
-        <v>337157.85805256251</v>
+        <v>339475.26820483629</v>
       </c>
       <c r="BL3" s="3">
         <f t="shared" si="24"/>
-        <v>340529.43663308816</v>
+        <v>342870.02088688465</v>
       </c>
       <c r="BM3" s="3">
         <f t="shared" ref="BM3" si="25">BL3*1.01</f>
-        <v>343934.73099941906</v>
+        <v>346298.72109575348</v>
       </c>
       <c r="BN3" s="3">
         <f t="shared" ref="BN3" si="26">BM3*1.01</f>
-        <v>347374.07830941328</v>
+        <v>349761.70830671105</v>
       </c>
     </row>
     <row r="4" spans="2:66" x14ac:dyDescent="0.3">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="AH5" s="9">
         <f t="shared" si="37"/>
-        <v>99775.66</v>
+        <v>101874.40000000001</v>
       </c>
       <c r="AI5" s="9"/>
       <c r="AJ5" s="9">
@@ -2024,47 +2024,47 @@
       </c>
       <c r="BD5" s="9">
         <f t="shared" si="38"/>
-        <v>413470.66</v>
+        <v>415569.39999999997</v>
       </c>
       <c r="BE5" s="9">
         <f t="shared" si="38"/>
-        <v>432362.39500000002</v>
+        <v>434524.09719999996</v>
       </c>
       <c r="BF5" s="9">
         <f t="shared" si="38"/>
-        <v>446902.56004000001</v>
+        <v>449107.49628399999</v>
       </c>
       <c r="BG5" s="9">
         <f t="shared" si="38"/>
-        <v>457677.00698020001</v>
+        <v>459903.99258664006</v>
       </c>
       <c r="BH5" s="9">
         <f t="shared" si="38"/>
-        <v>467600.77434615244</v>
+        <v>469850.02980865684</v>
       </c>
       <c r="BI5" s="9">
         <f t="shared" si="38"/>
-        <v>476487.54246033239</v>
+        <v>478759.29047746188</v>
       </c>
       <c r="BJ5" s="9">
         <f t="shared" ref="BJ5:BL5" si="41">BJ3+BJ4</f>
-        <v>484171.87840863387</v>
+        <v>486466.34390593466</v>
       </c>
       <c r="BK5" s="9">
         <f t="shared" si="41"/>
-        <v>492020.64153212926</v>
+        <v>494338.05168440304</v>
       </c>
       <c r="BL5" s="9">
         <f t="shared" si="41"/>
-        <v>500038.10361704195</v>
+        <v>502378.68787083845</v>
       </c>
       <c r="BM5" s="9">
         <f t="shared" ref="BM5:BN5" si="42">BM3+BM4</f>
-        <v>508228.65799289144</v>
+        <v>510592.64808922587</v>
       </c>
       <c r="BN5" s="9">
         <f t="shared" si="42"/>
-        <v>516596.82311268983</v>
+        <v>518984.4531099876</v>
       </c>
     </row>
     <row r="6" spans="2:66" x14ac:dyDescent="0.3">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="AH6" s="3">
         <f>AH3*0.66</f>
-        <v>47557.448400000008</v>
+        <v>48942.616800000011</v>
       </c>
       <c r="AI6" s="3"/>
       <c r="AJ6" s="3"/>
@@ -2212,47 +2212,47 @@
       </c>
       <c r="BD6" s="3">
         <f>SUM(AE6:AH6)</f>
-        <v>194654.44839999999</v>
+        <v>196039.61680000002</v>
       </c>
       <c r="BE6" s="3">
         <f>BE3*0.65</f>
-        <v>204427.63392999998</v>
+        <v>205832.74036</v>
       </c>
       <c r="BF6" s="3">
         <f t="shared" ref="BF6:BN6" si="43">BF3*0.65</f>
-        <v>208516.18660859999</v>
+        <v>209949.39516720001</v>
       </c>
       <c r="BG6" s="3">
         <f t="shared" si="43"/>
-        <v>210601.348474686</v>
+        <v>212048.88911887203</v>
       </c>
       <c r="BH6" s="3">
         <f t="shared" si="43"/>
-        <v>212707.36195943286</v>
+        <v>214169.37801006073</v>
       </c>
       <c r="BI6" s="3">
         <f t="shared" si="43"/>
-        <v>214834.43557902719</v>
+        <v>216311.07179016137</v>
       </c>
       <c r="BJ6" s="3">
         <f t="shared" si="43"/>
-        <v>216982.77993481746</v>
+        <v>218474.18250806298</v>
       </c>
       <c r="BK6" s="3">
         <f t="shared" si="43"/>
-        <v>219152.60773416565</v>
+        <v>220658.9243331436</v>
       </c>
       <c r="BL6" s="3">
         <f t="shared" si="43"/>
-        <v>221344.13381150732</v>
+        <v>222865.51357647503</v>
       </c>
       <c r="BM6" s="3">
         <f t="shared" si="43"/>
-        <v>223557.5751496224</v>
+        <v>225094.16871223977</v>
       </c>
       <c r="BN6" s="3">
         <f t="shared" si="43"/>
-        <v>225793.15090111864</v>
+        <v>227345.11039936219</v>
       </c>
     </row>
     <row r="7" spans="2:66" x14ac:dyDescent="0.3">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AH8" s="3">
         <f t="shared" si="54"/>
-        <v>54487.178400000012</v>
+        <v>55872.346800000014</v>
       </c>
       <c r="AI8" s="3"/>
       <c r="AJ8" s="3">
@@ -2645,47 +2645,47 @@
       </c>
       <c r="BD8" s="3">
         <f t="shared" si="55"/>
-        <v>221322.1784</v>
+        <v>222707.34680000003</v>
       </c>
       <c r="BE8" s="3">
         <f t="shared" si="55"/>
-        <v>232713.63620199999</v>
+        <v>234118.74263200001</v>
       </c>
       <c r="BF8" s="3">
         <f t="shared" si="55"/>
-        <v>238782.20903964</v>
+        <v>240215.41759824002</v>
       </c>
       <c r="BG8" s="3">
         <f t="shared" si="55"/>
-        <v>242683.33225158841</v>
+        <v>244130.87289577443</v>
       </c>
       <c r="BH8" s="3">
         <f t="shared" si="55"/>
-        <v>246393.4449251804</v>
+        <v>247855.46097580827</v>
       </c>
       <c r="BI8" s="3">
         <f t="shared" si="55"/>
-        <v>249867.96186340463</v>
+        <v>251344.59807453881</v>
       </c>
       <c r="BJ8" s="3">
         <f t="shared" si="55"/>
-        <v>253067.31200772623</v>
+        <v>254558.71458097175</v>
       </c>
       <c r="BK8" s="3">
         <f t="shared" si="55"/>
-        <v>256319.67576926167</v>
+        <v>257825.99236823962</v>
       </c>
       <c r="BL8" s="3">
         <f t="shared" si="55"/>
-        <v>259626.21388765622</v>
+        <v>261147.59365262394</v>
       </c>
       <c r="BM8" s="3">
         <f t="shared" si="55"/>
-        <v>262988.11762805574</v>
+        <v>264524.71119067317</v>
       </c>
       <c r="BN8" s="3">
         <f t="shared" si="55"/>
-        <v>266406.60965390503</v>
+        <v>267958.56915214856</v>
       </c>
     </row>
     <row r="9" spans="2:66" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="AH9" s="9">
         <f t="shared" si="64"/>
-        <v>45288.481599999992</v>
+        <v>46002.053199999995</v>
       </c>
       <c r="AI9" s="9"/>
       <c r="AJ9" s="9">
@@ -2903,47 +2903,47 @@
       </c>
       <c r="BD9" s="9">
         <f t="shared" si="72"/>
-        <v>192148.48159999997</v>
+        <v>192862.05319999994</v>
       </c>
       <c r="BE9" s="9">
         <f t="shared" si="72"/>
-        <v>199648.75879800002</v>
+        <v>200405.35456799995</v>
       </c>
       <c r="BF9" s="9">
         <f t="shared" si="72"/>
-        <v>208120.35100036001</v>
+        <v>208892.07868575997</v>
       </c>
       <c r="BG9" s="9">
         <f t="shared" si="72"/>
-        <v>214993.6747286116</v>
+        <v>215773.11969086563</v>
       </c>
       <c r="BH9" s="9">
         <f t="shared" si="72"/>
-        <v>221207.32942097203</v>
+        <v>221994.56883284857</v>
       </c>
       <c r="BI9" s="9">
         <f t="shared" si="72"/>
-        <v>226619.58059692776</v>
+        <v>227414.69240292307</v>
       </c>
       <c r="BJ9" s="9">
         <f t="shared" si="72"/>
-        <v>231104.56640090764</v>
+        <v>231907.62932496291</v>
       </c>
       <c r="BK9" s="9">
         <f t="shared" si="72"/>
-        <v>235700.96576286759</v>
+        <v>236512.05931616342</v>
       </c>
       <c r="BL9" s="9">
         <f t="shared" si="72"/>
-        <v>240411.88972938573</v>
+        <v>241231.09421821451</v>
       </c>
       <c r="BM9" s="9">
         <f t="shared" si="72"/>
-        <v>245240.5403648357</v>
+        <v>246067.9368985527</v>
       </c>
       <c r="BN9" s="9">
         <f t="shared" si="72"/>
-        <v>250190.2134587848</v>
+        <v>251025.88395783905</v>
       </c>
     </row>
     <row r="10" spans="2:66" x14ac:dyDescent="0.3">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="AH11" s="3">
         <f t="shared" ref="AH11" si="74">AH5*0.07</f>
-        <v>6984.2962000000007</v>
+        <v>7131.2080000000014</v>
       </c>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3">
@@ -3331,47 +3331,47 @@
       </c>
       <c r="BD11" s="3">
         <f>SUM(AE11:AH11)</f>
-        <v>27537.296200000001</v>
+        <v>27684.208000000002</v>
       </c>
       <c r="BE11" s="3">
         <f>BD11*1.02</f>
-        <v>28088.042124</v>
+        <v>28237.892160000003</v>
       </c>
       <c r="BF11" s="3">
         <f t="shared" ref="BF11:BJ11" si="75">BE11*1.02</f>
-        <v>28649.802966480001</v>
+        <v>28802.650003200004</v>
       </c>
       <c r="BG11" s="3">
         <f t="shared" si="75"/>
-        <v>29222.799025809603</v>
+        <v>29378.703003264003</v>
       </c>
       <c r="BH11" s="3">
         <f t="shared" si="75"/>
-        <v>29807.255006325795</v>
+        <v>29966.277063329282</v>
       </c>
       <c r="BI11" s="3">
         <f t="shared" si="75"/>
-        <v>30403.400106452311</v>
+        <v>30565.602604595868</v>
       </c>
       <c r="BJ11" s="3">
         <f t="shared" si="75"/>
-        <v>31011.468108581357</v>
+        <v>31176.914656687786</v>
       </c>
       <c r="BK11" s="3">
         <f>BJ11*1.01</f>
-        <v>31321.582789667173</v>
+        <v>31488.683803254666</v>
       </c>
       <c r="BL11" s="3">
         <f t="shared" ref="BL11:BN11" si="76">BK11*1.01</f>
-        <v>31634.798617563843</v>
+        <v>31803.570641287213</v>
       </c>
       <c r="BM11" s="3">
         <f t="shared" si="76"/>
-        <v>31951.146603739482</v>
+        <v>32121.606347700086</v>
       </c>
       <c r="BN11" s="3">
         <f t="shared" si="76"/>
-        <v>32270.658069776877</v>
+        <v>32442.822411177087</v>
       </c>
     </row>
     <row r="12" spans="2:66" x14ac:dyDescent="0.3">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="AH12" s="3">
         <f t="shared" si="85"/>
-        <v>15603.446200000002</v>
+        <v>15750.358000000004</v>
       </c>
       <c r="AI12" s="3"/>
       <c r="AJ12" s="3">
@@ -3589,47 +3589,47 @@
       </c>
       <c r="BD12" s="3">
         <f t="shared" ref="BD12:BI12" si="94">BD10+BD11</f>
-        <v>61840.446200000006</v>
+        <v>61987.358000000007</v>
       </c>
       <c r="BE12" s="3">
         <f t="shared" si="94"/>
-        <v>64106.349624000002</v>
+        <v>64256.199660000006</v>
       </c>
       <c r="BF12" s="3">
         <f t="shared" si="94"/>
-        <v>66108.842766480011</v>
+        <v>66261.689803200017</v>
       </c>
       <c r="BG12" s="3">
         <f t="shared" si="94"/>
-        <v>67805.61001980961</v>
+        <v>67961.513997264003</v>
       </c>
       <c r="BH12" s="3">
         <f t="shared" si="94"/>
-        <v>69547.550330145808</v>
+        <v>69706.572387149296</v>
       </c>
       <c r="BI12" s="3">
         <f t="shared" si="94"/>
-        <v>71335.904289986909</v>
+        <v>71498.106788130477</v>
       </c>
       <c r="BJ12" s="3">
         <f t="shared" ref="BJ12:BL12" si="95">BJ10+BJ11</f>
-        <v>72762.622375786654</v>
+        <v>72928.068923893079</v>
       </c>
       <c r="BK12" s="3">
         <f t="shared" si="95"/>
-        <v>73907.760142216575</v>
+        <v>74074.861155804072</v>
       </c>
       <c r="BL12" s="3">
         <f t="shared" si="95"/>
-        <v>75072.699517164234</v>
+        <v>75241.471540887607</v>
       </c>
       <c r="BM12" s="3">
         <f t="shared" ref="BM12:BN12" si="96">BM10+BM11</f>
-        <v>76257.805521331888</v>
+        <v>76428.265265292488</v>
       </c>
       <c r="BN12" s="3">
         <f t="shared" si="96"/>
-        <v>77463.450165721137</v>
+        <v>77635.61450712134</v>
       </c>
     </row>
     <row r="13" spans="2:66" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="AH13" s="9">
         <f t="shared" si="106"/>
-        <v>29685.03539999999</v>
+        <v>30251.695199999991</v>
       </c>
       <c r="AI13" s="9"/>
       <c r="AJ13" s="9">
@@ -3847,47 +3847,47 @@
       </c>
       <c r="BD13" s="9">
         <f t="shared" ref="BD13:BI13" si="115">BD9-BD12</f>
-        <v>130308.03539999996</v>
+        <v>130874.69519999993</v>
       </c>
       <c r="BE13" s="9">
         <f t="shared" si="115"/>
-        <v>135542.40917400003</v>
+        <v>136149.15490799994</v>
       </c>
       <c r="BF13" s="9">
         <f t="shared" si="115"/>
-        <v>142011.50823387998</v>
+        <v>142630.38888255996</v>
       </c>
       <c r="BG13" s="9">
         <f t="shared" si="115"/>
-        <v>147188.06470880198</v>
+        <v>147811.60569360162</v>
       </c>
       <c r="BH13" s="9">
         <f t="shared" si="115"/>
-        <v>151659.77909082623</v>
+        <v>152287.99644569927</v>
       </c>
       <c r="BI13" s="9">
         <f t="shared" si="115"/>
-        <v>155283.67630694085</v>
+        <v>155916.5856147926</v>
       </c>
       <c r="BJ13" s="9">
         <f t="shared" ref="BJ13:BL13" si="116">BJ9-BJ12</f>
-        <v>158341.94402512099</v>
+        <v>158979.56040106982</v>
       </c>
       <c r="BK13" s="9">
         <f t="shared" si="116"/>
-        <v>161793.20562065102</v>
+        <v>162437.19816035934</v>
       </c>
       <c r="BL13" s="9">
         <f t="shared" si="116"/>
-        <v>165339.1902122215</v>
+        <v>165989.6226773269</v>
       </c>
       <c r="BM13" s="9">
         <f t="shared" ref="BM13:BN13" si="117">BM9-BM12</f>
-        <v>168982.7348435038</v>
+        <v>169639.67163326021</v>
       </c>
       <c r="BN13" s="9">
         <f t="shared" si="117"/>
-        <v>172726.76329306368</v>
+        <v>173390.26945071772</v>
       </c>
     </row>
     <row r="14" spans="2:66" x14ac:dyDescent="0.3">
@@ -4064,43 +4064,43 @@
       </c>
       <c r="BE14" s="3">
         <f>BD17*0.005</f>
-        <v>547.39714867999987</v>
+        <v>549.77711983999961</v>
       </c>
       <c r="BF14" s="3">
         <f t="shared" ref="BF14:BN14" si="118">BE17*0.005</f>
-        <v>566.97905050634415</v>
+        <v>569.51738671027181</v>
       </c>
       <c r="BG14" s="3">
         <f t="shared" si="118"/>
-        <v>594.06702257016934</v>
+        <v>596.65566028256876</v>
       </c>
       <c r="BH14" s="3">
         <f t="shared" si="118"/>
-        <v>615.69479028217359</v>
+        <v>618.30279013994004</v>
       </c>
       <c r="BI14" s="3">
         <f t="shared" si="118"/>
-        <v>634.38515406228498</v>
+        <v>637.01271335334923</v>
       </c>
       <c r="BJ14" s="3">
         <f t="shared" si="118"/>
-        <v>649.52702284208999</v>
+        <v>652.1742061860449</v>
       </c>
       <c r="BK14" s="3">
         <f t="shared" si="118"/>
-        <v>662.30815140957145</v>
+        <v>664.97502201851182</v>
       </c>
       <c r="BL14" s="3">
         <f t="shared" si="118"/>
-        <v>676.74976937081408</v>
+        <v>679.44333718103155</v>
       </c>
       <c r="BM14" s="3">
         <f t="shared" si="118"/>
-        <v>691.58224985997276</v>
+        <v>694.30275322861269</v>
       </c>
       <c r="BN14" s="3">
         <f t="shared" si="118"/>
-        <v>706.82284089330415</v>
+        <v>709.57054929613264</v>
       </c>
     </row>
     <row r="15" spans="2:66" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="AH15" s="9">
         <f t="shared" si="127"/>
-        <v>29685.03539999999</v>
+        <v>30251.695199999991</v>
       </c>
       <c r="AI15" s="9"/>
       <c r="AJ15" s="9">
@@ -4318,47 +4318,47 @@
       </c>
       <c r="BD15" s="9">
         <f t="shared" ref="BD15:BI15" si="136">BD13-BD14</f>
-        <v>129610.03539999996</v>
+        <v>130176.69519999993</v>
       </c>
       <c r="BE15" s="9">
         <f t="shared" si="136"/>
-        <v>134995.01202532003</v>
+        <v>135599.37778815994</v>
       </c>
       <c r="BF15" s="9">
         <f t="shared" si="136"/>
-        <v>141444.52918337364</v>
+        <v>142060.87149584969</v>
       </c>
       <c r="BG15" s="9">
         <f t="shared" si="136"/>
-        <v>146593.9976862318</v>
+        <v>147214.95003331907</v>
       </c>
       <c r="BH15" s="9">
         <f t="shared" si="136"/>
-        <v>151044.08430054405</v>
+        <v>151669.69365555933</v>
       </c>
       <c r="BI15" s="9">
         <f t="shared" si="136"/>
-        <v>154649.29115287858</v>
+        <v>155279.57290143924</v>
       </c>
       <c r="BJ15" s="9">
         <f t="shared" ref="BJ15:BL15" si="137">BJ13-BJ14</f>
-        <v>157692.4170022789</v>
+        <v>158327.38619488376</v>
       </c>
       <c r="BK15" s="9">
         <f t="shared" si="137"/>
-        <v>161130.89746924143</v>
+        <v>161772.22313834084</v>
       </c>
       <c r="BL15" s="9">
         <f t="shared" si="137"/>
-        <v>164662.44044285067</v>
+        <v>165310.17934014587</v>
       </c>
       <c r="BM15" s="9">
         <f t="shared" ref="BM15:BN15" si="138">BM13-BM14</f>
-        <v>168291.15259364384</v>
+        <v>168945.3688800316</v>
       </c>
       <c r="BN15" s="9">
         <f t="shared" si="138"/>
-        <v>172019.94045217038</v>
+        <v>172680.69890142159</v>
       </c>
     </row>
     <row r="16" spans="2:66" x14ac:dyDescent="0.3">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="AH16" s="3">
         <f t="shared" ref="AH16" si="139">AH15*0.16</f>
-        <v>4749.6056639999988</v>
+        <v>4840.2712319999982</v>
       </c>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3">
@@ -4532,47 +4532,47 @@
       </c>
       <c r="BD16" s="3">
         <f>SUM(AE16:AH16)</f>
-        <v>20130.605663999999</v>
+        <v>20221.271231999999</v>
       </c>
       <c r="BE16" s="3">
         <f t="shared" ref="BE16:BL16" si="140">BE15*0.16</f>
-        <v>21599.201924051205</v>
+        <v>21695.900446105592</v>
       </c>
       <c r="BF16" s="3">
         <f t="shared" si="140"/>
-        <v>22631.124669339784</v>
+        <v>22729.73943933595</v>
       </c>
       <c r="BG16" s="3">
         <f t="shared" si="140"/>
-        <v>23455.039629797087</v>
+        <v>23554.39200533105</v>
       </c>
       <c r="BH16" s="3">
         <f t="shared" si="140"/>
-        <v>24167.053488087051</v>
+        <v>24267.150984889493</v>
       </c>
       <c r="BI16" s="3">
         <f t="shared" si="140"/>
-        <v>24743.886584460572</v>
+        <v>24844.731664230279</v>
       </c>
       <c r="BJ16" s="3">
         <f t="shared" si="140"/>
-        <v>25230.786720364624</v>
+        <v>25332.3817911814</v>
       </c>
       <c r="BK16" s="3">
         <f t="shared" si="140"/>
-        <v>25780.943595078628</v>
+        <v>25883.555702134534</v>
       </c>
       <c r="BL16" s="3">
         <f t="shared" si="140"/>
-        <v>26345.990470856108</v>
+        <v>26449.62869442334</v>
       </c>
       <c r="BM16" s="3">
         <f t="shared" ref="BM16:BN16" si="141">BM15*0.16</f>
-        <v>26926.584414983015</v>
+        <v>27031.259020805057</v>
       </c>
       <c r="BN16" s="3">
         <f t="shared" si="141"/>
-        <v>27523.190472347262</v>
+        <v>27628.911824227456</v>
       </c>
     </row>
     <row r="17" spans="2:179" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="AH17" s="9">
         <f t="shared" si="151"/>
-        <v>24935.429735999991</v>
+        <v>25411.423967999992</v>
       </c>
       <c r="AI17" s="9"/>
       <c r="AJ17" s="9">
@@ -4790,499 +4790,499 @@
       </c>
       <c r="BD17" s="9">
         <f t="shared" si="153"/>
-        <v>109479.42973599996</v>
+        <v>109955.42396799993</v>
       </c>
       <c r="BE17" s="9">
         <f t="shared" si="153"/>
-        <v>113395.81010126883</v>
+        <v>113903.47734205435</v>
       </c>
       <c r="BF17" s="9">
         <f t="shared" si="153"/>
-        <v>118813.40451403386</v>
+        <v>119331.13205651374</v>
       </c>
       <c r="BG17" s="9">
         <f t="shared" si="153"/>
-        <v>123138.95805643471</v>
+        <v>123660.55802798801</v>
       </c>
       <c r="BH17" s="9">
         <f t="shared" si="153"/>
-        <v>126877.030812457</v>
+        <v>127402.54267066983</v>
       </c>
       <c r="BI17" s="9">
         <f t="shared" si="153"/>
-        <v>129905.404568418</v>
+        <v>130434.84123720897</v>
       </c>
       <c r="BJ17" s="9">
         <f t="shared" ref="BJ17:BL17" si="156">BJ15-BJ16</f>
-        <v>132461.63028191429</v>
+        <v>132995.00440370236</v>
       </c>
       <c r="BK17" s="9">
         <f t="shared" si="156"/>
-        <v>135349.95387416281</v>
+        <v>135888.66743620631</v>
       </c>
       <c r="BL17" s="9">
         <f t="shared" si="156"/>
-        <v>138316.44997199456</v>
+        <v>138860.55064572254</v>
       </c>
       <c r="BM17" s="9">
         <f t="shared" ref="BM17:BN17" si="157">BM15-BM16</f>
-        <v>141364.56817866082</v>
+        <v>141914.10985922653</v>
       </c>
       <c r="BN17" s="9">
         <f t="shared" si="157"/>
-        <v>144496.74997982313</v>
+        <v>145051.78707719414</v>
       </c>
       <c r="BO17" s="6">
         <f>BN17*(1+$BQ$29)</f>
-        <v>143051.78248002491</v>
+        <v>143601.26920642221</v>
       </c>
       <c r="BP17" s="6">
         <f t="shared" ref="BP17:CT17" si="158">BM17*(1+$BQ$29)</f>
-        <v>139950.92249687421</v>
+        <v>140494.96876063428</v>
       </c>
       <c r="BQ17" s="6">
         <f t="shared" si="158"/>
-        <v>143051.78248002491</v>
+        <v>143601.26920642221</v>
       </c>
       <c r="BR17" s="6">
         <f t="shared" si="158"/>
-        <v>141621.26465522466</v>
+        <v>142165.25651435798</v>
       </c>
       <c r="BS17" s="6">
         <f t="shared" si="158"/>
-        <v>138551.41327190548</v>
+        <v>139090.01907302794</v>
       </c>
       <c r="BT17" s="6">
         <f t="shared" si="158"/>
-        <v>141621.26465522466</v>
+        <v>142165.25651435798</v>
       </c>
       <c r="BU17" s="6">
         <f t="shared" si="158"/>
-        <v>140205.05200867241</v>
+        <v>140743.60394921439</v>
       </c>
       <c r="BV17" s="6">
         <f t="shared" si="158"/>
-        <v>137165.89913918643</v>
+        <v>137699.11888229765</v>
       </c>
       <c r="BW17" s="6">
         <f t="shared" si="158"/>
-        <v>140205.05200867241</v>
+        <v>140743.60394921439</v>
       </c>
       <c r="BX17" s="6">
         <f t="shared" si="158"/>
-        <v>138803.00148858569</v>
+        <v>139336.16790972225</v>
       </c>
       <c r="BY17" s="6">
         <f t="shared" si="158"/>
-        <v>135794.24014779457</v>
+        <v>136322.12769347467</v>
       </c>
       <c r="BZ17" s="6">
         <f t="shared" si="158"/>
-        <v>138803.00148858569</v>
+        <v>139336.16790972225</v>
       </c>
       <c r="CA17" s="6">
         <f t="shared" si="158"/>
-        <v>137414.97147369984</v>
+        <v>137942.80623062502</v>
       </c>
       <c r="CB17" s="6">
         <f t="shared" si="158"/>
-        <v>134436.29774631662</v>
+        <v>134958.90641653992</v>
       </c>
       <c r="CC17" s="6">
         <f t="shared" si="158"/>
-        <v>137414.97147369984</v>
+        <v>137942.80623062502</v>
       </c>
       <c r="CD17" s="6">
         <f t="shared" si="158"/>
-        <v>136040.82175896285</v>
+        <v>136563.37816831877</v>
       </c>
       <c r="CE17" s="6">
         <f t="shared" si="158"/>
-        <v>133091.93476885345</v>
+        <v>133609.31735237452</v>
       </c>
       <c r="CF17" s="6">
         <f t="shared" si="158"/>
-        <v>136040.82175896285</v>
+        <v>136563.37816831877</v>
       </c>
       <c r="CG17" s="6">
         <f t="shared" si="158"/>
-        <v>134680.41354137321</v>
+        <v>135197.74438663558</v>
       </c>
       <c r="CH17" s="6">
         <f t="shared" si="158"/>
-        <v>131761.01542116492</v>
+        <v>132273.22417885077</v>
       </c>
       <c r="CI17" s="6">
         <f t="shared" si="158"/>
-        <v>134680.41354137321</v>
+        <v>135197.74438663558</v>
       </c>
       <c r="CJ17" s="6">
         <f t="shared" si="158"/>
-        <v>133333.60940595949</v>
+        <v>133845.76694276923</v>
       </c>
       <c r="CK17" s="6">
         <f t="shared" si="158"/>
-        <v>130443.40526695327</v>
+        <v>130950.49193706225</v>
       </c>
       <c r="CL17" s="6">
         <f t="shared" si="158"/>
-        <v>133333.60940595949</v>
+        <v>133845.76694276923</v>
       </c>
       <c r="CM17" s="6">
         <f t="shared" si="158"/>
-        <v>132000.27331189989</v>
+        <v>132507.30927334153</v>
       </c>
       <c r="CN17" s="6">
         <f t="shared" si="158"/>
-        <v>129138.97121428374</v>
+        <v>129640.98701769163</v>
       </c>
       <c r="CO17" s="6">
         <f t="shared" si="158"/>
-        <v>132000.27331189989</v>
+        <v>132507.30927334153</v>
       </c>
       <c r="CP17" s="6">
         <f t="shared" si="158"/>
-        <v>130680.27057878088</v>
+        <v>131182.2361806081</v>
       </c>
       <c r="CQ17" s="6">
         <f t="shared" si="158"/>
-        <v>127847.58150214089</v>
+        <v>128344.57714751472</v>
       </c>
       <c r="CR17" s="6">
         <f t="shared" si="158"/>
-        <v>130680.27057878088</v>
+        <v>131182.2361806081</v>
       </c>
       <c r="CS17" s="6">
         <f t="shared" si="158"/>
-        <v>129373.46787299307</v>
+        <v>129870.41381880202</v>
       </c>
       <c r="CT17" s="6">
         <f t="shared" si="158"/>
-        <v>126569.10568711949</v>
+        <v>127061.13137603957</v>
       </c>
       <c r="CU17" s="6">
         <f t="shared" ref="CU17:DZ17" si="159">CR17*(1+$BQ$29)</f>
-        <v>129373.46787299307</v>
+        <v>129870.41381880202</v>
       </c>
       <c r="CV17" s="6">
         <f t="shared" si="159"/>
-        <v>128079.73319426314</v>
+        <v>128571.70968061399</v>
       </c>
       <c r="CW17" s="6">
         <f t="shared" si="159"/>
-        <v>125303.4146302483</v>
+        <v>125790.52006227917</v>
       </c>
       <c r="CX17" s="6">
         <f t="shared" si="159"/>
-        <v>128079.73319426314</v>
+        <v>128571.70968061399</v>
       </c>
       <c r="CY17" s="6">
         <f t="shared" si="159"/>
-        <v>126798.9358623205</v>
+        <v>127285.99258380785</v>
       </c>
       <c r="CZ17" s="6">
         <f t="shared" si="159"/>
-        <v>124050.38048394582</v>
+        <v>124532.61486165639</v>
       </c>
       <c r="DA17" s="6">
         <f t="shared" si="159"/>
-        <v>126798.9358623205</v>
+        <v>127285.99258380785</v>
       </c>
       <c r="DB17" s="6">
         <f t="shared" si="159"/>
-        <v>125530.9465036973</v>
+        <v>126013.13265796976</v>
       </c>
       <c r="DC17" s="6">
         <f t="shared" si="159"/>
-        <v>122809.87667910635</v>
+        <v>123287.28871303982</v>
       </c>
       <c r="DD17" s="6">
         <f t="shared" si="159"/>
-        <v>125530.9465036973</v>
+        <v>126013.13265796976</v>
       </c>
       <c r="DE17" s="6">
         <f t="shared" si="159"/>
-        <v>124275.63703866032</v>
+        <v>124753.00133139007</v>
       </c>
       <c r="DF17" s="6">
         <f t="shared" si="159"/>
-        <v>121581.77791231529</v>
+        <v>122054.41582590941</v>
       </c>
       <c r="DG17" s="6">
         <f t="shared" si="159"/>
-        <v>124275.63703866032</v>
+        <v>124753.00133139007</v>
       </c>
       <c r="DH17" s="6">
         <f t="shared" si="159"/>
-        <v>123032.88066827372</v>
+        <v>123505.47131807618</v>
       </c>
       <c r="DI17" s="6">
         <f t="shared" si="159"/>
-        <v>120365.96013319213</v>
+        <v>120833.87166765031</v>
       </c>
       <c r="DJ17" s="6">
         <f t="shared" si="159"/>
-        <v>123032.88066827372</v>
+        <v>123505.47131807618</v>
       </c>
       <c r="DK17" s="6">
         <f t="shared" si="159"/>
-        <v>121802.55186159098</v>
+        <v>122270.41660489541</v>
       </c>
       <c r="DL17" s="6">
         <f t="shared" si="159"/>
-        <v>119162.30053186021</v>
+        <v>119625.53295097381</v>
       </c>
       <c r="DM17" s="6">
         <f t="shared" si="159"/>
-        <v>121802.55186159098</v>
+        <v>122270.41660489541</v>
       </c>
       <c r="DN17" s="6">
         <f t="shared" si="159"/>
-        <v>120584.52634297508</v>
+        <v>121047.71243884646</v>
       </c>
       <c r="DO17" s="6">
         <f t="shared" si="159"/>
-        <v>117970.67752654161</v>
+        <v>118429.27762146406</v>
       </c>
       <c r="DP17" s="6">
         <f t="shared" si="159"/>
-        <v>120584.52634297508</v>
+        <v>121047.71243884646</v>
       </c>
       <c r="DQ17" s="6">
         <f t="shared" si="159"/>
-        <v>119378.68107954532</v>
+        <v>119837.235314458</v>
       </c>
       <c r="DR17" s="6">
         <f t="shared" si="159"/>
-        <v>116790.9707512762</v>
+        <v>117244.98484524942</v>
       </c>
       <c r="DS17" s="6">
         <f t="shared" si="159"/>
-        <v>119378.68107954532</v>
+        <v>119837.235314458</v>
       </c>
       <c r="DT17" s="6">
         <f t="shared" si="159"/>
-        <v>118184.89426874986</v>
+        <v>118638.86296131341</v>
       </c>
       <c r="DU17" s="6">
         <f t="shared" si="159"/>
-        <v>115623.06104376343</v>
+        <v>116072.53499679692</v>
       </c>
       <c r="DV17" s="6">
         <f t="shared" si="159"/>
-        <v>118184.89426874986</v>
+        <v>118638.86296131341</v>
       </c>
       <c r="DW17" s="6">
         <f t="shared" si="159"/>
-        <v>117003.04532606236</v>
+        <v>117452.47433170027</v>
       </c>
       <c r="DX17" s="6">
         <f t="shared" si="159"/>
-        <v>114466.8304333258</v>
+        <v>114911.80964682896</v>
       </c>
       <c r="DY17" s="6">
         <f t="shared" si="159"/>
-        <v>117003.04532606236</v>
+        <v>117452.47433170027</v>
       </c>
       <c r="DZ17" s="6">
         <f t="shared" si="159"/>
-        <v>115833.01487280174</v>
+        <v>116277.94958838327</v>
       </c>
       <c r="EA17" s="6">
         <f t="shared" ref="EA17:FF17" si="160">DX17*(1+$BQ$29)</f>
-        <v>113322.16212899254</v>
+        <v>113762.69155036067</v>
       </c>
       <c r="EB17" s="6">
         <f t="shared" si="160"/>
-        <v>115833.01487280174</v>
+        <v>116277.94958838327</v>
       </c>
       <c r="EC17" s="6">
         <f t="shared" si="160"/>
-        <v>114674.68472407373</v>
+        <v>115115.17009249944</v>
       </c>
       <c r="ED17" s="6">
         <f t="shared" si="160"/>
-        <v>112188.94050770262</v>
+        <v>112625.06463485706</v>
       </c>
       <c r="EE17" s="6">
         <f t="shared" si="160"/>
-        <v>114674.68472407373</v>
+        <v>115115.17009249944</v>
       </c>
       <c r="EF17" s="6">
         <f t="shared" si="160"/>
-        <v>113527.93787683299</v>
+        <v>113964.01839157444</v>
       </c>
       <c r="EG17" s="6">
         <f t="shared" si="160"/>
-        <v>111067.05110262558</v>
+        <v>111498.81398850848</v>
       </c>
       <c r="EH17" s="6">
         <f t="shared" si="160"/>
-        <v>113527.93787683299</v>
+        <v>113964.01839157444</v>
       </c>
       <c r="EI17" s="6">
         <f t="shared" si="160"/>
-        <v>112392.65849806466</v>
+        <v>112824.37820765869</v>
       </c>
       <c r="EJ17" s="6">
         <f t="shared" si="160"/>
-        <v>109956.38059159933</v>
+        <v>110383.8258486234</v>
       </c>
       <c r="EK17" s="6">
         <f t="shared" si="160"/>
-        <v>112392.65849806466</v>
+        <v>112824.37820765869</v>
       </c>
       <c r="EL17" s="6">
         <f t="shared" si="160"/>
-        <v>111268.731913084</v>
+        <v>111696.1344255821</v>
       </c>
       <c r="EM17" s="6">
         <f t="shared" si="160"/>
-        <v>108856.81678568333</v>
+        <v>109279.98759013716</v>
       </c>
       <c r="EN17" s="6">
         <f t="shared" si="160"/>
-        <v>111268.731913084</v>
+        <v>111696.1344255821</v>
       </c>
       <c r="EO17" s="6">
         <f t="shared" si="160"/>
-        <v>110156.04459395316</v>
+        <v>110579.17308132628</v>
       </c>
       <c r="EP17" s="6">
         <f t="shared" si="160"/>
-        <v>107768.2486178265</v>
+        <v>108187.18771423578</v>
       </c>
       <c r="EQ17" s="6">
         <f t="shared" si="160"/>
-        <v>110156.04459395316</v>
+        <v>110579.17308132628</v>
       </c>
       <c r="ER17" s="6">
         <f t="shared" si="160"/>
-        <v>109054.48414801364</v>
+        <v>109473.38135051302</v>
       </c>
       <c r="ES17" s="6">
         <f t="shared" si="160"/>
-        <v>106690.56613164823</v>
+        <v>107105.31583709343</v>
       </c>
       <c r="ET17" s="6">
         <f t="shared" si="160"/>
-        <v>109054.48414801364</v>
+        <v>109473.38135051302</v>
       </c>
       <c r="EU17" s="6">
         <f t="shared" si="160"/>
-        <v>107963.9393065335</v>
+        <v>108378.6475370079</v>
       </c>
       <c r="EV17" s="6">
         <f t="shared" si="160"/>
-        <v>105623.66047033174</v>
+        <v>106034.26267872249</v>
       </c>
       <c r="EW17" s="6">
         <f t="shared" si="160"/>
-        <v>107963.9393065335</v>
+        <v>108378.6475370079</v>
       </c>
       <c r="EX17" s="6">
         <f t="shared" si="160"/>
-        <v>106884.29991346816</v>
+        <v>107294.86106163781</v>
       </c>
       <c r="EY17" s="6">
         <f t="shared" si="160"/>
-        <v>104567.42386562843</v>
+        <v>104973.92005193526</v>
       </c>
       <c r="EZ17" s="6">
         <f t="shared" si="160"/>
-        <v>106884.29991346816</v>
+        <v>107294.86106163781</v>
       </c>
       <c r="FA17" s="6">
         <f t="shared" si="160"/>
-        <v>105815.45691433348</v>
+        <v>106221.91245102143</v>
       </c>
       <c r="FB17" s="6">
         <f t="shared" si="160"/>
-        <v>103521.74962697215</v>
+        <v>103924.18085141591</v>
       </c>
       <c r="FC17" s="6">
         <f t="shared" si="160"/>
-        <v>105815.45691433348</v>
+        <v>106221.91245102143</v>
       </c>
       <c r="FD17" s="6">
         <f t="shared" si="160"/>
-        <v>104757.30234519014</v>
+        <v>105159.69332651122</v>
       </c>
       <c r="FE17" s="6">
         <f t="shared" si="160"/>
-        <v>102486.53213070243</v>
+        <v>102884.93904290175</v>
       </c>
       <c r="FF17" s="6">
         <f t="shared" si="160"/>
-        <v>104757.30234519014</v>
+        <v>105159.69332651122</v>
       </c>
       <c r="FG17" s="6">
         <f t="shared" ref="FG17:FW17" si="161">FD17*(1+$BQ$29)</f>
-        <v>103709.72932173824</v>
+        <v>104108.0963932461</v>
       </c>
       <c r="FH17" s="6">
         <f t="shared" si="161"/>
-        <v>101461.66680939541</v>
+        <v>101856.08965247273</v>
       </c>
       <c r="FI17" s="6">
         <f t="shared" si="161"/>
-        <v>103709.72932173824</v>
+        <v>104108.0963932461</v>
       </c>
       <c r="FJ17" s="6">
         <f t="shared" si="161"/>
-        <v>102672.63202852085</v>
+        <v>103067.01542931364</v>
       </c>
       <c r="FK17" s="6">
         <f t="shared" si="161"/>
-        <v>100447.05014130146</v>
+        <v>100837.52875594801</v>
       </c>
       <c r="FL17" s="6">
         <f t="shared" si="161"/>
-        <v>102672.63202852085</v>
+        <v>103067.01542931364</v>
       </c>
       <c r="FM17" s="6">
         <f t="shared" si="161"/>
-        <v>101645.90570823564</v>
+        <v>102036.3452750205</v>
       </c>
       <c r="FN17" s="6">
         <f t="shared" si="161"/>
-        <v>99442.579639888441</v>
+        <v>99829.153468388526</v>
       </c>
       <c r="FO17" s="6">
         <f t="shared" si="161"/>
-        <v>101645.90570823564</v>
+        <v>102036.3452750205</v>
       </c>
       <c r="FP17" s="6">
         <f t="shared" si="161"/>
-        <v>100629.44665115328</v>
+        <v>101015.9818222703</v>
       </c>
       <c r="FQ17" s="6">
         <f t="shared" si="161"/>
-        <v>98448.153843489563</v>
+        <v>98830.86193370464</v>
       </c>
       <c r="FR17" s="6">
         <f t="shared" si="161"/>
-        <v>100629.44665115328</v>
+        <v>101015.9818222703</v>
       </c>
       <c r="FS17" s="6">
         <f t="shared" si="161"/>
-        <v>99623.152184641745</v>
+        <v>100005.8220040476</v>
       </c>
       <c r="FT17" s="6">
         <f t="shared" si="161"/>
-        <v>97463.672305054672</v>
+        <v>97842.553314367586</v>
       </c>
       <c r="FU17" s="6">
         <f t="shared" si="161"/>
-        <v>99623.152184641745</v>
+        <v>100005.8220040476</v>
       </c>
       <c r="FV17" s="6">
         <f t="shared" si="161"/>
-        <v>98626.920662795324</v>
+        <v>99005.763784007126</v>
       </c>
       <c r="FW17" s="6">
         <f t="shared" si="161"/>
-        <v>96489.03558200413</v>
+        <v>96864.127781223913</v>
       </c>
     </row>
     <row r="18" spans="2:179" x14ac:dyDescent="0.3">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="AH19" s="7">
         <f t="shared" si="171"/>
-        <v>1.6731931191915661</v>
+        <v>1.7051328243496227</v>
       </c>
       <c r="AI19" s="7"/>
       <c r="AJ19" s="7">
@@ -5698,47 +5698,47 @@
       </c>
       <c r="BD19" s="7">
         <f t="shared" si="173"/>
-        <v>7.3461829399647023</v>
+        <v>7.3781226451227564</v>
       </c>
       <c r="BE19" s="7">
         <f t="shared" si="173"/>
-        <v>7.6089761121170261</v>
+        <v>7.6430411089153356</v>
       </c>
       <c r="BF19" s="7">
         <f t="shared" si="173"/>
-        <v>7.9725022991521017</v>
+        <v>8.0072423525967267</v>
       </c>
       <c r="BG19" s="7">
         <f t="shared" si="173"/>
-        <v>8.2627514145860683</v>
+        <v>8.2977513120257136</v>
       </c>
       <c r="BH19" s="7">
         <f t="shared" si="173"/>
-        <v>8.5135799617830763</v>
+        <v>8.5488423508625733</v>
       </c>
       <c r="BI19" s="7">
         <f t="shared" si="173"/>
-        <v>8.7167869722280908</v>
+        <v>8.7523127201557394</v>
       </c>
       <c r="BJ19" s="7">
         <f t="shared" ref="BJ19:BL19" si="176">BJ17/BJ18</f>
-        <v>8.8883123608099286</v>
+        <v>8.9241023159051167</v>
       </c>
       <c r="BK19" s="7">
         <f t="shared" si="176"/>
-        <v>9.082121860454194</v>
+        <v>9.1182700975116457</v>
       </c>
       <c r="BL19" s="7">
         <f t="shared" si="176"/>
-        <v>9.2811768160555701</v>
+        <v>9.3176865338774704</v>
       </c>
       <c r="BM19" s="7">
         <f t="shared" ref="BM19:BN19" si="177">BM17/BM18</f>
-        <v>9.4857086995592006</v>
+        <v>9.52258351456606</v>
       </c>
       <c r="BN19" s="7">
         <f t="shared" si="177"/>
-        <v>9.6958813371775374</v>
+        <v>9.7331249003344418</v>
       </c>
     </row>
     <row r="21" spans="2:179" x14ac:dyDescent="0.3">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="AH21" s="10">
         <f t="shared" si="187"/>
-        <v>0.33999999999999991</v>
+        <v>0.33999999999999997</v>
       </c>
       <c r="AI21" s="10"/>
       <c r="AJ21" s="10"/>
@@ -5916,11 +5916,11 @@
       </c>
       <c r="BD21" s="10">
         <f t="shared" ref="BD21:BN21" si="190">(BD3-BD6)/BD3</f>
-        <v>0.36250715865339173</v>
+        <v>0.36235351471273575</v>
       </c>
       <c r="BE21" s="10">
         <f t="shared" si="190"/>
-        <v>0.35000000000000003</v>
+        <v>0.35</v>
       </c>
       <c r="BF21" s="10">
         <f t="shared" si="190"/>
@@ -5928,7 +5928,7 @@
       </c>
       <c r="BG21" s="10">
         <f t="shared" si="190"/>
-        <v>0.34999999999999992</v>
+        <v>0.35</v>
       </c>
       <c r="BH21" s="10">
         <f t="shared" si="190"/>
@@ -5936,11 +5936,11 @@
       </c>
       <c r="BI21" s="10">
         <f t="shared" si="190"/>
-        <v>0.35</v>
+        <v>0.34999999999999992</v>
       </c>
       <c r="BJ21" s="10">
         <f t="shared" si="190"/>
-        <v>0.35000000000000003</v>
+        <v>0.35</v>
       </c>
       <c r="BK21" s="10">
         <f t="shared" si="190"/>
@@ -6307,7 +6307,7 @@
       </c>
       <c r="AH23" s="11">
         <f t="shared" si="212"/>
-        <v>0.45390310221951918</v>
+        <v>0.45155655591591204</v>
       </c>
       <c r="AI23" s="11"/>
       <c r="AJ23" s="11">
@@ -6392,47 +6392,47 @@
       </c>
       <c r="BD23" s="11">
         <f t="shared" si="204"/>
-        <v>0.46472095891882625</v>
+        <v>0.46409108370346797</v>
       </c>
       <c r="BE23" s="11">
         <f t="shared" si="204"/>
-        <v>0.46176254250326282</v>
+        <v>0.46120653804789719</v>
       </c>
       <c r="BF23" s="11">
         <f t="shared" si="204"/>
-        <v>0.46569514164728032</v>
+        <v>0.46512712527439948</v>
       </c>
       <c r="BG23" s="11">
         <f t="shared" si="204"/>
-        <v>0.46974978303402654</v>
+        <v>0.46916992061167356</v>
       </c>
       <c r="BH23" s="11">
         <f t="shared" si="204"/>
-        <v>0.47306878336608166</v>
+        <v>0.47247963126288256</v>
       </c>
       <c r="BI23" s="11">
         <f t="shared" si="204"/>
-        <v>0.47560441858937758</v>
+        <v>0.47500841639255642</v>
       </c>
       <c r="BJ23" s="11">
         <f t="shared" ref="BJ23:BL23" si="216">BJ9/BJ5</f>
-        <v>0.47731926761318183</v>
+        <v>0.47671875399011288</v>
       </c>
       <c r="BK23" s="11">
         <f t="shared" si="216"/>
-        <v>0.47904690548938317</v>
+        <v>0.4784419457702565</v>
       </c>
       <c r="BL23" s="11">
         <f t="shared" si="216"/>
-        <v>0.48078714000064887</v>
+        <v>0.48017780220851053</v>
       </c>
       <c r="BM23" s="11">
         <f t="shared" ref="BM23:BN23" si="217">BM9/BM5</f>
-        <v>0.48253977123868891</v>
+        <v>0.48192612607996743</v>
       </c>
       <c r="BN23" s="11">
         <f t="shared" si="217"/>
-        <v>0.48430459163742978</v>
+        <v>0.48368671248932288</v>
       </c>
     </row>
     <row r="24" spans="2:179" x14ac:dyDescent="0.3">
@@ -6893,47 +6893,47 @@
       </c>
       <c r="BD25" s="10">
         <f t="shared" si="249"/>
-        <v>6.6600363372820701E-2</v>
+        <v>6.6617532474720242E-2</v>
       </c>
       <c r="BE25" s="10">
         <f t="shared" si="249"/>
-        <v>6.4964119101986184E-2</v>
+        <v>6.4985790988256395E-2</v>
       </c>
       <c r="BF25" s="10">
         <f t="shared" si="249"/>
-        <v>6.4107493508015936E-2</v>
+        <v>6.4133086714246709E-2</v>
       </c>
       <c r="BG25" s="10">
         <f t="shared" si="249"/>
-        <v>6.3850266847846782E-2</v>
+        <v>6.3880078183338296E-2</v>
       </c>
       <c r="BH25" s="10">
         <f t="shared" si="249"/>
-        <v>6.3745093339516751E-2</v>
+        <v>6.3778387064342301E-2</v>
       </c>
       <c r="BI25" s="10">
         <f t="shared" si="249"/>
-        <v>6.380733470903574E-2</v>
+        <v>6.3843361815732275E-2</v>
       </c>
       <c r="BJ25" s="10">
         <f t="shared" ref="BJ25:BL25" si="252">BJ11/BJ5</f>
-        <v>6.4050535546403914E-2</v>
+        <v>6.4088533661675676E-2</v>
       </c>
       <c r="BK25" s="10">
         <f t="shared" si="252"/>
-        <v>6.3659082863136041E-2</v>
+        <v>6.3698684930201935E-2</v>
       </c>
       <c r="BL25" s="10">
         <f t="shared" si="252"/>
-        <v>6.3264776001533671E-2</v>
+        <v>6.3305970991874377E-2</v>
       </c>
       <c r="BM25" s="10">
         <f t="shared" ref="BM25:BN25" si="253">BM11/BM5</f>
-        <v>6.2867660257337116E-2</v>
+        <v>6.2910436466149133E-2</v>
       </c>
       <c r="BN25" s="10">
         <f t="shared" si="253"/>
-        <v>6.2467782661407102E-2</v>
+        <v>6.2512127707805398E-2</v>
       </c>
     </row>
     <row r="26" spans="2:179" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="AH26" s="11">
         <f t="shared" si="262"/>
-        <v>0.29751780544473461</v>
+        <v>0.29695090425072429</v>
       </c>
       <c r="AI26" s="11"/>
       <c r="AJ26" s="11">
@@ -7151,47 +7151,47 @@
       </c>
       <c r="BD26" s="11">
         <f t="shared" si="254"/>
-        <v>0.31515666770648243</v>
+        <v>0.31492861408948769</v>
       </c>
       <c r="BE26" s="11">
         <f t="shared" si="254"/>
-        <v>0.31349259496538784</v>
+        <v>0.31332935454057009</v>
       </c>
       <c r="BF26" s="11">
         <f t="shared" si="254"/>
-        <v>0.31776839278157021</v>
+        <v>0.31758630186026876</v>
       </c>
       <c r="BG26" s="11">
         <f t="shared" si="254"/>
-        <v>0.32159811933739907</v>
+        <v>0.32139665685932439</v>
       </c>
       <c r="BH26" s="11">
         <f t="shared" si="254"/>
-        <v>0.32433603067251665</v>
+        <v>0.32412043584996153</v>
       </c>
       <c r="BI26" s="11">
         <f t="shared" si="254"/>
-        <v>0.32589241579147521</v>
+        <v>0.32566801045113619</v>
       </c>
       <c r="BJ26" s="11">
         <f t="shared" ref="BJ26:BL26" si="267">BJ13/BJ5</f>
-        <v>0.32703663943795336</v>
+        <v>0.32680484969338564</v>
       </c>
       <c r="BK26" s="11">
         <f t="shared" si="267"/>
-        <v>0.32883418288475569</v>
+        <v>0.32859537639652114</v>
       </c>
       <c r="BL26" s="11">
         <f t="shared" si="267"/>
-        <v>0.33065318225998191</v>
+        <v>0.33040737333189346</v>
       </c>
       <c r="BM26" s="11">
         <f t="shared" ref="BM26:BN26" si="268">BM13/BM5</f>
-        <v>0.33249351878513578</v>
+        <v>0.33224072510267666</v>
       </c>
       <c r="BN26" s="11">
         <f t="shared" si="268"/>
-        <v>0.33435506291409239</v>
+        <v>0.33409530557550515</v>
       </c>
     </row>
     <row r="28" spans="2:179" x14ac:dyDescent="0.3">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="AH28" s="11">
         <f t="shared" ref="AH28:AH30" si="283">AH3/AD3-1</f>
-        <v>3.0000000000000027E-2</v>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="AI28" s="11"/>
       <c r="AJ28" s="11"/>
@@ -7349,7 +7349,7 @@
       </c>
       <c r="BD28" s="11">
         <f t="shared" si="285"/>
-        <v>3.5533903535843292E-2</v>
+        <v>4.2651509499230134E-2</v>
       </c>
       <c r="BE28" s="11">
         <f t="shared" si="285"/>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="AH30" s="11">
         <f t="shared" si="283"/>
-        <v>5.1044559148846647E-2</v>
+        <v>7.3152849468029135E-2</v>
       </c>
       <c r="AI30" s="11"/>
       <c r="AJ30" s="11"/>
@@ -7792,47 +7792,47 @@
       </c>
       <c r="BD30" s="11">
         <f t="shared" si="294"/>
-        <v>5.7375068727863132E-2</v>
+        <v>6.2742209776618374E-2</v>
       </c>
       <c r="BE30" s="11">
         <f t="shared" si="294"/>
-        <v>4.5690630140479804E-2</v>
+        <v>4.5611388133967479E-2</v>
       </c>
       <c r="BF30" s="11">
         <f t="shared" si="294"/>
-        <v>3.3629578354056333E-2</v>
+        <v>3.3561772932670486E-2</v>
       </c>
       <c r="BG30" s="11">
         <f t="shared" si="294"/>
-        <v>2.4109163615521956E-2</v>
+        <v>2.4039893326146533E-2</v>
       </c>
       <c r="BH30" s="11">
         <f t="shared" si="294"/>
-        <v>2.1682905661856378E-2</v>
+        <v>2.1626333718212098E-2</v>
       </c>
       <c r="BI30" s="11">
         <f t="shared" si="294"/>
-        <v>1.9005032929225507E-2</v>
+        <v>1.8961924238747541E-2</v>
       </c>
       <c r="BJ30" s="11">
         <f t="shared" si="294"/>
-        <v>1.61270448092381E-2</v>
+        <v>1.6097971531344291E-2</v>
       </c>
       <c r="BK30" s="11">
         <f t="shared" si="294"/>
-        <v>1.6210695981130785E-2</v>
+        <v>1.6181402633663966E-2</v>
       </c>
       <c r="BL30" s="11">
         <f t="shared" si="294"/>
-        <v>1.6294970999482183E-2</v>
+        <v>1.6265460769280926E-2</v>
       </c>
       <c r="BM30" s="11">
         <f t="shared" si="286"/>
-        <v>1.6379860487836462E-2</v>
+        <v>1.6350136693098039E-2</v>
       </c>
       <c r="BN30" s="11">
         <f t="shared" si="287"/>
-        <v>1.6465354694570333E-2</v>
+        <v>1.6435420784388644E-2</v>
       </c>
       <c r="BP30" t="s">
         <v>44</v>
@@ -7847,7 +7847,7 @@
       </c>
       <c r="BQ31" s="3">
         <f>NPV(BQ30,BD17:FW17)</f>
-        <v>2610911.3716823566</v>
+        <v>2621270.2347503863</v>
       </c>
     </row>
     <row r="32" spans="2:179" x14ac:dyDescent="0.3">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="AH32" s="10">
         <f t="shared" si="304"/>
-        <v>0.16</v>
+        <v>0.15999999999999998</v>
       </c>
       <c r="AI32" s="10"/>
       <c r="AJ32" s="10">
@@ -8065,7 +8065,7 @@
       </c>
       <c r="BD32" s="10">
         <f t="shared" si="296"/>
-        <v>0.15531672066806645</v>
+        <v>0.15533710700623171</v>
       </c>
       <c r="BE32" s="10">
         <f t="shared" si="296"/>
@@ -8121,7 +8121,7 @@
       </c>
       <c r="BQ33" s="3">
         <f>BQ31+BQ32</f>
-        <v>2642199.3716823566</v>
+        <v>2652558.2347503863</v>
       </c>
     </row>
     <row r="34" spans="2:69" x14ac:dyDescent="0.3">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="BQ34" s="12">
         <f>BQ33/BI18</f>
-        <v>177.2943099452024</v>
+        <v>177.9894003684106</v>
       </c>
     </row>
     <row r="35" spans="2:69" x14ac:dyDescent="0.3">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="BQ35" s="12">
         <f>Main!D3</f>
-        <v>231.02</v>
+        <v>256.69</v>
       </c>
     </row>
     <row r="36" spans="2:69" x14ac:dyDescent="0.3">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="BQ36" s="11">
         <f>BQ34/BQ35-1</f>
-        <v>-0.23255860988138521</v>
+        <v>-0.30659784031941018</v>
       </c>
     </row>
     <row r="37" spans="2:69" x14ac:dyDescent="0.3">
@@ -8928,47 +8928,47 @@
       </c>
       <c r="BD60" s="9">
         <f t="shared" ref="BD60:BN60" si="316">BD17</f>
-        <v>109479.42973599996</v>
+        <v>109955.42396799993</v>
       </c>
       <c r="BE60" s="9">
         <f t="shared" si="316"/>
-        <v>113395.81010126883</v>
+        <v>113903.47734205435</v>
       </c>
       <c r="BF60" s="9">
         <f t="shared" si="316"/>
-        <v>118813.40451403386</v>
+        <v>119331.13205651374</v>
       </c>
       <c r="BG60" s="9">
         <f t="shared" si="316"/>
-        <v>123138.95805643471</v>
+        <v>123660.55802798801</v>
       </c>
       <c r="BH60" s="9">
         <f t="shared" si="316"/>
-        <v>126877.030812457</v>
+        <v>127402.54267066983</v>
       </c>
       <c r="BI60" s="9">
         <f t="shared" si="316"/>
-        <v>129905.404568418</v>
+        <v>130434.84123720897</v>
       </c>
       <c r="BJ60" s="9">
         <f t="shared" si="316"/>
-        <v>132461.63028191429</v>
+        <v>132995.00440370236</v>
       </c>
       <c r="BK60" s="9">
         <f t="shared" si="316"/>
-        <v>135349.95387416281</v>
+        <v>135888.66743620631</v>
       </c>
       <c r="BL60" s="9">
         <f t="shared" si="316"/>
-        <v>138316.44997199456</v>
+        <v>138860.55064572254</v>
       </c>
       <c r="BM60" s="9">
         <f t="shared" si="316"/>
-        <v>141364.56817866082</v>
+        <v>141914.10985922653</v>
       </c>
       <c r="BN60" s="9">
         <f t="shared" si="316"/>
-        <v>144496.74997982313</v>
+        <v>145051.78707719414</v>
       </c>
     </row>
     <row r="61" spans="2:66" x14ac:dyDescent="0.3">
@@ -10057,47 +10057,47 @@
       </c>
       <c r="BD71" s="9">
         <f t="shared" si="321"/>
-        <v>132786.53473599994</v>
+        <v>133262.52896799991</v>
       </c>
       <c r="BE71" s="9">
         <f t="shared" ref="BE71:BN71" si="322">BE60+SUM(BE61:BE70)</f>
-        <v>136878.47502626883</v>
+        <v>137386.14226705435</v>
       </c>
       <c r="BF71" s="9">
         <f t="shared" si="322"/>
-        <v>142473.09740765885</v>
+        <v>142990.82495013875</v>
       </c>
       <c r="BG71" s="9">
         <f t="shared" si="322"/>
-        <v>146977.16020496783</v>
+        <v>147498.76017652114</v>
       </c>
       <c r="BH71" s="9">
         <f t="shared" si="322"/>
-        <v>150895.23687007718</v>
+        <v>151420.74872829003</v>
       </c>
       <c r="BI71" s="9">
         <f t="shared" si="322"/>
-        <v>154105.12268365413</v>
+        <v>154634.5593524451</v>
       </c>
       <c r="BJ71" s="9">
         <f t="shared" si="322"/>
-        <v>156844.38222532772</v>
+        <v>157377.75634711579</v>
       </c>
       <c r="BK71" s="9">
         <f t="shared" si="322"/>
-        <v>159917.27516727045</v>
+        <v>160455.98872931395</v>
       </c>
       <c r="BL71" s="9">
         <f t="shared" si="322"/>
-        <v>163069.89001744462</v>
+        <v>163613.9906911726</v>
       </c>
       <c r="BM71" s="9">
         <f t="shared" si="322"/>
-        <v>166305.69039167382</v>
+        <v>166855.23207223954</v>
       </c>
       <c r="BN71" s="9">
         <f t="shared" si="322"/>
-        <v>169627.13192091021</v>
+        <v>170182.16901828122</v>
       </c>
     </row>
     <row r="72" spans="2:151" x14ac:dyDescent="0.3">
@@ -10284,393 +10284,393 @@
       </c>
       <c r="BD73" s="9">
         <f t="shared" si="324"/>
-        <v>122786.53473599994</v>
+        <v>123262.52896799991</v>
       </c>
       <c r="BE73" s="9">
         <f t="shared" ref="BE73:BN73" si="325">BE71-BE72</f>
-        <v>126878.47502626883</v>
+        <v>127386.14226705435</v>
       </c>
       <c r="BF73" s="9">
         <f t="shared" si="325"/>
-        <v>132473.09740765885</v>
+        <v>132990.82495013875</v>
       </c>
       <c r="BG73" s="9">
         <f t="shared" si="325"/>
-        <v>136977.16020496783</v>
+        <v>137498.76017652114</v>
       </c>
       <c r="BH73" s="9">
         <f t="shared" si="325"/>
-        <v>140895.23687007718</v>
+        <v>141420.74872829003</v>
       </c>
       <c r="BI73" s="9">
         <f t="shared" si="325"/>
-        <v>144105.12268365413</v>
+        <v>144634.5593524451</v>
       </c>
       <c r="BJ73" s="9">
         <f t="shared" si="325"/>
-        <v>146844.38222532772</v>
+        <v>147377.75634711579</v>
       </c>
       <c r="BK73" s="9">
         <f t="shared" si="325"/>
-        <v>149917.27516727045</v>
+        <v>150455.98872931395</v>
       </c>
       <c r="BL73" s="9">
         <f t="shared" si="325"/>
-        <v>153069.89001744462</v>
+        <v>153613.9906911726</v>
       </c>
       <c r="BM73" s="9">
         <f t="shared" si="325"/>
-        <v>156305.69039167382</v>
+        <v>156855.23207223954</v>
       </c>
       <c r="BN73" s="9">
         <f t="shared" si="325"/>
-        <v>159627.13192091021</v>
+        <v>160182.16901828122</v>
       </c>
       <c r="BO73" s="6">
         <f>BN73*(1+$BQ$29)</f>
-        <v>158030.8606017011</v>
+        <v>158580.3473280984</v>
       </c>
       <c r="BP73" s="6">
         <f t="shared" ref="BP73:EA73" si="326">BO73*(1+$BQ$29)</f>
-        <v>156450.5519956841</v>
+        <v>156994.54385481743</v>
       </c>
       <c r="BQ73" s="6">
         <f t="shared" si="326"/>
-        <v>154886.04647572726</v>
+        <v>155424.59841626926</v>
       </c>
       <c r="BR73" s="6">
         <f t="shared" si="326"/>
-        <v>153337.18601096998</v>
+        <v>153870.35243210656</v>
       </c>
       <c r="BS73" s="6">
         <f t="shared" si="326"/>
-        <v>151803.81415086027</v>
+        <v>152331.64890778551</v>
       </c>
       <c r="BT73" s="6">
         <f t="shared" si="326"/>
-        <v>150285.77600935166</v>
+        <v>150808.33241870767</v>
       </c>
       <c r="BU73" s="6">
         <f t="shared" si="326"/>
-        <v>148782.91824925813</v>
+        <v>149300.24909452058</v>
       </c>
       <c r="BV73" s="6">
         <f t="shared" si="326"/>
-        <v>147295.08906676556</v>
+        <v>147807.24660357536</v>
       </c>
       <c r="BW73" s="6">
         <f t="shared" si="326"/>
-        <v>145822.13817609791</v>
+        <v>146329.17413753961</v>
       </c>
       <c r="BX73" s="6">
         <f t="shared" si="326"/>
-        <v>144363.91679433692</v>
+        <v>144865.8823961642</v>
       </c>
       <c r="BY73" s="6">
         <f t="shared" si="326"/>
-        <v>142920.27762639357</v>
+        <v>143417.22357220255</v>
       </c>
       <c r="BZ73" s="6">
         <f t="shared" si="326"/>
-        <v>141491.07485012963</v>
+        <v>141983.05133648054</v>
       </c>
       <c r="CA73" s="6">
         <f t="shared" si="326"/>
-        <v>140076.16410162832</v>
+        <v>140563.22082311573</v>
       </c>
       <c r="CB73" s="6">
         <f t="shared" si="326"/>
-        <v>138675.40246061204</v>
+        <v>139157.58861488456</v>
       </c>
       <c r="CC73" s="6">
         <f t="shared" si="326"/>
-        <v>137288.64843600593</v>
+        <v>137766.01272873572</v>
       </c>
       <c r="CD73" s="6">
         <f t="shared" si="326"/>
-        <v>135915.76195164587</v>
+        <v>136388.35260144837</v>
       </c>
       <c r="CE73" s="6">
         <f t="shared" si="326"/>
-        <v>134556.60433212941</v>
+        <v>135024.46907543388</v>
       </c>
       <c r="CF73" s="6">
         <f t="shared" si="326"/>
-        <v>133211.03828880811</v>
+        <v>133674.22438467955</v>
       </c>
       <c r="CG73" s="6">
         <f t="shared" si="326"/>
-        <v>131878.92790592002</v>
+        <v>132337.48214083276</v>
       </c>
       <c r="CH73" s="6">
         <f t="shared" si="326"/>
-        <v>130560.13862686082</v>
+        <v>131014.10731942442</v>
       </c>
       <c r="CI73" s="6">
         <f t="shared" si="326"/>
-        <v>129254.53724059221</v>
+        <v>129703.96624623018</v>
       </c>
       <c r="CJ73" s="6">
         <f t="shared" si="326"/>
-        <v>127961.99186818629</v>
+        <v>128406.92658376787</v>
       </c>
       <c r="CK73" s="6">
         <f t="shared" si="326"/>
-        <v>126682.37194950442</v>
+        <v>127122.85731793019</v>
       </c>
       <c r="CL73" s="6">
         <f t="shared" si="326"/>
-        <v>125415.54823000937</v>
+        <v>125851.62874475088</v>
       </c>
       <c r="CM73" s="6">
         <f t="shared" si="326"/>
-        <v>124161.39274770928</v>
+        <v>124593.11245730337</v>
       </c>
       <c r="CN73" s="6">
         <f t="shared" si="326"/>
-        <v>122919.77882023218</v>
+        <v>123347.18133273034</v>
       </c>
       <c r="CO73" s="6">
         <f t="shared" si="326"/>
-        <v>121690.58103202986</v>
+        <v>122113.70951940304</v>
       </c>
       <c r="CP73" s="6">
         <f t="shared" si="326"/>
-        <v>120473.67522170956</v>
+        <v>120892.57242420901</v>
       </c>
       <c r="CQ73" s="6">
         <f t="shared" si="326"/>
-        <v>119268.93846949247</v>
+        <v>119683.64669996692</v>
       </c>
       <c r="CR73" s="6">
         <f t="shared" si="326"/>
-        <v>118076.24908479754</v>
+        <v>118486.81023296725</v>
       </c>
       <c r="CS73" s="6">
         <f t="shared" si="326"/>
-        <v>116895.48659394956</v>
+        <v>117301.94213063759</v>
       </c>
       <c r="CT73" s="6">
         <f t="shared" si="326"/>
-        <v>115726.53172801007</v>
+        <v>116128.92270933121</v>
       </c>
       <c r="CU73" s="6">
         <f t="shared" si="326"/>
-        <v>114569.26641072996</v>
+        <v>114967.6334822379</v>
       </c>
       <c r="CV73" s="6">
         <f t="shared" si="326"/>
-        <v>113423.57374662266</v>
+        <v>113817.95714741552</v>
       </c>
       <c r="CW73" s="6">
         <f t="shared" si="326"/>
-        <v>112289.33800915643</v>
+        <v>112679.77757594136</v>
       </c>
       <c r="CX73" s="6">
         <f t="shared" si="326"/>
-        <v>111166.44462906486</v>
+        <v>111552.97980018194</v>
       </c>
       <c r="CY73" s="6">
         <f t="shared" si="326"/>
-        <v>110054.78018277421</v>
+        <v>110437.45000218012</v>
       </c>
       <c r="CZ73" s="6">
         <f t="shared" si="326"/>
-        <v>108954.23238094646</v>
+        <v>109333.07550215832</v>
       </c>
       <c r="DA73" s="6">
         <f t="shared" si="326"/>
-        <v>107864.69005713699</v>
+        <v>108239.74474713673</v>
       </c>
       <c r="DB73" s="6">
         <f t="shared" si="326"/>
-        <v>106786.04315656562</v>
+        <v>107157.34729966537</v>
       </c>
       <c r="DC73" s="6">
         <f t="shared" si="326"/>
-        <v>105718.18272499996</v>
+        <v>106085.77382666872</v>
       </c>
       <c r="DD73" s="6">
         <f t="shared" si="326"/>
-        <v>104661.00089774997</v>
+        <v>105024.91608840204</v>
       </c>
       <c r="DE73" s="6">
         <f t="shared" si="326"/>
-        <v>103614.39088877247</v>
+        <v>103974.66692751802</v>
       </c>
       <c r="DF73" s="6">
         <f t="shared" si="326"/>
-        <v>102578.24697988475</v>
+        <v>102934.92025824284</v>
       </c>
       <c r="DG73" s="6">
         <f t="shared" si="326"/>
-        <v>101552.46451008589</v>
+        <v>101905.57105566042</v>
       </c>
       <c r="DH73" s="6">
         <f t="shared" si="326"/>
-        <v>100536.93986498503</v>
+        <v>100886.51534510381</v>
       </c>
       <c r="DI73" s="6">
         <f t="shared" si="326"/>
-        <v>99531.570466335179</v>
+        <v>99877.650191652763</v>
       </c>
       <c r="DJ73" s="6">
         <f t="shared" si="326"/>
-        <v>98536.254761671822</v>
+        <v>98878.87368973624</v>
       </c>
       <c r="DK73" s="6">
         <f t="shared" si="326"/>
-        <v>97550.8922140551</v>
+        <v>97890.084952838879</v>
       </c>
       <c r="DL73" s="6">
         <f t="shared" si="326"/>
-        <v>96575.38329191455</v>
+        <v>96911.184103310487</v>
       </c>
       <c r="DM73" s="6">
         <f t="shared" si="326"/>
-        <v>95609.629458995405</v>
+        <v>95942.072262277376</v>
       </c>
       <c r="DN73" s="6">
         <f t="shared" si="326"/>
-        <v>94653.533164405453</v>
+        <v>94982.651539654602</v>
       </c>
       <c r="DO73" s="6">
         <f t="shared" si="326"/>
-        <v>93706.997832761394</v>
+        <v>94032.825024258054</v>
       </c>
       <c r="DP73" s="6">
         <f t="shared" si="326"/>
-        <v>92769.927854433772</v>
+        <v>93092.496774015468</v>
       </c>
       <c r="DQ73" s="6">
         <f t="shared" si="326"/>
-        <v>91842.228575889429</v>
+        <v>92161.571806275315</v>
       </c>
       <c r="DR73" s="6">
         <f t="shared" si="326"/>
-        <v>90923.806290130538</v>
+        <v>91239.956088212566</v>
       </c>
       <c r="DS73" s="6">
         <f t="shared" si="326"/>
-        <v>90014.568227229232</v>
+        <v>90327.556527330438</v>
       </c>
       <c r="DT73" s="6">
         <f t="shared" si="326"/>
-        <v>89114.422544956935</v>
+        <v>89424.280962057135</v>
       </c>
       <c r="DU73" s="6">
         <f t="shared" si="326"/>
-        <v>88223.278319507372</v>
+        <v>88530.038152436566</v>
       </c>
       <c r="DV73" s="6">
         <f t="shared" si="326"/>
-        <v>87341.045536312304</v>
+        <v>87644.737770912194</v>
       </c>
       <c r="DW73" s="6">
         <f t="shared" si="326"/>
-        <v>86467.635080949185</v>
+        <v>86768.290393203075</v>
       </c>
       <c r="DX73" s="6">
         <f t="shared" si="326"/>
-        <v>85602.958730139697</v>
+        <v>85900.607489271046</v>
       </c>
       <c r="DY73" s="6">
         <f t="shared" si="326"/>
-        <v>84746.9291428383</v>
+        <v>85041.60141437834</v>
       </c>
       <c r="DZ73" s="6">
         <f t="shared" si="326"/>
-        <v>83899.45985140992</v>
+        <v>84191.18540023455</v>
       </c>
       <c r="EA73" s="6">
         <f t="shared" si="326"/>
-        <v>83060.465252895825</v>
+        <v>83349.273546232202</v>
       </c>
       <c r="EB73" s="6">
         <f t="shared" ref="EB73:EU73" si="327">EA73*(1+$BQ$29)</f>
-        <v>82229.860600366868</v>
+        <v>82515.78081076988</v>
       </c>
       <c r="EC73" s="6">
         <f t="shared" si="327"/>
-        <v>81407.561994363205</v>
+        <v>81690.623002662178</v>
       </c>
       <c r="ED73" s="6">
         <f t="shared" si="327"/>
-        <v>80593.486374419575</v>
+        <v>80873.716772635555</v>
       </c>
       <c r="EE73" s="6">
         <f t="shared" si="327"/>
-        <v>79787.551510675374</v>
+        <v>80064.979604909196</v>
       </c>
       <c r="EF73" s="6">
         <f t="shared" si="327"/>
-        <v>78989.675995568614</v>
+        <v>79264.3298088601</v>
       </c>
       <c r="EG73" s="6">
         <f t="shared" si="327"/>
-        <v>78199.779235612921</v>
+        <v>78471.686510771498</v>
       </c>
       <c r="EH73" s="6">
         <f t="shared" si="327"/>
-        <v>77417.781443256798</v>
+        <v>77686.969645663776</v>
       </c>
       <c r="EI73" s="6">
         <f t="shared" si="327"/>
-        <v>76643.603628824232</v>
+        <v>76910.099949207142</v>
       </c>
       <c r="EJ73" s="6">
         <f t="shared" si="327"/>
-        <v>75877.167592535989</v>
+        <v>76140.998949715067</v>
       </c>
       <c r="EK73" s="6">
         <f t="shared" si="327"/>
-        <v>75118.395916610621</v>
+        <v>75379.588960217923</v>
       </c>
       <c r="EL73" s="6">
         <f t="shared" si="327"/>
-        <v>74367.21195744451</v>
+        <v>74625.793070615749</v>
       </c>
       <c r="EM73" s="6">
         <f t="shared" si="327"/>
-        <v>73623.539837870063</v>
+        <v>73879.535139909596</v>
       </c>
       <c r="EN73" s="6">
         <f t="shared" si="327"/>
-        <v>72887.30443949136</v>
+        <v>73140.739788510502</v>
       </c>
       <c r="EO73" s="6">
         <f t="shared" si="327"/>
-        <v>72158.431395096442</v>
+        <v>72409.332390625394</v>
       </c>
       <c r="EP73" s="6">
         <f t="shared" si="327"/>
-        <v>71436.847081145475</v>
+        <v>71685.239066719136</v>
       </c>
       <c r="EQ73" s="6">
         <f t="shared" si="327"/>
-        <v>70722.478610334016</v>
+        <v>70968.386676051945</v>
       </c>
       <c r="ER73" s="6">
         <f t="shared" si="327"/>
-        <v>70015.253824230676</v>
+        <v>70258.702809291426</v>
       </c>
       <c r="ES73" s="6">
         <f t="shared" si="327"/>
-        <v>69315.101285988363</v>
+        <v>69556.115781198518</v>
       </c>
       <c r="ET73" s="6">
         <f t="shared" si="327"/>
-        <v>68621.950273128474</v>
+        <v>68860.554623386532</v>
       </c>
       <c r="EU73" s="6">
         <f t="shared" si="327"/>
-        <v>67935.730770397189</v>
+        <v>68171.949077152662</v>
       </c>
     </row>
     <row r="75" spans="2:151" x14ac:dyDescent="0.3">
       <c r="BQ75" s="3">
         <f>NPV(BQ30,BD73:EU73)</f>
-        <v>2700460.8344837613</v>
+        <v>2710132.6467532795</v>
       </c>
     </row>
     <row r="76" spans="2:151" x14ac:dyDescent="0.3">
@@ -10682,25 +10682,25 @@
     <row r="77" spans="2:151" x14ac:dyDescent="0.3">
       <c r="BQ77" s="3">
         <f>BQ75+BQ76</f>
-        <v>2731748.8344837613</v>
+        <v>2741420.6467532795</v>
       </c>
     </row>
     <row r="78" spans="2:151" x14ac:dyDescent="0.3">
       <c r="BQ78" s="12">
         <f>BQ77/BN18</f>
-        <v>183.30317149573315</v>
+        <v>183.9521600999322</v>
       </c>
     </row>
     <row r="79" spans="2:151" x14ac:dyDescent="0.3">
       <c r="BQ79" s="12">
         <f>Main!D3</f>
-        <v>231.02</v>
+        <v>256.69</v>
       </c>
     </row>
     <row r="80" spans="2:151" x14ac:dyDescent="0.3">
       <c r="BQ80" s="11">
         <f>BQ78/BQ79-1</f>
-        <v>-0.2065484741765512</v>
+        <v>-0.28336842066332069</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/AAPL.xlsx
+++ b/Financial Analysis/AAPL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FBF8953-DE73-4BAF-8CC3-96F5DEFCFC2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D7E9E4B-11E1-40E1-95B6-36BFEF5A7809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{9DABBB29-C94C-41BD-A4AD-A53C3313D92F}"/>
   </bookViews>
@@ -343,9 +343,6 @@
     <t>D/T</t>
   </si>
   <si>
-    <t>Overvalued</t>
-  </si>
-  <si>
     <t>Q126</t>
   </si>
   <si>
@@ -359,6 +356,9 @@
   </si>
   <si>
     <t>Net Margin</t>
+  </si>
+  <si>
+    <t>Slightly overvalued</t>
   </si>
 </sst>
 </file>
@@ -502,14 +502,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
@@ -526,8 +526,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25359360" y="0"/>
-          <a:ext cx="0" cy="6713220"/>
+          <a:off x="26075640" y="0"/>
+          <a:ext cx="0" cy="6896100"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -552,13 +552,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>59</xdr:col>
+      <xdr:col>60</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>59</xdr:col>
+      <xdr:col>60</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>94</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
@@ -576,8 +576,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="30236160" y="0"/>
-          <a:ext cx="0" cy="17114520"/>
+          <a:off x="44180760" y="0"/>
+          <a:ext cx="0" cy="17297400"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -926,17 +926,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="12">
-        <v>276.72000000000003</v>
+        <v>256.72000000000003</v>
       </c>
       <c r="E3" s="2">
-        <v>45961</v>
+        <v>46052</v>
       </c>
       <c r="F3" s="2">
         <f ca="1">TODAY()</f>
-        <v>45961</v>
+        <v>46059</v>
       </c>
       <c r="G3" s="2">
-        <v>45686</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -944,11 +944,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="3">
-        <f>14815.3</f>
-        <v>14815.3</v>
+        <f>14748.2</f>
+        <v>14748.2</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -957,7 +957,7 @@
       </c>
       <c r="D5" s="3">
         <f>D3*D4</f>
-        <v>4099689.8160000001</v>
+        <v>3786157.9040000006</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -965,11 +965,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="3">
-        <f>35934+18763+77723</f>
-        <v>132420</v>
+        <f>45317+21590+77888</f>
+        <v>144795</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -977,11 +977,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="3">
-        <f>7979+12350+78328</f>
-        <v>98657</v>
+        <f>1997+11827+76685</f>
+        <v>90509</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -990,7 +990,7 @@
       </c>
       <c r="D8" s="3">
         <f>D6-D7</f>
-        <v>33763</v>
+        <v>54286</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -999,7 +999,7 @@
       </c>
       <c r="D9" s="3">
         <f>D5-D8</f>
-        <v>4065926.8160000001</v>
+        <v>3731871.9040000006</v>
       </c>
     </row>
   </sheetData>
@@ -1366,16 +1366,16 @@
         <v>92</v>
       </c>
       <c r="AI2" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="AJ2" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="AJ2" s="5" t="s">
+      <c r="AK2" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="AK2" s="5" t="s">
+      <c r="AL2" s="5" t="s">
         <v>108</v>
-      </c>
-      <c r="AL2" s="5" t="s">
-        <v>109</v>
       </c>
       <c r="AM2" s="5"/>
       <c r="AN2" s="5">
@@ -1590,7 +1590,9 @@
       <c r="AH3" s="3">
         <v>73716</v>
       </c>
-      <c r="AI3" s="3"/>
+      <c r="AI3" s="3">
+        <v>113743</v>
+      </c>
       <c r="AJ3" s="3"/>
       <c r="AK3" s="3"/>
       <c r="AL3" s="3"/>
@@ -1781,7 +1783,9 @@
       <c r="AH4" s="3">
         <v>28750</v>
       </c>
-      <c r="AI4" s="3"/>
+      <c r="AI4" s="3">
+        <v>30013</v>
+      </c>
       <c r="AJ4" s="3"/>
       <c r="AK4" s="3"/>
       <c r="AL4" s="3"/>
@@ -2004,7 +2008,10 @@
         <f t="shared" si="41"/>
         <v>102466</v>
       </c>
-      <c r="AI5" s="9"/>
+      <c r="AI5" s="9">
+        <f t="shared" ref="AI5" si="42">AI3+AI4</f>
+        <v>143756</v>
+      </c>
       <c r="AJ5" s="9"/>
       <c r="AK5" s="9"/>
       <c r="AL5" s="9"/>
@@ -2061,63 +2068,63 @@
         <v>274515</v>
       </c>
       <c r="BD5" s="9">
-        <f t="shared" ref="BD5:BM5" si="42">BD3+BD4</f>
+        <f t="shared" ref="BD5:BM5" si="43">BD3+BD4</f>
         <v>365817</v>
       </c>
       <c r="BE5" s="9">
-        <f t="shared" ref="BE5:BF5" si="43">BE3+BE4</f>
+        <f t="shared" ref="BE5:BF5" si="44">BE3+BE4</f>
         <v>394328</v>
       </c>
       <c r="BF5" s="9">
+        <f t="shared" si="44"/>
+        <v>383285</v>
+      </c>
+      <c r="BG5" s="9">
+        <f t="shared" ref="BG5" si="45">BG3+BG4</f>
+        <v>391035</v>
+      </c>
+      <c r="BH5" s="9">
         <f t="shared" si="43"/>
-        <v>383285</v>
-      </c>
-      <c r="BG5" s="9">
-        <f t="shared" ref="BG5" si="44">BG3+BG4</f>
-        <v>391035</v>
-      </c>
-      <c r="BH5" s="9">
-        <f t="shared" si="42"/>
         <v>416161</v>
       </c>
       <c r="BI5" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>435195.31000000006</v>
       </c>
       <c r="BJ5" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>449848.32720000006</v>
       </c>
       <c r="BK5" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>460712.35924200004</v>
       </c>
       <c r="BL5" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>470717.46819138003</v>
       </c>
       <c r="BM5" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>479675.55634189985</v>
       </c>
       <c r="BN5" s="9">
-        <f t="shared" ref="BN5:BP5" si="45">BN3+BN4</f>
+        <f t="shared" ref="BN5:BP5" si="46">BN3+BN4</f>
         <v>487419.61191021901</v>
       </c>
       <c r="BO5" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>495329.52703436837</v>
       </c>
       <c r="BP5" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>503409.61287991068</v>
       </c>
       <c r="BQ5" s="9">
-        <f t="shared" ref="BQ5:BR5" si="46">BQ3+BQ4</f>
+        <f t="shared" ref="BQ5:BR5" si="47">BQ3+BQ4</f>
         <v>511664.30330116436</v>
       </c>
       <c r="BR5" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>520098.15845540416</v>
       </c>
     </row>
@@ -2221,7 +2228,9 @@
       <c r="AH6" s="3">
         <v>47019</v>
       </c>
-      <c r="AI6" s="3"/>
+      <c r="AI6" s="3">
+        <v>67478</v>
+      </c>
       <c r="AJ6" s="3"/>
       <c r="AK6" s="3"/>
       <c r="AL6" s="3"/>
@@ -2276,39 +2285,39 @@
         <v>199214.24670000002</v>
       </c>
       <c r="BJ6" s="3">
-        <f t="shared" ref="BJ6:BR6" si="47">BJ3*0.63</f>
+        <f t="shared" ref="BJ6:BR6" si="48">BJ3*0.63</f>
         <v>203198.53163400001</v>
       </c>
       <c r="BK6" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>205230.51695034001</v>
       </c>
       <c r="BL6" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>207282.82211984342</v>
       </c>
       <c r="BM6" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>209355.65034104185</v>
       </c>
       <c r="BN6" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>211449.20684445227</v>
       </c>
       <c r="BO6" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>213563.6989128968</v>
       </c>
       <c r="BP6" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>215699.33590202578</v>
       </c>
       <c r="BQ6" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>217856.32926104605</v>
       </c>
       <c r="BR6" s="3">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>220034.89255365651</v>
       </c>
     </row>
@@ -2412,7 +2421,9 @@
       <c r="AH7" s="3">
         <v>7106</v>
       </c>
-      <c r="AI7" s="3"/>
+      <c r="AI7" s="3">
+        <v>7047</v>
+      </c>
       <c r="AJ7" s="3"/>
       <c r="AK7" s="3"/>
       <c r="AL7" s="3"/>
@@ -2467,39 +2478,39 @@
         <v>28555.732800000002</v>
       </c>
       <c r="BJ7" s="3">
-        <f t="shared" ref="BJ7:BR7" si="48">BJ4*0.24</f>
+        <f t="shared" ref="BJ7:BR7" si="49">BJ4*0.24</f>
         <v>30554.634096000005</v>
       </c>
       <c r="BK7" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>32387.912141760004</v>
       </c>
       <c r="BL7" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>34007.307748848005</v>
       </c>
       <c r="BM7" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>35367.600058801931</v>
       </c>
       <c r="BN7" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>36428.628060565985</v>
       </c>
       <c r="BO7" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>37521.486902382967</v>
       </c>
       <c r="BP7" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>38647.131509454455</v>
       </c>
       <c r="BQ7" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>39806.545454738087</v>
       </c>
       <c r="BR7" s="3">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>41000.741818380237</v>
       </c>
     </row>
@@ -2508,134 +2519,137 @@
         <v>30</v>
       </c>
       <c r="C8" s="3">
-        <f t="shared" ref="C8:N8" si="49">C6+C7</f>
+        <f t="shared" ref="C8:N8" si="50">C6+C7</f>
         <v>54381</v>
       </c>
       <c r="D8" s="3">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>37715</v>
       </c>
       <c r="E8" s="3">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>32844</v>
       </c>
       <c r="F8" s="3">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>38816</v>
       </c>
       <c r="G8" s="3">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>52279</v>
       </c>
       <c r="H8" s="3">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>36194</v>
       </c>
       <c r="I8" s="3">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>33582</v>
       </c>
       <c r="J8" s="3">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>39727</v>
       </c>
       <c r="K8" s="3">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>56602</v>
       </c>
       <c r="L8" s="3">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>35943</v>
       </c>
       <c r="M8" s="3">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>37005</v>
       </c>
       <c r="N8" s="3">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>40009</v>
       </c>
       <c r="O8" s="3">
-        <f t="shared" ref="O8:S8" si="50">O6+O7</f>
+        <f t="shared" ref="O8:S8" si="51">O6+O7</f>
         <v>67111</v>
       </c>
       <c r="P8" s="3">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>51505</v>
       </c>
       <c r="Q8" s="3">
-        <f t="shared" ref="Q8:R8" si="51">Q6+Q7</f>
+        <f t="shared" ref="Q8:R8" si="52">Q6+Q7</f>
         <v>46179</v>
       </c>
       <c r="R8" s="3">
+        <f t="shared" si="52"/>
+        <v>48186</v>
+      </c>
+      <c r="S8" s="3">
         <f t="shared" si="51"/>
-        <v>48186</v>
-      </c>
-      <c r="S8" s="3">
-        <f t="shared" si="50"/>
         <v>69702</v>
       </c>
       <c r="T8" s="3">
-        <f t="shared" ref="T8" si="52">T6+T7</f>
+        <f t="shared" ref="T8" si="53">T6+T7</f>
         <v>54719</v>
       </c>
       <c r="U8" s="3">
-        <f t="shared" ref="U8" si="53">U6+U7</f>
+        <f t="shared" ref="U8" si="54">U6+U7</f>
         <v>47074</v>
       </c>
       <c r="V8" s="3">
-        <f t="shared" ref="V8" si="54">V6+V7</f>
+        <f t="shared" ref="V8" si="55">V6+V7</f>
         <v>52051</v>
       </c>
       <c r="W8" s="3">
-        <f t="shared" ref="W8:X8" si="55">W6+W7</f>
+        <f t="shared" ref="W8:X8" si="56">W6+W7</f>
         <v>66822</v>
       </c>
       <c r="X8" s="3">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>52860</v>
       </c>
       <c r="Y8" s="3">
-        <f t="shared" ref="Y8:Z8" si="56">Y6+Y7</f>
+        <f t="shared" ref="Y8:Z8" si="57">Y6+Y7</f>
         <v>45384</v>
       </c>
       <c r="Z8" s="3">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>49071</v>
       </c>
       <c r="AA8" s="3">
-        <f t="shared" ref="AA8:AH8" si="57">AA6+AA7</f>
+        <f t="shared" ref="AA8:AH8" si="58">AA6+AA7</f>
         <v>64720</v>
       </c>
       <c r="AB8" s="3">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>48482</v>
       </c>
       <c r="AC8" s="3">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>46099</v>
       </c>
       <c r="AD8" s="3">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>51051</v>
       </c>
       <c r="AE8" s="3">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>66025</v>
       </c>
       <c r="AF8" s="3">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>50492</v>
       </c>
       <c r="AG8" s="3">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>50318</v>
       </c>
       <c r="AH8" s="3">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>54125</v>
       </c>
-      <c r="AI8" s="3"/>
+      <c r="AI8" s="3">
+        <f t="shared" ref="AI8" si="59">AI6+AI7</f>
+        <v>74525</v>
+      </c>
       <c r="AJ8" s="3"/>
       <c r="AK8" s="3"/>
       <c r="AL8" s="3"/>
@@ -2692,63 +2706,63 @@
         <v>169559</v>
       </c>
       <c r="BD8" s="3">
-        <f t="shared" ref="BD8:BR8" si="58">BD6+BD7</f>
+        <f t="shared" ref="BD8:BR8" si="60">BD6+BD7</f>
         <v>212981</v>
       </c>
       <c r="BE8" s="3">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>223546</v>
       </c>
       <c r="BF8" s="3">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>214137</v>
       </c>
       <c r="BG8" s="3">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>210352</v>
       </c>
       <c r="BH8" s="3">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>220960</v>
       </c>
       <c r="BI8" s="3">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>227769.97950000002</v>
       </c>
       <c r="BJ8" s="3">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>233753.16573000001</v>
       </c>
       <c r="BK8" s="3">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>237618.42909210001</v>
       </c>
       <c r="BL8" s="3">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>241290.12986869144</v>
       </c>
       <c r="BM8" s="3">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>244723.25039984379</v>
       </c>
       <c r="BN8" s="3">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>247877.83490501827</v>
       </c>
       <c r="BO8" s="3">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>251085.18581527978</v>
       </c>
       <c r="BP8" s="3">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>254346.46741148023</v>
       </c>
       <c r="BQ8" s="3">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>257662.87471578413</v>
       </c>
       <c r="BR8" s="3">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>261035.63437203673</v>
       </c>
     </row>
@@ -2757,260 +2771,263 @@
         <v>26</v>
       </c>
       <c r="C9" s="9">
-        <f t="shared" ref="C9:N9" si="59">C5-C8</f>
+        <f t="shared" ref="C9:N9" si="61">C5-C8</f>
         <v>33912</v>
       </c>
       <c r="D9" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>23422</v>
       </c>
       <c r="E9" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>20421</v>
       </c>
       <c r="F9" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>24084</v>
       </c>
       <c r="G9" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>32031</v>
       </c>
       <c r="H9" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>21821</v>
       </c>
       <c r="I9" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>20227</v>
       </c>
       <c r="J9" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>24313</v>
       </c>
       <c r="K9" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>35217</v>
       </c>
       <c r="L9" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>22370</v>
       </c>
       <c r="M9" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>22680</v>
       </c>
       <c r="N9" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>24689</v>
       </c>
       <c r="O9" s="9">
-        <f t="shared" ref="O9:S9" si="60">O5-O8</f>
+        <f t="shared" ref="O9:S9" si="62">O5-O8</f>
         <v>44328</v>
       </c>
       <c r="P9" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>38079</v>
       </c>
       <c r="Q9" s="9">
-        <f t="shared" ref="Q9:R9" si="61">Q5-Q8</f>
+        <f t="shared" ref="Q9:R9" si="63">Q5-Q8</f>
         <v>35255</v>
       </c>
       <c r="R9" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>35174</v>
       </c>
       <c r="S9" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>54243</v>
       </c>
       <c r="T9" s="9">
-        <f t="shared" ref="T9" si="62">T5-T8</f>
+        <f t="shared" ref="T9" si="64">T5-T8</f>
         <v>42559</v>
       </c>
       <c r="U9" s="9">
-        <f t="shared" ref="U9" si="63">U5-U8</f>
+        <f t="shared" ref="U9" si="65">U5-U8</f>
         <v>35885</v>
       </c>
       <c r="V9" s="9">
-        <f t="shared" ref="V9" si="64">V5-V8</f>
+        <f t="shared" ref="V9" si="66">V5-V8</f>
         <v>38095</v>
       </c>
       <c r="W9" s="9">
-        <f t="shared" ref="W9:X9" si="65">W5-W8</f>
+        <f t="shared" ref="W9:X9" si="67">W5-W8</f>
         <v>50332</v>
       </c>
       <c r="X9" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>41976</v>
       </c>
       <c r="Y9" s="9">
-        <f t="shared" ref="Y9:Z9" si="66">Y5-Y8</f>
+        <f t="shared" ref="Y9:Z9" si="68">Y5-Y8</f>
         <v>36413</v>
       </c>
       <c r="Z9" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>40427</v>
       </c>
       <c r="AA9" s="9">
-        <f t="shared" ref="AA9:AH9" si="67">AA5-AA8</f>
+        <f t="shared" ref="AA9:AH9" si="69">AA5-AA8</f>
         <v>54855</v>
       </c>
       <c r="AB9" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>42271</v>
       </c>
       <c r="AC9" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>39678</v>
       </c>
       <c r="AD9" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>43879</v>
       </c>
       <c r="AE9" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>58275</v>
       </c>
       <c r="AF9" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>44867</v>
       </c>
       <c r="AG9" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>43718</v>
       </c>
       <c r="AH9" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>48341</v>
       </c>
-      <c r="AI9" s="9"/>
+      <c r="AI9" s="9">
+        <f t="shared" ref="AI9" si="70">AI5-AI8</f>
+        <v>69231</v>
+      </c>
       <c r="AJ9" s="9"/>
       <c r="AK9" s="9"/>
       <c r="AL9" s="9"/>
       <c r="AM9" s="9"/>
       <c r="AN9" s="9">
-        <f t="shared" ref="AN9" si="68">AN5-AN8</f>
+        <f t="shared" ref="AN9" si="71">AN5-AN8</f>
         <v>4042</v>
       </c>
       <c r="AO9" s="9">
-        <f t="shared" ref="AO9:AP9" si="69">AO5-AO8</f>
+        <f t="shared" ref="AO9:AP9" si="72">AO5-AO8</f>
         <v>5598</v>
       </c>
       <c r="AP9" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="72"/>
         <v>8154</v>
       </c>
       <c r="AQ9" s="9">
-        <f t="shared" ref="AQ9:AR9" si="70">AQ5-AQ8</f>
+        <f t="shared" ref="AQ9:AR9" si="73">AQ5-AQ8</f>
         <v>13197</v>
       </c>
       <c r="AR9" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="73"/>
         <v>17222</v>
       </c>
       <c r="AS9" s="9">
-        <f t="shared" ref="AS9:AT9" si="71">AS5-AS8</f>
+        <f t="shared" ref="AS9:AT9" si="74">AS5-AS8</f>
         <v>25684</v>
       </c>
       <c r="AT9" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="74"/>
         <v>43818</v>
       </c>
       <c r="AU9" s="9">
-        <f t="shared" ref="AU9:AV9" si="72">AU5-AU8</f>
+        <f t="shared" ref="AU9:AV9" si="75">AU5-AU8</f>
         <v>68662</v>
       </c>
       <c r="AV9" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="75"/>
         <v>64304</v>
       </c>
       <c r="AW9" s="9">
-        <f t="shared" ref="AW9:AX9" si="73">AW5-AW8</f>
+        <f t="shared" ref="AW9:AX9" si="76">AW5-AW8</f>
         <v>70537</v>
       </c>
       <c r="AX9" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="76"/>
         <v>93626</v>
       </c>
       <c r="AY9" s="9">
-        <f t="shared" ref="AY9:AZ9" si="74">AY5-AY8</f>
+        <f t="shared" ref="AY9:AZ9" si="77">AY5-AY8</f>
         <v>84263</v>
       </c>
       <c r="AZ9" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="77"/>
         <v>88186</v>
       </c>
       <c r="BA9" s="9">
-        <f t="shared" ref="BA9:BR9" si="75">BA5-BA8</f>
+        <f t="shared" ref="BA9:BR9" si="78">BA5-BA8</f>
         <v>101839</v>
       </c>
       <c r="BB9" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>98392</v>
       </c>
       <c r="BC9" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>104956</v>
       </c>
       <c r="BD9" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>152836</v>
       </c>
       <c r="BE9" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>170782</v>
       </c>
       <c r="BF9" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>169148</v>
       </c>
       <c r="BG9" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>180683</v>
       </c>
       <c r="BH9" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>195201</v>
       </c>
       <c r="BI9" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>207425.33050000004</v>
       </c>
       <c r="BJ9" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>216095.16147000005</v>
       </c>
       <c r="BK9" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>223093.93014990003</v>
       </c>
       <c r="BL9" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>229427.33832268859</v>
       </c>
       <c r="BM9" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>234952.30594205606</v>
       </c>
       <c r="BN9" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>239541.77700520074</v>
       </c>
       <c r="BO9" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>244244.34121908859</v>
       </c>
       <c r="BP9" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>249063.14546843045</v>
       </c>
       <c r="BQ9" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>254001.42858538023</v>
       </c>
       <c r="BR9" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="78"/>
         <v>259062.52408336743</v>
       </c>
     </row>
@@ -3114,7 +3131,9 @@
       <c r="AH10" s="3">
         <v>8866</v>
       </c>
-      <c r="AI10" s="3"/>
+      <c r="AI10" s="3">
+        <v>10887</v>
+      </c>
       <c r="AJ10" s="3"/>
       <c r="AK10" s="3"/>
       <c r="AL10" s="3"/>
@@ -3191,44 +3210,44 @@
         <v>34550</v>
       </c>
       <c r="BI10" s="3">
-        <f>BH10*1.05</f>
-        <v>36277.5</v>
+        <f>BH10*1.2</f>
+        <v>41460</v>
       </c>
       <c r="BJ10" s="3">
         <f>BI10*1.04</f>
-        <v>37728.6</v>
+        <v>43118.400000000001</v>
       </c>
       <c r="BK10" s="3">
         <f>BJ10*1.03</f>
-        <v>38860.457999999999</v>
+        <v>44411.952000000005</v>
       </c>
       <c r="BL10" s="3">
         <f>BK10*1.03</f>
-        <v>40026.271739999996</v>
+        <v>45744.310560000005</v>
       </c>
       <c r="BM10" s="3">
         <f>BL10*1.03</f>
-        <v>41227.059892199999</v>
+        <v>47116.639876800007</v>
       </c>
       <c r="BN10" s="3">
         <f>BM10*1.02</f>
-        <v>42051.601090044001</v>
+        <v>48058.972674336008</v>
       </c>
       <c r="BO10" s="3">
         <f>BN10*1.02</f>
-        <v>42892.63311184488</v>
+        <v>49020.15212782273</v>
       </c>
       <c r="BP10" s="3">
         <f>BO10*1.02</f>
-        <v>43750.485774081775</v>
+        <v>50000.555170379186</v>
       </c>
       <c r="BQ10" s="3">
-        <f t="shared" ref="BQ10:BR10" si="76">BP10*1.02</f>
-        <v>44625.495489563415</v>
+        <f t="shared" ref="BQ10:BR10" si="79">BP10*1.02</f>
+        <v>51000.566273786768</v>
       </c>
       <c r="BR10" s="3">
-        <f t="shared" si="76"/>
-        <v>45518.005399354683</v>
+        <f t="shared" si="79"/>
+        <v>52020.577599262506</v>
       </c>
     </row>
     <row r="11" spans="2:70" x14ac:dyDescent="0.3">
@@ -3331,7 +3350,9 @@
       <c r="AH11" s="3">
         <v>7048</v>
       </c>
-      <c r="AI11" s="3"/>
+      <c r="AI11" s="3">
+        <v>7492</v>
+      </c>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
@@ -3412,23 +3433,23 @@
         <v>28153.02</v>
       </c>
       <c r="BJ11" s="3">
-        <f t="shared" ref="BJ11:BN11" si="77">BI11*1.02</f>
+        <f t="shared" ref="BJ11:BN11" si="80">BI11*1.02</f>
         <v>28716.080400000003</v>
       </c>
       <c r="BK11" s="3">
-        <f t="shared" si="77"/>
+        <f t="shared" si="80"/>
         <v>29290.402008000005</v>
       </c>
       <c r="BL11" s="3">
-        <f t="shared" si="77"/>
+        <f t="shared" si="80"/>
         <v>29876.210048160006</v>
       </c>
       <c r="BM11" s="3">
-        <f t="shared" si="77"/>
+        <f t="shared" si="80"/>
         <v>30473.734249123208</v>
       </c>
       <c r="BN11" s="3">
-        <f t="shared" si="77"/>
+        <f t="shared" si="80"/>
         <v>31083.208934105674</v>
       </c>
       <c r="BO11" s="3">
@@ -3436,15 +3457,15 @@
         <v>31394.041023446731</v>
       </c>
       <c r="BP11" s="3">
-        <f t="shared" ref="BP11:BR11" si="78">BO11*1.01</f>
+        <f t="shared" ref="BP11:BR11" si="81">BO11*1.01</f>
         <v>31707.981433681198</v>
       </c>
       <c r="BQ11" s="3">
-        <f t="shared" si="78"/>
+        <f t="shared" si="81"/>
         <v>32025.06124801801</v>
       </c>
       <c r="BR11" s="3">
-        <f t="shared" si="78"/>
+        <f t="shared" si="81"/>
         <v>32345.31186049819</v>
       </c>
     </row>
@@ -3453,261 +3474,264 @@
         <v>29</v>
       </c>
       <c r="C12" s="3">
-        <f t="shared" ref="C12:S12" si="79">C10+C11</f>
+        <f t="shared" ref="C12:S12" si="82">C10+C11</f>
         <v>7638</v>
       </c>
       <c r="D12" s="3">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>7528</v>
       </c>
       <c r="E12" s="3">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>7809</v>
       </c>
       <c r="F12" s="3">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>7966</v>
       </c>
       <c r="G12" s="3">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>8685</v>
       </c>
       <c r="H12" s="3">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>8406</v>
       </c>
       <c r="I12" s="3">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>8683</v>
       </c>
       <c r="J12" s="3">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>8688</v>
       </c>
       <c r="K12" s="3">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>9648</v>
       </c>
       <c r="L12" s="3">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>9517</v>
       </c>
       <c r="M12" s="3">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>9589</v>
       </c>
       <c r="N12" s="3">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>9914</v>
       </c>
       <c r="O12" s="3">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>10794</v>
       </c>
       <c r="P12" s="3">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>10576</v>
       </c>
       <c r="Q12" s="3">
-        <f t="shared" ref="Q12:R12" si="80">Q10+Q11</f>
+        <f t="shared" ref="Q12:R12" si="83">Q10+Q11</f>
         <v>11129</v>
       </c>
       <c r="R12" s="3">
-        <f t="shared" si="80"/>
+        <f t="shared" si="83"/>
         <v>11388</v>
       </c>
       <c r="S12" s="3">
-        <f t="shared" si="79"/>
+        <f t="shared" si="82"/>
         <v>12755</v>
       </c>
       <c r="T12" s="3">
-        <f t="shared" ref="T12" si="81">T10+T11</f>
+        <f t="shared" ref="T12" si="84">T10+T11</f>
         <v>12580</v>
       </c>
       <c r="U12" s="3">
-        <f t="shared" ref="U12" si="82">U10+U11</f>
+        <f t="shared" ref="U12" si="85">U10+U11</f>
         <v>12809</v>
       </c>
       <c r="V12" s="3">
-        <f t="shared" ref="V12" si="83">V10+V11</f>
+        <f t="shared" ref="V12" si="86">V10+V11</f>
         <v>13201</v>
       </c>
       <c r="W12" s="3">
-        <f t="shared" ref="W12:X12" si="84">W10+W11</f>
+        <f t="shared" ref="W12:X12" si="87">W10+W11</f>
         <v>14316</v>
       </c>
       <c r="X12" s="3">
-        <f t="shared" si="84"/>
+        <f t="shared" si="87"/>
         <v>13658</v>
       </c>
       <c r="Y12" s="3">
-        <f t="shared" ref="Y12:Z12" si="85">Y10+Y11</f>
+        <f t="shared" ref="Y12:Z12" si="88">Y10+Y11</f>
         <v>13415</v>
       </c>
       <c r="Z12" s="3">
-        <f t="shared" si="85"/>
+        <f t="shared" si="88"/>
         <v>13458</v>
       </c>
       <c r="AA12" s="3">
-        <f t="shared" ref="AA12:AD12" si="86">AA10+AA11</f>
+        <f t="shared" ref="AA12:AD12" si="89">AA10+AA11</f>
         <v>14482</v>
       </c>
       <c r="AB12" s="3">
-        <f t="shared" si="86"/>
+        <f t="shared" si="89"/>
         <v>14371</v>
       </c>
       <c r="AC12" s="3">
-        <f t="shared" si="86"/>
+        <f t="shared" si="89"/>
         <v>14326</v>
       </c>
       <c r="AD12" s="3">
-        <f t="shared" si="86"/>
+        <f t="shared" si="89"/>
         <v>14288</v>
       </c>
       <c r="AE12" s="3">
-        <f t="shared" ref="AE12:AH12" si="87">AE10+AE11</f>
+        <f t="shared" ref="AE12:AH12" si="90">AE10+AE11</f>
         <v>15443</v>
       </c>
       <c r="AF12" s="3">
-        <f t="shared" si="87"/>
+        <f t="shared" si="90"/>
         <v>15278</v>
       </c>
       <c r="AG12" s="3">
-        <f t="shared" si="87"/>
+        <f t="shared" si="90"/>
         <v>15516</v>
       </c>
       <c r="AH12" s="3">
-        <f t="shared" si="87"/>
+        <f t="shared" si="90"/>
         <v>15914</v>
       </c>
-      <c r="AI12" s="3"/>
+      <c r="AI12" s="3">
+        <f t="shared" ref="AI12" si="91">AI10+AI11</f>
+        <v>18379</v>
+      </c>
       <c r="AJ12" s="3"/>
       <c r="AK12" s="3"/>
       <c r="AL12" s="3"/>
       <c r="AM12" s="3"/>
       <c r="AN12" s="3">
-        <f t="shared" ref="AN12" si="88">AN10+AN11</f>
+        <f t="shared" ref="AN12" si="92">AN10+AN11</f>
         <v>2399</v>
       </c>
       <c r="AO12" s="3">
-        <f t="shared" ref="AO12:AP12" si="89">AO10+AO11</f>
+        <f t="shared" ref="AO12:AP12" si="93">AO10+AO11</f>
         <v>3145</v>
       </c>
       <c r="AP12" s="3">
-        <f t="shared" si="89"/>
+        <f t="shared" si="93"/>
         <v>3745</v>
       </c>
       <c r="AQ12" s="3">
-        <f t="shared" ref="AQ12:AR12" si="90">AQ10+AQ11</f>
+        <f t="shared" ref="AQ12:AR12" si="94">AQ10+AQ11</f>
         <v>4870</v>
       </c>
       <c r="AR12" s="3">
-        <f t="shared" si="90"/>
+        <f t="shared" si="94"/>
         <v>5482</v>
       </c>
       <c r="AS12" s="3">
-        <f t="shared" ref="AS12:AT12" si="91">AS10+AS11</f>
+        <f t="shared" ref="AS12:AT12" si="95">AS10+AS11</f>
         <v>7299</v>
       </c>
       <c r="AT12" s="3">
-        <f t="shared" si="91"/>
+        <f t="shared" si="95"/>
         <v>10028</v>
       </c>
       <c r="AU12" s="3">
-        <f t="shared" ref="AU12:AV12" si="92">AU10+AU11</f>
+        <f t="shared" ref="AU12:AV12" si="96">AU10+AU11</f>
         <v>13421</v>
       </c>
       <c r="AV12" s="3">
-        <f t="shared" si="92"/>
+        <f t="shared" si="96"/>
         <v>15305</v>
       </c>
       <c r="AW12" s="3">
-        <f t="shared" ref="AW12:AX12" si="93">AW10+AW11</f>
+        <f t="shared" ref="AW12:AX12" si="97">AW10+AW11</f>
         <v>18034</v>
       </c>
       <c r="AX12" s="3">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>22396</v>
       </c>
       <c r="AY12" s="3">
-        <f t="shared" ref="AY12:AZ12" si="94">AY10+AY11</f>
+        <f t="shared" ref="AY12:AZ12" si="98">AY10+AY11</f>
         <v>24239</v>
       </c>
       <c r="AZ12" s="3">
-        <f t="shared" si="94"/>
+        <f t="shared" si="98"/>
         <v>26842</v>
       </c>
       <c r="BA12" s="3">
-        <f t="shared" ref="BA12:BG12" si="95">BA10+BA11</f>
+        <f t="shared" ref="BA12:BG12" si="99">BA10+BA11</f>
         <v>30941</v>
       </c>
       <c r="BB12" s="3">
-        <f t="shared" si="95"/>
+        <f t="shared" si="99"/>
         <v>34462</v>
       </c>
       <c r="BC12" s="3">
-        <f t="shared" si="95"/>
+        <f t="shared" si="99"/>
         <v>38668</v>
       </c>
       <c r="BD12" s="3">
-        <f t="shared" si="95"/>
+        <f t="shared" si="99"/>
         <v>43887</v>
       </c>
       <c r="BE12" s="3">
-        <f t="shared" si="95"/>
+        <f t="shared" si="99"/>
         <v>51345</v>
       </c>
       <c r="BF12" s="3">
-        <f t="shared" si="95"/>
+        <f t="shared" si="99"/>
         <v>54847</v>
       </c>
       <c r="BG12" s="3">
-        <f t="shared" si="95"/>
+        <f t="shared" si="99"/>
         <v>57467</v>
       </c>
       <c r="BH12" s="3">
-        <f t="shared" ref="BH12:BM12" si="96">BH10+BH11</f>
+        <f t="shared" ref="BH12:BM12" si="100">BH10+BH11</f>
         <v>62151</v>
       </c>
       <c r="BI12" s="3">
-        <f t="shared" si="96"/>
-        <v>64430.520000000004</v>
+        <f t="shared" si="100"/>
+        <v>69613.02</v>
       </c>
       <c r="BJ12" s="3">
-        <f t="shared" si="96"/>
-        <v>66444.680399999997</v>
+        <f t="shared" si="100"/>
+        <v>71834.4804</v>
       </c>
       <c r="BK12" s="3">
-        <f t="shared" si="96"/>
-        <v>68150.860008000003</v>
+        <f t="shared" si="100"/>
+        <v>73702.354008000009</v>
       </c>
       <c r="BL12" s="3">
-        <f t="shared" si="96"/>
-        <v>69902.481788160003</v>
+        <f t="shared" si="100"/>
+        <v>75620.520608160004</v>
       </c>
       <c r="BM12" s="3">
-        <f t="shared" si="96"/>
-        <v>71700.794141323204</v>
+        <f t="shared" si="100"/>
+        <v>77590.374125923219</v>
       </c>
       <c r="BN12" s="3">
-        <f t="shared" ref="BN12:BP12" si="97">BN10+BN11</f>
-        <v>73134.810024149672</v>
+        <f t="shared" ref="BN12:BP12" si="101">BN10+BN11</f>
+        <v>79142.181608441679</v>
       </c>
       <c r="BO12" s="3">
-        <f t="shared" si="97"/>
-        <v>74286.674135291614</v>
+        <f t="shared" si="101"/>
+        <v>80414.193151269457</v>
       </c>
       <c r="BP12" s="3">
-        <f t="shared" si="97"/>
-        <v>75458.467207762966</v>
+        <f t="shared" si="101"/>
+        <v>81708.536604060384</v>
       </c>
       <c r="BQ12" s="3">
-        <f t="shared" ref="BQ12:BR12" si="98">BQ10+BQ11</f>
-        <v>76650.556737581428</v>
+        <f t="shared" ref="BQ12:BR12" si="102">BQ10+BQ11</f>
+        <v>83025.627521804781</v>
       </c>
       <c r="BR12" s="3">
-        <f t="shared" si="98"/>
-        <v>77863.317259852876</v>
+        <f t="shared" si="102"/>
+        <v>84365.8894597607</v>
       </c>
     </row>
     <row r="13" spans="2:70" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -3715,261 +3739,264 @@
         <v>32</v>
       </c>
       <c r="C13" s="9">
-        <f t="shared" ref="C13:N13" si="99">C9-C12</f>
+        <f t="shared" ref="C13:N13" si="103">C9-C12</f>
         <v>26274</v>
       </c>
       <c r="D13" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="103"/>
         <v>15894</v>
       </c>
       <c r="E13" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="103"/>
         <v>12612</v>
       </c>
       <c r="F13" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="103"/>
         <v>16118</v>
       </c>
       <c r="G13" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="103"/>
         <v>23346</v>
       </c>
       <c r="H13" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="103"/>
         <v>13415</v>
       </c>
       <c r="I13" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="103"/>
         <v>11544</v>
       </c>
       <c r="J13" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="103"/>
         <v>15625</v>
       </c>
       <c r="K13" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="103"/>
         <v>25569</v>
       </c>
       <c r="L13" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="103"/>
         <v>12853</v>
       </c>
       <c r="M13" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="103"/>
         <v>13091</v>
       </c>
       <c r="N13" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="103"/>
         <v>14775</v>
       </c>
       <c r="O13" s="9">
-        <f t="shared" ref="O13:S13" si="100">O9-O12</f>
+        <f t="shared" ref="O13:S13" si="104">O9-O12</f>
         <v>33534</v>
       </c>
       <c r="P13" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="104"/>
         <v>27503</v>
       </c>
       <c r="Q13" s="9">
-        <f t="shared" ref="Q13:R13" si="101">Q9-Q12</f>
+        <f t="shared" ref="Q13:R13" si="105">Q9-Q12</f>
         <v>24126</v>
       </c>
       <c r="R13" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="105"/>
         <v>23786</v>
       </c>
       <c r="S13" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="104"/>
         <v>41488</v>
       </c>
       <c r="T13" s="9">
-        <f t="shared" ref="T13" si="102">T9-T12</f>
+        <f t="shared" ref="T13" si="106">T9-T12</f>
         <v>29979</v>
       </c>
       <c r="U13" s="9">
-        <f t="shared" ref="U13" si="103">U9-U12</f>
+        <f t="shared" ref="U13" si="107">U9-U12</f>
         <v>23076</v>
       </c>
       <c r="V13" s="9">
-        <f t="shared" ref="V13" si="104">V9-V12</f>
+        <f t="shared" ref="V13" si="108">V9-V12</f>
         <v>24894</v>
       </c>
       <c r="W13" s="9">
-        <f t="shared" ref="W13:X13" si="105">W9-W12</f>
+        <f t="shared" ref="W13:X13" si="109">W9-W12</f>
         <v>36016</v>
       </c>
       <c r="X13" s="9">
-        <f t="shared" si="105"/>
+        <f t="shared" si="109"/>
         <v>28318</v>
       </c>
       <c r="Y13" s="9">
-        <f t="shared" ref="Y13:Z13" si="106">Y9-Y12</f>
+        <f t="shared" ref="Y13:Z13" si="110">Y9-Y12</f>
         <v>22998</v>
       </c>
       <c r="Z13" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="110"/>
         <v>26969</v>
       </c>
       <c r="AA13" s="9">
-        <f t="shared" ref="AA13:AD13" si="107">AA9-AA12</f>
+        <f t="shared" ref="AA13:AD13" si="111">AA9-AA12</f>
         <v>40373</v>
       </c>
       <c r="AB13" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="111"/>
         <v>27900</v>
       </c>
       <c r="AC13" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="111"/>
         <v>25352</v>
       </c>
       <c r="AD13" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="111"/>
         <v>29591</v>
       </c>
       <c r="AE13" s="9">
-        <f t="shared" ref="AE13:AH13" si="108">AE9-AE12</f>
+        <f t="shared" ref="AE13:AH13" si="112">AE9-AE12</f>
         <v>42832</v>
       </c>
       <c r="AF13" s="9">
-        <f t="shared" si="108"/>
+        <f t="shared" si="112"/>
         <v>29589</v>
       </c>
       <c r="AG13" s="9">
-        <f t="shared" si="108"/>
+        <f t="shared" si="112"/>
         <v>28202</v>
       </c>
       <c r="AH13" s="9">
-        <f t="shared" si="108"/>
+        <f t="shared" si="112"/>
         <v>32427</v>
       </c>
-      <c r="AI13" s="9"/>
+      <c r="AI13" s="9">
+        <f t="shared" ref="AI13" si="113">AI9-AI12</f>
+        <v>50852</v>
+      </c>
       <c r="AJ13" s="9"/>
       <c r="AK13" s="9"/>
       <c r="AL13" s="9"/>
       <c r="AM13" s="9"/>
       <c r="AN13" s="9">
-        <f t="shared" ref="AN13" si="109">AN9-AN12</f>
+        <f t="shared" ref="AN13" si="114">AN9-AN12</f>
         <v>1643</v>
       </c>
       <c r="AO13" s="9">
-        <f t="shared" ref="AO13:AP13" si="110">AO9-AO12</f>
+        <f t="shared" ref="AO13:AP13" si="115">AO9-AO12</f>
         <v>2453</v>
       </c>
       <c r="AP13" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="115"/>
         <v>4409</v>
       </c>
       <c r="AQ13" s="9">
-        <f t="shared" ref="AQ13:AR13" si="111">AQ9-AQ12</f>
+        <f t="shared" ref="AQ13:AR13" si="116">AQ9-AQ12</f>
         <v>8327</v>
       </c>
       <c r="AR13" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="116"/>
         <v>11740</v>
       </c>
       <c r="AS13" s="9">
-        <f t="shared" ref="AS13:AT13" si="112">AS9-AS12</f>
+        <f t="shared" ref="AS13:AT13" si="117">AS9-AS12</f>
         <v>18385</v>
       </c>
       <c r="AT13" s="9">
-        <f t="shared" si="112"/>
+        <f t="shared" si="117"/>
         <v>33790</v>
       </c>
       <c r="AU13" s="9">
-        <f t="shared" ref="AU13:AV13" si="113">AU9-AU12</f>
+        <f t="shared" ref="AU13:AV13" si="118">AU9-AU12</f>
         <v>55241</v>
       </c>
       <c r="AV13" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="118"/>
         <v>48999</v>
       </c>
       <c r="AW13" s="9">
-        <f t="shared" ref="AW13:AX13" si="114">AW9-AW12</f>
+        <f t="shared" ref="AW13:AX13" si="119">AW9-AW12</f>
         <v>52503</v>
       </c>
       <c r="AX13" s="9">
-        <f t="shared" si="114"/>
+        <f t="shared" si="119"/>
         <v>71230</v>
       </c>
       <c r="AY13" s="9">
-        <f t="shared" ref="AY13:AZ13" si="115">AY9-AY12</f>
+        <f t="shared" ref="AY13:AZ13" si="120">AY9-AY12</f>
         <v>60024</v>
       </c>
       <c r="AZ13" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="120"/>
         <v>61344</v>
       </c>
       <c r="BA13" s="9">
-        <f t="shared" ref="BA13:BG13" si="116">BA9-BA12</f>
+        <f t="shared" ref="BA13:BG13" si="121">BA9-BA12</f>
         <v>70898</v>
       </c>
       <c r="BB13" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="121"/>
         <v>63930</v>
       </c>
       <c r="BC13" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="121"/>
         <v>66288</v>
       </c>
       <c r="BD13" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="121"/>
         <v>108949</v>
       </c>
       <c r="BE13" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="121"/>
         <v>119437</v>
       </c>
       <c r="BF13" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="121"/>
         <v>114301</v>
       </c>
       <c r="BG13" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="121"/>
         <v>123216</v>
       </c>
       <c r="BH13" s="9">
-        <f t="shared" ref="BH13:BM13" si="117">BH9-BH12</f>
+        <f t="shared" ref="BH13:BM13" si="122">BH9-BH12</f>
         <v>133050</v>
       </c>
       <c r="BI13" s="9">
-        <f t="shared" si="117"/>
-        <v>142994.81050000002</v>
+        <f t="shared" si="122"/>
+        <v>137812.31050000002</v>
       </c>
       <c r="BJ13" s="9">
-        <f t="shared" si="117"/>
-        <v>149650.48107000004</v>
+        <f t="shared" si="122"/>
+        <v>144260.68107000005</v>
       </c>
       <c r="BK13" s="9">
-        <f t="shared" si="117"/>
-        <v>154943.07014190004</v>
+        <f t="shared" si="122"/>
+        <v>149391.57614190003</v>
       </c>
       <c r="BL13" s="9">
-        <f t="shared" si="117"/>
-        <v>159524.8565345286</v>
+        <f t="shared" si="122"/>
+        <v>153806.81771452859</v>
       </c>
       <c r="BM13" s="9">
-        <f t="shared" si="117"/>
-        <v>163251.51180073287</v>
+        <f t="shared" si="122"/>
+        <v>157361.93181613286</v>
       </c>
       <c r="BN13" s="9">
-        <f t="shared" ref="BN13:BP13" si="118">BN9-BN12</f>
-        <v>166406.96698105108</v>
+        <f t="shared" ref="BN13:BP13" si="123">BN9-BN12</f>
+        <v>160399.59539675905</v>
       </c>
       <c r="BO13" s="9">
-        <f t="shared" si="118"/>
-        <v>169957.66708379699</v>
+        <f t="shared" si="123"/>
+        <v>163830.14806781913</v>
       </c>
       <c r="BP13" s="9">
-        <f t="shared" si="118"/>
-        <v>173604.67826066748</v>
+        <f t="shared" si="123"/>
+        <v>167354.60886437006</v>
       </c>
       <c r="BQ13" s="9">
-        <f t="shared" ref="BQ13:BR13" si="119">BQ9-BQ12</f>
-        <v>177350.87184779881</v>
+        <f t="shared" ref="BQ13:BR13" si="124">BQ9-BQ12</f>
+        <v>170975.80106357543</v>
       </c>
       <c r="BR13" s="9">
-        <f t="shared" si="119"/>
-        <v>181199.20682351454</v>
+        <f t="shared" si="124"/>
+        <v>174696.63462360675</v>
       </c>
     </row>
     <row r="14" spans="2:70" x14ac:dyDescent="0.3">
@@ -4072,7 +4099,9 @@
       <c r="AH14" s="3">
         <v>-377</v>
       </c>
-      <c r="AI14" s="3"/>
+      <c r="AI14" s="3">
+        <v>-150</v>
+      </c>
       <c r="AJ14" s="3"/>
       <c r="AK14" s="3"/>
       <c r="AL14" s="3"/>
@@ -4153,40 +4182,40 @@
         <v>560.05000000000007</v>
       </c>
       <c r="BJ14" s="3">
-        <f t="shared" ref="BJ14:BR14" si="120">BI17*0.005</f>
-        <v>598.22599410000009</v>
+        <f t="shared" ref="BJ14:BR14" si="125">BI17*0.005</f>
+        <v>576.45949410000014</v>
       </c>
       <c r="BK14" s="3">
-        <f t="shared" si="120"/>
-        <v>626.01947131878012</v>
+        <f t="shared" si="125"/>
+        <v>603.47373061878022</v>
       </c>
       <c r="BL14" s="3">
-        <f t="shared" si="120"/>
-        <v>648.13161281644125</v>
+        <f t="shared" si="125"/>
+        <v>624.91003012738133</v>
       </c>
       <c r="BM14" s="3">
-        <f t="shared" si="120"/>
-        <v>667.28224467119105</v>
+        <f t="shared" si="125"/>
+        <v>643.36401227448505</v>
       </c>
       <c r="BN14" s="3">
-        <f t="shared" si="120"/>
-        <v>682.85376413545907</v>
+        <f t="shared" si="125"/>
+        <v>658.21798477620518</v>
       </c>
       <c r="BO14" s="3">
-        <f t="shared" si="120"/>
-        <v>696.04127551104568</v>
+        <f t="shared" si="125"/>
+        <v>670.91378513032794</v>
       </c>
       <c r="BP14" s="3">
-        <f t="shared" si="120"/>
-        <v>710.89882839480094</v>
+        <f t="shared" si="125"/>
+        <v>685.26878398729286</v>
       </c>
       <c r="BQ14" s="3">
-        <f t="shared" si="120"/>
-        <v>726.15387361554531</v>
+        <f t="shared" si="125"/>
+        <v>700.01122833760758</v>
       </c>
       <c r="BR14" s="3">
-        <f t="shared" si="120"/>
-        <v>741.82381549156969</v>
+        <f t="shared" si="125"/>
+        <v>715.1583173079988</v>
       </c>
     </row>
     <row r="15" spans="2:70" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -4194,261 +4223,264 @@
         <v>34</v>
       </c>
       <c r="C15" s="9">
-        <f t="shared" ref="C15:N15" si="121">C13-C14</f>
+        <f t="shared" ref="C15:N15" si="126">C13-C14</f>
         <v>27030</v>
       </c>
       <c r="D15" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="126"/>
         <v>16168</v>
       </c>
       <c r="E15" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="126"/>
         <v>13284</v>
       </c>
       <c r="F15" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="126"/>
         <v>16421</v>
       </c>
       <c r="G15" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="126"/>
         <v>23906</v>
       </c>
       <c r="H15" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="126"/>
         <v>13793</v>
       </c>
       <c r="I15" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="126"/>
         <v>11911</v>
       </c>
       <c r="J15" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="126"/>
         <v>16127</v>
       </c>
       <c r="K15" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="126"/>
         <v>25918</v>
       </c>
       <c r="L15" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="126"/>
         <v>13135</v>
       </c>
       <c r="M15" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="126"/>
         <v>13137</v>
       </c>
       <c r="N15" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="126"/>
         <v>14901</v>
       </c>
       <c r="O15" s="9">
-        <f t="shared" ref="O15:S15" si="122">O13-O14</f>
+        <f t="shared" ref="O15:S15" si="127">O13-O14</f>
         <v>33579</v>
       </c>
       <c r="P15" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="127"/>
         <v>28011</v>
       </c>
       <c r="Q15" s="9">
-        <f t="shared" ref="Q15:R15" si="123">Q13-Q14</f>
+        <f t="shared" ref="Q15:R15" si="128">Q13-Q14</f>
         <v>24369</v>
       </c>
       <c r="R15" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="128"/>
         <v>23248</v>
       </c>
       <c r="S15" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="127"/>
         <v>41241</v>
       </c>
       <c r="T15" s="9">
-        <f t="shared" ref="T15" si="124">T13-T14</f>
+        <f t="shared" ref="T15" si="129">T13-T14</f>
         <v>30139</v>
       </c>
       <c r="U15" s="9">
-        <f t="shared" ref="U15" si="125">U13-U14</f>
+        <f t="shared" ref="U15" si="130">U13-U14</f>
         <v>23066</v>
       </c>
       <c r="V15" s="9">
-        <f t="shared" ref="V15" si="126">V13-V14</f>
+        <f t="shared" ref="V15" si="131">V13-V14</f>
         <v>24657</v>
       </c>
       <c r="W15" s="9">
-        <f t="shared" ref="W15:X15" si="127">W13-W14</f>
+        <f t="shared" ref="W15:X15" si="132">W13-W14</f>
         <v>35623</v>
       </c>
       <c r="X15" s="9">
-        <f t="shared" si="127"/>
+        <f t="shared" si="132"/>
         <v>28382</v>
       </c>
       <c r="Y15" s="9">
-        <f t="shared" ref="Y15:Z15" si="128">Y13-Y14</f>
+        <f t="shared" ref="Y15:Z15" si="133">Y13-Y14</f>
         <v>22733</v>
       </c>
       <c r="Z15" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="133"/>
         <v>26998</v>
       </c>
       <c r="AA15" s="9">
-        <f t="shared" ref="AA15:AH15" si="129">AA13-AA14</f>
+        <f t="shared" ref="AA15:AH15" si="134">AA13-AA14</f>
         <v>40323</v>
       </c>
       <c r="AB15" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="134"/>
         <v>28058</v>
       </c>
       <c r="AC15" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="134"/>
         <v>25494</v>
       </c>
       <c r="AD15" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="134"/>
         <v>29610</v>
       </c>
       <c r="AE15" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="134"/>
         <v>42584</v>
       </c>
       <c r="AF15" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="134"/>
         <v>29310</v>
       </c>
       <c r="AG15" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="134"/>
         <v>28031</v>
       </c>
       <c r="AH15" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="134"/>
         <v>32804</v>
       </c>
-      <c r="AI15" s="9"/>
+      <c r="AI15" s="9">
+        <f t="shared" ref="AI15" si="135">AI13-AI14</f>
+        <v>51002</v>
+      </c>
       <c r="AJ15" s="9"/>
       <c r="AK15" s="9"/>
       <c r="AL15" s="9"/>
       <c r="AM15" s="9"/>
       <c r="AN15" s="9">
-        <f t="shared" ref="AN15" si="130">AN13-AN14</f>
+        <f t="shared" ref="AN15" si="136">AN13-AN14</f>
         <v>1808</v>
       </c>
       <c r="AO15" s="9">
-        <f t="shared" ref="AO15:AP15" si="131">AO13-AO14</f>
+        <f t="shared" ref="AO15:AP15" si="137">AO13-AO14</f>
         <v>2818</v>
       </c>
       <c r="AP15" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="137"/>
         <v>5008</v>
       </c>
       <c r="AQ15" s="9">
-        <f t="shared" ref="AQ15:AR15" si="132">AQ13-AQ14</f>
+        <f t="shared" ref="AQ15:AR15" si="138">AQ13-AQ14</f>
         <v>8947</v>
       </c>
       <c r="AR15" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="138"/>
         <v>12066</v>
       </c>
       <c r="AS15" s="9">
-        <f t="shared" ref="AS15:AT15" si="133">AS13-AS14</f>
+        <f t="shared" ref="AS15:AT15" si="139">AS13-AS14</f>
         <v>18540</v>
       </c>
       <c r="AT15" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="139"/>
         <v>34205</v>
       </c>
       <c r="AU15" s="9">
-        <f t="shared" ref="AU15:AV15" si="134">AU13-AU14</f>
+        <f t="shared" ref="AU15:AV15" si="140">AU13-AU14</f>
         <v>55763</v>
       </c>
       <c r="AV15" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="140"/>
         <v>50155</v>
       </c>
       <c r="AW15" s="9">
-        <f t="shared" ref="AW15:AX15" si="135">AW13-AW14</f>
+        <f t="shared" ref="AW15:AX15" si="141">AW13-AW14</f>
         <v>53483</v>
       </c>
       <c r="AX15" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="141"/>
         <v>72515</v>
       </c>
       <c r="AY15" s="9">
-        <f t="shared" ref="AY15:AZ15" si="136">AY13-AY14</f>
+        <f t="shared" ref="AY15:AZ15" si="142">AY13-AY14</f>
         <v>61372</v>
       </c>
       <c r="AZ15" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="142"/>
         <v>64089</v>
       </c>
       <c r="BA15" s="9">
-        <f t="shared" ref="BA15:BG15" si="137">BA13-BA14</f>
+        <f t="shared" ref="BA15:BG15" si="143">BA13-BA14</f>
         <v>72903</v>
       </c>
       <c r="BB15" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="143"/>
         <v>65737</v>
       </c>
       <c r="BC15" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="143"/>
         <v>67091</v>
       </c>
       <c r="BD15" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="143"/>
         <v>109207</v>
       </c>
       <c r="BE15" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="143"/>
         <v>119103</v>
       </c>
       <c r="BF15" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="143"/>
         <v>113736</v>
       </c>
       <c r="BG15" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="143"/>
         <v>123485</v>
       </c>
       <c r="BH15" s="9">
-        <f t="shared" ref="BH15:BM15" si="138">BH13-BH14</f>
+        <f t="shared" ref="BH15:BM15" si="144">BH13-BH14</f>
         <v>132729</v>
       </c>
       <c r="BI15" s="9">
-        <f t="shared" si="138"/>
-        <v>142434.76050000003</v>
+        <f t="shared" si="144"/>
+        <v>137252.26050000003</v>
       </c>
       <c r="BJ15" s="9">
-        <f t="shared" si="138"/>
-        <v>149052.25507590003</v>
+        <f t="shared" si="144"/>
+        <v>143684.22157590004</v>
       </c>
       <c r="BK15" s="9">
-        <f t="shared" si="138"/>
-        <v>154317.05067058126</v>
+        <f t="shared" si="144"/>
+        <v>148788.10241128126</v>
       </c>
       <c r="BL15" s="9">
-        <f t="shared" si="138"/>
-        <v>158876.72492171216</v>
+        <f t="shared" si="144"/>
+        <v>153181.9076844012</v>
       </c>
       <c r="BM15" s="9">
-        <f t="shared" si="138"/>
-        <v>162584.22955606168</v>
+        <f t="shared" si="144"/>
+        <v>156718.56780385837</v>
       </c>
       <c r="BN15" s="9">
-        <f t="shared" ref="BN15:BP15" si="139">BN13-BN14</f>
-        <v>165724.11321691563</v>
+        <f t="shared" ref="BN15:BP15" si="145">BN13-BN14</f>
+        <v>159741.37741198283</v>
       </c>
       <c r="BO15" s="9">
-        <f t="shared" si="139"/>
-        <v>169261.62580828593</v>
+        <f t="shared" si="145"/>
+        <v>163159.23428268879</v>
       </c>
       <c r="BP15" s="9">
-        <f t="shared" si="139"/>
-        <v>172893.77943227268</v>
+        <f t="shared" si="145"/>
+        <v>166669.34008038277</v>
       </c>
       <c r="BQ15" s="9">
-        <f t="shared" ref="BQ15:BR15" si="140">BQ13-BQ14</f>
-        <v>176624.71797418327</v>
+        <f t="shared" ref="BQ15:BR15" si="146">BQ13-BQ14</f>
+        <v>170275.78983523781</v>
       </c>
       <c r="BR15" s="9">
-        <f t="shared" si="140"/>
-        <v>180457.38300802297</v>
+        <f t="shared" si="146"/>
+        <v>173981.47630629875</v>
       </c>
     </row>
     <row r="16" spans="2:70" x14ac:dyDescent="0.3">
@@ -4551,7 +4583,9 @@
       <c r="AH16" s="3">
         <v>5338</v>
       </c>
-      <c r="AI16" s="3"/>
+      <c r="AI16" s="3">
+        <v>8905</v>
+      </c>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
@@ -4628,44 +4662,44 @@
         <v>20719</v>
       </c>
       <c r="BI16" s="3">
-        <f t="shared" ref="BI16:BP16" si="141">BI15*0.16</f>
-        <v>22789.561680000006</v>
+        <f t="shared" ref="BI16:BP16" si="147">BI15*0.16</f>
+        <v>21960.361680000005</v>
       </c>
       <c r="BJ16" s="3">
-        <f t="shared" si="141"/>
-        <v>23848.360812144005</v>
+        <f t="shared" si="147"/>
+        <v>22989.475452144008</v>
       </c>
       <c r="BK16" s="3">
-        <f t="shared" si="141"/>
-        <v>24690.728107293002</v>
+        <f t="shared" si="147"/>
+        <v>23806.096385805002</v>
       </c>
       <c r="BL16" s="3">
-        <f t="shared" si="141"/>
-        <v>25420.275987473946</v>
+        <f t="shared" si="147"/>
+        <v>24509.105229504192</v>
       </c>
       <c r="BM16" s="3">
-        <f t="shared" si="141"/>
-        <v>26013.476728969868</v>
+        <f t="shared" si="147"/>
+        <v>25074.97084861734</v>
       </c>
       <c r="BN16" s="3">
-        <f t="shared" si="141"/>
-        <v>26515.858114706502</v>
+        <f t="shared" si="147"/>
+        <v>25558.620385917253</v>
       </c>
       <c r="BO16" s="3">
-        <f t="shared" si="141"/>
-        <v>27081.860129325749</v>
+        <f t="shared" si="147"/>
+        <v>26105.477485230207</v>
       </c>
       <c r="BP16" s="3">
-        <f t="shared" si="141"/>
-        <v>27663.00470916363</v>
+        <f t="shared" si="147"/>
+        <v>26667.094412861243</v>
       </c>
       <c r="BQ16" s="3">
-        <f t="shared" ref="BQ16:BR16" si="142">BQ15*0.16</f>
-        <v>28259.954875869324</v>
+        <f t="shared" ref="BQ16:BR16" si="148">BQ15*0.16</f>
+        <v>27244.12637363805</v>
       </c>
       <c r="BR16" s="3">
-        <f t="shared" si="142"/>
-        <v>28873.181281283676</v>
+        <f t="shared" si="148"/>
+        <v>27837.036209007802</v>
       </c>
     </row>
     <row r="17" spans="2:183" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -4673,713 +4707,716 @@
         <v>36</v>
       </c>
       <c r="C17" s="9">
-        <f t="shared" ref="C17:N17" si="143">C15-C16</f>
+        <f t="shared" ref="C17:N17" si="149">C15-C16</f>
         <v>20065</v>
       </c>
       <c r="D17" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="149"/>
         <v>13822</v>
       </c>
       <c r="E17" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="149"/>
         <v>11519</v>
       </c>
       <c r="F17" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="149"/>
         <v>14125</v>
       </c>
       <c r="G17" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="149"/>
         <v>19965</v>
       </c>
       <c r="H17" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="149"/>
         <v>11561</v>
       </c>
       <c r="I17" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="149"/>
         <v>10044</v>
       </c>
       <c r="J17" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="149"/>
         <v>13686</v>
       </c>
       <c r="K17" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="149"/>
         <v>22236</v>
       </c>
       <c r="L17" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="149"/>
         <v>11249</v>
       </c>
       <c r="M17" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="149"/>
         <v>11253</v>
       </c>
       <c r="N17" s="9">
-        <f t="shared" si="143"/>
+        <f t="shared" si="149"/>
         <v>12673</v>
       </c>
       <c r="O17" s="9">
-        <f t="shared" ref="O17:S17" si="144">O15-O16</f>
+        <f t="shared" ref="O17:S17" si="150">O15-O16</f>
         <v>28755</v>
       </c>
       <c r="P17" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="150"/>
         <v>23630</v>
       </c>
       <c r="Q17" s="9">
-        <f t="shared" ref="Q17:R17" si="145">Q15-Q16</f>
+        <f t="shared" ref="Q17:R17" si="151">Q15-Q16</f>
         <v>21744</v>
       </c>
       <c r="R17" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="151"/>
         <v>20551</v>
       </c>
       <c r="S17" s="9">
-        <f t="shared" si="144"/>
+        <f t="shared" si="150"/>
         <v>34630</v>
       </c>
       <c r="T17" s="9">
-        <f t="shared" ref="T17" si="146">T15-T16</f>
+        <f t="shared" ref="T17" si="152">T15-T16</f>
         <v>25010</v>
       </c>
       <c r="U17" s="9">
-        <f t="shared" ref="U17" si="147">U15-U16</f>
+        <f t="shared" ref="U17" si="153">U15-U16</f>
         <v>19442</v>
       </c>
       <c r="V17" s="9">
-        <f t="shared" ref="V17" si="148">V15-V16</f>
+        <f t="shared" ref="V17" si="154">V15-V16</f>
         <v>20721</v>
       </c>
       <c r="W17" s="9">
-        <f t="shared" ref="W17:X17" si="149">W15-W16</f>
+        <f t="shared" ref="W17:X17" si="155">W15-W16</f>
         <v>29998</v>
       </c>
       <c r="X17" s="9">
-        <f t="shared" si="149"/>
+        <f t="shared" si="155"/>
         <v>24160</v>
       </c>
       <c r="Y17" s="9">
-        <f t="shared" ref="Y17:Z17" si="150">Y15-Y16</f>
+        <f t="shared" ref="Y17:Z17" si="156">Y15-Y16</f>
         <v>19881</v>
       </c>
       <c r="Z17" s="9">
-        <f t="shared" si="150"/>
+        <f t="shared" si="156"/>
         <v>22956</v>
       </c>
       <c r="AA17" s="9">
-        <f t="shared" ref="AA17:AD17" si="151">AA15-AA16</f>
+        <f t="shared" ref="AA17:AD17" si="157">AA15-AA16</f>
         <v>33916</v>
       </c>
       <c r="AB17" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="157"/>
         <v>23636</v>
       </c>
       <c r="AC17" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="157"/>
         <v>21448</v>
       </c>
       <c r="AD17" s="9">
-        <f t="shared" si="151"/>
+        <f t="shared" si="157"/>
         <v>14736</v>
       </c>
       <c r="AE17" s="9">
-        <f t="shared" ref="AE17:AH17" si="152">AE15-AE16</f>
+        <f t="shared" ref="AE17:AH17" si="158">AE15-AE16</f>
         <v>36330</v>
       </c>
       <c r="AF17" s="9">
-        <f t="shared" si="152"/>
+        <f t="shared" si="158"/>
         <v>24780</v>
       </c>
       <c r="AG17" s="9">
-        <f t="shared" si="152"/>
+        <f t="shared" si="158"/>
         <v>23434</v>
       </c>
       <c r="AH17" s="9">
-        <f t="shared" si="152"/>
+        <f t="shared" si="158"/>
         <v>27466</v>
       </c>
-      <c r="AI17" s="9"/>
+      <c r="AI17" s="9">
+        <f t="shared" ref="AI17" si="159">AI15-AI16</f>
+        <v>42097</v>
+      </c>
       <c r="AJ17" s="9"/>
       <c r="AK17" s="9"/>
       <c r="AL17" s="9"/>
       <c r="AM17" s="9"/>
       <c r="AN17" s="9">
-        <f t="shared" ref="AN17:BC17" si="153">AN15-AN16</f>
+        <f t="shared" ref="AN17:BC17" si="160">AN15-AN16</f>
         <v>1328</v>
       </c>
       <c r="AO17" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="160"/>
         <v>1989</v>
       </c>
       <c r="AP17" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="160"/>
         <v>3496</v>
       </c>
       <c r="AQ17" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="160"/>
         <v>6119</v>
       </c>
       <c r="AR17" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="160"/>
         <v>8235</v>
       </c>
       <c r="AS17" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="160"/>
         <v>14013</v>
       </c>
       <c r="AT17" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="160"/>
         <v>25922</v>
       </c>
       <c r="AU17" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="160"/>
         <v>41733</v>
       </c>
       <c r="AV17" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="160"/>
         <v>37037</v>
       </c>
       <c r="AW17" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="160"/>
         <v>39510</v>
       </c>
       <c r="AX17" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="160"/>
         <v>53394</v>
       </c>
       <c r="AY17" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="160"/>
         <v>45687</v>
       </c>
       <c r="AZ17" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="160"/>
         <v>48351</v>
       </c>
       <c r="BA17" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="160"/>
         <v>59531</v>
       </c>
       <c r="BB17" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="160"/>
         <v>55256</v>
       </c>
       <c r="BC17" s="9">
-        <f t="shared" si="153"/>
+        <f t="shared" si="160"/>
         <v>57411</v>
       </c>
       <c r="BD17" s="9">
-        <f t="shared" ref="BD17:BM17" si="154">BD15-BD16</f>
+        <f t="shared" ref="BD17:BM17" si="161">BD15-BD16</f>
         <v>94680</v>
       </c>
       <c r="BE17" s="9">
-        <f t="shared" ref="BE17:BF17" si="155">BE15-BE16</f>
+        <f t="shared" ref="BE17:BF17" si="162">BE15-BE16</f>
         <v>99803</v>
       </c>
       <c r="BF17" s="9">
-        <f t="shared" si="155"/>
+        <f t="shared" si="162"/>
         <v>96995</v>
       </c>
       <c r="BG17" s="9">
-        <f t="shared" ref="BG17" si="156">BG15-BG16</f>
+        <f t="shared" ref="BG17" si="163">BG15-BG16</f>
         <v>93736</v>
       </c>
       <c r="BH17" s="9">
-        <f t="shared" si="154"/>
+        <f t="shared" si="161"/>
         <v>112010</v>
       </c>
       <c r="BI17" s="9">
-        <f t="shared" si="154"/>
-        <v>119645.19882000002</v>
+        <f t="shared" si="161"/>
+        <v>115291.89882000003</v>
       </c>
       <c r="BJ17" s="9">
-        <f t="shared" si="154"/>
-        <v>125203.89426375602</v>
+        <f t="shared" si="161"/>
+        <v>120694.74612375603</v>
       </c>
       <c r="BK17" s="9">
-        <f t="shared" si="154"/>
-        <v>129626.32256328825</v>
+        <f t="shared" si="161"/>
+        <v>124982.00602547626</v>
       </c>
       <c r="BL17" s="9">
-        <f t="shared" si="154"/>
-        <v>133456.4489342382</v>
+        <f t="shared" si="161"/>
+        <v>128672.80245489701</v>
       </c>
       <c r="BM17" s="9">
-        <f t="shared" si="154"/>
-        <v>136570.75282709181</v>
+        <f t="shared" si="161"/>
+        <v>131643.59695524102</v>
       </c>
       <c r="BN17" s="9">
-        <f t="shared" ref="BN17:BP17" si="157">BN15-BN16</f>
-        <v>139208.25510220914</v>
+        <f t="shared" ref="BN17:BP17" si="164">BN15-BN16</f>
+        <v>134182.75702606558</v>
       </c>
       <c r="BO17" s="9">
-        <f t="shared" si="157"/>
-        <v>142179.76567896019</v>
+        <f t="shared" si="164"/>
+        <v>137053.75679745857</v>
       </c>
       <c r="BP17" s="9">
-        <f t="shared" si="157"/>
-        <v>145230.77472310906</v>
+        <f t="shared" si="164"/>
+        <v>140002.24566752152</v>
       </c>
       <c r="BQ17" s="9">
-        <f t="shared" ref="BQ17:BR17" si="158">BQ15-BQ16</f>
-        <v>148364.76309831394</v>
+        <f t="shared" ref="BQ17:BR17" si="165">BQ15-BQ16</f>
+        <v>143031.66346159976</v>
       </c>
       <c r="BR17" s="9">
-        <f t="shared" si="158"/>
-        <v>151584.20172673929</v>
+        <f t="shared" si="165"/>
+        <v>146144.44009729094</v>
       </c>
       <c r="BS17" s="6">
         <f>BR17*(1+$BU$30)</f>
-        <v>150068.3597094719</v>
+        <v>144682.99569631802</v>
       </c>
       <c r="BT17" s="6">
-        <f t="shared" ref="BT17:CX17" si="159">BQ17*(1+$BU$30)</f>
-        <v>146881.11546733079</v>
+        <f t="shared" ref="BT17:CX17" si="166">BQ17*(1+$BU$30)</f>
+        <v>141601.34682698376</v>
       </c>
       <c r="BU17" s="6">
-        <f t="shared" si="159"/>
-        <v>150068.3597094719</v>
+        <f t="shared" si="166"/>
+        <v>144682.99569631802</v>
       </c>
       <c r="BV17" s="6">
-        <f t="shared" si="159"/>
-        <v>148567.67611237717</v>
+        <f t="shared" si="166"/>
+        <v>143236.16573935482</v>
       </c>
       <c r="BW17" s="6">
-        <f t="shared" si="159"/>
-        <v>145412.30431265748</v>
+        <f t="shared" si="166"/>
+        <v>140185.33335871392</v>
       </c>
       <c r="BX17" s="6">
-        <f t="shared" si="159"/>
-        <v>148567.67611237717</v>
+        <f t="shared" si="166"/>
+        <v>143236.16573935482</v>
       </c>
       <c r="BY17" s="6">
-        <f t="shared" si="159"/>
-        <v>147081.99935125341</v>
+        <f t="shared" si="166"/>
+        <v>141803.80408196128</v>
       </c>
       <c r="BZ17" s="6">
-        <f t="shared" si="159"/>
-        <v>143958.18126953091</v>
+        <f t="shared" si="166"/>
+        <v>138783.48002512677</v>
       </c>
       <c r="CA17" s="6">
-        <f t="shared" si="159"/>
-        <v>147081.99935125341</v>
+        <f t="shared" si="166"/>
+        <v>141803.80408196128</v>
       </c>
       <c r="CB17" s="6">
-        <f t="shared" si="159"/>
-        <v>145611.17935774088</v>
+        <f t="shared" si="166"/>
+        <v>140385.76604114167</v>
       </c>
       <c r="CC17" s="6">
-        <f t="shared" si="159"/>
-        <v>142518.5994568356</v>
+        <f t="shared" si="166"/>
+        <v>137395.64522487551</v>
       </c>
       <c r="CD17" s="6">
-        <f t="shared" si="159"/>
-        <v>145611.17935774088</v>
+        <f t="shared" si="166"/>
+        <v>140385.76604114167</v>
       </c>
       <c r="CE17" s="6">
-        <f t="shared" si="159"/>
-        <v>144155.06756416347</v>
+        <f t="shared" si="166"/>
+        <v>138981.90838073025</v>
       </c>
       <c r="CF17" s="6">
-        <f t="shared" si="159"/>
-        <v>141093.41346226723</v>
+        <f t="shared" si="166"/>
+        <v>136021.68877262675</v>
       </c>
       <c r="CG17" s="6">
-        <f t="shared" si="159"/>
-        <v>144155.06756416347</v>
+        <f t="shared" si="166"/>
+        <v>138981.90838073025</v>
       </c>
       <c r="CH17" s="6">
-        <f t="shared" si="159"/>
-        <v>142713.51688852184</v>
+        <f t="shared" si="166"/>
+        <v>137592.08929692296</v>
       </c>
       <c r="CI17" s="6">
-        <f t="shared" si="159"/>
-        <v>139682.47932764454</v>
+        <f t="shared" si="166"/>
+        <v>134661.47188490047</v>
       </c>
       <c r="CJ17" s="6">
-        <f t="shared" si="159"/>
-        <v>142713.51688852184</v>
+        <f t="shared" si="166"/>
+        <v>137592.08929692296</v>
       </c>
       <c r="CK17" s="6">
-        <f t="shared" si="159"/>
-        <v>141286.38171963661</v>
+        <f t="shared" si="166"/>
+        <v>136216.16840395372</v>
       </c>
       <c r="CL17" s="6">
-        <f t="shared" si="159"/>
-        <v>138285.65453436811</v>
+        <f t="shared" si="166"/>
+        <v>133314.85716605146</v>
       </c>
       <c r="CM17" s="6">
-        <f t="shared" si="159"/>
-        <v>141286.38171963661</v>
+        <f t="shared" si="166"/>
+        <v>136216.16840395372</v>
       </c>
       <c r="CN17" s="6">
-        <f t="shared" si="159"/>
-        <v>139873.51790244025</v>
+        <f t="shared" si="166"/>
+        <v>134854.00671991418</v>
       </c>
       <c r="CO17" s="6">
-        <f t="shared" si="159"/>
-        <v>136902.79798902443</v>
+        <f t="shared" si="166"/>
+        <v>131981.70859439095</v>
       </c>
       <c r="CP17" s="6">
-        <f t="shared" si="159"/>
-        <v>139873.51790244025</v>
+        <f t="shared" si="166"/>
+        <v>134854.00671991418</v>
       </c>
       <c r="CQ17" s="6">
-        <f t="shared" si="159"/>
-        <v>138474.78272341585</v>
+        <f t="shared" si="166"/>
+        <v>133505.46665271503</v>
       </c>
       <c r="CR17" s="6">
-        <f t="shared" si="159"/>
-        <v>135533.7700091342</v>
+        <f t="shared" si="166"/>
+        <v>130661.89150844704</v>
       </c>
       <c r="CS17" s="6">
-        <f t="shared" si="159"/>
-        <v>138474.78272341585</v>
+        <f t="shared" si="166"/>
+        <v>133505.46665271503</v>
       </c>
       <c r="CT17" s="6">
-        <f t="shared" si="159"/>
-        <v>137090.03489618169</v>
+        <f t="shared" si="166"/>
+        <v>132170.41198618789</v>
       </c>
       <c r="CU17" s="6">
-        <f t="shared" si="159"/>
-        <v>134178.43230904287</v>
+        <f t="shared" si="166"/>
+        <v>129355.27259336256</v>
       </c>
       <c r="CV17" s="6">
-        <f t="shared" si="159"/>
-        <v>137090.03489618169</v>
+        <f t="shared" si="166"/>
+        <v>132170.41198618789</v>
       </c>
       <c r="CW17" s="6">
-        <f t="shared" si="159"/>
-        <v>135719.13454721987</v>
+        <f t="shared" si="166"/>
+        <v>130848.707866326</v>
       </c>
       <c r="CX17" s="6">
-        <f t="shared" si="159"/>
-        <v>132836.64798595244</v>
+        <f t="shared" si="166"/>
+        <v>128061.71986742894</v>
       </c>
       <c r="CY17" s="6">
-        <f t="shared" ref="CY17:ED17" si="160">CV17*(1+$BU$30)</f>
-        <v>135719.13454721987</v>
+        <f t="shared" ref="CY17:ED17" si="167">CV17*(1+$BU$30)</f>
+        <v>130848.707866326</v>
       </c>
       <c r="CZ17" s="6">
-        <f t="shared" si="160"/>
-        <v>134361.94320174766</v>
+        <f t="shared" si="167"/>
+        <v>129540.22078766274</v>
       </c>
       <c r="DA17" s="6">
-        <f t="shared" si="160"/>
-        <v>131508.28150609293</v>
+        <f t="shared" si="167"/>
+        <v>126781.10266875465</v>
       </c>
       <c r="DB17" s="6">
-        <f t="shared" si="160"/>
-        <v>134361.94320174766</v>
+        <f t="shared" si="167"/>
+        <v>129540.22078766274</v>
       </c>
       <c r="DC17" s="6">
-        <f t="shared" si="160"/>
-        <v>133018.3237697302</v>
+        <f t="shared" si="167"/>
+        <v>128244.81857978611</v>
       </c>
       <c r="DD17" s="6">
-        <f t="shared" si="160"/>
-        <v>130193.198691032</v>
+        <f t="shared" si="167"/>
+        <v>125513.29164206711</v>
       </c>
       <c r="DE17" s="6">
-        <f t="shared" si="160"/>
-        <v>133018.3237697302</v>
+        <f t="shared" si="167"/>
+        <v>128244.81857978611</v>
       </c>
       <c r="DF17" s="6">
-        <f t="shared" si="160"/>
-        <v>131688.14053203291</v>
+        <f t="shared" si="167"/>
+        <v>126962.37039398824</v>
       </c>
       <c r="DG17" s="6">
-        <f t="shared" si="160"/>
-        <v>128891.26670412168</v>
+        <f t="shared" si="167"/>
+        <v>124258.15872564644</v>
       </c>
       <c r="DH17" s="6">
-        <f t="shared" si="160"/>
-        <v>131688.14053203291</v>
+        <f t="shared" si="167"/>
+        <v>126962.37039398824</v>
       </c>
       <c r="DI17" s="6">
-        <f t="shared" si="160"/>
-        <v>130371.25912671258</v>
+        <f t="shared" si="167"/>
+        <v>125692.74669004836</v>
       </c>
       <c r="DJ17" s="6">
-        <f t="shared" si="160"/>
-        <v>127602.35403708045</v>
+        <f t="shared" si="167"/>
+        <v>123015.57713838997</v>
       </c>
       <c r="DK17" s="6">
-        <f t="shared" si="160"/>
-        <v>130371.25912671258</v>
+        <f t="shared" si="167"/>
+        <v>125692.74669004836</v>
       </c>
       <c r="DL17" s="6">
-        <f t="shared" si="160"/>
-        <v>129067.54653544545</v>
+        <f t="shared" si="167"/>
+        <v>124435.81922314788</v>
       </c>
       <c r="DM17" s="6">
-        <f t="shared" si="160"/>
-        <v>126326.33049670965</v>
+        <f t="shared" si="167"/>
+        <v>121785.42136700607</v>
       </c>
       <c r="DN17" s="6">
-        <f t="shared" si="160"/>
-        <v>129067.54653544545</v>
+        <f t="shared" si="167"/>
+        <v>124435.81922314788</v>
       </c>
       <c r="DO17" s="6">
-        <f t="shared" si="160"/>
-        <v>127776.871070091</v>
+        <f t="shared" si="167"/>
+        <v>123191.4610309164</v>
       </c>
       <c r="DP17" s="6">
-        <f t="shared" si="160"/>
-        <v>125063.06719174255</v>
+        <f t="shared" si="167"/>
+        <v>120567.56715333601</v>
       </c>
       <c r="DQ17" s="6">
-        <f t="shared" si="160"/>
-        <v>127776.871070091</v>
+        <f t="shared" si="167"/>
+        <v>123191.4610309164</v>
       </c>
       <c r="DR17" s="6">
-        <f t="shared" si="160"/>
-        <v>126499.10235939009</v>
+        <f t="shared" si="167"/>
+        <v>121959.54642060724</v>
       </c>
       <c r="DS17" s="6">
-        <f t="shared" si="160"/>
-        <v>123812.43651982512</v>
+        <f t="shared" si="167"/>
+        <v>119361.89148180265</v>
       </c>
       <c r="DT17" s="6">
-        <f t="shared" si="160"/>
-        <v>126499.10235939009</v>
+        <f t="shared" si="167"/>
+        <v>121959.54642060724</v>
       </c>
       <c r="DU17" s="6">
-        <f t="shared" si="160"/>
-        <v>125234.11133579619</v>
+        <f t="shared" si="167"/>
+        <v>120739.95095640117</v>
       </c>
       <c r="DV17" s="6">
-        <f t="shared" si="160"/>
-        <v>122574.31215462687</v>
+        <f t="shared" si="167"/>
+        <v>118168.27256698463</v>
       </c>
       <c r="DW17" s="6">
-        <f t="shared" si="160"/>
-        <v>125234.11133579619</v>
+        <f t="shared" si="167"/>
+        <v>120739.95095640117</v>
       </c>
       <c r="DX17" s="6">
-        <f t="shared" si="160"/>
-        <v>123981.77022243822</v>
+        <f t="shared" si="167"/>
+        <v>119532.55144683715</v>
       </c>
       <c r="DY17" s="6">
-        <f t="shared" si="160"/>
-        <v>121348.5690330806</v>
+        <f t="shared" si="167"/>
+        <v>116986.58984131478</v>
       </c>
       <c r="DZ17" s="6">
-        <f t="shared" si="160"/>
-        <v>123981.77022243822</v>
+        <f t="shared" si="167"/>
+        <v>119532.55144683715</v>
       </c>
       <c r="EA17" s="6">
-        <f t="shared" si="160"/>
-        <v>122741.95252021385</v>
+        <f t="shared" si="167"/>
+        <v>118337.22593236878</v>
       </c>
       <c r="EB17" s="6">
-        <f t="shared" si="160"/>
-        <v>120135.08334274979</v>
+        <f t="shared" si="167"/>
+        <v>115816.72394290163</v>
       </c>
       <c r="EC17" s="6">
-        <f t="shared" si="160"/>
-        <v>122741.95252021385</v>
+        <f t="shared" si="167"/>
+        <v>118337.22593236878</v>
       </c>
       <c r="ED17" s="6">
-        <f t="shared" si="160"/>
-        <v>121514.5329950117</v>
+        <f t="shared" si="167"/>
+        <v>117153.85367304509</v>
       </c>
       <c r="EE17" s="6">
-        <f t="shared" ref="EE17:FJ17" si="161">EB17*(1+$BU$30)</f>
-        <v>118933.73250932229</v>
+        <f t="shared" ref="EE17:FJ17" si="168">EB17*(1+$BU$30)</f>
+        <v>114658.55670347261</v>
       </c>
       <c r="EF17" s="6">
-        <f t="shared" si="161"/>
-        <v>121514.5329950117</v>
+        <f t="shared" si="168"/>
+        <v>117153.85367304509</v>
       </c>
       <c r="EG17" s="6">
-        <f t="shared" si="161"/>
-        <v>120299.38766506159</v>
+        <f t="shared" si="168"/>
+        <v>115982.31513631463</v>
       </c>
       <c r="EH17" s="6">
-        <f t="shared" si="161"/>
-        <v>117744.39518422907</v>
+        <f t="shared" si="168"/>
+        <v>113511.97113643789</v>
       </c>
       <c r="EI17" s="6">
-        <f t="shared" si="161"/>
-        <v>120299.38766506159</v>
+        <f t="shared" si="168"/>
+        <v>115982.31513631463</v>
       </c>
       <c r="EJ17" s="6">
-        <f t="shared" si="161"/>
-        <v>119096.39378841096</v>
+        <f t="shared" si="168"/>
+        <v>114822.49198495148</v>
       </c>
       <c r="EK17" s="6">
-        <f t="shared" si="161"/>
-        <v>116566.95123238678</v>
+        <f t="shared" si="168"/>
+        <v>112376.8514250735</v>
       </c>
       <c r="EL17" s="6">
-        <f t="shared" si="161"/>
-        <v>119096.39378841096</v>
+        <f t="shared" si="168"/>
+        <v>114822.49198495148</v>
       </c>
       <c r="EM17" s="6">
-        <f t="shared" si="161"/>
-        <v>117905.42985052685</v>
+        <f t="shared" si="168"/>
+        <v>113674.26706510197</v>
       </c>
       <c r="EN17" s="6">
-        <f t="shared" si="161"/>
-        <v>115401.28172006291</v>
+        <f t="shared" si="168"/>
+        <v>111253.08291082276</v>
       </c>
       <c r="EO17" s="6">
-        <f t="shared" si="161"/>
-        <v>117905.42985052685</v>
+        <f t="shared" si="168"/>
+        <v>113674.26706510197</v>
       </c>
       <c r="EP17" s="6">
-        <f t="shared" si="161"/>
-        <v>116726.37555202158</v>
+        <f t="shared" si="168"/>
+        <v>112537.52439445096</v>
       </c>
       <c r="EQ17" s="6">
-        <f t="shared" si="161"/>
-        <v>114247.26890286227</v>
+        <f t="shared" si="168"/>
+        <v>110140.55208171453</v>
       </c>
       <c r="ER17" s="6">
-        <f t="shared" si="161"/>
-        <v>116726.37555202158</v>
+        <f t="shared" si="168"/>
+        <v>112537.52439445096</v>
       </c>
       <c r="ES17" s="6">
-        <f t="shared" si="161"/>
-        <v>115559.11179650135</v>
+        <f t="shared" si="168"/>
+        <v>111412.14915050645</v>
       </c>
       <c r="ET17" s="6">
-        <f t="shared" si="161"/>
-        <v>113104.79621383364</v>
+        <f t="shared" si="168"/>
+        <v>109039.14656089738</v>
       </c>
       <c r="EU17" s="6">
-        <f t="shared" si="161"/>
-        <v>115559.11179650135</v>
+        <f t="shared" si="168"/>
+        <v>111412.14915050645</v>
       </c>
       <c r="EV17" s="6">
-        <f t="shared" si="161"/>
-        <v>114403.52067853634</v>
+        <f t="shared" si="168"/>
+        <v>110298.02765900138</v>
       </c>
       <c r="EW17" s="6">
-        <f t="shared" si="161"/>
-        <v>111973.7482516953</v>
+        <f t="shared" si="168"/>
+        <v>107948.7550952884</v>
       </c>
       <c r="EX17" s="6">
-        <f t="shared" si="161"/>
-        <v>114403.52067853634</v>
+        <f t="shared" si="168"/>
+        <v>110298.02765900138</v>
       </c>
       <c r="EY17" s="6">
-        <f t="shared" si="161"/>
-        <v>113259.48547175097</v>
+        <f t="shared" si="168"/>
+        <v>109195.04738241137</v>
       </c>
       <c r="EZ17" s="6">
-        <f t="shared" si="161"/>
-        <v>110854.01076917835</v>
+        <f t="shared" si="168"/>
+        <v>106869.26754433553</v>
       </c>
       <c r="FA17" s="6">
-        <f t="shared" si="161"/>
-        <v>113259.48547175097</v>
+        <f t="shared" si="168"/>
+        <v>109195.04738241137</v>
       </c>
       <c r="FB17" s="6">
-        <f t="shared" si="161"/>
-        <v>112126.89061703347</v>
+        <f t="shared" si="168"/>
+        <v>108103.09690858726</v>
       </c>
       <c r="FC17" s="6">
-        <f t="shared" si="161"/>
-        <v>109745.47066148656</v>
+        <f t="shared" si="168"/>
+        <v>105800.57486889217</v>
       </c>
       <c r="FD17" s="6">
-        <f t="shared" si="161"/>
-        <v>112126.89061703347</v>
+        <f t="shared" si="168"/>
+        <v>108103.09690858726</v>
       </c>
       <c r="FE17" s="6">
-        <f t="shared" si="161"/>
-        <v>111005.62171086312</v>
+        <f t="shared" si="168"/>
+        <v>107022.06593950139</v>
       </c>
       <c r="FF17" s="6">
-        <f t="shared" si="161"/>
-        <v>108648.01595487169</v>
+        <f t="shared" si="168"/>
+        <v>104742.56912020325</v>
       </c>
       <c r="FG17" s="6">
-        <f t="shared" si="161"/>
-        <v>111005.62171086312</v>
+        <f t="shared" si="168"/>
+        <v>107022.06593950139</v>
       </c>
       <c r="FH17" s="6">
-        <f t="shared" si="161"/>
-        <v>109895.56549375449</v>
+        <f t="shared" si="168"/>
+        <v>105951.84528010638</v>
       </c>
       <c r="FI17" s="6">
-        <f t="shared" si="161"/>
-        <v>107561.53579532297</v>
+        <f t="shared" si="168"/>
+        <v>103695.14342900121</v>
       </c>
       <c r="FJ17" s="6">
-        <f t="shared" si="161"/>
-        <v>109895.56549375449</v>
+        <f t="shared" si="168"/>
+        <v>105951.84528010638</v>
       </c>
       <c r="FK17" s="6">
-        <f t="shared" ref="FK17:GA17" si="162">FH17*(1+$BU$30)</f>
-        <v>108796.60983881695</v>
+        <f t="shared" ref="FK17:GA17" si="169">FH17*(1+$BU$30)</f>
+        <v>104892.32682730533</v>
       </c>
       <c r="FL17" s="6">
-        <f t="shared" si="162"/>
-        <v>106485.92043736974</v>
+        <f t="shared" si="169"/>
+        <v>102658.1919947112</v>
       </c>
       <c r="FM17" s="6">
-        <f t="shared" si="162"/>
-        <v>108796.60983881695</v>
+        <f t="shared" si="169"/>
+        <v>104892.32682730533</v>
       </c>
       <c r="FN17" s="6">
-        <f t="shared" si="162"/>
-        <v>107708.64374042877</v>
+        <f t="shared" si="169"/>
+        <v>103843.40355903227</v>
       </c>
       <c r="FO17" s="6">
-        <f t="shared" si="162"/>
-        <v>105421.06123299604</v>
+        <f t="shared" si="169"/>
+        <v>101631.61007476409</v>
       </c>
       <c r="FP17" s="6">
-        <f t="shared" si="162"/>
-        <v>107708.64374042877</v>
+        <f t="shared" si="169"/>
+        <v>103843.40355903227</v>
       </c>
       <c r="FQ17" s="6">
-        <f t="shared" si="162"/>
-        <v>106631.55730302449</v>
+        <f t="shared" si="169"/>
+        <v>102804.96952344195</v>
       </c>
       <c r="FR17" s="6">
-        <f t="shared" si="162"/>
-        <v>104366.85062066608</v>
+        <f t="shared" si="169"/>
+        <v>100615.29397401644</v>
       </c>
       <c r="FS17" s="6">
-        <f t="shared" si="162"/>
-        <v>106631.55730302449</v>
+        <f t="shared" si="169"/>
+        <v>102804.96952344195</v>
       </c>
       <c r="FT17" s="6">
-        <f t="shared" si="162"/>
-        <v>105565.24172999425</v>
+        <f t="shared" si="169"/>
+        <v>101776.91982820752</v>
       </c>
       <c r="FU17" s="6">
-        <f t="shared" si="162"/>
-        <v>103323.18211445941</v>
+        <f t="shared" si="169"/>
+        <v>99609.141034276283</v>
       </c>
       <c r="FV17" s="6">
-        <f t="shared" si="162"/>
-        <v>105565.24172999425</v>
+        <f t="shared" si="169"/>
+        <v>101776.91982820752</v>
       </c>
       <c r="FW17" s="6">
-        <f t="shared" si="162"/>
-        <v>104509.5893126943</v>
+        <f t="shared" si="169"/>
+        <v>100759.15062992544</v>
       </c>
       <c r="FX17" s="6">
-        <f t="shared" si="162"/>
-        <v>102289.95029331482</v>
+        <f t="shared" si="169"/>
+        <v>98613.049623933519</v>
       </c>
       <c r="FY17" s="6">
-        <f t="shared" si="162"/>
-        <v>104509.5893126943</v>
+        <f t="shared" si="169"/>
+        <v>100759.15062992544</v>
       </c>
       <c r="FZ17" s="6">
-        <f t="shared" si="162"/>
-        <v>103464.49341956736</v>
+        <f t="shared" si="169"/>
+        <v>99751.559123626183</v>
       </c>
       <c r="GA17" s="6">
-        <f t="shared" si="162"/>
-        <v>101267.05079038166</v>
+        <f t="shared" si="169"/>
+        <v>97626.919127694186</v>
       </c>
     </row>
     <row r="18" spans="2:183" x14ac:dyDescent="0.3">
@@ -5484,7 +5521,10 @@
         <f>14815.3</f>
         <v>14815.3</v>
       </c>
-      <c r="AI18" s="3"/>
+      <c r="AI18" s="3">
+        <f>14748.2</f>
+        <v>14748.2</v>
+      </c>
       <c r="AJ18" s="3"/>
       <c r="AK18" s="3"/>
       <c r="AL18" s="3"/>
@@ -5590,261 +5630,264 @@
         <v>37</v>
       </c>
       <c r="C19" s="7">
-        <f t="shared" ref="C19:N19" si="163">C17/C18</f>
+        <f t="shared" ref="C19:N19" si="170">C17/C18</f>
         <v>1.1732178198601657</v>
       </c>
       <c r="D19" s="7">
-        <f t="shared" si="163"/>
+        <f t="shared" si="170"/>
         <v>0.80818423653661653</v>
       </c>
       <c r="E19" s="7">
-        <f t="shared" si="163"/>
+        <f t="shared" si="170"/>
         <v>0.67352584435431095</v>
       </c>
       <c r="F19" s="7">
-        <f t="shared" si="163"/>
+        <f t="shared" si="170"/>
         <v>0.82590090732742794</v>
       </c>
       <c r="G19" s="7">
-        <f t="shared" si="163"/>
+        <f t="shared" si="170"/>
         <v>1.167370733790591</v>
       </c>
       <c r="H19" s="7">
-        <f t="shared" si="163"/>
+        <f t="shared" si="170"/>
         <v>0.67598162050353239</v>
       </c>
       <c r="I19" s="7">
-        <f t="shared" si="163"/>
+        <f t="shared" si="170"/>
         <v>0.58728132482808393</v>
       </c>
       <c r="J19" s="7">
-        <f t="shared" si="163"/>
+        <f t="shared" si="170"/>
         <v>0.80023219948199498</v>
       </c>
       <c r="K19" s="7">
-        <f t="shared" si="163"/>
+        <f t="shared" si="170"/>
         <v>1.3001580584306327</v>
       </c>
       <c r="L19" s="7">
-        <f t="shared" si="163"/>
+        <f t="shared" si="170"/>
         <v>0.65773871196645928</v>
       </c>
       <c r="M19" s="7">
-        <f t="shared" si="163"/>
+        <f t="shared" si="170"/>
         <v>0.65797259540924224</v>
       </c>
       <c r="N19" s="7">
-        <f t="shared" si="163"/>
+        <f t="shared" si="170"/>
         <v>0.74100121759720317</v>
       </c>
       <c r="O19" s="7">
-        <f t="shared" ref="O19:S19" si="164">O17/O18</f>
+        <f t="shared" ref="O19:S19" si="171">O17/O18</f>
         <v>1.6813295993062081</v>
       </c>
       <c r="P19" s="7">
-        <f t="shared" si="164"/>
+        <f t="shared" si="171"/>
         <v>1.4160214770248569</v>
       </c>
       <c r="Q19" s="7">
-        <f t="shared" ref="Q19:R19" si="165">Q17/Q18</f>
+        <f t="shared" ref="Q19:R19" si="172">Q17/Q18</f>
         <v>1.3980582524271845</v>
       </c>
       <c r="R19" s="7">
-        <f t="shared" si="165"/>
+        <f t="shared" si="172"/>
         <v>1.3213527936732463</v>
       </c>
       <c r="S19" s="7">
-        <f t="shared" si="164"/>
+        <f t="shared" si="171"/>
         <v>2.2265800810133092</v>
       </c>
       <c r="T19" s="7">
-        <f t="shared" ref="T19" si="166">T17/T18</f>
+        <f t="shared" ref="T19" si="173">T17/T18</f>
         <v>1.6080498939111425</v>
       </c>
       <c r="U19" s="7">
-        <f t="shared" ref="U19" si="167">U17/U18</f>
+        <f t="shared" ref="U19" si="174">U17/U18</f>
         <v>1.2500482222079341</v>
       </c>
       <c r="V19" s="7">
-        <f t="shared" ref="V19" si="168">V17/V18</f>
+        <f t="shared" ref="V19" si="175">V17/V18</f>
         <v>1.3322831608049894</v>
       </c>
       <c r="W19" s="7">
-        <f t="shared" ref="W19:X19" si="169">W17/W18</f>
+        <f t="shared" ref="W19:X19" si="176">W17/W18</f>
         <v>1.9287597248119335</v>
       </c>
       <c r="X19" s="7">
-        <f t="shared" si="169"/>
+        <f t="shared" si="176"/>
         <v>1.5533980582524272</v>
       </c>
       <c r="Y19" s="7">
-        <f t="shared" ref="Y19:Z19" si="170">Y17/Y18</f>
+        <f t="shared" ref="Y19:Z19" si="177">Y17/Y18</f>
         <v>1.2782742879187294</v>
       </c>
       <c r="Z19" s="7">
-        <f t="shared" si="170"/>
+        <f t="shared" si="177"/>
         <v>1.4759853404487879</v>
       </c>
       <c r="AA19" s="7">
-        <f t="shared" ref="AA19:AD19" si="171">AA17/AA18</f>
+        <f t="shared" ref="AA19:AD19" si="178">AA17/AA18</f>
         <v>2.1806725390599886</v>
       </c>
       <c r="AB19" s="7">
-        <f t="shared" si="171"/>
+        <f t="shared" si="178"/>
         <v>1.5197068089757604</v>
       </c>
       <c r="AC19" s="7">
-        <f t="shared" si="171"/>
+        <f t="shared" si="178"/>
         <v>1.3790265543625024</v>
       </c>
       <c r="AD19" s="7">
-        <f t="shared" si="171"/>
+        <f t="shared" si="178"/>
         <v>0.9712628526232534</v>
       </c>
       <c r="AE19" s="7">
-        <f t="shared" ref="AE19:AH19" si="172">AE17/AE18</f>
+        <f t="shared" ref="AE19:AH19" si="179">AE17/AE18</f>
         <v>2.4184368363943789</v>
       </c>
       <c r="AF19" s="7">
-        <f t="shared" si="172"/>
+        <f t="shared" si="179"/>
         <v>1.6591009520748805</v>
       </c>
       <c r="AG19" s="7">
-        <f t="shared" si="172"/>
+        <f t="shared" si="179"/>
         <v>1.5724456313871797</v>
       </c>
       <c r="AH19" s="7">
-        <f t="shared" si="172"/>
+        <f t="shared" si="179"/>
         <v>1.8538942849621676</v>
       </c>
-      <c r="AI19" s="7"/>
+      <c r="AI19" s="7">
+        <f t="shared" ref="AI19" si="180">AI17/AI18</f>
+        <v>2.854382229695827</v>
+      </c>
       <c r="AJ19" s="7"/>
       <c r="AK19" s="7"/>
       <c r="AL19" s="7"/>
       <c r="AM19" s="7"/>
       <c r="AN19" s="7">
-        <f t="shared" ref="AN19:BC19" si="173">AN17/AN18</f>
+        <f t="shared" ref="AN19:BC19" si="181">AN17/AN18</f>
         <v>1.6427511133102426</v>
       </c>
       <c r="AO19" s="7">
-        <f t="shared" si="173"/>
+        <f t="shared" si="181"/>
         <v>2.3563558820045016</v>
       </c>
       <c r="AP19" s="7">
-        <f t="shared" si="173"/>
+        <f t="shared" si="181"/>
         <v>4.0434883182974781</v>
       </c>
       <c r="AQ19" s="7">
-        <f t="shared" si="173"/>
+        <f t="shared" si="181"/>
         <v>6.9407894736842106</v>
       </c>
       <c r="AR19" s="7">
-        <f t="shared" si="173"/>
+        <f t="shared" si="181"/>
         <v>9.2217245240761478</v>
       </c>
       <c r="AS19" s="7">
-        <f t="shared" si="173"/>
+        <f t="shared" si="181"/>
         <v>15.407366684991754</v>
       </c>
       <c r="AT19" s="7">
-        <f t="shared" si="173"/>
+        <f t="shared" si="181"/>
         <v>28.045007032348806</v>
       </c>
       <c r="AU19" s="7">
-        <f t="shared" si="173"/>
+        <f t="shared" si="181"/>
         <v>6.3775845469688406</v>
       </c>
       <c r="AV19" s="7">
-        <f t="shared" si="173"/>
+        <f t="shared" si="181"/>
         <v>5.7179689067975854</v>
       </c>
       <c r="AW19" s="7">
-        <f t="shared" si="173"/>
+        <f t="shared" si="181"/>
         <v>6.4923754436703032</v>
       </c>
       <c r="AX19" s="7">
-        <f t="shared" si="173"/>
+        <f t="shared" si="181"/>
         <v>3.1219931359887214</v>
       </c>
       <c r="AY19" s="7">
-        <f t="shared" si="173"/>
+        <f t="shared" si="181"/>
         <v>2.6713582126065982</v>
       </c>
       <c r="AZ19" s="7">
-        <f t="shared" si="173"/>
+        <f t="shared" si="181"/>
         <v>2.8271245855000684</v>
       </c>
       <c r="BA19" s="7">
-        <f t="shared" si="173"/>
+        <f t="shared" si="181"/>
         <v>3.4808288080785212</v>
       </c>
       <c r="BB19" s="7">
-        <f t="shared" si="173"/>
+        <f t="shared" si="181"/>
         <v>3.2308658786042024</v>
       </c>
       <c r="BC19" s="7">
-        <f t="shared" si="173"/>
+        <f t="shared" si="181"/>
         <v>3.3568705834035373</v>
       </c>
       <c r="BD19" s="7">
-        <f t="shared" ref="BD19:BM19" si="174">BD17/BD18</f>
+        <f t="shared" ref="BD19:BM19" si="182">BD17/BD18</f>
         <v>5.6736738656247754</v>
       </c>
       <c r="BE19" s="7">
-        <f t="shared" ref="BE19:BF19" si="175">BE17/BE18</f>
+        <f t="shared" ref="BE19:BF19" si="183">BE17/BE18</f>
         <v>6.4169613579373754</v>
       </c>
       <c r="BF19" s="7">
-        <f t="shared" si="175"/>
+        <f t="shared" si="183"/>
         <v>6.2364174114318782</v>
       </c>
       <c r="BG19" s="7">
-        <f t="shared" ref="BG19" si="176">BG17/BG18</f>
+        <f t="shared" ref="BG19" si="184">BG17/BG18</f>
         <v>6.1782230424466125</v>
       </c>
       <c r="BH19" s="7">
-        <f t="shared" si="174"/>
+        <f t="shared" si="182"/>
         <v>7.5159868213569174</v>
       </c>
       <c r="BI19" s="7">
-        <f t="shared" si="174"/>
-        <v>8.0283165571801476</v>
+        <f t="shared" si="182"/>
+        <v>7.7362056257506948</v>
       </c>
       <c r="BJ19" s="7">
-        <f t="shared" si="174"/>
-        <v>8.4013107692969839</v>
+        <f t="shared" si="182"/>
+        <v>8.0987422665223576</v>
       </c>
       <c r="BK19" s="7">
-        <f t="shared" si="174"/>
-        <v>8.6980602811055743</v>
+        <f t="shared" si="182"/>
+        <v>8.3864218390699978</v>
       </c>
       <c r="BL19" s="7">
-        <f t="shared" si="174"/>
-        <v>8.9550657210501452</v>
+        <f t="shared" si="182"/>
+        <v>8.6340780958670464</v>
       </c>
       <c r="BM19" s="7">
-        <f t="shared" si="174"/>
-        <v>9.1640387325347294</v>
+        <f t="shared" si="182"/>
+        <v>8.8334214787216592</v>
       </c>
       <c r="BN19" s="7">
-        <f t="shared" ref="BN19:BP19" si="177">BN17/BN18</f>
-        <v>9.3410178624434934</v>
+        <f t="shared" ref="BN19:BP19" si="185">BN17/BN18</f>
+        <v>9.0038017450338916</v>
       </c>
       <c r="BO19" s="7">
-        <f t="shared" si="177"/>
-        <v>9.5404092947654622</v>
+        <f t="shared" si="185"/>
+        <v>9.1964487983854539</v>
       </c>
       <c r="BP19" s="7">
-        <f t="shared" si="177"/>
-        <v>9.7451351564533795</v>
+        <f t="shared" si="185"/>
+        <v>9.3942954503835843</v>
       </c>
       <c r="BQ19" s="7">
-        <f t="shared" ref="BQ19:BR19" si="178">BQ17/BQ18</f>
-        <v>9.9554290170580177</v>
+        <f t="shared" ref="BQ19:BR19" si="186">BQ17/BQ18</f>
+        <v>9.5975725168658297</v>
       </c>
       <c r="BR19" s="7">
-        <f t="shared" si="178"/>
-        <v>10.171456678011616</v>
+        <f t="shared" si="186"/>
+        <v>9.8064430478155895</v>
       </c>
     </row>
     <row r="21" spans="2:183" x14ac:dyDescent="0.3">
@@ -5856,143 +5899,143 @@
         <v>0.36113637512000402</v>
       </c>
       <c r="D21" s="10">
-        <f t="shared" ref="D21:M21" si="179">(D3-D6)/D3</f>
+        <f t="shared" ref="D21:M21" si="187">(D3-D6)/D3</f>
         <v>0.33831185290619453</v>
       </c>
       <c r="E21" s="10">
-        <f t="shared" si="179"/>
+        <f t="shared" si="187"/>
         <v>0.32808910546467107</v>
       </c>
       <c r="F21" s="10">
-        <f t="shared" si="179"/>
+        <f t="shared" si="187"/>
         <v>0.33659012255979809</v>
       </c>
       <c r="G21" s="10">
-        <f t="shared" si="179"/>
+        <f t="shared" si="187"/>
         <v>0.34311976577926057</v>
       </c>
       <c r="H21" s="10">
-        <f t="shared" si="179"/>
+        <f t="shared" si="187"/>
         <v>0.3117792333297541</v>
       </c>
       <c r="I21" s="10">
-        <f t="shared" si="179"/>
+        <f t="shared" si="187"/>
         <v>0.30412711904424611</v>
       </c>
       <c r="J21" s="10">
-        <f t="shared" si="179"/>
+        <f t="shared" si="187"/>
         <v>0.31615206970831961</v>
       </c>
       <c r="K21" s="10">
-        <f t="shared" si="179"/>
+        <f t="shared" si="187"/>
         <v>0.3416894215210356</v>
       </c>
       <c r="L21" s="10">
-        <f t="shared" si="179"/>
+        <f t="shared" si="187"/>
         <v>0.30343600578227509</v>
       </c>
       <c r="M21" s="10">
-        <f t="shared" si="179"/>
+        <f t="shared" si="187"/>
         <v>0.29736293494379851</v>
       </c>
       <c r="N21" s="10">
-        <f t="shared" ref="N21:BC21" si="180">(N3-N6)/N3</f>
+        <f t="shared" ref="N21:BC21" si="188">(N3-N6)/N3</f>
         <v>0.2981515085046561</v>
       </c>
       <c r="O21" s="10">
-        <f t="shared" ref="O21:S21" si="181">(O3-O6)/O3</f>
+        <f t="shared" ref="O21:S21" si="189">(O3-O6)/O3</f>
         <v>0.35063441961579467</v>
       </c>
       <c r="P21" s="10">
-        <f t="shared" si="181"/>
+        <f t="shared" si="189"/>
         <v>0.3609647372838215</v>
       </c>
       <c r="Q21" s="10">
-        <f t="shared" ref="Q21:R21" si="182">(Q3-Q6)/Q3</f>
+        <f t="shared" ref="Q21:R21" si="190">(Q3-Q6)/Q3</f>
         <v>0.36043347720022517</v>
       </c>
       <c r="R21" s="10">
-        <f t="shared" si="182"/>
+        <f t="shared" si="190"/>
         <v>0.34253184395310604</v>
       </c>
       <c r="S21" s="10">
-        <f t="shared" si="181"/>
+        <f t="shared" si="189"/>
         <v>0.38418446983117716</v>
       </c>
       <c r="T21" s="10">
-        <f t="shared" ref="T21:U21" si="183">(T3-T6)/T3</f>
+        <f t="shared" ref="T21:U21" si="191">(T3-T6)/T3</f>
         <v>0.36364692668190091</v>
       </c>
       <c r="U21" s="10">
-        <f t="shared" si="183"/>
+        <f t="shared" si="191"/>
         <v>0.34519769552521506</v>
       </c>
       <c r="V21" s="10">
-        <f t="shared" ref="V21:V22" si="184">(V3-V6)/V3</f>
+        <f t="shared" ref="V21:V22" si="192">(V3-V6)/V3</f>
         <v>0.34627526142224979</v>
       </c>
       <c r="W21" s="10">
-        <f t="shared" ref="W21:X21" si="185">(W3-W6)/W3</f>
+        <f t="shared" ref="W21:X21" si="193">(W3-W6)/W3</f>
         <v>0.36957920073038136</v>
       </c>
       <c r="X21" s="10">
-        <f t="shared" si="185"/>
+        <f t="shared" si="193"/>
         <v>0.36702782399329087</v>
       </c>
       <c r="Y21" s="10">
-        <f t="shared" ref="Y21:Z21" si="186">(Y3-Y6)/Y3</f>
+        <f t="shared" ref="Y21:Z21" si="194">(Y3-Y6)/Y3</f>
         <v>0.35402086359434837</v>
       </c>
       <c r="Z21" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="194"/>
         <v>0.36612884020004766</v>
       </c>
       <c r="AA21" s="10">
-        <f t="shared" ref="AA21:AD21" si="187">(AA3-AA6)/AA3</f>
+        <f t="shared" ref="AA21:AD21" si="195">(AA3-AA6)/AA3</f>
         <v>0.39414045491301913</v>
       </c>
       <c r="AB21" s="10">
-        <f t="shared" si="187"/>
+        <f t="shared" si="195"/>
         <v>0.36572675896301171</v>
       </c>
       <c r="AC21" s="10">
-        <f t="shared" si="187"/>
+        <f t="shared" si="195"/>
         <v>0.35346956013254499</v>
       </c>
       <c r="AD21" s="10">
-        <f t="shared" si="187"/>
+        <f t="shared" si="195"/>
         <v>0.36296063352297092</v>
       </c>
       <c r="AE21" s="10">
-        <f t="shared" ref="AE21:AH21" si="188">(AE3-AE6)/AE3</f>
+        <f t="shared" ref="AE21:AH21" si="196">(AE3-AE6)/AE3</f>
         <v>0.39315026541445486</v>
       </c>
       <c r="AF21" s="10">
-        <f t="shared" si="188"/>
+        <f t="shared" si="196"/>
         <v>0.35922810489856505</v>
       </c>
       <c r="AG21" s="10">
-        <f t="shared" si="188"/>
+        <f t="shared" si="196"/>
         <v>0.3451728641556453</v>
       </c>
       <c r="AH21" s="10">
-        <f t="shared" si="188"/>
+        <f t="shared" si="196"/>
         <v>0.36216018232134134</v>
       </c>
-      <c r="AI21" s="10" t="e">
-        <f t="shared" ref="AI21:AL21" si="189">(AI3-AI6)/AI3</f>
+      <c r="AI21" s="10">
+        <f t="shared" ref="AI21:AL21" si="197">(AI3-AI6)/AI3</f>
+        <v>0.40675030551330632</v>
+      </c>
+      <c r="AJ21" s="10" t="e">
+        <f t="shared" si="197"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AJ21" s="10" t="e">
-        <f t="shared" si="189"/>
+      <c r="AK21" s="10" t="e">
+        <f t="shared" si="197"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AK21" s="10" t="e">
-        <f t="shared" si="189"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="AL21" s="10" t="e">
-        <f t="shared" si="189"/>
+        <f t="shared" si="197"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AM21" s="10"/>
@@ -6009,75 +6052,75 @@
       <c r="AX21" s="10"/>
       <c r="AY21" s="10"/>
       <c r="BA21" s="10">
-        <f t="shared" si="180"/>
+        <f t="shared" si="188"/>
         <v>0.34396294836770025</v>
       </c>
       <c r="BB21" s="10">
-        <f t="shared" si="180"/>
+        <f t="shared" si="188"/>
         <v>0.32207795851002652</v>
       </c>
       <c r="BC21" s="10">
-        <f t="shared" si="180"/>
+        <f t="shared" si="188"/>
         <v>0.31466339293399231</v>
       </c>
       <c r="BD21" s="10">
-        <f t="shared" ref="BD21:BE21" si="190">(BD3-BD6)/BD3</f>
+        <f t="shared" ref="BD21:BE21" si="198">(BD3-BD6)/BD3</f>
         <v>0.35349303276483562</v>
       </c>
       <c r="BE21" s="10">
-        <f t="shared" si="190"/>
+        <f t="shared" si="198"/>
         <v>0.36283479707399452</v>
       </c>
       <c r="BF21" s="10">
-        <f t="shared" ref="BF21:BG21" si="191">(BF3-BF6)/BF3</f>
+        <f t="shared" ref="BF21:BG21" si="199">(BF3-BF6)/BF3</f>
         <v>0.36500662562691849</v>
       </c>
       <c r="BG21" s="10">
-        <f t="shared" si="191"/>
+        <f t="shared" si="199"/>
         <v>0.37180617636485724</v>
       </c>
       <c r="BH21" s="10">
-        <f t="shared" ref="BH21:BR21" si="192">(BH3-BH6)/BH3</f>
+        <f t="shared" ref="BH21:BR21" si="200">(BH3-BH6)/BH3</f>
         <v>0.36770650449669873</v>
       </c>
       <c r="BI21" s="10">
-        <f t="shared" si="192"/>
+        <f t="shared" si="200"/>
         <v>0.37</v>
       </c>
       <c r="BJ21" s="10">
-        <f t="shared" si="192"/>
+        <f t="shared" si="200"/>
         <v>0.36999999999999994</v>
       </c>
       <c r="BK21" s="10">
-        <f t="shared" si="192"/>
+        <f t="shared" si="200"/>
         <v>0.37</v>
       </c>
       <c r="BL21" s="10">
-        <f t="shared" si="192"/>
+        <f t="shared" si="200"/>
         <v>0.37</v>
       </c>
       <c r="BM21" s="10">
-        <f t="shared" si="192"/>
+        <f t="shared" si="200"/>
         <v>0.37</v>
       </c>
       <c r="BN21" s="10">
-        <f t="shared" si="192"/>
+        <f t="shared" si="200"/>
         <v>0.37</v>
       </c>
       <c r="BO21" s="10">
-        <f t="shared" si="192"/>
+        <f t="shared" si="200"/>
         <v>0.37</v>
       </c>
       <c r="BP21" s="10">
-        <f t="shared" si="192"/>
+        <f t="shared" si="200"/>
         <v>0.37</v>
       </c>
       <c r="BQ21" s="10">
-        <f t="shared" si="192"/>
+        <f t="shared" si="200"/>
         <v>0.37000000000000005</v>
       </c>
       <c r="BR21" s="10">
-        <f t="shared" si="192"/>
+        <f t="shared" si="200"/>
         <v>0.37</v>
       </c>
     </row>
@@ -6090,143 +6133,143 @@
         <v>0.58308686603132875</v>
       </c>
       <c r="D22" s="10">
-        <f t="shared" ref="D22:M22" si="193">(D4-D7)/D4</f>
+        <f t="shared" ref="D22:M22" si="201">(D4-D7)/D4</f>
         <v>0.61634517766497465</v>
       </c>
       <c r="E22" s="10">
-        <f t="shared" si="193"/>
+        <f t="shared" si="201"/>
         <v>0.61769911504424779</v>
       </c>
       <c r="F22" s="10">
-        <f t="shared" si="193"/>
+        <f t="shared" si="201"/>
         <v>0.61137843192754038</v>
       </c>
       <c r="G22" s="10">
-        <f t="shared" si="193"/>
+        <f t="shared" si="201"/>
         <v>0.62841379310344825</v>
       </c>
       <c r="H22" s="10">
-        <f t="shared" si="193"/>
+        <f t="shared" si="201"/>
         <v>0.63781659388646283</v>
       </c>
       <c r="I22" s="10">
-        <f t="shared" si="193"/>
+        <f t="shared" si="201"/>
         <v>0.64129201222173726</v>
       </c>
       <c r="J22" s="10">
-        <f t="shared" si="193"/>
+        <f t="shared" si="201"/>
         <v>0.64119574774198707</v>
       </c>
       <c r="K22" s="10">
-        <f t="shared" si="193"/>
+        <f t="shared" si="201"/>
         <v>0.64396382225717652</v>
       </c>
       <c r="L22" s="10">
-        <f t="shared" si="193"/>
+        <f t="shared" si="201"/>
         <v>0.65373089601438417</v>
       </c>
       <c r="M22" s="10">
-        <f t="shared" si="193"/>
+        <f t="shared" si="201"/>
         <v>0.67224080267558528</v>
       </c>
       <c r="N22" s="10">
-        <f t="shared" ref="N22:BC22" si="194">(N4-N7)/N4</f>
+        <f t="shared" ref="N22:BC22" si="202">(N4-N7)/N4</f>
         <v>0.66925561894288266</v>
       </c>
       <c r="O22" s="10">
-        <f t="shared" ref="O22:S22" si="195">(O4-O7)/O4</f>
+        <f t="shared" ref="O22:S22" si="203">(O4-O7)/O4</f>
         <v>0.6839667533785927</v>
       </c>
       <c r="P22" s="10">
-        <f t="shared" si="195"/>
+        <f t="shared" si="203"/>
         <v>0.70072776758771671</v>
       </c>
       <c r="Q22" s="10">
-        <f t="shared" ref="Q22:R22" si="196">(Q4-Q7)/Q4</f>
+        <f t="shared" ref="Q22:R22" si="204">(Q4-Q7)/Q4</f>
         <v>0.69804414960539862</v>
       </c>
       <c r="R22" s="10">
-        <f t="shared" si="196"/>
+        <f t="shared" si="204"/>
         <v>0.704765552333534</v>
       </c>
       <c r="S22" s="10">
-        <f t="shared" si="195"/>
+        <f t="shared" si="203"/>
         <v>0.72366263578602175</v>
       </c>
       <c r="T22" s="10">
-        <f t="shared" ref="T22:U22" si="197">(T4-T7)/T4</f>
+        <f t="shared" ref="T22:U22" si="205">(T4-T7)/T4</f>
         <v>0.72609858231168967</v>
       </c>
       <c r="U22" s="10">
-        <f t="shared" si="197"/>
+        <f t="shared" si="205"/>
         <v>0.71490512140379514</v>
       </c>
       <c r="V22" s="10">
-        <f t="shared" si="184"/>
+        <f t="shared" si="192"/>
         <v>0.70481550969355844</v>
       </c>
       <c r="W22" s="10">
-        <f t="shared" ref="W22:X22" si="198">(W4-W7)/W4</f>
+        <f t="shared" ref="W22:X22" si="206">(W4-W7)/W4</f>
         <v>0.70832129442357705</v>
       </c>
       <c r="X22" s="10">
-        <f t="shared" si="198"/>
+        <f t="shared" si="206"/>
         <v>0.70990577318601422</v>
       </c>
       <c r="Y22" s="10">
-        <f t="shared" ref="Y22:Z22" si="199">(Y4-Y7)/Y4</f>
+        <f t="shared" ref="Y22:Z22" si="207">(Y4-Y7)/Y4</f>
         <v>0.70546363079243857</v>
       </c>
       <c r="Z22" s="10">
-        <f t="shared" si="199"/>
+        <f t="shared" si="207"/>
         <v>0.70937528009321504</v>
       </c>
       <c r="AA22" s="10">
-        <f t="shared" ref="AA22:AD22" si="200">(AA4-AA7)/AA4</f>
+        <f t="shared" ref="AA22:AD22" si="208">(AA4-AA7)/AA4</f>
         <v>0.728338452221309</v>
       </c>
       <c r="AB22" s="10">
-        <f t="shared" si="200"/>
+        <f t="shared" si="208"/>
         <v>0.74617672937528801</v>
       </c>
       <c r="AC22" s="10">
-        <f t="shared" si="200"/>
+        <f t="shared" si="208"/>
         <v>0.73997439392062114</v>
       </c>
       <c r="AD22" s="10">
-        <f t="shared" si="200"/>
+        <f t="shared" si="208"/>
         <v>0.74030914624379307</v>
       </c>
       <c r="AE22" s="10">
-        <f t="shared" ref="AE22:AH22" si="201">(AE4-AE7)/AE4</f>
+        <f t="shared" ref="AE22:AH22" si="209">(AE4-AE7)/AE4</f>
         <v>0.75026575550493546</v>
       </c>
       <c r="AF22" s="10">
-        <f t="shared" si="201"/>
+        <f t="shared" si="209"/>
         <v>0.75747795083505343</v>
       </c>
       <c r="AG22" s="10">
-        <f t="shared" si="201"/>
+        <f t="shared" si="209"/>
         <v>0.75575247055391459</v>
       </c>
       <c r="AH22" s="10">
-        <f t="shared" si="201"/>
+        <f t="shared" si="209"/>
         <v>0.75283478260869563</v>
       </c>
-      <c r="AI22" s="10" t="e">
-        <f t="shared" ref="AI22:AL22" si="202">(AI4-AI7)/AI4</f>
+      <c r="AI22" s="10">
+        <f t="shared" ref="AI22:AL22" si="210">(AI4-AI7)/AI4</f>
+        <v>0.76520174591010559</v>
+      </c>
+      <c r="AJ22" s="10" t="e">
+        <f t="shared" si="210"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AJ22" s="10" t="e">
-        <f t="shared" si="202"/>
+      <c r="AK22" s="10" t="e">
+        <f t="shared" si="210"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AK22" s="10" t="e">
-        <f t="shared" si="202"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="AL22" s="10" t="e">
-        <f t="shared" si="202"/>
+        <f t="shared" si="210"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AM22" s="10"/>
@@ -6243,75 +6286,75 @@
       <c r="AX22" s="10"/>
       <c r="AY22" s="10"/>
       <c r="BA22" s="10">
-        <f t="shared" si="194"/>
+        <f t="shared" si="202"/>
         <v>0.60772869075173597</v>
       </c>
       <c r="BB22" s="10">
-        <f t="shared" si="194"/>
+        <f t="shared" si="202"/>
         <v>0.63738091637683347</v>
       </c>
       <c r="BC22" s="10">
-        <f t="shared" si="194"/>
+        <f t="shared" si="202"/>
         <v>0.66015101919357233</v>
       </c>
       <c r="BD22" s="10">
-        <f t="shared" ref="BD22:BE22" si="203">(BD4-BD7)/BD4</f>
+        <f t="shared" ref="BD22:BE22" si="211">(BD4-BD7)/BD4</f>
         <v>0.69725977347460721</v>
       </c>
       <c r="BE22" s="10">
-        <f t="shared" si="203"/>
+        <f t="shared" si="211"/>
         <v>0.71745446633132381</v>
       </c>
       <c r="BF22" s="10">
-        <f t="shared" ref="BF22:BG22" si="204">(BF4-BF7)/BF4</f>
+        <f t="shared" ref="BF22:BG22" si="212">(BF4-BF7)/BF4</f>
         <v>0.70827464788732397</v>
       </c>
       <c r="BG22" s="10">
-        <f t="shared" si="204"/>
+        <f t="shared" si="212"/>
         <v>0.7388035645582256</v>
       </c>
       <c r="BH22" s="10">
-        <f t="shared" ref="BH22:BR22" si="205">(BH4-BH7)/BH4</f>
+        <f t="shared" ref="BH22:BR22" si="213">(BH4-BH7)/BH4</f>
         <v>0.75408124003737698</v>
       </c>
       <c r="BI22" s="10">
-        <f t="shared" si="205"/>
+        <f t="shared" si="213"/>
         <v>0.76</v>
       </c>
       <c r="BJ22" s="10">
-        <f t="shared" si="205"/>
+        <f t="shared" si="213"/>
         <v>0.76</v>
       </c>
       <c r="BK22" s="10">
-        <f t="shared" si="205"/>
+        <f t="shared" si="213"/>
         <v>0.76000000000000012</v>
       </c>
       <c r="BL22" s="10">
-        <f t="shared" si="205"/>
+        <f t="shared" si="213"/>
         <v>0.76</v>
       </c>
       <c r="BM22" s="10">
-        <f t="shared" si="205"/>
+        <f t="shared" si="213"/>
         <v>0.7599999999999999</v>
       </c>
       <c r="BN22" s="10">
-        <f t="shared" si="205"/>
+        <f t="shared" si="213"/>
         <v>0.76</v>
       </c>
       <c r="BO22" s="10">
-        <f t="shared" si="205"/>
+        <f t="shared" si="213"/>
         <v>0.76</v>
       </c>
       <c r="BP22" s="10">
-        <f t="shared" si="205"/>
+        <f t="shared" si="213"/>
         <v>0.76</v>
       </c>
       <c r="BQ22" s="10">
-        <f t="shared" si="205"/>
+        <f t="shared" si="213"/>
         <v>0.76</v>
       </c>
       <c r="BR22" s="10">
-        <f t="shared" si="205"/>
+        <f t="shared" si="213"/>
         <v>0.76</v>
       </c>
     </row>
@@ -6324,268 +6367,268 @@
         <v>0.38408480853521798</v>
       </c>
       <c r="D23" s="11">
-        <f t="shared" ref="D23:M23" si="206">D9/D5</f>
+        <f t="shared" ref="D23:M23" si="214">D9/D5</f>
         <v>0.38310679294044525</v>
       </c>
       <c r="E23" s="11">
-        <f t="shared" si="206"/>
+        <f t="shared" si="214"/>
         <v>0.38338496198254013</v>
       </c>
       <c r="F23" s="11">
-        <f t="shared" si="206"/>
+        <f t="shared" si="214"/>
         <v>0.38289348171701115</v>
       </c>
       <c r="G23" s="11">
-        <f t="shared" si="206"/>
+        <f t="shared" si="214"/>
         <v>0.37991934527339583</v>
       </c>
       <c r="H23" s="11">
-        <f t="shared" si="206"/>
+        <f t="shared" si="214"/>
         <v>0.37612686374213566</v>
       </c>
       <c r="I23" s="11">
-        <f t="shared" si="206"/>
+        <f t="shared" si="214"/>
         <v>0.37590365923916075</v>
       </c>
       <c r="J23" s="11">
-        <f t="shared" si="206"/>
+        <f t="shared" si="214"/>
         <v>0.37965334166146159</v>
       </c>
       <c r="K23" s="11">
-        <f t="shared" si="206"/>
+        <f t="shared" si="214"/>
         <v>0.38354806739345887</v>
       </c>
       <c r="L23" s="11">
-        <f t="shared" si="206"/>
+        <f t="shared" si="214"/>
         <v>0.38361943305952362</v>
       </c>
       <c r="M23" s="11">
-        <f t="shared" si="206"/>
+        <f t="shared" si="214"/>
         <v>0.37999497361146017</v>
       </c>
       <c r="N23" s="11">
-        <f t="shared" ref="N23:BM23" si="207">N9/N5</f>
+        <f t="shared" ref="N23:BM23" si="215">N9/N5</f>
         <v>0.38160375900336951</v>
       </c>
       <c r="O23" s="11">
-        <f t="shared" ref="O23:S23" si="208">O9/O5</f>
+        <f t="shared" ref="O23:S23" si="216">O9/O5</f>
         <v>0.39777815665969724</v>
       </c>
       <c r="P23" s="11">
-        <f t="shared" si="208"/>
+        <f t="shared" si="216"/>
         <v>0.42506474370423292</v>
       </c>
       <c r="Q23" s="11">
-        <f t="shared" ref="Q23:R23" si="209">Q9/Q5</f>
+        <f t="shared" ref="Q23:R23" si="217">Q9/Q5</f>
         <v>0.43292727853230839</v>
       </c>
       <c r="R23" s="11">
-        <f t="shared" si="209"/>
+        <f t="shared" si="217"/>
         <v>0.42195297504798462</v>
       </c>
       <c r="S23" s="11">
-        <f t="shared" si="208"/>
+        <f t="shared" si="216"/>
         <v>0.43763766186615033</v>
       </c>
       <c r="T23" s="11">
-        <f t="shared" ref="T23:U23" si="210">T9/T5</f>
+        <f t="shared" ref="T23:U23" si="218">T9/T5</f>
         <v>0.43749871502292398</v>
       </c>
       <c r="U23" s="11">
-        <f t="shared" si="210"/>
+        <f t="shared" si="218"/>
         <v>0.43256307332537758</v>
       </c>
       <c r="V23" s="11">
-        <f t="shared" ref="V23" si="211">V9/V5</f>
+        <f t="shared" ref="V23" si="219">V9/V5</f>
         <v>0.4225922392563175</v>
       </c>
       <c r="W23" s="11">
-        <f t="shared" ref="W23:X23" si="212">W9/W5</f>
+        <f t="shared" ref="W23:X23" si="220">W9/W5</f>
         <v>0.42962254809908323</v>
       </c>
       <c r="X23" s="11">
-        <f t="shared" si="212"/>
+        <f t="shared" si="220"/>
         <v>0.44261672782487665</v>
       </c>
       <c r="Y23" s="11">
-        <f t="shared" ref="Y23:Z23" si="213">Y9/Y5</f>
+        <f t="shared" ref="Y23:Z23" si="221">Y9/Y5</f>
         <v>0.44516302553883397</v>
       </c>
       <c r="Z23" s="11">
-        <f t="shared" si="213"/>
+        <f t="shared" si="221"/>
         <v>0.45170841806520817</v>
       </c>
       <c r="AA23" s="11">
-        <f t="shared" ref="AA23:AD23" si="214">AA9/AA5</f>
+        <f t="shared" ref="AA23:AD23" si="222">AA9/AA5</f>
         <v>0.45874973865774621</v>
       </c>
       <c r="AB23" s="11">
-        <f t="shared" si="214"/>
+        <f t="shared" si="222"/>
         <v>0.46578074554009236</v>
       </c>
       <c r="AC23" s="11">
-        <f t="shared" si="214"/>
+        <f t="shared" si="222"/>
         <v>0.46257155181458898</v>
       </c>
       <c r="AD23" s="11">
-        <f t="shared" si="214"/>
+        <f t="shared" si="222"/>
         <v>0.4622247972190035</v>
       </c>
       <c r="AE23" s="11">
-        <f t="shared" ref="AE23:AH23" si="215">AE9/AE5</f>
+        <f t="shared" ref="AE23:AH23" si="223">AE9/AE5</f>
         <v>0.46882542236524538</v>
       </c>
       <c r="AF23" s="11">
-        <f t="shared" si="215"/>
+        <f t="shared" si="223"/>
         <v>0.47050619238876246</v>
       </c>
       <c r="AG23" s="11">
-        <f t="shared" si="215"/>
+        <f t="shared" si="223"/>
         <v>0.46490705687183631</v>
       </c>
       <c r="AH23" s="11">
-        <f t="shared" si="215"/>
+        <f t="shared" si="223"/>
         <v>0.47177600374758455</v>
       </c>
-      <c r="AI23" s="11" t="e">
-        <f t="shared" ref="AI23:AL23" si="216">AI9/AI5</f>
+      <c r="AI23" s="11">
+        <f t="shared" ref="AI23:AL23" si="224">AI9/AI5</f>
+        <v>0.4815868555051615</v>
+      </c>
+      <c r="AJ23" s="11" t="e">
+        <f t="shared" si="224"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AJ23" s="11" t="e">
-        <f t="shared" si="216"/>
+      <c r="AK23" s="11" t="e">
+        <f t="shared" si="224"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AK23" s="11" t="e">
-        <f t="shared" si="216"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="AL23" s="11" t="e">
-        <f t="shared" si="216"/>
+        <f t="shared" si="224"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AM23" s="11"/>
       <c r="AN23" s="11">
-        <f t="shared" ref="AN23:AT23" si="217">AN9/AN5</f>
+        <f t="shared" ref="AN23:AT23" si="225">AN9/AN5</f>
         <v>0.29014428253535279</v>
       </c>
       <c r="AO23" s="11">
-        <f t="shared" si="217"/>
+        <f t="shared" si="225"/>
         <v>0.28982655966865128</v>
       </c>
       <c r="AP23" s="11">
-        <f t="shared" si="217"/>
+        <f t="shared" si="225"/>
         <v>0.33966508372906773</v>
       </c>
       <c r="AQ23" s="11">
-        <f t="shared" si="217"/>
+        <f t="shared" si="225"/>
         <v>0.35200448107545812</v>
       </c>
       <c r="AR23" s="11">
-        <f t="shared" si="217"/>
+        <f t="shared" si="225"/>
         <v>0.40139843841044165</v>
       </c>
       <c r="AS23" s="11">
-        <f t="shared" si="217"/>
+        <f t="shared" si="225"/>
         <v>0.39377539287083174</v>
       </c>
       <c r="AT23" s="11">
-        <f t="shared" si="217"/>
+        <f t="shared" si="225"/>
         <v>0.40478895878945764</v>
       </c>
       <c r="AU23" s="11">
-        <f t="shared" si="207"/>
+        <f t="shared" si="215"/>
         <v>0.43871239808827661</v>
       </c>
       <c r="AV23" s="11">
-        <f t="shared" si="207"/>
+        <f t="shared" si="215"/>
         <v>0.37624480720847231</v>
       </c>
       <c r="AW23" s="11">
-        <f t="shared" si="207"/>
+        <f t="shared" si="215"/>
         <v>0.38588035777783858</v>
       </c>
       <c r="AX23" s="11">
-        <f t="shared" si="207"/>
+        <f t="shared" si="215"/>
         <v>0.40059902017414373</v>
       </c>
       <c r="AY23" s="11">
-        <f t="shared" si="207"/>
+        <f t="shared" si="215"/>
         <v>0.39075955648097049</v>
       </c>
       <c r="AZ23" s="11">
-        <f t="shared" si="207"/>
+        <f t="shared" si="215"/>
         <v>0.38469860491899105</v>
       </c>
       <c r="BA23" s="11">
-        <f t="shared" si="207"/>
+        <f t="shared" si="215"/>
         <v>0.38343718820007905</v>
       </c>
       <c r="BB23" s="11">
-        <f t="shared" si="207"/>
+        <f t="shared" si="215"/>
         <v>0.37817768109034722</v>
       </c>
       <c r="BC23" s="11">
-        <f t="shared" si="207"/>
+        <f t="shared" si="215"/>
         <v>0.38233247727810865</v>
       </c>
       <c r="BD23" s="11">
-        <f t="shared" si="207"/>
+        <f t="shared" si="215"/>
         <v>0.41779359625167778</v>
       </c>
       <c r="BE23" s="11">
-        <f t="shared" ref="BE23:BF23" si="218">BE9/BE5</f>
+        <f t="shared" ref="BE23:BF23" si="226">BE9/BE5</f>
         <v>0.43309630561360085</v>
       </c>
       <c r="BF23" s="11">
-        <f t="shared" si="218"/>
+        <f t="shared" si="226"/>
         <v>0.44131129577207562</v>
       </c>
       <c r="BG23" s="11">
-        <f t="shared" ref="BG23" si="219">BG9/BG5</f>
+        <f t="shared" ref="BG23" si="227">BG9/BG5</f>
         <v>0.46206349815233932</v>
       </c>
       <c r="BH23" s="11">
-        <f t="shared" si="207"/>
+        <f t="shared" si="215"/>
         <v>0.46905164107160452</v>
       </c>
       <c r="BI23" s="11">
-        <f t="shared" si="207"/>
+        <f t="shared" si="215"/>
         <v>0.47662584070586611</v>
       </c>
       <c r="BJ23" s="11">
-        <f t="shared" si="207"/>
+        <f t="shared" si="215"/>
         <v>0.48037338010134545</v>
       </c>
       <c r="BK23" s="11">
-        <f t="shared" si="207"/>
+        <f t="shared" si="215"/>
         <v>0.48423691197898749</v>
       </c>
       <c r="BL23" s="11">
-        <f t="shared" si="207"/>
+        <f t="shared" si="215"/>
         <v>0.48739924440069876</v>
       </c>
       <c r="BM23" s="11">
-        <f t="shared" si="207"/>
+        <f t="shared" si="215"/>
         <v>0.48981504860045105</v>
       </c>
       <c r="BN23" s="11">
-        <f t="shared" ref="BN23:BP23" si="220">BN9/BN5</f>
+        <f t="shared" ref="BN23:BP23" si="228">BN9/BN5</f>
         <v>0.49144878694237581</v>
       </c>
       <c r="BO23" s="11">
-        <f t="shared" si="220"/>
+        <f t="shared" si="228"/>
         <v>0.49309465293019311</v>
       </c>
       <c r="BP23" s="11">
-        <f t="shared" si="220"/>
+        <f t="shared" si="228"/>
         <v>0.4947524622018788</v>
       </c>
       <c r="BQ23" s="11">
-        <f t="shared" ref="BQ23:BR23" si="221">BQ9/BQ5</f>
+        <f t="shared" ref="BQ23:BR23" si="229">BQ9/BQ5</f>
         <v>0.49642202308546746</v>
       </c>
       <c r="BR23" s="11">
-        <f t="shared" si="221"/>
+        <f t="shared" si="229"/>
         <v>0.49810313663239159</v>
       </c>
     </row>
@@ -6602,181 +6645,181 @@
         <v>0.14528911065453487</v>
       </c>
       <c r="H24" s="10">
-        <f t="shared" ref="H24:N24" si="222">H10/D10-1</f>
+        <f t="shared" ref="H24:N24" si="230">H10/D10-1</f>
         <v>0.1687388987566607</v>
       </c>
       <c r="I24" s="10">
-        <f t="shared" si="222"/>
+        <f t="shared" si="230"/>
         <v>0.15022966765738999</v>
       </c>
       <c r="J24" s="10">
-        <f t="shared" si="222"/>
+        <f t="shared" si="230"/>
         <v>9.6000000000000085E-2</v>
       </c>
       <c r="K24" s="10">
-        <f t="shared" si="222"/>
+        <f t="shared" si="230"/>
         <v>0.1406970784213224</v>
       </c>
       <c r="L24" s="10">
-        <f t="shared" si="222"/>
+        <f t="shared" si="230"/>
         <v>0.15628166160081047</v>
       </c>
       <c r="M24" s="10">
-        <f t="shared" si="222"/>
+        <f t="shared" si="230"/>
         <v>0.11768851303735017</v>
       </c>
       <c r="N24" s="10">
-        <f t="shared" si="222"/>
+        <f t="shared" si="230"/>
         <v>0.21119221411192224</v>
       </c>
       <c r="O24" s="10">
-        <f t="shared" ref="O24" si="223">O10/K10-1</f>
+        <f t="shared" ref="O24" si="231">O10/K10-1</f>
         <v>0.15996405302179295</v>
       </c>
       <c r="P24" s="10">
-        <f t="shared" ref="P24" si="224">P10/L10-1</f>
+        <f t="shared" ref="P24" si="232">P10/L10-1</f>
         <v>0.15268346111719611</v>
       </c>
       <c r="Q24" s="10">
-        <f t="shared" ref="Q24:S24" si="225">Q10/M10-1</f>
+        <f t="shared" ref="Q24:S24" si="233">Q10/M10-1</f>
         <v>0.20155527532576722</v>
       </c>
       <c r="R24" s="10">
-        <f t="shared" si="225"/>
+        <f t="shared" si="233"/>
         <v>0.15950180795500191</v>
       </c>
       <c r="S24" s="10">
-        <f t="shared" si="225"/>
+        <f t="shared" si="233"/>
         <v>0.22138291690877399</v>
       </c>
       <c r="T24" s="10">
-        <f t="shared" ref="T24:U24" si="226">T10/P10-1</f>
+        <f t="shared" ref="T24:U24" si="234">T10/P10-1</f>
         <v>0.2137970353477765</v>
       </c>
       <c r="U24" s="10">
-        <f t="shared" si="226"/>
+        <f t="shared" si="234"/>
         <v>0.1889102676228791</v>
       </c>
       <c r="V24" s="10">
-        <f t="shared" ref="V24" si="227">V10/R10-1</f>
+        <f t="shared" ref="V24" si="235">V10/R10-1</f>
         <v>0.17134442134442129</v>
       </c>
       <c r="W24" s="10">
-        <f t="shared" ref="W24:X24" si="228">W10/S10-1</f>
+        <f t="shared" ref="W24:X24" si="236">W10/S10-1</f>
         <v>0.22248652077386621</v>
       </c>
       <c r="X24" s="10">
-        <f t="shared" si="228"/>
+        <f t="shared" si="236"/>
         <v>0.1675277908251136</v>
       </c>
       <c r="Y24" s="10">
-        <f t="shared" ref="Y24:AA24" si="229">Y10/U10-1</f>
+        <f t="shared" ref="Y24:AA24" si="237">Y10/U10-1</f>
         <v>9.4894806532293652E-2</v>
       </c>
       <c r="Z24" s="10">
-        <f t="shared" si="229"/>
+        <f t="shared" si="237"/>
         <v>8.0757284425380771E-2</v>
       </c>
       <c r="AA24" s="10">
-        <f t="shared" si="229"/>
+        <f t="shared" si="237"/>
         <v>-1.6863406408094139E-3</v>
       </c>
       <c r="AB24" s="10">
-        <f t="shared" ref="AB24" si="230">AB10/X10-1</f>
+        <f t="shared" ref="AB24" si="238">AB10/X10-1</f>
         <v>5.980957489607075E-2</v>
       </c>
       <c r="AC24" s="10">
-        <f t="shared" ref="AC24" si="231">AC10/Y10-1</f>
+        <f t="shared" ref="AC24" si="239">AC10/Y10-1</f>
         <v>7.5786079011018526E-2</v>
       </c>
       <c r="AD24" s="10">
-        <f t="shared" ref="AD24" si="232">AD10/Z10-1</f>
+        <f t="shared" ref="AD24" si="240">AD10/Z10-1</f>
         <v>6.2679622280005454E-2</v>
       </c>
       <c r="AE24" s="10">
-        <f t="shared" ref="AE24" si="233">AE10/AA10-1</f>
+        <f t="shared" ref="AE24" si="241">AE10/AA10-1</f>
         <v>7.4324324324324342E-2</v>
       </c>
       <c r="AF24" s="10">
-        <f t="shared" ref="AF24" si="234">AF10/AB10-1</f>
+        <f t="shared" ref="AF24" si="242">AF10/AB10-1</f>
         <v>8.1867645198026029E-2</v>
       </c>
       <c r="AG24" s="10">
-        <f t="shared" ref="AG24" si="235">AG10/AC10-1</f>
+        <f t="shared" ref="AG24" si="243">AG10/AC10-1</f>
         <v>0.10741943542343235</v>
       </c>
       <c r="AH24" s="10">
-        <f t="shared" ref="AH24" si="236">AH10/AD10-1</f>
+        <f t="shared" ref="AH24" si="244">AH10/AD10-1</f>
         <v>0.14179008370895052</v>
       </c>
       <c r="AI24" s="10">
-        <f t="shared" ref="AI24" si="237">AI10/AE10-1</f>
+        <f t="shared" ref="AI24" si="245">AI10/AE10-1</f>
+        <v>0.31676342525399126</v>
+      </c>
+      <c r="AJ24" s="10">
+        <f t="shared" ref="AJ24" si="246">AJ10/AF10-1</f>
         <v>-1</v>
       </c>
-      <c r="AJ24" s="10">
-        <f t="shared" ref="AJ24" si="238">AJ10/AF10-1</f>
+      <c r="AK24" s="10">
+        <f t="shared" ref="AK24" si="247">AK10/AG10-1</f>
         <v>-1</v>
       </c>
-      <c r="AK24" s="10">
-        <f t="shared" ref="AK24" si="239">AK10/AG10-1</f>
-        <v>-1</v>
-      </c>
       <c r="AL24" s="10">
-        <f t="shared" ref="AL24" si="240">AL10/AH10-1</f>
+        <f t="shared" ref="AL24" si="248">AL10/AH10-1</f>
         <v>-1</v>
       </c>
       <c r="AM24" s="10"/>
       <c r="AN24" s="10"/>
       <c r="AO24" s="10">
-        <f t="shared" ref="AO24:AT24" si="241">AO10/AN10-1</f>
+        <f t="shared" ref="AO24:AT24" si="249">AO10/AN10-1</f>
         <v>0.33084112149532707</v>
       </c>
       <c r="AP24" s="10">
-        <f t="shared" si="241"/>
+        <f t="shared" si="249"/>
         <v>9.8314606741572996E-2</v>
       </c>
       <c r="AQ24" s="10">
-        <f t="shared" si="241"/>
+        <f t="shared" si="249"/>
         <v>0.41815856777493599</v>
       </c>
       <c r="AR24" s="10">
-        <f t="shared" si="241"/>
+        <f t="shared" si="249"/>
         <v>0.20198376916140659</v>
       </c>
       <c r="AS24" s="10">
-        <f t="shared" si="241"/>
+        <f t="shared" si="249"/>
         <v>0.33683420855213808</v>
       </c>
       <c r="AT24" s="10">
-        <f t="shared" si="241"/>
+        <f t="shared" si="249"/>
         <v>0.3630751964085297</v>
       </c>
       <c r="AU24" s="10">
-        <f t="shared" ref="AU24:BA24" si="242">AU10/AT10-1</f>
+        <f t="shared" ref="AU24:BA24" si="250">AU10/AT10-1</f>
         <v>0.39193083573487031</v>
       </c>
       <c r="AV24" s="10">
-        <f t="shared" si="242"/>
+        <f t="shared" si="250"/>
         <v>0.32357290742383915</v>
       </c>
       <c r="AW24" s="10">
-        <f t="shared" si="242"/>
+        <f t="shared" si="250"/>
         <v>0.34994413407821234</v>
       </c>
       <c r="AX24" s="10">
-        <f t="shared" si="242"/>
+        <f t="shared" si="250"/>
         <v>0.33537493792418482</v>
       </c>
       <c r="AY24" s="10">
-        <f t="shared" si="242"/>
+        <f t="shared" si="250"/>
         <v>0.24519647948431889</v>
       </c>
       <c r="AZ24" s="10">
-        <f t="shared" si="242"/>
+        <f t="shared" si="250"/>
         <v>0.15291189646590353</v>
       </c>
       <c r="BA24" s="10">
-        <f t="shared" si="242"/>
+        <f t="shared" si="250"/>
         <v>0.22925481391935065</v>
       </c>
       <c r="BB24" s="10">
@@ -6784,67 +6827,67 @@
         <v>0.13915425681371163</v>
       </c>
       <c r="BC24" s="10">
-        <f t="shared" ref="BC24:BP24" si="243">BC10/BB10-1</f>
+        <f t="shared" ref="BC24:BP24" si="251">BC10/BB10-1</f>
         <v>0.15631744465684161</v>
       </c>
       <c r="BD24" s="10">
-        <f t="shared" si="243"/>
+        <f t="shared" si="251"/>
         <v>0.16862201365187723</v>
       </c>
       <c r="BE24" s="10">
-        <f t="shared" si="243"/>
+        <f t="shared" si="251"/>
         <v>0.19791001186456136</v>
       </c>
       <c r="BF24" s="10">
-        <f t="shared" si="243"/>
+        <f t="shared" si="251"/>
         <v>0.1395756352138966</v>
       </c>
       <c r="BG24" s="10">
-        <f t="shared" si="243"/>
+        <f t="shared" si="251"/>
         <v>4.8637807120173848E-2</v>
       </c>
       <c r="BH24" s="10">
-        <f t="shared" si="243"/>
+        <f t="shared" si="251"/>
         <v>0.10137073637233018</v>
       </c>
       <c r="BI24" s="10">
-        <f t="shared" si="243"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="251"/>
+        <v>0.19999999999999996</v>
       </c>
       <c r="BJ24" s="10">
-        <f t="shared" si="243"/>
+        <f t="shared" si="251"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="BK24" s="10">
-        <f t="shared" si="243"/>
+        <f t="shared" si="251"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BL24" s="10">
-        <f t="shared" si="243"/>
+        <f t="shared" si="251"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BM24" s="10">
-        <f t="shared" si="243"/>
+        <f t="shared" si="251"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BN24" s="10">
-        <f t="shared" si="243"/>
+        <f t="shared" si="251"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BO24" s="10">
-        <f t="shared" si="243"/>
+        <f t="shared" si="251"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BP24" s="10">
-        <f t="shared" si="243"/>
+        <f t="shared" si="251"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BQ24" s="10">
-        <f t="shared" ref="BQ24" si="244">BQ10/BP10-1</f>
+        <f t="shared" ref="BQ24" si="252">BQ10/BP10-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BR24" s="10">
-        <f t="shared" ref="BR24" si="245">BR10/BQ10-1</f>
+        <f t="shared" ref="BR24" si="253">BR10/BQ10-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -6857,268 +6900,268 @@
         <v>4.7919993657481341E-2</v>
       </c>
       <c r="D25" s="10">
-        <f t="shared" ref="D25:N25" si="246">D11/D5</f>
+        <f t="shared" ref="D25:N25" si="254">D11/D5</f>
         <v>6.788033433109246E-2</v>
       </c>
       <c r="E25" s="10">
-        <f t="shared" si="246"/>
+        <f t="shared" si="254"/>
         <v>7.7123814887825021E-2</v>
       </c>
       <c r="F25" s="10">
-        <f t="shared" si="246"/>
+        <f t="shared" si="254"/>
         <v>6.7027027027027022E-2</v>
       </c>
       <c r="G25" s="10">
-        <f t="shared" si="246"/>
+        <f t="shared" si="254"/>
         <v>5.6731111374688649E-2</v>
       </c>
       <c r="H25" s="10">
-        <f t="shared" si="246"/>
+        <f t="shared" si="254"/>
         <v>7.6842195983797296E-2</v>
       </c>
       <c r="I25" s="10">
-        <f t="shared" si="246"/>
+        <f t="shared" si="254"/>
         <v>8.2253898046795143E-2</v>
       </c>
       <c r="J25" s="10">
-        <f t="shared" si="246"/>
+        <f t="shared" si="254"/>
         <v>7.1486570893191756E-2</v>
       </c>
       <c r="K25" s="10">
-        <f t="shared" si="246"/>
+        <f t="shared" si="254"/>
         <v>5.6600485738245894E-2</v>
       </c>
       <c r="L25" s="10">
-        <f t="shared" si="246"/>
+        <f t="shared" si="254"/>
         <v>8.4921029616037591E-2</v>
       </c>
       <c r="M25" s="10">
-        <f t="shared" si="246"/>
+        <f t="shared" si="254"/>
         <v>8.0941610119795587E-2</v>
       </c>
       <c r="N25" s="10">
-        <f t="shared" si="246"/>
+        <f t="shared" si="254"/>
         <v>7.6292930229682532E-2</v>
       </c>
       <c r="O25" s="10">
-        <f t="shared" ref="O25:S25" si="247">O11/O5</f>
+        <f t="shared" ref="O25:S25" si="255">O11/O5</f>
         <v>5.0529886305512431E-2</v>
       </c>
       <c r="P25" s="10">
-        <f t="shared" si="247"/>
+        <f t="shared" si="255"/>
         <v>5.9318628326486871E-2</v>
       </c>
       <c r="Q25" s="10">
-        <f t="shared" ref="Q25:R25" si="248">Q11/Q5</f>
+        <f t="shared" ref="Q25:R25" si="256">Q11/Q5</f>
         <v>6.645872731291598E-2</v>
       </c>
       <c r="R25" s="10">
-        <f t="shared" si="248"/>
+        <f t="shared" si="256"/>
         <v>6.7370441458733207E-2</v>
       </c>
       <c r="S25" s="10">
-        <f t="shared" si="247"/>
+        <f t="shared" si="255"/>
         <v>5.2031142845617009E-2</v>
       </c>
       <c r="T25" s="10">
-        <f t="shared" ref="T25:U25" si="249">T11/T5</f>
+        <f t="shared" ref="T25:U25" si="257">T11/T5</f>
         <v>6.3662904253788108E-2</v>
       </c>
       <c r="U25" s="10">
-        <f t="shared" si="249"/>
+        <f t="shared" si="257"/>
         <v>7.2469533142877809E-2</v>
       </c>
       <c r="V25" s="10">
-        <f t="shared" ref="V25" si="250">V11/V5</f>
+        <f t="shared" ref="V25" si="258">V11/V5</f>
         <v>7.1439664544183878E-2</v>
       </c>
       <c r="W25" s="10">
-        <f t="shared" ref="W25:X25" si="251">W11/W5</f>
+        <f t="shared" ref="W25:X25" si="259">W11/W5</f>
         <v>5.6395855028424126E-2</v>
       </c>
       <c r="X25" s="10">
-        <f t="shared" si="251"/>
+        <f t="shared" si="259"/>
         <v>6.5386562065038595E-2</v>
       </c>
       <c r="Y25" s="10">
-        <f t="shared" ref="Y25:Z25" si="252">Y11/Y5</f>
+        <f t="shared" ref="Y25:Z25" si="260">Y11/Y5</f>
         <v>7.3022237979387991E-2</v>
       </c>
       <c r="Z25" s="10">
-        <f t="shared" si="252"/>
+        <f t="shared" si="260"/>
         <v>6.8727792799839107E-2</v>
       </c>
       <c r="AA25" s="10">
-        <f t="shared" ref="AA25:AD25" si="253">AA11/AA5</f>
+        <f t="shared" ref="AA25:AD25" si="261">AA11/AA5</f>
         <v>5.6750993100564501E-2</v>
       </c>
       <c r="AB25" s="10">
-        <f t="shared" si="253"/>
+        <f t="shared" si="261"/>
         <v>7.1270371227397447E-2</v>
       </c>
       <c r="AC25" s="10">
-        <f t="shared" si="253"/>
+        <f t="shared" si="261"/>
         <v>7.3679424554367726E-2</v>
       </c>
       <c r="AD25" s="10">
-        <f t="shared" si="253"/>
+        <f t="shared" si="261"/>
         <v>6.8713789107763615E-2</v>
       </c>
       <c r="AE25" s="10">
-        <f t="shared" ref="AE25:AH25" si="254">AE11/AE5</f>
+        <f t="shared" ref="AE25:AH25" si="262">AE11/AE5</f>
         <v>5.7723250201126307E-2</v>
       </c>
       <c r="AF25" s="10">
-        <f t="shared" si="254"/>
+        <f t="shared" si="262"/>
         <v>7.0554431149655511E-2</v>
       </c>
       <c r="AG25" s="10">
-        <f t="shared" si="254"/>
+        <f t="shared" si="262"/>
         <v>7.0717597515844999E-2</v>
       </c>
       <c r="AH25" s="10">
-        <f t="shared" si="254"/>
+        <f t="shared" si="262"/>
         <v>6.8783791696757954E-2</v>
       </c>
-      <c r="AI25" s="10" t="e">
-        <f t="shared" ref="AI25:AL25" si="255">AI11/AI5</f>
+      <c r="AI25" s="10">
+        <f t="shared" ref="AI25:AL25" si="263">AI11/AI5</f>
+        <v>5.2116085589471048E-2</v>
+      </c>
+      <c r="AJ25" s="10" t="e">
+        <f t="shared" si="263"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AJ25" s="10" t="e">
-        <f t="shared" si="255"/>
+      <c r="AK25" s="10" t="e">
+        <f t="shared" si="263"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AK25" s="10" t="e">
-        <f t="shared" si="255"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="AL25" s="10" t="e">
-        <f t="shared" si="255"/>
+        <f t="shared" si="263"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AM25" s="10"/>
       <c r="AN25" s="10">
-        <f t="shared" ref="AN25:AT25" si="256">AN11/AN5</f>
+        <f t="shared" ref="AN25:AT25" si="264">AN11/AN5</f>
         <v>0.13380231139185988</v>
       </c>
       <c r="AO25" s="10">
-        <f t="shared" si="256"/>
+        <f t="shared" si="264"/>
         <v>0.12596427646906549</v>
       </c>
       <c r="AP25" s="10">
-        <f t="shared" si="256"/>
+        <f t="shared" si="264"/>
         <v>0.12342747646421728</v>
       </c>
       <c r="AQ25" s="10">
-        <f t="shared" si="256"/>
+        <f t="shared" si="264"/>
         <v>0.10031740951161612</v>
       </c>
       <c r="AR25" s="10">
-        <f t="shared" si="256"/>
+        <f t="shared" si="264"/>
         <v>9.6702016082041722E-2</v>
       </c>
       <c r="AS25" s="10">
-        <f t="shared" si="256"/>
+        <f t="shared" si="264"/>
         <v>8.4584131851284022E-2</v>
       </c>
       <c r="AT25" s="10">
-        <f t="shared" si="256"/>
+        <f t="shared" si="264"/>
         <v>7.0199262810741903E-2</v>
       </c>
       <c r="AU25" s="10">
-        <f t="shared" ref="AU25:BA25" si="257">AU11/AU5</f>
+        <f t="shared" ref="AU25:BA25" si="265">AU11/AU5</f>
         <v>6.4150075395506934E-2</v>
       </c>
       <c r="AV25" s="10">
-        <f t="shared" si="257"/>
+        <f t="shared" si="265"/>
         <v>6.3366684219764782E-2</v>
       </c>
       <c r="AW25" s="10">
-        <f t="shared" si="257"/>
+        <f t="shared" si="265"/>
         <v>6.5609015563883044E-2</v>
       </c>
       <c r="AX25" s="10">
-        <f t="shared" si="257"/>
+        <f t="shared" si="265"/>
         <v>6.1309714823609952E-2</v>
       </c>
       <c r="AY25" s="10">
-        <f t="shared" si="257"/>
+        <f t="shared" si="265"/>
         <v>6.5822972653369755E-2</v>
       </c>
       <c r="AZ25" s="10">
-        <f t="shared" si="257"/>
+        <f t="shared" si="265"/>
         <v>6.6573893924984945E-2</v>
       </c>
       <c r="BA25" s="10">
-        <f t="shared" si="257"/>
+        <f t="shared" si="265"/>
         <v>6.2896515371147807E-2</v>
       </c>
       <c r="BB25" s="10">
-        <f t="shared" ref="BB25:BM25" si="258">BB11/BB5</f>
+        <f t="shared" ref="BB25:BM25" si="266">BB11/BB5</f>
         <v>7.0126146348213125E-2</v>
       </c>
       <c r="BC25" s="10">
-        <f t="shared" si="258"/>
+        <f t="shared" si="266"/>
         <v>7.2549769593646979E-2</v>
       </c>
       <c r="BD25" s="10">
-        <f t="shared" si="258"/>
+        <f t="shared" si="266"/>
         <v>6.006555190163388E-2</v>
       </c>
       <c r="BE25" s="10">
-        <f t="shared" ref="BE25:BF25" si="259">BE11/BE5</f>
+        <f t="shared" ref="BE25:BF25" si="267">BE11/BE5</f>
         <v>6.3637378020328261E-2</v>
       </c>
       <c r="BF25" s="10">
-        <f t="shared" si="259"/>
+        <f t="shared" si="267"/>
         <v>6.5048201729783317E-2</v>
       </c>
       <c r="BG25" s="10">
-        <f t="shared" ref="BG25" si="260">BG11/BG5</f>
+        <f t="shared" ref="BG25" si="268">BG11/BG5</f>
         <v>6.6738271510222866E-2</v>
       </c>
       <c r="BH25" s="10">
-        <f t="shared" si="258"/>
+        <f t="shared" si="266"/>
         <v>6.6322889458647019E-2</v>
       </c>
       <c r="BI25" s="10">
-        <f t="shared" si="258"/>
+        <f t="shared" si="266"/>
         <v>6.4690540897602955E-2</v>
       </c>
       <c r="BJ25" s="10">
-        <f t="shared" si="258"/>
+        <f t="shared" si="266"/>
         <v>6.3835027638622283E-2</v>
       </c>
       <c r="BK25" s="10">
-        <f t="shared" si="258"/>
+        <f t="shared" si="266"/>
         <v>6.357633221776568E-2</v>
       </c>
       <c r="BL25" s="10">
-        <f t="shared" si="258"/>
+        <f t="shared" si="266"/>
         <v>6.3469516359680136E-2</v>
       </c>
       <c r="BM25" s="10">
-        <f t="shared" si="258"/>
+        <f t="shared" si="266"/>
         <v>6.3529887746463259E-2</v>
       </c>
       <c r="BN25" s="10">
-        <f t="shared" ref="BN25:BP25" si="261">BN11/BN5</f>
+        <f t="shared" ref="BN25:BP25" si="269">BN11/BN5</f>
         <v>6.3770944325135387E-2</v>
       </c>
       <c r="BO25" s="10">
-        <f t="shared" si="261"/>
+        <f t="shared" si="269"/>
         <v>6.3380112248524328E-2</v>
       </c>
       <c r="BP25" s="10">
-        <f t="shared" si="261"/>
+        <f t="shared" si="269"/>
         <v>6.298644408533613E-2</v>
       </c>
       <c r="BQ25" s="10">
-        <f t="shared" ref="BQ25:BR25" si="262">BQ11/BQ5</f>
+        <f t="shared" ref="BQ25:BR25" si="270">BQ11/BQ5</f>
         <v>6.2589985350547578E-2</v>
       </c>
       <c r="BR25" s="10">
-        <f t="shared" si="262"/>
+        <f t="shared" si="270"/>
         <v>6.2190783287058377E-2</v>
       </c>
     </row>
@@ -7131,543 +7174,543 @@
         <v>0.29757738439060855</v>
       </c>
       <c r="D26" s="11">
-        <f t="shared" ref="D26:BM26" si="263">D13/D5</f>
+        <f t="shared" ref="D26:BM26" si="271">D13/D5</f>
         <v>0.25997350213455028</v>
       </c>
       <c r="E26" s="11">
-        <f t="shared" si="263"/>
+        <f t="shared" si="271"/>
         <v>0.23677837228949591</v>
       </c>
       <c r="F26" s="11">
-        <f t="shared" si="263"/>
+        <f t="shared" si="271"/>
         <v>0.25624801271860098</v>
       </c>
       <c r="G26" s="11">
-        <f t="shared" si="263"/>
+        <f t="shared" si="271"/>
         <v>0.27690665401494485</v>
       </c>
       <c r="H26" s="11">
-        <f t="shared" si="263"/>
+        <f t="shared" si="271"/>
         <v>0.2312333017323106</v>
       </c>
       <c r="I26" s="11">
-        <f t="shared" si="263"/>
+        <f t="shared" si="271"/>
         <v>0.2145366016837332</v>
       </c>
       <c r="J26" s="11">
-        <f t="shared" si="263"/>
+        <f t="shared" si="271"/>
         <v>0.24398813241723921</v>
       </c>
       <c r="K26" s="11">
-        <f t="shared" si="263"/>
+        <f t="shared" si="271"/>
         <v>0.2784717759940753</v>
       </c>
       <c r="L26" s="11">
-        <f t="shared" si="263"/>
+        <f t="shared" si="271"/>
         <v>0.22041397287054346</v>
       </c>
       <c r="M26" s="11">
-        <f t="shared" si="263"/>
+        <f t="shared" si="271"/>
         <v>0.21933484124989527</v>
       </c>
       <c r="N26" s="11">
-        <f t="shared" si="263"/>
+        <f t="shared" si="271"/>
         <v>0.2283687285542057</v>
       </c>
       <c r="O26" s="11">
-        <f t="shared" ref="O26:S26" si="264">O13/O5</f>
+        <f t="shared" ref="O26:S26" si="272">O13/O5</f>
         <v>0.30091799100853384</v>
       </c>
       <c r="P26" s="11">
-        <f t="shared" si="264"/>
+        <f t="shared" si="272"/>
         <v>0.30700794784782998</v>
       </c>
       <c r="Q26" s="11">
-        <f t="shared" ref="Q26:R26" si="265">Q13/Q5</f>
+        <f t="shared" ref="Q26:R26" si="273">Q13/Q5</f>
         <v>0.29626445956234498</v>
       </c>
       <c r="R26" s="11">
-        <f t="shared" si="265"/>
+        <f t="shared" si="273"/>
         <v>0.28534069097888676</v>
       </c>
       <c r="S26" s="11">
-        <f t="shared" si="264"/>
+        <f t="shared" si="272"/>
         <v>0.33472911371979508</v>
       </c>
       <c r="T26" s="11">
-        <f t="shared" ref="T26:U26" si="266">T13/T5</f>
+        <f t="shared" ref="T26:U26" si="274">T13/T5</f>
         <v>0.30817862209338187</v>
       </c>
       <c r="U26" s="11">
-        <f t="shared" si="266"/>
+        <f t="shared" si="274"/>
         <v>0.27816150146457891</v>
       </c>
       <c r="V26" s="11">
-        <f t="shared" ref="V26" si="267">V13/V5</f>
+        <f t="shared" ref="V26" si="275">V13/V5</f>
         <v>0.27615202005635303</v>
       </c>
       <c r="W26" s="11">
-        <f t="shared" ref="W26:X26" si="268">W13/W5</f>
+        <f t="shared" ref="W26:X26" si="276">W13/W5</f>
         <v>0.30742441572630896</v>
       </c>
       <c r="X26" s="11">
-        <f t="shared" si="268"/>
+        <f t="shared" si="276"/>
         <v>0.29859968788223878</v>
       </c>
       <c r="Y26" s="11">
-        <f t="shared" ref="Y26:Z26" si="269">Y13/Y5</f>
+        <f t="shared" ref="Y26:Z26" si="277">Y13/Y5</f>
         <v>0.28115945572576012</v>
       </c>
       <c r="Z26" s="11">
-        <f t="shared" si="269"/>
+        <f t="shared" si="277"/>
         <v>0.30133634271156895</v>
       </c>
       <c r="AA26" s="11">
-        <f t="shared" ref="AA26:AD26" si="270">AA13/AA5</f>
+        <f t="shared" ref="AA26:AD26" si="278">AA13/AA5</f>
         <v>0.33763746602550698</v>
       </c>
       <c r="AB26" s="11">
-        <f t="shared" si="270"/>
+        <f t="shared" si="278"/>
         <v>0.30742785362467356</v>
       </c>
       <c r="AC26" s="11">
-        <f t="shared" si="270"/>
+        <f t="shared" si="278"/>
         <v>0.29555708406682446</v>
       </c>
       <c r="AD26" s="11">
-        <f t="shared" si="270"/>
+        <f t="shared" si="278"/>
         <v>0.31171389444854103</v>
       </c>
       <c r="AE26" s="11">
-        <f t="shared" ref="AE26:AH26" si="271">AE13/AE5</f>
+        <f t="shared" ref="AE26:AH26" si="279">AE13/AE5</f>
         <v>0.34458567980691873</v>
       </c>
       <c r="AF26" s="11">
-        <f t="shared" si="271"/>
+        <f t="shared" si="279"/>
         <v>0.31029058610094484</v>
       </c>
       <c r="AG26" s="11">
-        <f t="shared" si="271"/>
+        <f t="shared" si="279"/>
         <v>0.29990641881832492</v>
       </c>
       <c r="AH26" s="11">
-        <f t="shared" si="271"/>
+        <f t="shared" si="279"/>
         <v>0.31646594968086977</v>
       </c>
-      <c r="AI26" s="11" t="e">
-        <f t="shared" ref="AI26:AL26" si="272">AI13/AI5</f>
+      <c r="AI26" s="11">
+        <f t="shared" ref="AI26:AL26" si="280">AI13/AI5</f>
+        <v>0.35373827875010433</v>
+      </c>
+      <c r="AJ26" s="11" t="e">
+        <f t="shared" si="280"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AJ26" s="11" t="e">
-        <f t="shared" si="272"/>
+      <c r="AK26" s="11" t="e">
+        <f t="shared" si="280"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AK26" s="11" t="e">
-        <f t="shared" si="272"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="AL26" s="11" t="e">
-        <f t="shared" si="272"/>
+        <f t="shared" si="280"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AM26" s="11"/>
       <c r="AN26" s="11">
-        <f t="shared" ref="AN26:AT26" si="273">AN13/AN5</f>
+        <f t="shared" ref="AN26:AT26" si="281">AN13/AN5</f>
         <v>0.11793841073864045</v>
       </c>
       <c r="AO26" s="11">
-        <f t="shared" si="273"/>
+        <f t="shared" si="281"/>
         <v>0.1269997411338338</v>
       </c>
       <c r="AP26" s="11">
-        <f t="shared" si="273"/>
+        <f t="shared" si="281"/>
         <v>0.1836624177289011</v>
       </c>
       <c r="AQ26" s="11">
-        <f t="shared" si="273"/>
+        <f t="shared" si="281"/>
         <v>0.22210663892667573</v>
       </c>
       <c r="AR26" s="11">
-        <f t="shared" si="273"/>
+        <f t="shared" si="281"/>
         <v>0.2736277823097541</v>
       </c>
       <c r="AS26" s="11">
-        <f t="shared" si="273"/>
+        <f t="shared" si="281"/>
         <v>0.28187044844768111</v>
       </c>
       <c r="AT26" s="11">
-        <f t="shared" si="273"/>
+        <f t="shared" si="281"/>
         <v>0.31215068961376086</v>
       </c>
       <c r="AU26" s="11">
-        <f t="shared" ref="AU26:BA26" si="274">AU13/AU5</f>
+        <f t="shared" ref="AU26:BA26" si="282">AU13/AU5</f>
         <v>0.35295959311984054</v>
       </c>
       <c r="AV26" s="11">
-        <f t="shared" si="274"/>
+        <f t="shared" si="282"/>
         <v>0.28669475162366159</v>
       </c>
       <c r="AW26" s="11">
-        <f t="shared" si="274"/>
+        <f t="shared" si="282"/>
         <v>0.28722339232473537</v>
       </c>
       <c r="AX26" s="11">
-        <f t="shared" si="274"/>
+        <f t="shared" si="282"/>
         <v>0.30477290717326661</v>
       </c>
       <c r="AY26" s="11">
-        <f t="shared" si="274"/>
+        <f t="shared" si="282"/>
         <v>0.27835410106706115</v>
       </c>
       <c r="AZ26" s="11">
-        <f t="shared" si="274"/>
+        <f t="shared" si="282"/>
         <v>0.26760428208729942</v>
       </c>
       <c r="BA26" s="11">
-        <f t="shared" si="274"/>
+        <f t="shared" si="282"/>
         <v>0.26694026619477024</v>
       </c>
       <c r="BB26" s="11">
-        <f t="shared" si="263"/>
+        <f t="shared" si="271"/>
         <v>0.24572017188496928</v>
       </c>
       <c r="BC26" s="11">
-        <f t="shared" si="263"/>
+        <f t="shared" si="271"/>
         <v>0.24147314354406862</v>
       </c>
       <c r="BD26" s="11">
-        <f t="shared" si="263"/>
+        <f t="shared" si="271"/>
         <v>0.29782377527561593</v>
       </c>
       <c r="BE26" s="11">
-        <f t="shared" ref="BE26:BF26" si="275">BE13/BE5</f>
+        <f t="shared" ref="BE26:BF26" si="283">BE13/BE5</f>
         <v>0.30288744395528594</v>
       </c>
       <c r="BF26" s="11">
-        <f t="shared" si="275"/>
+        <f t="shared" si="283"/>
         <v>0.29821412265024722</v>
       </c>
       <c r="BG26" s="11">
-        <f t="shared" ref="BG26" si="276">BG13/BG5</f>
+        <f t="shared" ref="BG26" si="284">BG13/BG5</f>
         <v>0.31510222870075566</v>
       </c>
       <c r="BH26" s="11">
-        <f t="shared" si="263"/>
+        <f t="shared" si="271"/>
         <v>0.31970799762591884</v>
       </c>
       <c r="BI26" s="11">
-        <f t="shared" si="263"/>
-        <v>0.32857617537284584</v>
+        <f t="shared" si="271"/>
+        <v>0.31666772902492907</v>
       </c>
       <c r="BJ26" s="11">
-        <f t="shared" si="263"/>
-        <v>0.33266875082424452</v>
+        <f t="shared" si="271"/>
+        <v>0.32068737916160472</v>
       </c>
       <c r="BK26" s="11">
-        <f t="shared" si="263"/>
-        <v>0.33631194612800158</v>
+        <f t="shared" si="271"/>
+        <v>0.32426214132325587</v>
       </c>
       <c r="BL26" s="11">
-        <f t="shared" si="263"/>
-        <v>0.338897252204098</v>
+        <f t="shared" si="271"/>
+        <v>0.32674975565596648</v>
       </c>
       <c r="BM26" s="11">
-        <f t="shared" si="263"/>
-        <v>0.34033735853817737</v>
+        <f t="shared" si="271"/>
+        <v>0.32805910106449016</v>
       </c>
       <c r="BN26" s="11">
-        <f t="shared" ref="BN26:BP26" si="277">BN13/BN5</f>
-        <v>0.34140392162082855</v>
+        <f t="shared" ref="BN26:BP26" si="285">BN13/BN5</f>
+        <v>0.3290790757641982</v>
       </c>
       <c r="BO26" s="11">
-        <f t="shared" si="277"/>
-        <v>0.34312040330275828</v>
+        <f t="shared" si="285"/>
+        <v>0.33074981224862815</v>
       </c>
       <c r="BP26" s="11">
-        <f t="shared" si="277"/>
-        <v>0.34485769405059258</v>
+        <f t="shared" si="285"/>
+        <v>0.33244221918402822</v>
       </c>
       <c r="BQ26" s="11">
-        <f t="shared" ref="BQ26:BR26" si="278">BQ13/BQ5</f>
-        <v>0.34661568278960148</v>
+        <f t="shared" ref="BQ26:BR26" si="286">BQ13/BQ5</f>
+        <v>0.33415620351169878</v>
       </c>
       <c r="BR26" s="11">
-        <f t="shared" si="278"/>
-        <v>0.348394248042798</v>
+        <f t="shared" si="286"/>
+        <v>0.33589166157100731</v>
       </c>
     </row>
     <row r="27" spans="2:183" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B27" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C27" s="11">
         <f>C17/C5</f>
         <v>0.22725470875380835</v>
       </c>
       <c r="D27" s="11">
-        <f t="shared" ref="D27:AL27" si="279">D17/D5</f>
+        <f t="shared" ref="D27:AL27" si="287">D17/D5</f>
         <v>0.22608240509020724</v>
       </c>
       <c r="E27" s="11">
-        <f t="shared" si="279"/>
+        <f t="shared" si="287"/>
         <v>0.21625833098657654</v>
       </c>
       <c r="F27" s="11">
-        <f t="shared" si="279"/>
+        <f t="shared" si="287"/>
         <v>0.22456279809220986</v>
       </c>
       <c r="G27" s="11">
-        <f t="shared" si="279"/>
+        <f t="shared" si="287"/>
         <v>0.23680464950776894</v>
       </c>
       <c r="H27" s="11">
-        <f t="shared" si="279"/>
+        <f t="shared" si="287"/>
         <v>0.19927604929759546</v>
       </c>
       <c r="I27" s="11">
-        <f t="shared" si="279"/>
+        <f t="shared" si="287"/>
         <v>0.18666022412607555</v>
       </c>
       <c r="J27" s="11">
-        <f t="shared" si="279"/>
+        <f t="shared" si="287"/>
         <v>0.2137101811367895</v>
       </c>
       <c r="K27" s="11">
-        <f t="shared" si="279"/>
+        <f t="shared" si="287"/>
         <v>0.2421720994565395</v>
       </c>
       <c r="L27" s="11">
-        <f t="shared" si="279"/>
+        <f t="shared" si="287"/>
         <v>0.19290724195290929</v>
       </c>
       <c r="M27" s="11">
-        <f t="shared" si="279"/>
+        <f t="shared" si="287"/>
         <v>0.18853983412917819</v>
       </c>
       <c r="N27" s="11">
-        <f t="shared" si="279"/>
+        <f t="shared" si="287"/>
         <v>0.19587931620761073</v>
       </c>
       <c r="O27" s="11">
-        <f t="shared" si="279"/>
+        <f t="shared" si="287"/>
         <v>0.25803354301456405</v>
       </c>
       <c r="P27" s="11">
-        <f t="shared" si="279"/>
+        <f t="shared" si="287"/>
         <v>0.26377478121093051</v>
       </c>
       <c r="Q27" s="11">
-        <f t="shared" si="279"/>
+        <f t="shared" si="287"/>
         <v>0.26701377802883319</v>
       </c>
       <c r="R27" s="11">
-        <f t="shared" si="279"/>
+        <f t="shared" si="287"/>
         <v>0.2465331094049904</v>
       </c>
       <c r="S27" s="11">
-        <f t="shared" si="279"/>
+        <f t="shared" si="287"/>
         <v>0.27939812013393039</v>
       </c>
       <c r="T27" s="11">
-        <f t="shared" si="279"/>
+        <f t="shared" si="287"/>
         <v>0.25709821336787353</v>
       </c>
       <c r="U27" s="11">
-        <f t="shared" si="279"/>
+        <f t="shared" si="287"/>
         <v>0.23435673043310551</v>
       </c>
       <c r="V27" s="11">
-        <f t="shared" si="279"/>
+        <f t="shared" si="287"/>
         <v>0.22986044860559537</v>
       </c>
       <c r="W27" s="11">
-        <f t="shared" si="279"/>
+        <f t="shared" si="287"/>
         <v>0.2560561312460522</v>
       </c>
       <c r="X27" s="11">
-        <f t="shared" si="279"/>
+        <f t="shared" si="287"/>
         <v>0.25475557805052934</v>
       </c>
       <c r="Y27" s="11">
-        <f t="shared" si="279"/>
+        <f t="shared" si="287"/>
         <v>0.24305292370135825</v>
       </c>
       <c r="Z27" s="11">
-        <f t="shared" si="279"/>
+        <f t="shared" si="287"/>
         <v>0.25649735189613176</v>
       </c>
       <c r="AA27" s="11">
-        <f t="shared" si="279"/>
+        <f t="shared" si="287"/>
         <v>0.28363788417311309</v>
       </c>
       <c r="AB27" s="11">
-        <f t="shared" si="279"/>
+        <f t="shared" si="287"/>
         <v>0.26044318094167684</v>
       </c>
       <c r="AC27" s="11">
-        <f t="shared" si="279"/>
+        <f t="shared" si="287"/>
         <v>0.25004371801298714</v>
       </c>
       <c r="AD27" s="11">
-        <f t="shared" si="279"/>
+        <f t="shared" si="287"/>
         <v>0.15523016959865163</v>
       </c>
       <c r="AE27" s="11">
-        <f t="shared" si="279"/>
+        <f t="shared" si="287"/>
         <v>0.29227674979887369</v>
       </c>
       <c r="AF27" s="11">
-        <f t="shared" si="279"/>
+        <f t="shared" si="287"/>
         <v>0.25986010759341016</v>
       </c>
       <c r="AG27" s="11">
-        <f t="shared" si="279"/>
+        <f t="shared" si="287"/>
         <v>0.24920243311072354</v>
       </c>
       <c r="AH27" s="11">
-        <f t="shared" si="279"/>
+        <f t="shared" si="287"/>
         <v>0.26804988971951671</v>
       </c>
-      <c r="AI27" s="11" t="e">
-        <f t="shared" si="279"/>
+      <c r="AI27" s="11">
+        <f t="shared" si="287"/>
+        <v>0.29283647291243498</v>
+      </c>
+      <c r="AJ27" s="11" t="e">
+        <f t="shared" si="287"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AJ27" s="11" t="e">
-        <f t="shared" si="279"/>
+      <c r="AK27" s="11" t="e">
+        <f t="shared" si="287"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AK27" s="11" t="e">
-        <f t="shared" si="279"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="AL27" s="11" t="e">
-        <f t="shared" si="279"/>
+        <f t="shared" si="287"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AM27" s="11"/>
       <c r="AN27" s="11">
-        <f t="shared" ref="AN27:BR27" si="280">AN17/AN5</f>
+        <f t="shared" ref="AN27:BR27" si="288">AN17/AN5</f>
         <v>9.5326968631110467E-2</v>
       </c>
       <c r="AO27" s="11">
-        <f t="shared" si="280"/>
+        <f t="shared" si="288"/>
         <v>0.10297696091120891</v>
       </c>
       <c r="AP27" s="11">
-        <f t="shared" si="280"/>
+        <f t="shared" si="288"/>
         <v>0.1456302591018912</v>
       </c>
       <c r="AQ27" s="11">
-        <f t="shared" si="280"/>
+        <f t="shared" si="288"/>
         <v>0.16321250433437359</v>
       </c>
       <c r="AR27" s="11">
-        <f t="shared" si="280"/>
+        <f t="shared" si="288"/>
         <v>0.19193567183311969</v>
       </c>
       <c r="AS27" s="11">
-        <f t="shared" si="280"/>
+        <f t="shared" si="288"/>
         <v>0.21484093522422384</v>
       </c>
       <c r="AT27" s="11">
-        <f t="shared" si="280"/>
+        <f t="shared" si="288"/>
         <v>0.2394664153941376</v>
       </c>
       <c r="AU27" s="11">
-        <f t="shared" si="280"/>
+        <f t="shared" si="288"/>
         <v>0.26665090602397323</v>
       </c>
       <c r="AV27" s="11">
-        <f t="shared" si="280"/>
+        <f t="shared" si="288"/>
         <v>0.21670469837926393</v>
       </c>
       <c r="AW27" s="11">
-        <f t="shared" si="280"/>
+        <f t="shared" si="288"/>
         <v>0.21614376760852322</v>
       </c>
       <c r="AX27" s="11">
-        <f t="shared" si="280"/>
+        <f t="shared" si="288"/>
         <v>0.22845773698735639</v>
       </c>
       <c r="AY27" s="11">
-        <f t="shared" si="280"/>
+        <f t="shared" si="288"/>
         <v>0.211867983064288</v>
       </c>
       <c r="AZ27" s="11">
-        <f t="shared" si="280"/>
+        <f t="shared" si="288"/>
         <v>0.21092420845075338</v>
       </c>
       <c r="BA27" s="11">
-        <f t="shared" si="280"/>
+        <f t="shared" si="288"/>
         <v>0.22414202074587247</v>
       </c>
       <c r="BB27" s="11">
-        <f t="shared" si="280"/>
+        <f t="shared" si="288"/>
         <v>0.21238094505984456</v>
       </c>
       <c r="BC27" s="11">
-        <f t="shared" si="280"/>
+        <f t="shared" si="288"/>
         <v>0.20913611278072236</v>
       </c>
       <c r="BD27" s="11">
-        <f t="shared" si="280"/>
+        <f t="shared" si="288"/>
         <v>0.25881793355694238</v>
       </c>
       <c r="BE27" s="11">
-        <f t="shared" si="280"/>
+        <f t="shared" si="288"/>
         <v>0.25309640705199732</v>
       </c>
       <c r="BF27" s="11">
-        <f t="shared" si="280"/>
+        <f t="shared" si="288"/>
         <v>0.25306234264320282</v>
       </c>
       <c r="BG27" s="11">
-        <f t="shared" si="280"/>
+        <f t="shared" si="288"/>
         <v>0.23971255769943867</v>
       </c>
       <c r="BH27" s="11">
-        <f t="shared" si="280"/>
+        <f t="shared" si="288"/>
         <v>0.26915064121818238</v>
       </c>
       <c r="BI27" s="11">
-        <f t="shared" si="280"/>
-        <v>0.27492299680343524</v>
+        <f t="shared" si="288"/>
+        <v>0.26491990187118519</v>
       </c>
       <c r="BJ27" s="11">
-        <f t="shared" si="280"/>
-        <v>0.27832468566253238</v>
+        <f t="shared" si="288"/>
+        <v>0.2683009779651705</v>
       </c>
       <c r="BK27" s="11">
-        <f t="shared" si="280"/>
-        <v>0.28136063633404496</v>
+        <f t="shared" si="288"/>
+        <v>0.27127990712275751</v>
       </c>
       <c r="BL27" s="11">
-        <f t="shared" si="280"/>
-        <v>0.28351709454720869</v>
+        <f t="shared" si="288"/>
+        <v>0.27335463659186404</v>
       </c>
       <c r="BM27" s="11">
-        <f t="shared" si="280"/>
-        <v>0.28471484740353925</v>
+        <f t="shared" si="288"/>
+        <v>0.27444299634357228</v>
       </c>
       <c r="BN27" s="11">
-        <f t="shared" si="280"/>
-        <v>0.28560249054535541</v>
+        <f t="shared" si="288"/>
+        <v>0.27529207636967545</v>
       </c>
       <c r="BO27" s="11">
-        <f t="shared" si="280"/>
-        <v>0.2870407636108781</v>
+        <f t="shared" si="288"/>
+        <v>0.27669207934771295</v>
       </c>
       <c r="BP27" s="11">
-        <f t="shared" si="280"/>
-        <v>0.28849424207907237</v>
+        <f t="shared" si="288"/>
+        <v>0.27810801002904034</v>
       </c>
       <c r="BQ27" s="11">
-        <f t="shared" si="280"/>
-        <v>0.28996504571667725</v>
+        <f t="shared" si="288"/>
+        <v>0.27954200154043513</v>
       </c>
       <c r="BR27" s="11">
-        <f t="shared" si="280"/>
-        <v>0.29145306373880747</v>
+        <f t="shared" si="288"/>
+        <v>0.28099395800845178</v>
       </c>
     </row>
     <row r="29" spans="2:183" x14ac:dyDescent="0.3">
@@ -7675,131 +7718,131 @@
         <v>52</v>
       </c>
       <c r="G29" s="11">
-        <f t="shared" ref="G29:N29" si="281">G3/C3-1</f>
+        <f t="shared" ref="G29:N29" si="289">G3/C3-1</f>
         <v>-7.2368753473801228E-2</v>
       </c>
       <c r="H29" s="11">
-        <f t="shared" si="281"/>
+        <f t="shared" si="289"/>
         <v>-9.2070115233879979E-2</v>
       </c>
       <c r="I29" s="11">
-        <f t="shared" si="281"/>
+        <f t="shared" si="289"/>
         <v>-1.7194570135746656E-2</v>
       </c>
       <c r="J29" s="11">
-        <f t="shared" si="281"/>
+        <f t="shared" si="289"/>
         <v>-1.4760712032274692E-2</v>
       </c>
       <c r="K29" s="11">
-        <f t="shared" si="281"/>
+        <f t="shared" si="289"/>
         <v>7.719752161775717E-2</v>
       </c>
       <c r="L29" s="11">
-        <f t="shared" si="281"/>
+        <f t="shared" si="289"/>
         <v>-3.4360571244496985E-2</v>
       </c>
       <c r="M29" s="11">
-        <f t="shared" si="281"/>
+        <f t="shared" si="289"/>
         <v>9.8573924540775293E-2</v>
       </c>
       <c r="N29" s="11">
-        <f t="shared" si="281"/>
+        <f t="shared" si="289"/>
         <v>-2.6781035921519925E-2</v>
       </c>
       <c r="O29" s="11">
-        <f>O3/K3-1</f>
+        <f t="shared" ref="O29:X31" si="290">O3/K3-1</f>
         <v>0.20952164239482207</v>
       </c>
       <c r="P29" s="11">
-        <f>P3/L3-1</f>
+        <f t="shared" si="290"/>
         <v>0.61643500500389181</v>
       </c>
       <c r="Q29" s="11">
-        <f>Q3/M3-1</f>
+        <f t="shared" si="290"/>
         <v>0.37436867330052226</v>
       </c>
       <c r="R29" s="11">
-        <f>R3/N3-1</f>
+        <f t="shared" si="290"/>
         <v>0.2977925781172106</v>
       </c>
       <c r="S29" s="11">
-        <f>S3/O3-1</f>
+        <f t="shared" si="290"/>
         <v>9.1463032254018639E-2</v>
       </c>
       <c r="T29" s="11">
-        <f>T3/P3-1</f>
+        <f t="shared" si="290"/>
         <v>6.5682484212264303E-2</v>
       </c>
       <c r="U29" s="11">
-        <f>U3/Q3-1</f>
+        <f t="shared" si="290"/>
         <v>-9.2731594420466523E-3</v>
       </c>
       <c r="V29" s="11">
-        <f>V3/R3-1</f>
+        <f t="shared" si="290"/>
         <v>9.0269348370542124E-2</v>
       </c>
       <c r="W29" s="11">
-        <f>W3/S3-1</f>
+        <f t="shared" si="290"/>
         <v>-7.6999683995824908E-2</v>
       </c>
       <c r="X29" s="11">
-        <f>X3/T3-1</f>
+        <f t="shared" si="290"/>
         <v>-4.5547852356791485E-2</v>
       </c>
       <c r="Y29" s="11">
-        <f>Y3/U3-1</f>
+        <f t="shared" ref="Y29:AH31" si="291">Y3/U3-1</f>
         <v>-4.3737668692289455E-2</v>
       </c>
       <c r="Z29" s="11">
-        <f>Z3/V3-1</f>
+        <f t="shared" si="291"/>
         <v>-5.3186391950167722E-2</v>
       </c>
       <c r="AA29" s="11">
-        <f>AA3/W3-1</f>
+        <f t="shared" si="291"/>
         <v>7.2623148109718372E-4</v>
       </c>
       <c r="AB29" s="14">
-        <f>AB3/X3-1</f>
+        <f t="shared" si="291"/>
         <v>-9.5267080577310703E-2</v>
       </c>
       <c r="AC29" s="11">
-        <f>AC3/Y3-1</f>
+        <f t="shared" si="291"/>
         <v>1.6175888023240548E-2</v>
       </c>
       <c r="AD29" s="11">
-        <f>AD3/Z3-1</f>
+        <f t="shared" si="291"/>
         <v>4.1289592760181071E-2</v>
       </c>
       <c r="AE29" s="11">
-        <f>AE3/AA3-1</f>
+        <f t="shared" si="291"/>
         <v>1.5571544091729006E-2</v>
       </c>
       <c r="AF29" s="11">
-        <f>AF3/AB3-1</f>
+        <f t="shared" si="291"/>
         <v>2.7330084023562407E-2</v>
       </c>
       <c r="AG29" s="11">
-        <f>AG3/AC3-1</f>
+        <f t="shared" si="291"/>
         <v>8.2012214930803795E-2</v>
       </c>
       <c r="AH29" s="11">
-        <f>AH3/AD3-1</f>
+        <f t="shared" si="291"/>
         <v>5.3717945052745852E-2</v>
       </c>
       <c r="AI29" s="11">
-        <f>AI3/AE3-1</f>
+        <f t="shared" ref="AI29:AL31" si="292">AI3/AE3-1</f>
+        <v>0.16111678236014693</v>
+      </c>
+      <c r="AJ29" s="11">
+        <f t="shared" si="292"/>
         <v>-1</v>
       </c>
-      <c r="AJ29" s="11">
-        <f>AJ3/AF3-1</f>
+      <c r="AK29" s="11">
+        <f t="shared" si="292"/>
         <v>-1</v>
       </c>
-      <c r="AK29" s="11">
-        <f>AK3/AG3-1</f>
-        <v>-1</v>
-      </c>
       <c r="AL29" s="11">
-        <f>AL3/AH3-1</f>
+        <f t="shared" si="292"/>
         <v>-1</v>
       </c>
       <c r="AM29" s="11"/>
@@ -7816,71 +7859,71 @@
       <c r="AX29" s="11"/>
       <c r="AY29" s="11"/>
       <c r="BB29" s="11">
-        <f t="shared" ref="BB29:BC29" si="282">BB3/BA3-1</f>
+        <f t="shared" ref="BB29:BC29" si="293">BB3/BA3-1</f>
         <v>-5.2973915969660834E-2</v>
       </c>
       <c r="BC29" s="11">
-        <f t="shared" si="282"/>
+        <f t="shared" si="293"/>
         <v>3.2092312151970948E-2</v>
       </c>
       <c r="BD29" s="11">
-        <f t="shared" ref="BD29:BP29" si="283">BD3/BC3-1</f>
+        <f t="shared" ref="BD29:BP29" si="294">BD3/BC3-1</f>
         <v>0.34720743656765429</v>
       </c>
       <c r="BE29" s="11">
-        <f t="shared" si="283"/>
+        <f t="shared" si="294"/>
         <v>6.3239764351428418E-2</v>
       </c>
       <c r="BF29" s="11">
-        <f t="shared" si="283"/>
+        <f t="shared" si="294"/>
         <v>-5.7286708686618226E-2</v>
       </c>
       <c r="BG29" s="11">
-        <f t="shared" si="283"/>
+        <f t="shared" si="294"/>
         <v>-1.0798933190197424E-2</v>
       </c>
       <c r="BH29" s="11">
-        <f t="shared" si="283"/>
+        <f t="shared" si="294"/>
         <v>4.1161069774066972E-2</v>
       </c>
       <c r="BI29" s="11">
-        <f t="shared" si="283"/>
+        <f t="shared" si="294"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BJ29" s="11">
-        <f t="shared" si="283"/>
+        <f t="shared" si="294"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BK29" s="11">
-        <f t="shared" si="283"/>
+        <f t="shared" si="294"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BL29" s="11">
-        <f t="shared" si="283"/>
+        <f t="shared" si="294"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BM29" s="11">
-        <f t="shared" si="283"/>
+        <f t="shared" si="294"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BN29" s="11">
-        <f t="shared" si="283"/>
+        <f t="shared" si="294"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BO29" s="11">
-        <f t="shared" si="283"/>
+        <f t="shared" si="294"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BP29" s="11">
-        <f t="shared" si="283"/>
+        <f t="shared" si="294"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BQ29" s="11">
-        <f>BQ3/BP3-1</f>
+        <f t="shared" ref="BQ29:BR31" si="295">BQ3/BP3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BR29" s="11">
-        <f>BR3/BQ3-1</f>
+        <f t="shared" si="295"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -7889,131 +7932,131 @@
         <v>53</v>
       </c>
       <c r="G30" s="11">
-        <f t="shared" ref="G30:N30" si="284">G4/C4-1</f>
+        <f t="shared" ref="G30:N30" si="296">G4/C4-1</f>
         <v>0.19125862635557023</v>
       </c>
       <c r="H30" s="11">
-        <f t="shared" si="284"/>
+        <f t="shared" si="296"/>
         <v>0.1624365482233503</v>
       </c>
       <c r="I30" s="11">
-        <f t="shared" si="284"/>
+        <f t="shared" si="296"/>
         <v>0.12635201573254662</v>
       </c>
       <c r="J30" s="11">
-        <f t="shared" si="284"/>
+        <f t="shared" si="296"/>
         <v>0.18039437682800274</v>
       </c>
       <c r="K30" s="11">
-        <f t="shared" si="284"/>
+        <f t="shared" si="296"/>
         <v>0.16919540229885066</v>
       </c>
       <c r="L30" s="11">
-        <f t="shared" si="284"/>
+        <f t="shared" si="296"/>
         <v>0.16576419213973792</v>
       </c>
       <c r="M30" s="11">
-        <f t="shared" si="284"/>
+        <f t="shared" si="296"/>
         <v>0.14849410737669144</v>
       </c>
       <c r="N30" s="11">
-        <f t="shared" si="284"/>
+        <f t="shared" si="296"/>
         <v>0.16289665094716654</v>
       </c>
       <c r="O30" s="11">
-        <f>O4/K4-1</f>
+        <f t="shared" si="290"/>
         <v>0.23955957530475813</v>
       </c>
       <c r="P30" s="11">
-        <f>P4/L4-1</f>
+        <f t="shared" si="290"/>
         <v>0.26618219958046141</v>
       </c>
       <c r="Q30" s="11">
-        <f>Q4/M4-1</f>
+        <f t="shared" si="290"/>
         <v>0.32912739434478566</v>
       </c>
       <c r="R30" s="11">
-        <f>R4/N4-1</f>
+        <f t="shared" si="290"/>
         <v>0.25623754209911342</v>
       </c>
       <c r="S30" s="11">
-        <f>S4/O4-1</f>
+        <f t="shared" si="290"/>
         <v>0.23824630416851722</v>
       </c>
       <c r="T30" s="11">
-        <f>T4/P4-1</f>
+        <f t="shared" si="290"/>
         <v>0.17277084196201398</v>
       </c>
       <c r="U30" s="11">
-        <f>U4/Q4-1</f>
+        <f t="shared" si="290"/>
         <v>0.12112547180601618</v>
       </c>
       <c r="V30" s="11">
-        <f>V4/R4-1</f>
+        <f t="shared" si="290"/>
         <v>4.984406631285232E-2</v>
       </c>
       <c r="W30" s="11">
-        <f>W4/S4-1</f>
+        <f t="shared" si="290"/>
         <v>6.4050010248001721E-2</v>
       </c>
       <c r="X30" s="11">
-        <f>X4/T4-1</f>
+        <f t="shared" si="290"/>
         <v>5.4790373845921003E-2</v>
       </c>
       <c r="Y30" s="11">
-        <f>Y4/U4-1</f>
+        <f t="shared" si="291"/>
         <v>8.2075086716996593E-2</v>
       </c>
       <c r="Z30" s="11">
-        <f>Z4/V4-1</f>
+        <f t="shared" si="291"/>
         <v>0.16291432145090678</v>
       </c>
       <c r="AA30" s="11">
-        <f>AA4/W4-1</f>
+        <f t="shared" si="291"/>
         <v>0.11321390734855052</v>
       </c>
       <c r="AB30" s="11">
-        <f>AB4/X4-1</f>
+        <f t="shared" si="291"/>
         <v>0.14157937532883724</v>
       </c>
       <c r="AC30" s="11">
-        <f>AC4/Y4-1</f>
+        <f t="shared" si="291"/>
         <v>0.1414227124876255</v>
       </c>
       <c r="AD30" s="11">
-        <f>AD4/Z4-1</f>
+        <f t="shared" si="291"/>
         <v>0.11911804248453883</v>
       </c>
       <c r="AE30" s="11">
-        <f>AE4/AA4-1</f>
+        <f t="shared" si="291"/>
         <v>0.13942120517368162</v>
       </c>
       <c r="AF30" s="11">
-        <f>AF4/AB4-1</f>
+        <f t="shared" si="291"/>
         <v>0.11639502241588806</v>
       </c>
       <c r="AG30" s="11">
-        <f>AG4/AC4-1</f>
+        <f t="shared" si="291"/>
         <v>0.13257341097757402</v>
       </c>
       <c r="AH30" s="11">
-        <f>AH4/AD4-1</f>
+        <f t="shared" si="291"/>
         <v>0.1512894441774788</v>
       </c>
       <c r="AI30" s="11">
-        <f>AI4/AE4-1</f>
+        <f t="shared" si="292"/>
+        <v>0.13944570994684891</v>
+      </c>
+      <c r="AJ30" s="11">
+        <f t="shared" si="292"/>
         <v>-1</v>
       </c>
-      <c r="AJ30" s="11">
-        <f>AJ4/AF4-1</f>
+      <c r="AK30" s="11">
+        <f t="shared" si="292"/>
         <v>-1</v>
       </c>
-      <c r="AK30" s="11">
-        <f>AK4/AG4-1</f>
-        <v>-1</v>
-      </c>
       <c r="AL30" s="11">
-        <f>AL4/AH4-1</f>
+        <f t="shared" si="292"/>
         <v>-1</v>
       </c>
       <c r="AM30" s="11"/>
@@ -8030,71 +8073,71 @@
       <c r="AX30" s="11"/>
       <c r="AY30" s="11"/>
       <c r="BB30" s="11">
-        <f t="shared" ref="BB30:BC30" si="285">BB4/BA4-1</f>
+        <f t="shared" ref="BB30:BC30" si="297">BB4/BA4-1</f>
         <v>0.16461205595250084</v>
       </c>
       <c r="BC30" s="11">
-        <f t="shared" si="285"/>
+        <f t="shared" si="297"/>
         <v>0.16152167807997242</v>
       </c>
       <c r="BD30" s="11">
-        <f t="shared" ref="BD30:BP30" si="286">BD4/BC4-1</f>
+        <f t="shared" ref="BD30:BP30" si="298">BD4/BC4-1</f>
         <v>0.27259708376729663</v>
       </c>
       <c r="BE30" s="11">
-        <f t="shared" si="286"/>
+        <f t="shared" si="298"/>
         <v>0.14181951041286078</v>
       </c>
       <c r="BF30" s="11">
-        <f t="shared" si="286"/>
+        <f t="shared" si="298"/>
         <v>9.0504166186691215E-2</v>
       </c>
       <c r="BG30" s="11">
-        <f t="shared" si="286"/>
+        <f t="shared" si="298"/>
         <v>0.12874413145539898</v>
       </c>
       <c r="BH30" s="11">
-        <f t="shared" si="286"/>
+        <f t="shared" si="298"/>
         <v>0.13506431386413498</v>
       </c>
       <c r="BI30" s="11">
-        <f t="shared" si="286"/>
+        <f t="shared" si="298"/>
         <v>9.000000000000008E-2</v>
       </c>
       <c r="BJ30" s="11">
-        <f t="shared" si="286"/>
+        <f t="shared" si="298"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="BK30" s="11">
-        <f t="shared" si="286"/>
+        <f t="shared" si="298"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="BL30" s="11">
-        <f t="shared" si="286"/>
+        <f t="shared" si="298"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BM30" s="11">
-        <f t="shared" si="286"/>
+        <f t="shared" si="298"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="BN30" s="11">
-        <f t="shared" si="286"/>
+        <f t="shared" si="298"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BO30" s="11">
-        <f t="shared" si="286"/>
+        <f t="shared" si="298"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BP30" s="11">
-        <f t="shared" si="286"/>
+        <f t="shared" si="298"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BQ30" s="11">
-        <f>BQ4/BP4-1</f>
+        <f t="shared" si="295"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BR30" s="11">
-        <f>BR4/BQ4-1</f>
+        <f t="shared" si="295"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BT30" t="s">
@@ -8113,181 +8156,181 @@
         <v>-4.5111163965433243E-2</v>
       </c>
       <c r="H31" s="11">
-        <f t="shared" ref="H31:N31" si="287">H5/D5-1</f>
+        <f t="shared" ref="H31:N31" si="299">H5/D5-1</f>
         <v>-5.1065639465462831E-2</v>
       </c>
       <c r="I31" s="11">
-        <f t="shared" si="287"/>
+        <f t="shared" si="299"/>
         <v>1.0213085515817122E-2</v>
       </c>
       <c r="J31" s="11">
-        <f t="shared" si="287"/>
+        <f t="shared" si="299"/>
         <v>1.8124006359300449E-2</v>
       </c>
       <c r="K31" s="11">
-        <f t="shared" si="287"/>
+        <f t="shared" si="299"/>
         <v>8.9064167951607098E-2</v>
       </c>
       <c r="L31" s="11">
-        <f t="shared" si="287"/>
+        <f t="shared" si="299"/>
         <v>5.1366026027750422E-3</v>
       </c>
       <c r="M31" s="11">
-        <f t="shared" si="287"/>
+        <f t="shared" si="299"/>
         <v>0.10920106301919752</v>
       </c>
       <c r="N31" s="11">
-        <f t="shared" si="287"/>
+        <f t="shared" si="299"/>
         <v>1.0274828232354816E-2</v>
       </c>
       <c r="O31" s="11">
-        <f>O5/K5-1</f>
+        <f t="shared" si="290"/>
         <v>0.21368126422635836</v>
       </c>
       <c r="P31" s="11">
-        <f>P5/L5-1</f>
+        <f t="shared" si="290"/>
         <v>0.53626121105070901</v>
       </c>
       <c r="Q31" s="11">
-        <f>Q5/M5-1</f>
+        <f t="shared" si="290"/>
         <v>0.36439641450950822</v>
       </c>
       <c r="R31" s="11">
-        <f>R5/N5-1</f>
+        <f t="shared" si="290"/>
         <v>0.28844786546724777</v>
       </c>
       <c r="S31" s="11">
-        <f>S5/O5-1</f>
+        <f t="shared" si="290"/>
         <v>0.11222283042740866</v>
       </c>
       <c r="T31" s="11">
-        <f>T5/P5-1</f>
+        <f t="shared" si="290"/>
         <v>8.5885872477228009E-2</v>
       </c>
       <c r="U31" s="11">
-        <f>U5/Q5-1</f>
+        <f t="shared" si="290"/>
         <v>1.8726821720657316E-2</v>
       </c>
       <c r="V31" s="11">
-        <f>V5/R5-1</f>
+        <f t="shared" si="290"/>
         <v>8.1405950095969182E-2</v>
       </c>
       <c r="W31" s="11">
-        <f>W5/S5-1</f>
+        <f t="shared" si="290"/>
         <v>-5.4790431239662762E-2</v>
       </c>
       <c r="X31" s="11">
-        <f>X5/T5-1</f>
+        <f t="shared" si="290"/>
         <v>-2.5103312156911084E-2</v>
       </c>
       <c r="Y31" s="11">
-        <f>Y5/U5-1</f>
+        <f t="shared" si="291"/>
         <v>-1.4006919080509661E-2</v>
       </c>
       <c r="Z31" s="11">
-        <f>Z5/V5-1</f>
+        <f t="shared" si="291"/>
         <v>-7.1883389168682088E-3</v>
       </c>
       <c r="AA31" s="11">
-        <f>AA5/W5-1</f>
+        <f t="shared" si="291"/>
         <v>2.0665107465387411E-2</v>
       </c>
       <c r="AB31" s="11">
-        <f>AB5/X5-1</f>
+        <f t="shared" si="291"/>
         <v>-4.3053270909781061E-2</v>
       </c>
       <c r="AC31" s="11">
-        <f>AC5/Y5-1</f>
+        <f t="shared" si="291"/>
         <v>4.8657041211780383E-2</v>
       </c>
       <c r="AD31" s="11">
-        <f>AD5/Z5-1</f>
+        <f t="shared" si="291"/>
         <v>6.0694093722764686E-2</v>
       </c>
       <c r="AE31" s="11">
-        <f>AE5/AA5-1</f>
+        <f t="shared" si="291"/>
         <v>3.9514948776918191E-2</v>
       </c>
       <c r="AF31" s="11">
-        <f>AF5/AB5-1</f>
+        <f t="shared" si="291"/>
         <v>5.075314314678292E-2</v>
       </c>
       <c r="AG31" s="11">
-        <f>AG5/AC5-1</f>
+        <f t="shared" si="291"/>
         <v>9.628455180293094E-2</v>
       </c>
       <c r="AH31" s="11">
-        <f>AH5/AD5-1</f>
+        <f t="shared" si="291"/>
         <v>7.9384809859896821E-2</v>
       </c>
       <c r="AI31" s="11">
-        <f>AI5/AE5-1</f>
+        <f t="shared" si="292"/>
+        <v>0.15652453740949324</v>
+      </c>
+      <c r="AJ31" s="11">
+        <f t="shared" si="292"/>
         <v>-1</v>
       </c>
-      <c r="AJ31" s="11">
-        <f>AJ5/AF5-1</f>
+      <c r="AK31" s="11">
+        <f t="shared" si="292"/>
         <v>-1</v>
       </c>
-      <c r="AK31" s="11">
-        <f>AK5/AG5-1</f>
-        <v>-1</v>
-      </c>
       <c r="AL31" s="11">
-        <f>AL5/AH5-1</f>
+        <f t="shared" si="292"/>
         <v>-1</v>
       </c>
       <c r="AM31" s="11"/>
       <c r="AN31" s="11"/>
       <c r="AO31" s="11">
-        <f t="shared" ref="AO31:AT31" si="288">AO5/AN5-1</f>
+        <f t="shared" ref="AO31:AT31" si="300">AO5/AN5-1</f>
         <v>0.38647620414902017</v>
       </c>
       <c r="AP31" s="11">
-        <f t="shared" si="288"/>
+        <f t="shared" si="300"/>
         <v>0.24286823712140815</v>
       </c>
       <c r="AQ31" s="11">
-        <f t="shared" si="288"/>
+        <f t="shared" si="300"/>
         <v>0.56173456635841035</v>
       </c>
       <c r="AR31" s="11">
-        <f t="shared" si="288"/>
+        <f t="shared" si="300"/>
         <v>0.14440799125123371</v>
       </c>
       <c r="AS31" s="11">
-        <f t="shared" si="288"/>
+        <f t="shared" si="300"/>
         <v>0.52021908868430256</v>
       </c>
       <c r="AT31" s="11">
-        <f t="shared" si="288"/>
+        <f t="shared" si="300"/>
         <v>0.65962437715599842</v>
       </c>
       <c r="AU31" s="11">
-        <f t="shared" ref="AU31:BA31" si="289">AU5/AT5-1</f>
+        <f t="shared" ref="AU31:BA31" si="301">AU5/AT5-1</f>
         <v>0.44581474193756976</v>
       </c>
       <c r="AV31" s="11">
-        <f t="shared" si="289"/>
+        <f t="shared" si="301"/>
         <v>9.2020855163953197E-2</v>
       </c>
       <c r="AW31" s="11">
-        <f t="shared" si="289"/>
+        <f t="shared" si="301"/>
         <v>6.9539523725937524E-2</v>
       </c>
       <c r="AX31" s="11">
-        <f t="shared" si="289"/>
+        <f t="shared" si="301"/>
         <v>0.27856341803659834</v>
       </c>
       <c r="AY31" s="11">
-        <f t="shared" si="289"/>
+        <f t="shared" si="301"/>
         <v>-7.7342061913013738E-2</v>
       </c>
       <c r="AZ31" s="11">
-        <f t="shared" si="289"/>
+        <f t="shared" si="301"/>
         <v>6.304518199398057E-2</v>
       </c>
       <c r="BA31" s="11">
-        <f t="shared" si="289"/>
+        <f t="shared" si="301"/>
         <v>0.15861957650261305</v>
       </c>
       <c r="BB31" s="11">
@@ -8295,67 +8338,67 @@
         <v>-2.04107758052674E-2</v>
       </c>
       <c r="BC31" s="11">
-        <f t="shared" ref="BC31:BP31" si="290">BC5/BB5-1</f>
+        <f t="shared" ref="BC31:BP31" si="302">BC5/BB5-1</f>
         <v>5.5120803769784787E-2</v>
       </c>
       <c r="BD31" s="11">
-        <f t="shared" si="290"/>
+        <f t="shared" si="302"/>
         <v>0.33259384733074704</v>
       </c>
       <c r="BE31" s="11">
-        <f t="shared" si="290"/>
+        <f t="shared" si="302"/>
         <v>7.7937876041846099E-2</v>
       </c>
       <c r="BF31" s="11">
-        <f t="shared" si="290"/>
+        <f t="shared" si="302"/>
         <v>-2.800460530319937E-2</v>
       </c>
       <c r="BG31" s="11">
-        <f t="shared" si="290"/>
+        <f t="shared" si="302"/>
         <v>2.021994077514111E-2</v>
       </c>
       <c r="BH31" s="11">
-        <f t="shared" si="290"/>
+        <f t="shared" si="302"/>
         <v>6.425511782832749E-2</v>
       </c>
       <c r="BI31" s="11">
-        <f t="shared" si="290"/>
+        <f t="shared" si="302"/>
         <v>4.5737851456527867E-2</v>
       </c>
       <c r="BJ31" s="11">
-        <f t="shared" si="290"/>
+        <f t="shared" si="302"/>
         <v>3.3669979577675146E-2</v>
       </c>
       <c r="BK31" s="11">
-        <f t="shared" si="290"/>
+        <f t="shared" si="302"/>
         <v>2.4150433346326272E-2</v>
       </c>
       <c r="BL31" s="11">
-        <f t="shared" si="290"/>
+        <f t="shared" si="302"/>
         <v>2.1716606356819268E-2</v>
       </c>
       <c r="BM31" s="11">
-        <f t="shared" si="290"/>
+        <f t="shared" si="302"/>
         <v>1.9030711107746123E-2</v>
       </c>
       <c r="BN31" s="11">
-        <f t="shared" si="290"/>
+        <f t="shared" si="302"/>
         <v>1.6144361466689849E-2</v>
       </c>
       <c r="BO31" s="11">
-        <f t="shared" si="290"/>
+        <f t="shared" si="302"/>
         <v>1.6228142920121869E-2</v>
       </c>
       <c r="BP31" s="11">
-        <f t="shared" si="290"/>
+        <f t="shared" si="302"/>
         <v>1.6312546304112496E-2</v>
       </c>
       <c r="BQ31" s="11">
-        <f>BQ5/BP5-1</f>
+        <f t="shared" si="295"/>
         <v>1.6397562164198964E-2</v>
       </c>
       <c r="BR31" s="11">
-        <f>BR5/BQ5-1</f>
+        <f t="shared" si="295"/>
         <v>1.648318067104948E-2</v>
       </c>
       <c r="BT31" t="s">
@@ -8370,8 +8413,8 @@
         <v>45</v>
       </c>
       <c r="BU32" s="3">
-        <f>NPV(BU31,BH17:GA17)</f>
-        <v>2738917.5694854497</v>
+        <f>NPV(BU31,BI17:GA17)</f>
+        <v>2664498.7980459058</v>
       </c>
     </row>
     <row r="33" spans="2:73" x14ac:dyDescent="0.3">
@@ -8383,268 +8426,268 @@
         <v>0.25767665556788755</v>
       </c>
       <c r="D33" s="10">
-        <f t="shared" ref="D33:M33" si="291">D16/D15</f>
+        <f t="shared" ref="D33:M33" si="303">D16/D15</f>
         <v>0.14510143493320138</v>
       </c>
       <c r="E33" s="10">
-        <f t="shared" si="291"/>
+        <f t="shared" si="303"/>
         <v>0.13286660644384221</v>
       </c>
       <c r="F33" s="10">
-        <f t="shared" si="291"/>
+        <f t="shared" si="303"/>
         <v>0.13982096096461846</v>
       </c>
       <c r="G33" s="10">
-        <f t="shared" si="291"/>
+        <f t="shared" si="303"/>
         <v>0.16485401154521878</v>
       </c>
       <c r="H33" s="10">
-        <f t="shared" si="291"/>
+        <f t="shared" si="303"/>
         <v>0.16182121365910243</v>
       </c>
       <c r="I33" s="10">
-        <f t="shared" si="291"/>
+        <f t="shared" si="303"/>
         <v>0.15674586516665268</v>
       </c>
       <c r="J33" s="10">
-        <f t="shared" si="291"/>
+        <f t="shared" si="303"/>
         <v>0.15136107149500838</v>
       </c>
       <c r="K33" s="10">
-        <f t="shared" si="291"/>
+        <f t="shared" si="303"/>
         <v>0.14206343082027933</v>
       </c>
       <c r="L33" s="10">
-        <f t="shared" si="291"/>
+        <f t="shared" si="303"/>
         <v>0.14358583936048724</v>
       </c>
       <c r="M33" s="10">
-        <f t="shared" si="291"/>
+        <f t="shared" si="303"/>
         <v>0.14341173783968944</v>
       </c>
       <c r="N33" s="10">
-        <f t="shared" ref="N33:BM33" si="292">N16/N15</f>
+        <f t="shared" ref="N33:BM33" si="304">N16/N15</f>
         <v>0.14952016643178309</v>
       </c>
       <c r="O33" s="10">
-        <f t="shared" ref="O33:S33" si="293">O16/O15</f>
+        <f t="shared" ref="O33:S33" si="305">O16/O15</f>
         <v>0.14366121683194855</v>
       </c>
       <c r="P33" s="10">
-        <f t="shared" si="293"/>
+        <f t="shared" si="305"/>
         <v>0.1564028417407447</v>
       </c>
       <c r="Q33" s="10">
-        <f t="shared" ref="Q33:R33" si="294">Q16/Q15</f>
+        <f t="shared" ref="Q33:R33" si="306">Q16/Q15</f>
         <v>0.10771882309491568</v>
       </c>
       <c r="R33" s="10">
-        <f t="shared" si="294"/>
+        <f t="shared" si="306"/>
         <v>0.11600997935306263</v>
       </c>
       <c r="S33" s="10">
-        <f t="shared" si="293"/>
+        <f t="shared" si="305"/>
         <v>0.16030164157028201</v>
       </c>
       <c r="T33" s="10">
-        <f t="shared" ref="T33:U33" si="295">T16/T15</f>
+        <f t="shared" ref="T33:U33" si="307">T16/T15</f>
         <v>0.17017817445834302</v>
       </c>
       <c r="U33" s="10">
-        <f t="shared" si="295"/>
+        <f t="shared" si="307"/>
         <v>0.15711436746726784</v>
       </c>
       <c r="V33" s="10">
-        <f t="shared" ref="V33" si="296">V16/V15</f>
+        <f t="shared" ref="V33" si="308">V16/V15</f>
         <v>0.15963012531938192</v>
       </c>
       <c r="W33" s="10">
-        <f t="shared" ref="W33:X33" si="297">W16/W15</f>
+        <f t="shared" ref="W33:X33" si="309">W16/W15</f>
         <v>0.15790360160570419</v>
       </c>
       <c r="X33" s="10">
-        <f t="shared" si="297"/>
+        <f t="shared" si="309"/>
         <v>0.14875625396377987</v>
       </c>
       <c r="Y33" s="10">
-        <f t="shared" ref="Y33:Z33" si="298">Y16/Y15</f>
+        <f t="shared" ref="Y33:Z33" si="310">Y16/Y15</f>
         <v>0.12545638499098227</v>
       </c>
       <c r="Z33" s="10">
-        <f t="shared" si="298"/>
+        <f t="shared" si="310"/>
         <v>0.14971479368842136</v>
       </c>
       <c r="AA33" s="10">
-        <f t="shared" ref="AA33:AD33" si="299">AA16/AA15</f>
+        <f t="shared" ref="AA33:AD33" si="311">AA16/AA15</f>
         <v>0.15889194752374575</v>
       </c>
       <c r="AB33" s="10">
-        <f t="shared" si="299"/>
+        <f t="shared" si="311"/>
         <v>0.1576021099151757</v>
       </c>
       <c r="AC33" s="10">
-        <f t="shared" si="299"/>
+        <f t="shared" si="311"/>
         <v>0.15870400878638111</v>
       </c>
       <c r="AD33" s="10">
-        <f t="shared" si="299"/>
+        <f t="shared" si="311"/>
         <v>0.50233029381965555</v>
       </c>
       <c r="AE33" s="10">
-        <f t="shared" ref="AE33:AH33" si="300">AE16/AE15</f>
+        <f t="shared" ref="AE33:AH33" si="312">AE16/AE15</f>
         <v>0.14686267142588766</v>
       </c>
       <c r="AF33" s="10">
-        <f t="shared" si="300"/>
+        <f t="shared" si="312"/>
         <v>0.15455475946775846</v>
       </c>
       <c r="AG33" s="10">
-        <f t="shared" si="300"/>
+        <f t="shared" si="312"/>
         <v>0.16399700331775535</v>
       </c>
       <c r="AH33" s="10">
-        <f t="shared" si="300"/>
+        <f t="shared" si="312"/>
         <v>0.16272405804170223</v>
       </c>
-      <c r="AI33" s="10" t="e">
-        <f t="shared" ref="AI33:AL33" si="301">AI16/AI15</f>
+      <c r="AI33" s="10">
+        <f t="shared" ref="AI33:AL33" si="313">AI16/AI15</f>
+        <v>0.17460099603937101</v>
+      </c>
+      <c r="AJ33" s="10" t="e">
+        <f t="shared" si="313"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AJ33" s="10" t="e">
-        <f t="shared" si="301"/>
+      <c r="AK33" s="10" t="e">
+        <f t="shared" si="313"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AK33" s="10" t="e">
-        <f t="shared" si="301"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="AL33" s="10" t="e">
-        <f t="shared" si="301"/>
+        <f t="shared" si="313"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AM33" s="10"/>
       <c r="AN33" s="10">
-        <f t="shared" ref="AN33:AT33" si="302">AN16/AN15</f>
+        <f t="shared" ref="AN33:AT33" si="314">AN16/AN15</f>
         <v>0.26548672566371684</v>
       </c>
       <c r="AO33" s="10">
-        <f t="shared" si="302"/>
+        <f t="shared" si="314"/>
         <v>0.29418026969481903</v>
       </c>
       <c r="AP33" s="10">
-        <f t="shared" si="302"/>
+        <f t="shared" si="314"/>
         <v>0.30191693290734822</v>
       </c>
       <c r="AQ33" s="10">
-        <f t="shared" si="302"/>
+        <f t="shared" si="314"/>
         <v>0.3160836034424947</v>
       </c>
       <c r="AR33" s="10">
-        <f t="shared" si="302"/>
+        <f t="shared" si="314"/>
         <v>0.31750372948781702</v>
       </c>
       <c r="AS33" s="10">
-        <f t="shared" si="302"/>
+        <f t="shared" si="314"/>
         <v>0.24417475728155341</v>
       </c>
       <c r="AT33" s="10">
-        <f t="shared" si="302"/>
+        <f t="shared" si="314"/>
         <v>0.24215757930127174</v>
       </c>
       <c r="AU33" s="10">
-        <f t="shared" si="292"/>
+        <f t="shared" si="304"/>
         <v>0.25160052364471064</v>
       </c>
       <c r="AV33" s="10">
-        <f t="shared" si="292"/>
+        <f t="shared" si="304"/>
         <v>0.26154919748778788</v>
       </c>
       <c r="AW33" s="10">
-        <f t="shared" si="292"/>
+        <f t="shared" si="304"/>
         <v>0.26126058747639436</v>
       </c>
       <c r="AX33" s="10">
-        <f t="shared" si="292"/>
+        <f t="shared" si="304"/>
         <v>0.26368337585327173</v>
       </c>
       <c r="AY33" s="10">
-        <f t="shared" si="292"/>
+        <f t="shared" si="304"/>
         <v>0.25557257381216192</v>
       </c>
       <c r="AZ33" s="10">
-        <f t="shared" si="292"/>
+        <f t="shared" si="304"/>
         <v>0.24556476150353415</v>
       </c>
       <c r="BA33" s="10">
-        <f t="shared" si="292"/>
+        <f t="shared" si="304"/>
         <v>0.18342180705869443</v>
       </c>
       <c r="BB33" s="10">
-        <f t="shared" si="292"/>
+        <f t="shared" si="304"/>
         <v>0.15943836804235059</v>
       </c>
       <c r="BC33" s="10">
-        <f t="shared" si="292"/>
+        <f t="shared" si="304"/>
         <v>0.14428164731484103</v>
       </c>
       <c r="BD33" s="10">
-        <f t="shared" si="292"/>
+        <f t="shared" si="304"/>
         <v>0.13302260844085087</v>
       </c>
       <c r="BE33" s="10">
-        <f t="shared" ref="BE33:BF33" si="303">BE16/BE15</f>
+        <f t="shared" ref="BE33:BF33" si="315">BE16/BE15</f>
         <v>0.16204461684424407</v>
       </c>
       <c r="BF33" s="10">
-        <f t="shared" si="303"/>
+        <f t="shared" si="315"/>
         <v>0.14719174228036858</v>
       </c>
       <c r="BG33" s="10">
-        <f t="shared" ref="BG33" si="304">BG16/BG15</f>
+        <f t="shared" ref="BG33" si="316">BG16/BG15</f>
         <v>0.24091185164189982</v>
       </c>
       <c r="BH33" s="10">
-        <f t="shared" si="292"/>
+        <f t="shared" si="304"/>
         <v>0.15610002335586043</v>
       </c>
       <c r="BI33" s="10">
-        <f t="shared" si="292"/>
+        <f t="shared" si="304"/>
         <v>0.16</v>
       </c>
       <c r="BJ33" s="10">
-        <f t="shared" si="292"/>
+        <f t="shared" si="304"/>
         <v>0.16</v>
       </c>
       <c r="BK33" s="10">
-        <f t="shared" si="292"/>
+        <f t="shared" si="304"/>
         <v>0.16</v>
       </c>
       <c r="BL33" s="10">
-        <f t="shared" si="292"/>
+        <f t="shared" si="304"/>
         <v>0.16</v>
       </c>
       <c r="BM33" s="10">
-        <f t="shared" si="292"/>
+        <f t="shared" si="304"/>
         <v>0.16</v>
       </c>
       <c r="BN33" s="10">
-        <f t="shared" ref="BN33:BP33" si="305">BN16/BN15</f>
+        <f t="shared" ref="BN33:BP33" si="317">BN16/BN15</f>
         <v>0.16</v>
       </c>
       <c r="BO33" s="10">
-        <f t="shared" si="305"/>
+        <f t="shared" si="317"/>
         <v>0.16</v>
       </c>
       <c r="BP33" s="10">
-        <f t="shared" si="305"/>
+        <f t="shared" si="317"/>
         <v>0.16</v>
       </c>
       <c r="BQ33" s="10">
-        <f t="shared" ref="BQ33:BR33" si="306">BQ16/BQ15</f>
+        <f t="shared" ref="BQ33:BR33" si="318">BQ16/BQ15</f>
         <v>0.16</v>
       </c>
       <c r="BR33" s="10">
-        <f t="shared" si="306"/>
+        <f t="shared" si="318"/>
         <v>0.16</v>
       </c>
       <c r="BT33" t="s">
@@ -8652,7 +8695,7 @@
       </c>
       <c r="BU33" s="3">
         <f>Main!D8</f>
-        <v>33763</v>
+        <v>54286</v>
       </c>
     </row>
     <row r="34" spans="2:73" x14ac:dyDescent="0.3">
@@ -8661,7 +8704,7 @@
       </c>
       <c r="BU34" s="3">
         <f>BU32+BU33</f>
-        <v>2772680.5694854497</v>
+        <v>2718784.7980459058</v>
       </c>
     </row>
     <row r="35" spans="2:73" x14ac:dyDescent="0.3">
@@ -8670,7 +8713,7 @@
       </c>
       <c r="BU35" s="12">
         <f>BU34/BM18</f>
-        <v>186.0497332388629</v>
+        <v>182.43327124559016</v>
       </c>
     </row>
     <row r="36" spans="2:73" x14ac:dyDescent="0.3">
@@ -8682,7 +8725,7 @@
       </c>
       <c r="BU36" s="12">
         <f>Main!D3</f>
-        <v>276.72000000000003</v>
+        <v>256.72000000000003</v>
       </c>
     </row>
     <row r="37" spans="2:73" x14ac:dyDescent="0.3">
@@ -8692,7 +8735,7 @@
       </c>
       <c r="BU37" s="11">
         <f>BU35/BU36-1</f>
-        <v>-0.32766069225620531</v>
+        <v>-0.28936868477099509</v>
       </c>
     </row>
     <row r="38" spans="2:73" x14ac:dyDescent="0.3">
@@ -8732,7 +8775,7 @@
         <v>51</v>
       </c>
       <c r="BU38" s="5" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="39" spans="2:73" x14ac:dyDescent="0.3">
@@ -9459,71 +9502,71 @@
         <v>94</v>
       </c>
       <c r="AN61" s="9">
-        <f t="shared" ref="AN61" si="307">AN17</f>
+        <f t="shared" ref="AN61" si="319">AN17</f>
         <v>1328</v>
       </c>
       <c r="AO61" s="9">
-        <f t="shared" ref="AO61:AP61" si="308">AO17</f>
+        <f t="shared" ref="AO61:AP61" si="320">AO17</f>
         <v>1989</v>
       </c>
       <c r="AP61" s="9">
-        <f t="shared" si="308"/>
+        <f t="shared" si="320"/>
         <v>3496</v>
       </c>
       <c r="AQ61" s="9">
-        <f t="shared" ref="AQ61:AR61" si="309">AQ17</f>
+        <f t="shared" ref="AQ61:AR61" si="321">AQ17</f>
         <v>6119</v>
       </c>
       <c r="AR61" s="9">
-        <f t="shared" si="309"/>
+        <f t="shared" si="321"/>
         <v>8235</v>
       </c>
       <c r="AS61" s="9">
-        <f t="shared" ref="AS61:AT61" si="310">AS17</f>
+        <f t="shared" ref="AS61:AT61" si="322">AS17</f>
         <v>14013</v>
       </c>
       <c r="AT61" s="9">
-        <f t="shared" si="310"/>
+        <f t="shared" si="322"/>
         <v>25922</v>
       </c>
       <c r="AU61" s="9">
-        <f t="shared" ref="AU61:BA61" si="311">AU17</f>
+        <f t="shared" ref="AU61:BA61" si="323">AU17</f>
         <v>41733</v>
       </c>
       <c r="AV61" s="9">
-        <f t="shared" si="311"/>
+        <f t="shared" si="323"/>
         <v>37037</v>
       </c>
       <c r="AW61" s="9">
-        <f t="shared" si="311"/>
+        <f t="shared" si="323"/>
         <v>39510</v>
       </c>
       <c r="AX61" s="9">
-        <f t="shared" si="311"/>
+        <f t="shared" si="323"/>
         <v>53394</v>
       </c>
       <c r="AY61" s="9">
-        <f t="shared" si="311"/>
+        <f t="shared" si="323"/>
         <v>45687</v>
       </c>
       <c r="AZ61" s="9">
-        <f t="shared" si="311"/>
+        <f t="shared" si="323"/>
         <v>48351</v>
       </c>
       <c r="BA61" s="9">
-        <f t="shared" si="311"/>
+        <f t="shared" si="323"/>
         <v>59531</v>
       </c>
       <c r="BB61" s="9">
-        <f t="shared" ref="BB61:BD61" si="312">BB17</f>
+        <f t="shared" ref="BB61:BD61" si="324">BB17</f>
         <v>55256</v>
       </c>
       <c r="BC61" s="9">
-        <f t="shared" si="312"/>
+        <f t="shared" si="324"/>
         <v>57411</v>
       </c>
       <c r="BD61" s="9">
-        <f t="shared" si="312"/>
+        <f t="shared" si="324"/>
         <v>94680</v>
       </c>
       <c r="BE61" s="9">
@@ -9539,48 +9582,48 @@
         <v>93736</v>
       </c>
       <c r="BH61" s="9">
-        <f t="shared" ref="BH61:BR61" si="313">BH17</f>
+        <f t="shared" ref="BH61:BR61" si="325">BH17</f>
         <v>112010</v>
       </c>
       <c r="BI61" s="9">
-        <f t="shared" si="313"/>
-        <v>119645.19882000002</v>
+        <f t="shared" si="325"/>
+        <v>115291.89882000003</v>
       </c>
       <c r="BJ61" s="9">
-        <f t="shared" si="313"/>
-        <v>125203.89426375602</v>
+        <f t="shared" si="325"/>
+        <v>120694.74612375603</v>
       </c>
       <c r="BK61" s="9">
-        <f t="shared" si="313"/>
-        <v>129626.32256328825</v>
+        <f t="shared" si="325"/>
+        <v>124982.00602547626</v>
       </c>
       <c r="BL61" s="9">
-        <f t="shared" si="313"/>
-        <v>133456.4489342382</v>
+        <f t="shared" si="325"/>
+        <v>128672.80245489701</v>
       </c>
       <c r="BM61" s="9">
-        <f t="shared" si="313"/>
-        <v>136570.75282709181</v>
+        <f t="shared" si="325"/>
+        <v>131643.59695524102</v>
       </c>
       <c r="BN61" s="9">
-        <f t="shared" si="313"/>
-        <v>139208.25510220914</v>
+        <f t="shared" si="325"/>
+        <v>134182.75702606558</v>
       </c>
       <c r="BO61" s="9">
-        <f t="shared" si="313"/>
-        <v>142179.76567896019</v>
+        <f t="shared" si="325"/>
+        <v>137053.75679745857</v>
       </c>
       <c r="BP61" s="9">
-        <f t="shared" si="313"/>
-        <v>145230.77472310906</v>
+        <f t="shared" si="325"/>
+        <v>140002.24566752152</v>
       </c>
       <c r="BQ61" s="9">
-        <f t="shared" si="313"/>
-        <v>148364.76309831394</v>
+        <f t="shared" si="325"/>
+        <v>143031.66346159976</v>
       </c>
       <c r="BR61" s="9">
-        <f t="shared" si="313"/>
-        <v>151584.20172673929</v>
+        <f t="shared" si="325"/>
+        <v>146144.44009729094</v>
       </c>
     </row>
     <row r="62" spans="2:70" x14ac:dyDescent="0.3">
@@ -9648,48 +9691,47 @@
         <v>11445</v>
       </c>
       <c r="BH62" s="3">
-        <f>BG62*1.005</f>
-        <v>11502.224999999999</v>
+        <v>11698</v>
       </c>
       <c r="BI62" s="3">
-        <f t="shared" ref="BI62:BR62" si="314">BH62*1.005</f>
-        <v>11559.736124999998</v>
+        <f t="shared" ref="BI62:BR62" si="326">BH62*1.005</f>
+        <v>11756.489999999998</v>
       </c>
       <c r="BJ62" s="3">
-        <f t="shared" si="314"/>
-        <v>11617.534805624997</v>
+        <f t="shared" si="326"/>
+        <v>11815.272449999997</v>
       </c>
       <c r="BK62" s="3">
-        <f t="shared" si="314"/>
-        <v>11675.622479653121</v>
+        <f t="shared" si="326"/>
+        <v>11874.348812249995</v>
       </c>
       <c r="BL62" s="3">
-        <f t="shared" si="314"/>
-        <v>11734.000592051385</v>
+        <f t="shared" si="326"/>
+        <v>11933.720556311244</v>
       </c>
       <c r="BM62" s="3">
-        <f t="shared" si="314"/>
-        <v>11792.670595011641</v>
+        <f t="shared" si="326"/>
+        <v>11993.3891590928</v>
       </c>
       <c r="BN62" s="3">
-        <f t="shared" si="314"/>
-        <v>11851.633947986698</v>
+        <f t="shared" si="326"/>
+        <v>12053.356104888262</v>
       </c>
       <c r="BO62" s="3">
-        <f t="shared" si="314"/>
-        <v>11910.892117726631</v>
+        <f t="shared" si="326"/>
+        <v>12113.622885412702</v>
       </c>
       <c r="BP62" s="3">
-        <f t="shared" si="314"/>
-        <v>11970.446578315263</v>
+        <f t="shared" si="326"/>
+        <v>12174.190999839764</v>
       </c>
       <c r="BQ62" s="3">
-        <f t="shared" si="314"/>
-        <v>12030.298811206838</v>
+        <f t="shared" si="326"/>
+        <v>12235.061954838962</v>
       </c>
       <c r="BR62" s="3">
-        <f t="shared" si="314"/>
-        <v>12090.450305262872</v>
+        <f t="shared" si="326"/>
+        <v>12296.237264613155</v>
       </c>
     </row>
     <row r="63" spans="2:70" x14ac:dyDescent="0.3">
@@ -9757,48 +9799,47 @@
         <v>11688</v>
       </c>
       <c r="BH63" s="3">
-        <f>BG63*1.01</f>
-        <v>11804.88</v>
+        <v>12863</v>
       </c>
       <c r="BI63" s="3">
-        <f t="shared" ref="BI63:BR63" si="315">BH63*1.01</f>
-        <v>11922.9288</v>
+        <f>BH63*1.03</f>
+        <v>13248.890000000001</v>
       </c>
       <c r="BJ63" s="3">
-        <f t="shared" si="315"/>
-        <v>12042.158088</v>
+        <f t="shared" ref="BJ63:BR63" si="327">BI63*1.03</f>
+        <v>13646.356700000002</v>
       </c>
       <c r="BK63" s="3">
-        <f t="shared" si="315"/>
-        <v>12162.57966888</v>
+        <f t="shared" si="327"/>
+        <v>14055.747401000002</v>
       </c>
       <c r="BL63" s="3">
-        <f t="shared" si="315"/>
-        <v>12284.205465568801</v>
+        <f t="shared" si="327"/>
+        <v>14477.419823030003</v>
       </c>
       <c r="BM63" s="3">
-        <f t="shared" si="315"/>
-        <v>12407.047520224489</v>
+        <f t="shared" si="327"/>
+        <v>14911.742417720903</v>
       </c>
       <c r="BN63" s="3">
-        <f t="shared" si="315"/>
-        <v>12531.117995426734</v>
+        <f t="shared" si="327"/>
+        <v>15359.09469025253</v>
       </c>
       <c r="BO63" s="3">
-        <f t="shared" si="315"/>
-        <v>12656.429175381001</v>
+        <f t="shared" si="327"/>
+        <v>15819.867530960106</v>
       </c>
       <c r="BP63" s="3">
-        <f t="shared" si="315"/>
-        <v>12782.993467134811</v>
+        <f t="shared" si="327"/>
+        <v>16294.46355688891</v>
       </c>
       <c r="BQ63" s="3">
-        <f t="shared" si="315"/>
-        <v>12910.823401806159</v>
+        <f t="shared" si="327"/>
+        <v>16783.297463595576</v>
       </c>
       <c r="BR63" s="3">
-        <f t="shared" si="315"/>
-        <v>13039.931635824221</v>
+        <f t="shared" si="327"/>
+        <v>17286.796387503444</v>
       </c>
     </row>
     <row r="64" spans="2:70" x14ac:dyDescent="0.3">
@@ -9948,7 +9989,7 @@
         <v>-2266</v>
       </c>
       <c r="BH65" s="3">
-        <v>0</v>
+        <v>-89</v>
       </c>
       <c r="BI65" s="3">
         <v>0</v>
@@ -10046,7 +10087,7 @@
         <v>-3788</v>
       </c>
       <c r="BH66" s="3">
-        <v>0</v>
+        <v>-6682</v>
       </c>
       <c r="BI66" s="3">
         <v>0</v>
@@ -10138,7 +10179,7 @@
         <v>-1356</v>
       </c>
       <c r="BH67" s="3">
-        <v>0</v>
+        <v>-347</v>
       </c>
       <c r="BI67" s="3">
         <v>0</v>
@@ -10236,7 +10277,7 @@
         <v>-1046</v>
       </c>
       <c r="BH68" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="BI68" s="3">
         <v>0</v>
@@ -10340,7 +10381,7 @@
         <v>-11731</v>
       </c>
       <c r="BH69" s="3">
-        <v>0</v>
+        <v>-9197</v>
       </c>
       <c r="BI69" s="3">
         <v>0</v>
@@ -10438,7 +10479,7 @@
         <v>6020</v>
       </c>
       <c r="BH70" s="3">
-        <v>0</v>
+        <v>902</v>
       </c>
       <c r="BI70" s="3">
         <v>0</v>
@@ -10550,7 +10591,7 @@
         <v>15552</v>
       </c>
       <c r="BH71" s="3">
-        <v>0</v>
+        <v>-11076</v>
       </c>
       <c r="BI71" s="3">
         <v>0</v>
@@ -10588,128 +10629,128 @@
         <v>101</v>
       </c>
       <c r="AN72" s="9">
-        <f t="shared" ref="AN72:AU72" si="316">AN61+SUM(AN62:AN71)</f>
+        <f t="shared" ref="AN72:AU72" si="328">AN61+SUM(AN62:AN71)</f>
         <v>2535</v>
       </c>
       <c r="AO72" s="9">
-        <f t="shared" si="316"/>
+        <f t="shared" si="328"/>
         <v>2220</v>
       </c>
       <c r="AP72" s="9">
-        <f t="shared" si="316"/>
+        <f t="shared" si="328"/>
         <v>5470</v>
       </c>
       <c r="AQ72" s="9">
-        <f t="shared" si="316"/>
+        <f t="shared" si="328"/>
         <v>9596</v>
       </c>
       <c r="AR72" s="9">
-        <f t="shared" si="316"/>
+        <f t="shared" si="328"/>
         <v>10159</v>
       </c>
       <c r="AS72" s="9">
-        <f t="shared" si="316"/>
+        <f t="shared" si="328"/>
         <v>18595</v>
       </c>
       <c r="AT72" s="9">
-        <f t="shared" si="316"/>
+        <f t="shared" si="328"/>
         <v>37529</v>
       </c>
       <c r="AU72" s="9">
-        <f t="shared" si="316"/>
+        <f t="shared" si="328"/>
         <v>50856</v>
       </c>
       <c r="AV72" s="9">
-        <f t="shared" ref="AV72:BA72" si="317">AV61+SUM(AV62:AV71)</f>
+        <f t="shared" ref="AV72:BA72" si="329">AV61+SUM(AV62:AV71)</f>
         <v>53666</v>
       </c>
       <c r="AW72" s="9">
-        <f t="shared" si="317"/>
+        <f t="shared" si="329"/>
         <v>59713</v>
       </c>
       <c r="AX72" s="9">
-        <f t="shared" si="317"/>
+        <f t="shared" si="329"/>
         <v>81266</v>
       </c>
       <c r="AY72" s="9">
-        <f t="shared" si="317"/>
+        <f t="shared" si="329"/>
         <v>65824</v>
       </c>
       <c r="AZ72" s="9">
-        <f t="shared" si="317"/>
+        <f t="shared" si="329"/>
         <v>64225</v>
       </c>
       <c r="BA72" s="9">
-        <f t="shared" si="317"/>
+        <f t="shared" si="329"/>
         <v>77434</v>
       </c>
       <c r="BB72" s="9">
-        <f t="shared" ref="BB72:BH72" si="318">BB61+SUM(BB62:BB71)</f>
+        <f t="shared" ref="BB72:BH72" si="330">BB61+SUM(BB62:BB71)</f>
         <v>69391</v>
       </c>
       <c r="BC72" s="9">
-        <f t="shared" si="318"/>
+        <f t="shared" si="330"/>
         <v>80674</v>
       </c>
       <c r="BD72" s="9">
-        <f t="shared" si="318"/>
+        <f t="shared" si="330"/>
         <v>104038</v>
       </c>
       <c r="BE72" s="9">
-        <f t="shared" si="318"/>
+        <f t="shared" si="330"/>
         <v>122151</v>
       </c>
       <c r="BF72" s="9">
-        <f t="shared" si="318"/>
+        <f t="shared" si="330"/>
         <v>110543</v>
       </c>
       <c r="BG72" s="9">
-        <f t="shared" si="318"/>
+        <f t="shared" si="330"/>
         <v>118254</v>
       </c>
       <c r="BH72" s="9">
-        <f t="shared" si="318"/>
-        <v>135317.10499999998</v>
+        <f t="shared" si="330"/>
+        <v>111482</v>
       </c>
       <c r="BI72" s="9">
-        <f t="shared" ref="BI72:BR72" si="319">BI61+SUM(BI62:BI71)</f>
-        <v>143127.86374500001</v>
+        <f t="shared" ref="BI72:BR72" si="331">BI61+SUM(BI62:BI71)</f>
+        <v>140297.27882000004</v>
       </c>
       <c r="BJ72" s="9">
-        <f t="shared" si="319"/>
-        <v>148863.58715738103</v>
+        <f t="shared" si="331"/>
+        <v>146156.37527375604</v>
       </c>
       <c r="BK72" s="9">
-        <f t="shared" si="319"/>
-        <v>153464.52471182137</v>
+        <f t="shared" si="331"/>
+        <v>150912.10223872628</v>
       </c>
       <c r="BL72" s="9">
-        <f t="shared" si="319"/>
-        <v>157474.65499185838</v>
+        <f t="shared" si="331"/>
+        <v>155083.94283423826</v>
       </c>
       <c r="BM72" s="9">
-        <f t="shared" si="319"/>
-        <v>160770.47094232793</v>
+        <f t="shared" si="331"/>
+        <v>158548.72853205472</v>
       </c>
       <c r="BN72" s="9">
-        <f t="shared" si="319"/>
-        <v>163591.00704562257</v>
+        <f t="shared" si="331"/>
+        <v>161595.20782120636</v>
       </c>
       <c r="BO72" s="9">
-        <f t="shared" si="319"/>
-        <v>166747.08697206783</v>
+        <f t="shared" si="331"/>
+        <v>164987.24721383138</v>
       </c>
       <c r="BP72" s="9">
-        <f t="shared" si="319"/>
-        <v>169984.21476855915</v>
+        <f t="shared" si="331"/>
+        <v>168470.90022425019</v>
       </c>
       <c r="BQ72" s="9">
-        <f t="shared" si="319"/>
-        <v>173305.88531132694</v>
+        <f t="shared" si="331"/>
+        <v>172050.02288003429</v>
       </c>
       <c r="BR72" s="9">
-        <f t="shared" si="319"/>
-        <v>176714.58366782637</v>
+        <f t="shared" si="331"/>
+        <v>175727.47374940754</v>
       </c>
     </row>
     <row r="73" spans="2:155" x14ac:dyDescent="0.3">
@@ -10777,37 +10818,47 @@
         <v>9447</v>
       </c>
       <c r="BH73" s="3">
-        <v>10000</v>
+        <v>12715</v>
       </c>
       <c r="BI73" s="3">
-        <v>10000</v>
+        <f>BH73*1.25</f>
+        <v>15893.75</v>
       </c>
       <c r="BJ73" s="3">
-        <v>10000</v>
+        <f>BI73*0.9</f>
+        <v>14304.375</v>
       </c>
       <c r="BK73" s="3">
-        <v>10000</v>
+        <f t="shared" ref="BK73:BR73" si="332">BJ73*0.9</f>
+        <v>12873.9375</v>
       </c>
       <c r="BL73" s="3">
-        <v>10000</v>
+        <f t="shared" si="332"/>
+        <v>11586.543750000001</v>
       </c>
       <c r="BM73" s="3">
-        <v>10000</v>
+        <f>BL73*1.05</f>
+        <v>12165.870937500002</v>
       </c>
       <c r="BN73" s="3">
-        <v>10000</v>
+        <f t="shared" ref="BN73:BR73" si="333">BM73*1.05</f>
+        <v>12774.164484375002</v>
       </c>
       <c r="BO73" s="3">
-        <v>10000</v>
+        <f t="shared" si="333"/>
+        <v>13412.872708593752</v>
       </c>
       <c r="BP73" s="3">
-        <v>10000</v>
+        <f t="shared" si="333"/>
+        <v>14083.516344023439</v>
       </c>
       <c r="BQ73" s="3">
-        <v>10000</v>
+        <f t="shared" si="333"/>
+        <v>14787.692161224611</v>
       </c>
       <c r="BR73" s="3">
-        <v>10000</v>
+        <f t="shared" si="333"/>
+        <v>15527.076769285843</v>
       </c>
     </row>
     <row r="74" spans="2:155" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -10815,504 +10866,504 @@
         <v>103</v>
       </c>
       <c r="AN74" s="9">
-        <f t="shared" ref="AN74:BA74" si="320">AN72-AN73</f>
+        <f t="shared" ref="AN74:BA74" si="334">AN72-AN73</f>
         <v>2275</v>
       </c>
       <c r="AO74" s="9">
-        <f t="shared" si="320"/>
+        <f t="shared" si="334"/>
         <v>1563</v>
       </c>
       <c r="AP74" s="9">
-        <f t="shared" si="320"/>
+        <f t="shared" si="334"/>
         <v>4735</v>
       </c>
       <c r="AQ74" s="9">
-        <f t="shared" si="320"/>
+        <f t="shared" si="334"/>
         <v>8505</v>
       </c>
       <c r="AR74" s="9">
-        <f t="shared" si="320"/>
+        <f t="shared" si="334"/>
         <v>9015</v>
       </c>
       <c r="AS74" s="9">
-        <f t="shared" si="320"/>
+        <f t="shared" si="334"/>
         <v>16590</v>
       </c>
       <c r="AT74" s="9">
-        <f t="shared" si="320"/>
+        <f t="shared" si="334"/>
         <v>33269</v>
       </c>
       <c r="AU74" s="9">
-        <f t="shared" si="320"/>
+        <f t="shared" si="334"/>
         <v>42561</v>
       </c>
       <c r="AV74" s="9">
-        <f t="shared" si="320"/>
+        <f t="shared" si="334"/>
         <v>45501</v>
       </c>
       <c r="AW74" s="9">
-        <f t="shared" si="320"/>
+        <f t="shared" si="334"/>
         <v>50142</v>
       </c>
       <c r="AX74" s="9">
-        <f t="shared" si="320"/>
+        <f t="shared" si="334"/>
         <v>70019</v>
       </c>
       <c r="AY74" s="9">
-        <f t="shared" si="320"/>
+        <f t="shared" si="334"/>
         <v>53090</v>
       </c>
       <c r="AZ74" s="9">
-        <f t="shared" si="320"/>
+        <f t="shared" si="334"/>
         <v>51774</v>
       </c>
       <c r="BA74" s="9">
-        <f t="shared" si="320"/>
+        <f t="shared" si="334"/>
         <v>64121</v>
       </c>
       <c r="BB74" s="9">
-        <f t="shared" ref="BB74:BH74" si="321">BB72-BB73</f>
+        <f t="shared" ref="BB74:BH74" si="335">BB72-BB73</f>
         <v>58896</v>
       </c>
       <c r="BC74" s="9">
-        <f t="shared" si="321"/>
+        <f t="shared" si="335"/>
         <v>73365</v>
       </c>
       <c r="BD74" s="9">
-        <f t="shared" si="321"/>
+        <f t="shared" si="335"/>
         <v>92953</v>
       </c>
       <c r="BE74" s="9">
-        <f t="shared" si="321"/>
+        <f t="shared" si="335"/>
         <v>111443</v>
       </c>
       <c r="BF74" s="9">
-        <f t="shared" si="321"/>
+        <f t="shared" si="335"/>
         <v>99584</v>
       </c>
       <c r="BG74" s="9">
-        <f t="shared" si="321"/>
+        <f t="shared" si="335"/>
         <v>108807</v>
       </c>
       <c r="BH74" s="9">
-        <f t="shared" si="321"/>
-        <v>125317.10499999998</v>
+        <f t="shared" si="335"/>
+        <v>98767</v>
       </c>
       <c r="BI74" s="9">
-        <f t="shared" ref="BI74:BR74" si="322">BI72-BI73</f>
-        <v>133127.86374500001</v>
+        <f t="shared" ref="BI74:BR74" si="336">BI72-BI73</f>
+        <v>124403.52882000004</v>
       </c>
       <c r="BJ74" s="9">
-        <f t="shared" si="322"/>
-        <v>138863.58715738103</v>
+        <f t="shared" si="336"/>
+        <v>131852.00027375604</v>
       </c>
       <c r="BK74" s="9">
-        <f t="shared" si="322"/>
-        <v>143464.52471182137</v>
+        <f t="shared" si="336"/>
+        <v>138038.16473872628</v>
       </c>
       <c r="BL74" s="9">
-        <f t="shared" si="322"/>
-        <v>147474.65499185838</v>
+        <f t="shared" si="336"/>
+        <v>143497.39908423825</v>
       </c>
       <c r="BM74" s="9">
-        <f t="shared" si="322"/>
-        <v>150770.47094232793</v>
+        <f t="shared" si="336"/>
+        <v>146382.85759455472</v>
       </c>
       <c r="BN74" s="9">
-        <f t="shared" si="322"/>
-        <v>153591.00704562257</v>
+        <f t="shared" si="336"/>
+        <v>148821.04333683135</v>
       </c>
       <c r="BO74" s="9">
-        <f t="shared" si="322"/>
-        <v>156747.08697206783</v>
+        <f t="shared" si="336"/>
+        <v>151574.37450523762</v>
       </c>
       <c r="BP74" s="9">
-        <f t="shared" si="322"/>
-        <v>159984.21476855915</v>
+        <f t="shared" si="336"/>
+        <v>154387.38388022676</v>
       </c>
       <c r="BQ74" s="9">
-        <f t="shared" si="322"/>
-        <v>163305.88531132694</v>
+        <f t="shared" si="336"/>
+        <v>157262.33071880968</v>
       </c>
       <c r="BR74" s="9">
-        <f t="shared" si="322"/>
-        <v>166714.58366782637</v>
+        <f t="shared" si="336"/>
+        <v>160200.3969801217</v>
       </c>
       <c r="BS74" s="6">
         <f>BR74*(1+$BU$30)</f>
-        <v>165047.4378311481</v>
+        <v>158598.39301032049</v>
       </c>
       <c r="BT74" s="6">
-        <f t="shared" ref="BT74:EE74" si="323">BS74*(1+$BU$30)</f>
-        <v>163396.96345283662</v>
+        <f t="shared" ref="BT74:EE74" si="337">BS74*(1+$BU$30)</f>
+        <v>157012.40908021727</v>
       </c>
       <c r="BU74" s="6">
-        <f t="shared" si="323"/>
-        <v>161762.99381830826</v>
+        <f t="shared" si="337"/>
+        <v>155442.28498941509</v>
       </c>
       <c r="BV74" s="6">
-        <f t="shared" si="323"/>
-        <v>160145.36388012517</v>
+        <f t="shared" si="337"/>
+        <v>153887.86213952093</v>
       </c>
       <c r="BW74" s="6">
-        <f t="shared" si="323"/>
-        <v>158543.9102413239</v>
+        <f t="shared" si="337"/>
+        <v>152348.98351812572</v>
       </c>
       <c r="BX74" s="6">
-        <f t="shared" si="323"/>
-        <v>156958.47113891065</v>
+        <f t="shared" si="337"/>
+        <v>150825.49368294448</v>
       </c>
       <c r="BY74" s="6">
-        <f t="shared" si="323"/>
-        <v>155388.88642752153</v>
+        <f t="shared" si="337"/>
+        <v>149317.23874611504</v>
       </c>
       <c r="BZ74" s="6">
-        <f t="shared" si="323"/>
-        <v>153834.99756324632</v>
+        <f t="shared" si="337"/>
+        <v>147824.06635865389</v>
       </c>
       <c r="CA74" s="6">
-        <f t="shared" si="323"/>
-        <v>152296.64758761384</v>
+        <f t="shared" si="337"/>
+        <v>146345.82569506735</v>
       </c>
       <c r="CB74" s="6">
-        <f t="shared" si="323"/>
-        <v>150773.68111173771</v>
+        <f t="shared" si="337"/>
+        <v>144882.36743811666</v>
       </c>
       <c r="CC74" s="6">
-        <f t="shared" si="323"/>
-        <v>149265.94430062032</v>
+        <f t="shared" si="337"/>
+        <v>143433.54376373551</v>
       </c>
       <c r="CD74" s="6">
-        <f t="shared" si="323"/>
-        <v>147773.28485761411</v>
+        <f t="shared" si="337"/>
+        <v>141999.20832609816</v>
       </c>
       <c r="CE74" s="6">
-        <f t="shared" si="323"/>
-        <v>146295.55200903796</v>
+        <f t="shared" si="337"/>
+        <v>140579.21624283717</v>
       </c>
       <c r="CF74" s="6">
-        <f t="shared" si="323"/>
-        <v>144832.59648894757</v>
+        <f t="shared" si="337"/>
+        <v>139173.42408040879</v>
       </c>
       <c r="CG74" s="6">
-        <f t="shared" si="323"/>
-        <v>143384.27052405808</v>
+        <f t="shared" si="337"/>
+        <v>137781.68983960469</v>
       </c>
       <c r="CH74" s="6">
-        <f t="shared" si="323"/>
-        <v>141950.42781881749</v>
+        <f t="shared" si="337"/>
+        <v>136403.87294120865</v>
       </c>
       <c r="CI74" s="6">
-        <f t="shared" si="323"/>
-        <v>140530.92354062933</v>
+        <f t="shared" si="337"/>
+        <v>135039.83421179658</v>
       </c>
       <c r="CJ74" s="6">
-        <f t="shared" si="323"/>
-        <v>139125.61430522305</v>
+        <f t="shared" si="337"/>
+        <v>133689.43586967862</v>
       </c>
       <c r="CK74" s="6">
-        <f t="shared" si="323"/>
-        <v>137734.35816217083</v>
+        <f t="shared" si="337"/>
+        <v>132352.54151098183</v>
       </c>
       <c r="CL74" s="6">
-        <f t="shared" si="323"/>
-        <v>136357.01458054912</v>
+        <f t="shared" si="337"/>
+        <v>131029.01609587201</v>
       </c>
       <c r="CM74" s="6">
-        <f t="shared" si="323"/>
-        <v>134993.44443474364</v>
+        <f t="shared" si="337"/>
+        <v>129718.72593491328</v>
       </c>
       <c r="CN74" s="6">
-        <f t="shared" si="323"/>
-        <v>133643.50999039621</v>
+        <f t="shared" si="337"/>
+        <v>128421.53867556415</v>
       </c>
       <c r="CO74" s="6">
-        <f t="shared" si="323"/>
-        <v>132307.07489049225</v>
+        <f t="shared" si="337"/>
+        <v>127137.3232888085</v>
       </c>
       <c r="CP74" s="6">
-        <f t="shared" si="323"/>
-        <v>130984.00414158733</v>
+        <f t="shared" si="337"/>
+        <v>125865.95005592042</v>
       </c>
       <c r="CQ74" s="6">
-        <f t="shared" si="323"/>
-        <v>129674.16410017146</v>
+        <f t="shared" si="337"/>
+        <v>124607.29055536121</v>
       </c>
       <c r="CR74" s="6">
-        <f t="shared" si="323"/>
-        <v>128377.42245916974</v>
+        <f t="shared" si="337"/>
+        <v>123361.2176498076</v>
       </c>
       <c r="CS74" s="6">
-        <f t="shared" si="323"/>
-        <v>127093.64823457804</v>
+        <f t="shared" si="337"/>
+        <v>122127.60547330952</v>
       </c>
       <c r="CT74" s="6">
-        <f t="shared" si="323"/>
-        <v>125822.71175223225</v>
+        <f t="shared" si="337"/>
+        <v>120906.32941857642</v>
       </c>
       <c r="CU74" s="6">
-        <f t="shared" si="323"/>
-        <v>124564.48463470992</v>
+        <f t="shared" si="337"/>
+        <v>119697.26612439066</v>
       </c>
       <c r="CV74" s="6">
-        <f t="shared" si="323"/>
-        <v>123318.83978836282</v>
+        <f t="shared" si="337"/>
+        <v>118500.29346314675</v>
       </c>
       <c r="CW74" s="6">
-        <f t="shared" si="323"/>
-        <v>122085.65139047919</v>
+        <f t="shared" si="337"/>
+        <v>117315.29052851528</v>
       </c>
       <c r="CX74" s="6">
-        <f t="shared" si="323"/>
-        <v>120864.79487657441</v>
+        <f t="shared" si="337"/>
+        <v>116142.13762323013</v>
       </c>
       <c r="CY74" s="6">
-        <f t="shared" si="323"/>
-        <v>119656.14692780866</v>
+        <f t="shared" si="337"/>
+        <v>114980.71624699782</v>
       </c>
       <c r="CZ74" s="6">
-        <f t="shared" si="323"/>
-        <v>118459.58545853056</v>
+        <f t="shared" si="337"/>
+        <v>113830.90908452784</v>
       </c>
       <c r="DA74" s="6">
-        <f t="shared" si="323"/>
-        <v>117274.98960394526</v>
+        <f t="shared" si="337"/>
+        <v>112692.59999368257</v>
       </c>
       <c r="DB74" s="6">
-        <f t="shared" si="323"/>
-        <v>116102.2397079058</v>
+        <f t="shared" si="337"/>
+        <v>111565.67399374575</v>
       </c>
       <c r="DC74" s="6">
-        <f t="shared" si="323"/>
-        <v>114941.21731082675</v>
+        <f t="shared" si="337"/>
+        <v>110450.01725380828</v>
       </c>
       <c r="DD74" s="6">
-        <f t="shared" si="323"/>
-        <v>113791.80513771847</v>
+        <f t="shared" si="337"/>
+        <v>109345.5170812702</v>
       </c>
       <c r="DE74" s="6">
-        <f t="shared" si="323"/>
-        <v>112653.88708634129</v>
+        <f t="shared" si="337"/>
+        <v>108252.0619104575</v>
       </c>
       <c r="DF74" s="6">
-        <f t="shared" si="323"/>
-        <v>111527.34821547788</v>
+        <f t="shared" si="337"/>
+        <v>107169.54129135293</v>
       </c>
       <c r="DG74" s="6">
-        <f t="shared" si="323"/>
-        <v>110412.0747333231</v>
+        <f t="shared" si="337"/>
+        <v>106097.8458784394</v>
       </c>
       <c r="DH74" s="6">
-        <f t="shared" si="323"/>
-        <v>109307.95398598987</v>
+        <f t="shared" si="337"/>
+        <v>105036.86741965501</v>
       </c>
       <c r="DI74" s="6">
-        <f t="shared" si="323"/>
-        <v>108214.87444612996</v>
+        <f t="shared" si="337"/>
+        <v>103986.49874545846</v>
       </c>
       <c r="DJ74" s="6">
-        <f t="shared" si="323"/>
-        <v>107132.72570166866</v>
+        <f t="shared" si="337"/>
+        <v>102946.63375800388</v>
       </c>
       <c r="DK74" s="6">
-        <f t="shared" si="323"/>
-        <v>106061.39844465198</v>
+        <f t="shared" si="337"/>
+        <v>101917.16742042384</v>
       </c>
       <c r="DL74" s="6">
-        <f t="shared" si="323"/>
-        <v>105000.78446020545</v>
+        <f t="shared" si="337"/>
+        <v>100897.9957462196</v>
       </c>
       <c r="DM74" s="6">
-        <f t="shared" si="323"/>
-        <v>103950.7766156034</v>
+        <f t="shared" si="337"/>
+        <v>99889.015788757402</v>
       </c>
       <c r="DN74" s="6">
-        <f t="shared" si="323"/>
-        <v>102911.26884944737</v>
+        <f t="shared" si="337"/>
+        <v>98890.125630869821</v>
       </c>
       <c r="DO74" s="6">
-        <f t="shared" si="323"/>
-        <v>101882.1561609529</v>
+        <f t="shared" si="337"/>
+        <v>97901.224374561119</v>
       </c>
       <c r="DP74" s="6">
-        <f t="shared" si="323"/>
-        <v>100863.33459934338</v>
+        <f t="shared" si="337"/>
+        <v>96922.212130815504</v>
       </c>
       <c r="DQ74" s="6">
-        <f t="shared" si="323"/>
-        <v>99854.701253349936</v>
+        <f t="shared" si="337"/>
+        <v>95952.990009507354</v>
       </c>
       <c r="DR74" s="6">
-        <f t="shared" si="323"/>
-        <v>98856.154240816439</v>
+        <f t="shared" si="337"/>
+        <v>94993.460109412277</v>
       </c>
       <c r="DS74" s="6">
-        <f t="shared" si="323"/>
-        <v>97867.592698408276</v>
+        <f t="shared" si="337"/>
+        <v>94043.525508318155</v>
       </c>
       <c r="DT74" s="6">
-        <f t="shared" si="323"/>
-        <v>96888.916771424192</v>
+        <f t="shared" si="337"/>
+        <v>93103.090253234972</v>
       </c>
       <c r="DU74" s="6">
-        <f t="shared" si="323"/>
-        <v>95920.027603709954</v>
+        <f t="shared" si="337"/>
+        <v>92172.059350702621</v>
       </c>
       <c r="DV74" s="6">
-        <f t="shared" si="323"/>
-        <v>94960.827327672858</v>
+        <f t="shared" si="337"/>
+        <v>91250.338757195597</v>
       </c>
       <c r="DW74" s="6">
-        <f t="shared" si="323"/>
-        <v>94011.219054396133</v>
+        <f t="shared" si="337"/>
+        <v>90337.835369623645</v>
       </c>
       <c r="DX74" s="6">
-        <f t="shared" si="323"/>
-        <v>93071.106863852168</v>
+        <f t="shared" si="337"/>
+        <v>89434.457015927401</v>
       </c>
       <c r="DY74" s="6">
-        <f t="shared" si="323"/>
-        <v>92140.395795213641</v>
+        <f t="shared" si="337"/>
+        <v>88540.112445768129</v>
       </c>
       <c r="DZ74" s="6">
-        <f t="shared" si="323"/>
-        <v>91218.991837261507</v>
+        <f t="shared" si="337"/>
+        <v>87654.711321310446</v>
       </c>
       <c r="EA74" s="6">
-        <f t="shared" si="323"/>
-        <v>90306.801918888887</v>
+        <f t="shared" si="337"/>
+        <v>86778.16420809734</v>
       </c>
       <c r="EB74" s="6">
-        <f t="shared" si="323"/>
-        <v>89403.73389969999</v>
+        <f t="shared" si="337"/>
+        <v>85910.382566016371</v>
       </c>
       <c r="EC74" s="6">
-        <f t="shared" si="323"/>
-        <v>88509.696560702985</v>
+        <f t="shared" si="337"/>
+        <v>85051.278740356211</v>
       </c>
       <c r="ED74" s="6">
-        <f t="shared" si="323"/>
-        <v>87624.599595095948</v>
+        <f t="shared" si="337"/>
+        <v>84200.765952952643</v>
       </c>
       <c r="EE74" s="6">
-        <f t="shared" si="323"/>
-        <v>86748.35359914499</v>
+        <f t="shared" si="337"/>
+        <v>83358.758293423118</v>
       </c>
       <c r="EF74" s="6">
-        <f t="shared" ref="EF74:EY74" si="324">EE74*(1+$BU$30)</f>
-        <v>85880.870063153532</v>
+        <f t="shared" ref="EF74:EY74" si="338">EE74*(1+$BU$30)</f>
+        <v>82525.170710488892</v>
       </c>
       <c r="EG74" s="6">
-        <f t="shared" si="324"/>
-        <v>85022.061362521999</v>
+        <f t="shared" si="338"/>
+        <v>81699.919003383999</v>
       </c>
       <c r="EH74" s="6">
-        <f t="shared" si="324"/>
-        <v>84171.840748896779</v>
+        <f t="shared" si="338"/>
+        <v>80882.919813350163</v>
       </c>
       <c r="EI74" s="6">
-        <f t="shared" si="324"/>
-        <v>83330.122341407812</v>
+        <f t="shared" si="338"/>
+        <v>80074.090615216657</v>
       </c>
       <c r="EJ74" s="6">
-        <f t="shared" si="324"/>
-        <v>82496.821117993735</v>
+        <f t="shared" si="338"/>
+        <v>79273.349709064496</v>
       </c>
       <c r="EK74" s="6">
-        <f t="shared" si="324"/>
-        <v>81671.852906813801</v>
+        <f t="shared" si="338"/>
+        <v>78480.616211973844</v>
       </c>
       <c r="EL74" s="6">
-        <f t="shared" si="324"/>
-        <v>80855.134377745664</v>
+        <f t="shared" si="338"/>
+        <v>77695.810049854103</v>
       </c>
       <c r="EM74" s="6">
-        <f t="shared" si="324"/>
-        <v>80046.5830339682</v>
+        <f t="shared" si="338"/>
+        <v>76918.851949355565</v>
       </c>
       <c r="EN74" s="6">
-        <f t="shared" si="324"/>
-        <v>79246.117203628513</v>
+        <f t="shared" si="338"/>
+        <v>76149.663429862005</v>
       </c>
       <c r="EO74" s="6">
-        <f t="shared" si="324"/>
-        <v>78453.656031592225</v>
+        <f t="shared" si="338"/>
+        <v>75388.166795563389</v>
       </c>
       <c r="EP74" s="6">
-        <f t="shared" si="324"/>
-        <v>77669.119471276295</v>
+        <f t="shared" si="338"/>
+        <v>74634.285127607756</v>
       </c>
       <c r="EQ74" s="6">
-        <f t="shared" si="324"/>
-        <v>76892.428276563529</v>
+        <f t="shared" si="338"/>
+        <v>73887.942276331683</v>
       </c>
       <c r="ER74" s="6">
-        <f t="shared" si="324"/>
-        <v>76123.503993797887</v>
+        <f t="shared" si="338"/>
+        <v>73149.062853568365</v>
       </c>
       <c r="ES74" s="6">
-        <f t="shared" si="324"/>
-        <v>75362.268953859908</v>
+        <f t="shared" si="338"/>
+        <v>72417.57222503268</v>
       </c>
       <c r="ET74" s="6">
-        <f t="shared" si="324"/>
-        <v>74608.646264321302</v>
+        <f t="shared" si="338"/>
+        <v>71693.396502782358</v>
       </c>
       <c r="EU74" s="6">
-        <f t="shared" si="324"/>
-        <v>73862.559801678086</v>
+        <f t="shared" si="338"/>
+        <v>70976.462537754531</v>
       </c>
       <c r="EV74" s="6">
-        <f t="shared" si="324"/>
-        <v>73123.934203661309</v>
+        <f t="shared" si="338"/>
+        <v>70266.697912376985</v>
       </c>
       <c r="EW74" s="6">
-        <f t="shared" si="324"/>
-        <v>72392.694861624695</v>
+        <f t="shared" si="338"/>
+        <v>69564.03093325322</v>
       </c>
       <c r="EX74" s="6">
-        <f t="shared" si="324"/>
-        <v>71668.767913008443</v>
+        <f t="shared" si="338"/>
+        <v>68868.390623920684</v>
       </c>
       <c r="EY74" s="6">
-        <f t="shared" si="324"/>
-        <v>70952.080233878354</v>
+        <f t="shared" si="338"/>
+        <v>68179.706717681474</v>
       </c>
     </row>
     <row r="76" spans="2:155" x14ac:dyDescent="0.3">
       <c r="BU76" s="3">
-        <f>NPV(BU31,BH74:EY74)</f>
-        <v>2819755.6349074603</v>
+        <f>NPV(BU31,BI74:EY74)</f>
+        <v>2724899.7697861902</v>
       </c>
     </row>
     <row r="77" spans="2:155" x14ac:dyDescent="0.3">
       <c r="BU77" s="3">
         <f>Main!D8</f>
-        <v>33763</v>
+        <v>54286</v>
       </c>
     </row>
     <row r="78" spans="2:155" x14ac:dyDescent="0.3">
       <c r="BU78" s="3">
         <f>BU76+BU77</f>
-        <v>2853518.6349074603</v>
+        <v>2779185.7697861902</v>
       </c>
     </row>
     <row r="79" spans="2:155" x14ac:dyDescent="0.3">
       <c r="BU79" s="12">
         <f>BU78/BR18</f>
-        <v>191.47405101741677</v>
+        <v>186.48623890559492</v>
       </c>
     </row>
     <row r="80" spans="2:155" x14ac:dyDescent="0.3">
       <c r="BU80" s="12">
         <f>Main!D3</f>
-        <v>276.72000000000003</v>
+        <v>256.72000000000003</v>
       </c>
     </row>
     <row r="81" spans="73:73" x14ac:dyDescent="0.3">
       <c r="BU81" s="11">
         <f>BU79/BU80-1</f>
-        <v>-0.30805850311716987</v>
+        <v>-0.27358118220008221</v>
       </c>
     </row>
   </sheetData>
